--- a/gstdatabase/GSTR-3B-2025-2026.xlsx
+++ b/gstdatabase/GSTR-3B-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0615ECB-7143-4365-9AAE-F5E1D308FA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A29D22F-EE48-45D6-8E73-9ABA72EDCFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="51">
   <si>
     <t>STATE CD</t>
   </si>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -415,6 +415,9 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -423,9 +426,6 @@
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -727,16 +727,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:BJ59"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="2" max="2" width="29.77734375" customWidth="1"/>
     <col min="3" max="31" width="18.44140625" customWidth="1"/>
-    <col min="32" max="52" width="19" customWidth="1"/>
+    <col min="32" max="51" width="19" customWidth="1"/>
+    <col min="52" max="56" width="18.77734375" customWidth="1"/>
+    <col min="57" max="62" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>46</v>
       </c>
@@ -792,7 +794,7 @@
       <c r="AY1" s="2"/>
       <c r="AZ1" s="2"/>
     </row>
-    <row r="2" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -826,11 +828,11 @@
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
     </row>
-    <row r="3" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -862,7 +864,7 @@
       <c r="AE3" s="2"/>
       <c r="AF3" s="2"/>
     </row>
-    <row r="4" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -896,7 +898,7 @@
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
     </row>
-    <row r="5" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>49</v>
       </c>
@@ -932,7 +934,7 @@
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
     </row>
-    <row r="6" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -966,7 +968,7 @@
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1000,85 +1002,99 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:52" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <v>45748</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="24">
         <v>45778</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23">
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="24">
         <v>45809</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23">
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="24">
         <v>45839</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="24">
         <v>45870</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="23">
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="24">
         <v>45901</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="23">
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="24">
         <v>45931</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="23">
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="24">
         <v>45962</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="23">
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="26"/>
+      <c r="AQ8" s="24">
         <v>45992</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="23">
+      <c r="AR8" s="25"/>
+      <c r="AS8" s="25"/>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="26"/>
+      <c r="AV8" s="24">
         <v>46023</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="25"/>
+      <c r="AW8" s="25"/>
+      <c r="AX8" s="25"/>
+      <c r="AY8" s="25"/>
+      <c r="AZ8" s="26"/>
+      <c r="BA8" s="24">
+        <v>46054</v>
+      </c>
+      <c r="BB8" s="25"/>
+      <c r="BC8" s="25"/>
+      <c r="BD8" s="25"/>
+      <c r="BE8" s="26"/>
+      <c r="BF8" s="24">
+        <v>46082</v>
+      </c>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="25"/>
+      <c r="BI8" s="25"/>
+      <c r="BJ8" s="26"/>
     </row>
-    <row r="9" spans="1:52" s="15" customFormat="1" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62" s="15" customFormat="1" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28"/>
       <c r="B9" s="29"/>
       <c r="C9" s="16" t="s">
@@ -1231,8 +1247,38 @@
       <c r="AZ9" s="16" t="s">
         <v>50</v>
       </c>
+      <c r="BA9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ9" s="16" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <v>1</v>
       </c>
@@ -1247,14 +1293,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>14937</v>
+        <v>15039</v>
       </c>
       <c r="F10" s="13">
-        <v>74169</v>
+        <v>74271</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>0.99973041825607567</v>
+        <v>1.0011052851500897</v>
       </c>
       <c r="H10" s="7">
         <v>75899</v>
@@ -1264,14 +1310,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>14763</v>
+        <v>14887</v>
       </c>
       <c r="K10" s="13">
-        <v>74847</v>
+        <v>74971</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.98613947482839037</v>
+        <v>0.98777322494367514</v>
       </c>
       <c r="M10" s="7">
         <v>134494</v>
@@ -1281,14 +1327,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>25884</v>
+        <v>26203</v>
       </c>
       <c r="P10" s="13">
-        <v>133720</v>
+        <v>134039</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99424509643552872</v>
+        <v>0.99661694945499424</v>
       </c>
       <c r="R10" s="7">
         <v>73914</v>
@@ -1298,14 +1344,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>13674</v>
+        <v>13907</v>
       </c>
       <c r="U10" s="13">
-        <v>73530</v>
+        <v>73763</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>0.99480477311470084</v>
+        <v>0.9979570852612496</v>
       </c>
       <c r="W10" s="7">
         <v>75592</v>
@@ -1315,14 +1361,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>13656</v>
+        <v>13978</v>
       </c>
       <c r="Z10" s="13">
-        <v>74339</v>
+        <v>74661</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.98342417187003917</v>
+        <v>0.98768388189226375</v>
       </c>
       <c r="AB10" s="7">
         <v>136558</v>
@@ -1332,14 +1378,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>23071</v>
+        <v>23953</v>
       </c>
       <c r="AE10" s="13">
-        <v>134923</v>
+        <v>135805</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.98802706542275076</v>
+        <v>0.99448585948827606</v>
       </c>
       <c r="AG10" s="7">
         <v>73704</v>
@@ -1349,14 +1395,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>13341</v>
+        <v>13974</v>
       </c>
       <c r="AJ10" s="13">
-        <v>72753</v>
+        <v>73386</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.98709703679583194</v>
+        <v>0.99568544448062524</v>
       </c>
       <c r="AL10" s="7">
         <v>75897</v>
@@ -1366,14 +1412,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>11711</v>
+        <v>12714</v>
       </c>
       <c r="AO10" s="13">
-        <v>74906</v>
+        <v>75909</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.98694283041490438</v>
+        <v>1.0001581090161666</v>
       </c>
       <c r="AQ10" s="7">
         <v>140117</v>
@@ -1383,14 +1429,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>20846</v>
+        <v>24516</v>
       </c>
       <c r="AT10" s="13">
-        <v>135804</v>
+        <v>139474</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.96921858161393692</v>
+        <v>0.99541097796841216</v>
       </c>
       <c r="AV10" s="7">
         <v>75508</v>
@@ -1400,17 +1446,51 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>7978</v>
+        <v>13069</v>
       </c>
       <c r="AY10" s="13">
-        <v>70374</v>
+        <v>75465</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.93200720453461883</v>
+        <v>0.99943052391799547</v>
+      </c>
+      <c r="BA10" s="7">
+        <v>78056</v>
+      </c>
+      <c r="BB10" s="6">
+        <v>63996</v>
+      </c>
+      <c r="BC10" s="4">
+        <f>BD10-BB10</f>
+        <v>12641</v>
+      </c>
+      <c r="BD10" s="13">
+        <v>76637</v>
+      </c>
+      <c r="BE10" s="5">
+        <f>BD10/BA10</f>
+        <v>0.98182074408117248</v>
+      </c>
+      <c r="BF10" s="7">
+        <v>144885</v>
+      </c>
+      <c r="BG10" s="6">
+        <v>110042</v>
+      </c>
+      <c r="BH10" s="4">
+        <f>BI10-BG10</f>
+        <v>28182</v>
+      </c>
+      <c r="BI10" s="13">
+        <v>138224</v>
+      </c>
+      <c r="BJ10" s="5">
+        <f>BI10/BF10</f>
+        <v>0.95402560651551227</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
         <v>2</v>
       </c>
@@ -1425,14 +1505,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8523</v>
+        <v>8620</v>
       </c>
       <c r="F11" s="13">
-        <v>47669</v>
+        <v>47766</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99652973763980346</v>
+        <v>0.99855754154907495</v>
       </c>
       <c r="H11" s="7">
         <v>49123</v>
@@ -1442,14 +1522,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8176</v>
+        <v>8289</v>
       </c>
       <c r="K11" s="13">
-        <v>48162</v>
+        <v>48275</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98043686256946849</v>
+        <v>0.98273721067524378</v>
       </c>
       <c r="M11" s="7">
         <v>111861</v>
@@ -1459,14 +1539,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>18640</v>
+        <v>18957</v>
       </c>
       <c r="P11" s="13">
-        <v>110829</v>
+        <v>111146</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.990774264488964</v>
+        <v>0.99360813867210196</v>
       </c>
       <c r="R11" s="7">
         <v>47958</v>
@@ -1476,14 +1556,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>7887</v>
+        <v>8063</v>
       </c>
       <c r="U11" s="13">
-        <v>47481</v>
+        <v>47657</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99005379707243835</v>
+        <v>0.9937236748821886</v>
       </c>
       <c r="W11" s="7">
         <v>49731</v>
@@ -1493,14 +1573,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>7820</v>
+        <v>8077</v>
       </c>
       <c r="Z11" s="13">
-        <v>48022</v>
+        <v>48279</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.96563511692907844</v>
+        <v>0.97080291970802923</v>
       </c>
       <c r="AB11" s="7">
         <v>113134</v>
@@ -1510,14 +1590,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>18639</v>
+        <v>19452</v>
       </c>
       <c r="AE11" s="13">
-        <v>111019</v>
+        <v>111832</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.98130535471211133</v>
+        <v>0.98849152332632095</v>
       </c>
       <c r="AG11" s="7">
         <v>48119</v>
@@ -1527,14 +1607,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>7283</v>
+        <v>7798</v>
       </c>
       <c r="AJ11" s="13">
-        <v>47155</v>
+        <v>47670</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.97996633346495143</v>
+        <v>0.99066896652050129</v>
       </c>
       <c r="AL11" s="7">
         <v>49938</v>
@@ -1544,14 +1624,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>6506</v>
+        <v>7247</v>
       </c>
       <c r="AO11" s="13">
-        <v>48192</v>
+        <v>48933</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.96503664544034606</v>
+        <v>0.97987504505586931</v>
       </c>
       <c r="AQ11" s="7">
         <v>114343</v>
@@ -1561,14 +1641,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>12366</v>
+        <v>15431</v>
       </c>
       <c r="AT11" s="13">
-        <v>110105</v>
+        <v>113170</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.96293607829075678</v>
+        <v>0.98974139212719625</v>
       </c>
       <c r="AV11" s="7">
         <v>49251</v>
@@ -1578,17 +1658,51 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>3505</v>
+        <v>6712</v>
       </c>
       <c r="AY11" s="13">
-        <v>45268</v>
+        <v>48475</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.91912854561328705</v>
+        <v>0.98424397474162961</v>
+      </c>
+      <c r="BA11" s="7">
+        <v>50523</v>
+      </c>
+      <c r="BB11" s="6">
+        <v>42199</v>
+      </c>
+      <c r="BC11" s="4">
+        <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
+        <v>6791</v>
+      </c>
+      <c r="BD11" s="13">
+        <v>48990</v>
+      </c>
+      <c r="BE11" s="5">
+        <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
+        <v>0.96965738376580968</v>
+      </c>
+      <c r="BF11" s="7">
+        <v>116408</v>
+      </c>
+      <c r="BG11" s="6">
+        <v>95457</v>
+      </c>
+      <c r="BH11" s="4">
+        <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
+        <v>15349</v>
+      </c>
+      <c r="BI11" s="13">
+        <v>110806</v>
+      </c>
+      <c r="BJ11" s="5">
+        <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
+        <v>0.95187615971410899</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>3</v>
       </c>
@@ -1603,14 +1717,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>29056</v>
+        <v>29233</v>
       </c>
       <c r="F12" s="13">
-        <v>182029</v>
+        <v>182206</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99606562041718649</v>
+        <v>0.9970341672685884</v>
       </c>
       <c r="H12" s="7">
         <v>186824</v>
@@ -1620,14 +1734,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>26294</v>
+        <v>26505</v>
       </c>
       <c r="K12" s="13">
-        <v>184409</v>
+        <v>184620</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98707339528112015</v>
+        <v>0.98820280049672415</v>
       </c>
       <c r="M12" s="7">
         <v>372375</v>
@@ -1637,14 +1751,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>60238</v>
+        <v>60867</v>
       </c>
       <c r="P12" s="13">
-        <v>369852</v>
+        <v>370481</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99322457200402825</v>
+        <v>0.99491372943940914</v>
       </c>
       <c r="R12" s="7">
         <v>184659</v>
@@ -1654,14 +1768,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27867</v>
+        <v>28266</v>
       </c>
       <c r="U12" s="13">
-        <v>183211</v>
+        <v>183610</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99215851921650178</v>
+        <v>0.99431925874178895</v>
       </c>
       <c r="W12" s="7">
         <v>189081</v>
@@ -1671,14 +1785,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>29034</v>
+        <v>29666</v>
       </c>
       <c r="Z12" s="13">
-        <v>184951</v>
+        <v>185583</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.97815750921562716</v>
+        <v>0.98149999206689198</v>
       </c>
       <c r="AB12" s="7">
         <v>377441</v>
@@ -1688,14 +1802,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>62797</v>
+        <v>65087</v>
       </c>
       <c r="AE12" s="13">
-        <v>371418</v>
+        <v>373708</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.984042539098826</v>
+        <v>0.99010971251135937</v>
       </c>
       <c r="AG12" s="7">
         <v>186148</v>
@@ -1705,14 +1819,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>26839</v>
+        <v>28288</v>
       </c>
       <c r="AJ12" s="13">
-        <v>183280</v>
+        <v>184729</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.98459290457055682</v>
+        <v>0.99237703332831939</v>
       </c>
       <c r="AL12" s="7">
         <v>192239</v>
@@ -1722,14 +1836,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>24241</v>
+        <v>26389</v>
       </c>
       <c r="AO12" s="13">
-        <v>188494</v>
+        <v>190642</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98051904140158863</v>
+        <v>0.99169263260836771</v>
       </c>
       <c r="AQ12" s="7">
         <v>384779</v>
@@ -1739,14 +1853,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>49031</v>
+        <v>59044</v>
       </c>
       <c r="AT12" s="13">
-        <v>371233</v>
+        <v>381246</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.96479537604702958</v>
+        <v>0.99081810597771713</v>
       </c>
       <c r="AV12" s="7">
         <v>191743</v>
@@ -1756,17 +1870,51 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>14228</v>
+        <v>24565</v>
       </c>
       <c r="AY12" s="13">
-        <v>179733</v>
+        <v>190070</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.93736407587239168</v>
+        <v>0.99127477926182439</v>
+      </c>
+      <c r="BA12" s="7">
+        <v>197493</v>
+      </c>
+      <c r="BB12" s="6">
+        <v>167307</v>
+      </c>
+      <c r="BC12" s="4">
+        <f t="shared" si="20"/>
+        <v>25301</v>
+      </c>
+      <c r="BD12" s="13">
+        <v>192608</v>
+      </c>
+      <c r="BE12" s="5">
+        <f t="shared" si="21"/>
+        <v>0.97526494609935543</v>
+      </c>
+      <c r="BF12" s="7">
+        <v>393305</v>
+      </c>
+      <c r="BG12" s="6">
+        <v>315979</v>
+      </c>
+      <c r="BH12" s="4">
+        <f t="shared" si="22"/>
+        <v>59818</v>
+      </c>
+      <c r="BI12" s="13">
+        <v>375797</v>
+      </c>
+      <c r="BJ12" s="5">
+        <f t="shared" si="23"/>
+        <v>0.95548492899912285</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>4</v>
       </c>
@@ -1781,14 +1929,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2872</v>
+        <v>2889</v>
       </c>
       <c r="F13" s="13">
-        <v>18049</v>
+        <v>18066</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.000776268367064</v>
+        <v>1.0017188799556418</v>
       </c>
       <c r="H13" s="7">
         <v>18257</v>
@@ -1798,14 +1946,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2601</v>
+        <v>2620</v>
       </c>
       <c r="K13" s="13">
-        <v>18079</v>
+        <v>18098</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>0.99025031494769133</v>
+        <v>0.99129101166675793</v>
       </c>
       <c r="M13" s="7">
         <v>29011</v>
@@ -1815,14 +1963,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>4934</v>
+        <v>4996</v>
       </c>
       <c r="P13" s="13">
-        <v>28928</v>
+        <v>28990</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99713901623522117</v>
+        <v>0.99927613663782699</v>
       </c>
       <c r="R13" s="7">
         <v>18140</v>
@@ -1832,14 +1980,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2749</v>
+        <v>2793</v>
       </c>
       <c r="U13" s="13">
-        <v>18116</v>
+        <v>18160</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>0.99867695700110248</v>
+        <v>1.0011025358324146</v>
       </c>
       <c r="W13" s="7">
         <v>18401</v>
@@ -1849,14 +1997,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2718</v>
+        <v>2801</v>
       </c>
       <c r="Z13" s="13">
-        <v>18149</v>
+        <v>18232</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.98630509211455897</v>
+        <v>0.99081571653714473</v>
       </c>
       <c r="AB13" s="7">
         <v>29242</v>
@@ -1866,14 +2014,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4578</v>
+        <v>4797</v>
       </c>
       <c r="AE13" s="13">
-        <v>28941</v>
+        <v>29160</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.98970658641679776</v>
+        <v>0.99719581423979209</v>
       </c>
       <c r="AG13" s="7">
         <v>18261</v>
@@ -1883,14 +2031,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2503</v>
+        <v>2679</v>
       </c>
       <c r="AJ13" s="13">
-        <v>18210</v>
+        <v>18386</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>0.99720716280597999</v>
+        <v>1.0068451892010295</v>
       </c>
       <c r="AL13" s="7">
         <v>18637</v>
@@ -1900,14 +2048,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2264</v>
+        <v>2518</v>
       </c>
       <c r="AO13" s="13">
-        <v>18426</v>
+        <v>18680</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>0.9886784353704996</v>
+        <v>1.0023072382894243</v>
       </c>
       <c r="AQ13" s="7">
         <v>29668</v>
@@ -1917,14 +2065,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>3271</v>
+        <v>4151</v>
       </c>
       <c r="AT13" s="13">
-        <v>28747</v>
+        <v>29627</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>0.96895645139544295</v>
+        <v>0.99861803963866791</v>
       </c>
       <c r="AV13" s="7">
         <v>18676</v>
@@ -1934,17 +2082,51 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>1227</v>
+        <v>2381</v>
       </c>
       <c r="AY13" s="13">
-        <v>17598</v>
+        <v>18752</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>0.9422788605697151</v>
+        <v>1.0040693938744913</v>
+      </c>
+      <c r="BA13" s="7">
+        <v>19025</v>
+      </c>
+      <c r="BB13" s="6">
+        <v>16587</v>
+      </c>
+      <c r="BC13" s="4">
+        <f t="shared" si="20"/>
+        <v>2337</v>
+      </c>
+      <c r="BD13" s="13">
+        <v>18924</v>
+      </c>
+      <c r="BE13" s="5">
+        <f t="shared" si="21"/>
+        <v>0.99469119579500653</v>
+      </c>
+      <c r="BF13" s="7">
+        <v>30254</v>
+      </c>
+      <c r="BG13" s="6">
+        <v>25125</v>
+      </c>
+      <c r="BH13" s="4">
+        <f t="shared" si="22"/>
+        <v>3992</v>
+      </c>
+      <c r="BI13" s="13">
+        <v>29117</v>
+      </c>
+      <c r="BJ13" s="5">
+        <f t="shared" si="23"/>
+        <v>0.96241819263568451</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>5</v>
       </c>
@@ -1959,14 +2141,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>19156</v>
+        <v>19304</v>
       </c>
       <c r="F14" s="13">
-        <v>95304</v>
+        <v>95452</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>1.0073034361028612</v>
+        <v>1.0088677031697546</v>
       </c>
       <c r="H14" s="7">
         <v>97351</v>
@@ -1976,14 +2158,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18663</v>
+        <v>18839</v>
       </c>
       <c r="K14" s="13">
-        <v>97089</v>
+        <v>97265</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.99730870766607427</v>
+        <v>0.99911659869955116</v>
       </c>
       <c r="M14" s="7">
         <v>172809</v>
@@ -1993,14 +2175,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>35147</v>
+        <v>35633</v>
       </c>
       <c r="P14" s="13">
-        <v>171910</v>
+        <v>172396</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99479772465554461</v>
+        <v>0.99761007817879854</v>
       </c>
       <c r="R14" s="7">
         <v>97326</v>
@@ -2010,14 +2192,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>17586</v>
+        <v>17897</v>
       </c>
       <c r="U14" s="13">
-        <v>96439</v>
+        <v>96750</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99088629965271358</v>
+        <v>0.9940817458849639</v>
       </c>
       <c r="W14" s="7">
         <v>98912</v>
@@ -2027,14 +2209,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17076</v>
+        <v>17588</v>
       </c>
       <c r="Z14" s="13">
-        <v>97355</v>
+        <v>97867</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98425873503720474</v>
+        <v>0.98943505338078297</v>
       </c>
       <c r="AB14" s="7">
         <v>175426</v>
@@ -2044,14 +2226,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>32698</v>
+        <v>34187</v>
       </c>
       <c r="AE14" s="13">
-        <v>173406</v>
+        <v>174895</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.98848517323543827</v>
+        <v>0.99697308266733553</v>
       </c>
       <c r="AG14" s="7">
         <v>98057</v>
@@ -2061,14 +2243,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>17351</v>
+        <v>18400</v>
       </c>
       <c r="AJ14" s="13">
-        <v>96949</v>
+        <v>97998</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.98870044973841742</v>
+        <v>0.99939830914672079</v>
       </c>
       <c r="AL14" s="7">
         <v>101581</v>
@@ -2078,14 +2260,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>15944</v>
+        <v>17527</v>
       </c>
       <c r="AO14" s="13">
-        <v>100623</v>
+        <v>102206</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.99056910248963881</v>
+        <v>1.0061527254112481</v>
       </c>
       <c r="AQ14" s="7">
         <v>182247</v>
@@ -2095,14 +2277,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>24241</v>
+        <v>30198</v>
       </c>
       <c r="AT14" s="13">
-        <v>175135</v>
+        <v>181092</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.96097603801434317</v>
+        <v>0.99366244711847107</v>
       </c>
       <c r="AV14" s="7">
         <v>102257</v>
@@ -2112,17 +2294,51 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>9628</v>
+        <v>16876</v>
       </c>
       <c r="AY14" s="13">
-        <v>95136</v>
+        <v>102384</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.93036173562690083</v>
+        <v>1.0012419687649745</v>
+      </c>
+      <c r="BA14" s="7">
+        <v>106311</v>
+      </c>
+      <c r="BB14" s="6">
+        <v>87910</v>
+      </c>
+      <c r="BC14" s="4">
+        <f t="shared" si="20"/>
+        <v>16480</v>
+      </c>
+      <c r="BD14" s="13">
+        <v>104390</v>
+      </c>
+      <c r="BE14" s="5">
+        <f t="shared" si="21"/>
+        <v>0.98193037409111006</v>
+      </c>
+      <c r="BF14" s="7">
+        <v>189210</v>
+      </c>
+      <c r="BG14" s="6">
+        <v>147639</v>
+      </c>
+      <c r="BH14" s="4">
+        <f t="shared" si="22"/>
+        <v>32443</v>
+      </c>
+      <c r="BI14" s="13">
+        <v>180082</v>
+      </c>
+      <c r="BJ14" s="5">
+        <f t="shared" si="23"/>
+        <v>0.95175730669626346</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>6</v>
       </c>
@@ -2137,14 +2353,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>54934</v>
+        <v>55159</v>
       </c>
       <c r="F15" s="13">
-        <v>324107</v>
+        <v>324332</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99787866845650808</v>
+        <v>0.99857141097796775</v>
       </c>
       <c r="H15" s="7">
         <v>331968</v>
@@ -2154,14 +2370,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>51838</v>
+        <v>52142</v>
       </c>
       <c r="K15" s="13">
-        <v>329201</v>
+        <v>329505</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.99166485926354342</v>
+        <v>0.99258061017929444</v>
       </c>
       <c r="M15" s="7">
         <v>549212</v>
@@ -2171,14 +2387,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>92544</v>
+        <v>93275</v>
       </c>
       <c r="P15" s="13">
-        <v>546480</v>
+        <v>547211</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99502560031463261</v>
+        <v>0.99635659818066613</v>
       </c>
       <c r="R15" s="7">
         <v>333160</v>
@@ -2188,14 +2404,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>53148</v>
+        <v>53827</v>
       </c>
       <c r="U15" s="13">
-        <v>331480</v>
+        <v>332159</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99495737783647498</v>
+        <v>0.99699543762756637</v>
       </c>
       <c r="W15" s="7">
         <v>340519</v>
@@ -2205,14 +2421,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>53461</v>
+        <v>54730</v>
       </c>
       <c r="Z15" s="13">
-        <v>335356</v>
+        <v>336625</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98483785045768368</v>
+        <v>0.98856451475541751</v>
       </c>
       <c r="AB15" s="7">
         <v>562036</v>
@@ -2222,14 +2438,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>90988</v>
+        <v>94528</v>
       </c>
       <c r="AE15" s="13">
-        <v>554402</v>
+        <v>557942</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.98641724017678578</v>
+        <v>0.9927157690966415</v>
       </c>
       <c r="AG15" s="7">
         <v>340264</v>
@@ -2239,14 +2455,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>52398</v>
+        <v>55615</v>
       </c>
       <c r="AJ15" s="13">
-        <v>335532</v>
+        <v>338749</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.98609315120024454</v>
+        <v>0.99554757482425416</v>
       </c>
       <c r="AL15" s="7">
         <v>350627</v>
@@ -2256,14 +2472,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>48796</v>
+        <v>53720</v>
       </c>
       <c r="AO15" s="13">
-        <v>346679</v>
+        <v>351603</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98874017117905921</v>
+        <v>1.0027835848351667</v>
       </c>
       <c r="AQ15" s="7">
         <v>580651</v>
@@ -2273,14 +2489,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>63812</v>
+        <v>80350</v>
       </c>
       <c r="AT15" s="13">
-        <v>561737</v>
+        <v>578275</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.96742621643637916</v>
+        <v>0.99590804114691955</v>
       </c>
       <c r="AV15" s="7">
         <v>355536</v>
@@ -2290,17 +2506,51 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>25069</v>
+        <v>49375</v>
       </c>
       <c r="AY15" s="13">
-        <v>330089</v>
+        <v>354395</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.92842637595067734</v>
+        <v>0.9967907609918546</v>
+      </c>
+      <c r="BA15" s="7">
+        <v>365201</v>
+      </c>
+      <c r="BB15" s="6">
+        <v>310982</v>
+      </c>
+      <c r="BC15" s="4">
+        <f t="shared" si="20"/>
+        <v>48638</v>
+      </c>
+      <c r="BD15" s="13">
+        <v>359620</v>
+      </c>
+      <c r="BE15" s="5">
+        <f t="shared" si="21"/>
+        <v>0.98471800460568293</v>
+      </c>
+      <c r="BF15" s="7">
+        <v>600313</v>
+      </c>
+      <c r="BG15" s="6">
+        <v>491036</v>
+      </c>
+      <c r="BH15" s="4">
+        <f t="shared" si="22"/>
+        <v>85276</v>
+      </c>
+      <c r="BI15" s="13">
+        <v>576312</v>
+      </c>
+      <c r="BJ15" s="5">
+        <f t="shared" si="23"/>
+        <v>0.96001918998922231</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>7</v>
       </c>
@@ -2315,14 +2565,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>76429</v>
+        <v>76969</v>
       </c>
       <c r="F16" s="13">
-        <v>451168</v>
+        <v>451708</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99481828725651467</v>
+        <v>0.99600897869544314</v>
       </c>
       <c r="H16" s="7">
         <v>461360</v>
@@ -2332,14 +2582,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>73996</v>
+        <v>74690</v>
       </c>
       <c r="K16" s="13">
-        <v>457815</v>
+        <v>458509</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.99231619559563033</v>
+        <v>0.99382044390497659</v>
       </c>
       <c r="M16" s="7">
         <v>788355</v>
@@ -2349,14 +2599,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>132451</v>
+        <v>133994</v>
       </c>
       <c r="P16" s="13">
-        <v>785450</v>
+        <v>786993</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99631511184682031</v>
+        <v>0.99827235192267438</v>
       </c>
       <c r="R16" s="7">
         <v>462019</v>
@@ -2366,14 +2616,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>76738</v>
+        <v>77940</v>
       </c>
       <c r="U16" s="13">
-        <v>460886</v>
+        <v>462088</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.99754771989896518</v>
+        <v>1.0001493445074769</v>
       </c>
       <c r="W16" s="7">
         <v>472236</v>
@@ -2383,14 +2633,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>76628</v>
+        <v>78556</v>
       </c>
       <c r="Z16" s="13">
-        <v>464707</v>
+        <v>466635</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.9840567004633276</v>
+        <v>0.98813940487383423</v>
       </c>
       <c r="AB16" s="7">
         <v>804216</v>
@@ -2400,14 +2650,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>127527</v>
+        <v>132851</v>
       </c>
       <c r="AE16" s="13">
-        <v>793588</v>
+        <v>798912</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.98678464492126494</v>
+        <v>0.99340475693097374</v>
       </c>
       <c r="AG16" s="7">
         <v>471201</v>
@@ -2417,14 +2667,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>73843</v>
+        <v>78259</v>
       </c>
       <c r="AJ16" s="13">
-        <v>464232</v>
+        <v>468648</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98521013325523499</v>
+        <v>0.99458193000439299</v>
       </c>
       <c r="AL16" s="7">
         <v>484445</v>
@@ -2434,14 +2684,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70920</v>
+        <v>77739</v>
       </c>
       <c r="AO16" s="13">
-        <v>481064</v>
+        <v>487883</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.9930208795632115</v>
+        <v>1.0070967808523155</v>
       </c>
       <c r="AQ16" s="7">
         <v>831010</v>
@@ -2451,14 +2701,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>101767</v>
+        <v>125606</v>
       </c>
       <c r="AT16" s="13">
-        <v>803949</v>
+        <v>827788</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.96743601160034176</v>
+        <v>0.99612279033946638</v>
       </c>
       <c r="AV16" s="7">
         <v>496237</v>
@@ -2468,17 +2718,51 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>38099</v>
+        <v>70572</v>
       </c>
       <c r="AY16" s="13">
-        <v>460967</v>
+        <v>493440</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.92892509022906389</v>
+        <v>0.9943635803053783</v>
+      </c>
+      <c r="BA16" s="7">
+        <v>510690</v>
+      </c>
+      <c r="BB16" s="6">
+        <v>429901</v>
+      </c>
+      <c r="BC16" s="4">
+        <f t="shared" si="20"/>
+        <v>70040</v>
+      </c>
+      <c r="BD16" s="13">
+        <v>499941</v>
+      </c>
+      <c r="BE16" s="5">
+        <f t="shared" si="21"/>
+        <v>0.97895200610938138</v>
+      </c>
+      <c r="BF16" s="7">
+        <v>859721</v>
+      </c>
+      <c r="BG16" s="6">
+        <v>709693</v>
+      </c>
+      <c r="BH16" s="4">
+        <f t="shared" si="22"/>
+        <v>114704</v>
+      </c>
+      <c r="BI16" s="13">
+        <v>824397</v>
+      </c>
+      <c r="BJ16" s="5">
+        <f t="shared" si="23"/>
+        <v>0.95891225176539829</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>8</v>
       </c>
@@ -2493,14 +2777,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>58102</v>
+        <v>58522</v>
       </c>
       <c r="F17" s="13">
-        <v>340870</v>
+        <v>341290</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99594166990495503</v>
+        <v>0.99716881075442865</v>
       </c>
       <c r="H17" s="7">
         <v>352243</v>
@@ -2510,14 +2794,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>54542</v>
+        <v>55045</v>
       </c>
       <c r="K17" s="13">
-        <v>347761</v>
+        <v>348264</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98727582946999659</v>
+        <v>0.98870382094179299</v>
       </c>
       <c r="M17" s="7">
         <v>765449</v>
@@ -2527,14 +2811,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>131010</v>
+        <v>132854</v>
       </c>
       <c r="P17" s="13">
-        <v>761764</v>
+        <v>763608</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99518583210638467</v>
+        <v>0.99759487568734173</v>
       </c>
       <c r="R17" s="7">
         <v>346814</v>
@@ -2544,14 +2828,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55902</v>
+        <v>56808</v>
       </c>
       <c r="U17" s="13">
-        <v>347369</v>
+        <v>348275</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0016002814188585</v>
+        <v>1.0042126327080221</v>
       </c>
       <c r="W17" s="7">
         <v>360071</v>
@@ -2561,14 +2845,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>57613</v>
+        <v>59078</v>
       </c>
       <c r="Z17" s="13">
-        <v>354818</v>
+        <v>356283</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.98541121056680492</v>
+        <v>0.98947985258462912</v>
       </c>
       <c r="AB17" s="7">
         <v>784641</v>
@@ -2578,14 +2862,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>138810</v>
+        <v>144607</v>
       </c>
       <c r="AE17" s="13">
-        <v>775688</v>
+        <v>781485</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.98858968623867471</v>
+        <v>0.99597777837252965</v>
       </c>
       <c r="AG17" s="7">
         <v>355351</v>
@@ -2595,14 +2879,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>56426</v>
+        <v>59545</v>
       </c>
       <c r="AJ17" s="13">
-        <v>352993</v>
+        <v>356112</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99336430740310289</v>
+        <v>1.0021415445573532</v>
       </c>
       <c r="AL17" s="7">
         <v>371770</v>
@@ -2612,14 +2896,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>49975</v>
+        <v>54691</v>
       </c>
       <c r="AO17" s="13">
-        <v>366932</v>
+        <v>371648</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98698657772278564</v>
+        <v>0.99967184011620092</v>
       </c>
       <c r="AQ17" s="7">
         <v>810773</v>
@@ -2629,14 +2913,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>97449</v>
+        <v>120145</v>
       </c>
       <c r="AT17" s="13">
-        <v>784104</v>
+        <v>806800</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.96710669940908245</v>
+        <v>0.9950997381511224</v>
       </c>
       <c r="AV17" s="7">
         <v>369648</v>
@@ -2646,17 +2930,51 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>30952</v>
+        <v>52395</v>
       </c>
       <c r="AY17" s="13">
-        <v>348383</v>
+        <v>369826</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.94247229796996057</v>
+        <v>1.000481539194044</v>
+      </c>
+      <c r="BA17" s="7">
+        <v>385393</v>
+      </c>
+      <c r="BB17" s="6">
+        <v>326949</v>
+      </c>
+      <c r="BC17" s="4">
+        <f t="shared" si="20"/>
+        <v>52551</v>
+      </c>
+      <c r="BD17" s="13">
+        <v>379500</v>
+      </c>
+      <c r="BE17" s="5">
+        <f t="shared" si="21"/>
+        <v>0.9847091151110684</v>
+      </c>
+      <c r="BF17" s="7">
+        <v>839843</v>
+      </c>
+      <c r="BG17" s="6">
+        <v>675432</v>
+      </c>
+      <c r="BH17" s="4">
+        <f t="shared" si="22"/>
+        <v>126996</v>
+      </c>
+      <c r="BI17" s="13">
+        <v>802428</v>
+      </c>
+      <c r="BJ17" s="5">
+        <f t="shared" si="23"/>
+        <v>0.95545000672744784</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>9</v>
       </c>
@@ -2671,14 +2989,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>188949</v>
+        <v>190217</v>
       </c>
       <c r="F18" s="13">
-        <v>1062485</v>
+        <v>1063753</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99218288920265651</v>
+        <v>0.99336698865206896</v>
       </c>
       <c r="H18" s="7">
         <v>1089051</v>
@@ -2688,14 +3006,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>193041</v>
+        <v>194743</v>
       </c>
       <c r="K18" s="13">
-        <v>1077599</v>
+        <v>1079301</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98948442267625669</v>
+        <v>0.99104725123065862</v>
       </c>
       <c r="M18" s="7">
         <v>1637429</v>
@@ -2705,14 +3023,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>295800</v>
+        <v>299299</v>
       </c>
       <c r="P18" s="13">
-        <v>1619837</v>
+        <v>1623336</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.98925632806063657</v>
+        <v>0.99139321460655694</v>
       </c>
       <c r="R18" s="7">
         <v>1090030</v>
@@ -2722,14 +3040,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>186960</v>
+        <v>190052</v>
       </c>
       <c r="U18" s="13">
-        <v>1075686</v>
+        <v>1078778</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.98684072915424348</v>
+        <v>0.98967734832986243</v>
       </c>
       <c r="W18" s="7">
         <v>1107435</v>
@@ -2739,14 +3057,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>187617</v>
+        <v>192684</v>
       </c>
       <c r="Z18" s="13">
-        <v>1083879</v>
+        <v>1088946</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.97872922564303999</v>
+        <v>0.98330466347912071</v>
       </c>
       <c r="AB18" s="7">
         <v>1665905</v>
@@ -2756,14 +3074,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>287400</v>
+        <v>299808</v>
       </c>
       <c r="AE18" s="13">
-        <v>1633045</v>
+        <v>1645453</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.9802749856684505</v>
+        <v>0.98772318949760041</v>
       </c>
       <c r="AG18" s="7">
         <v>1104366</v>
@@ -2773,14 +3091,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>189388</v>
+        <v>200452</v>
       </c>
       <c r="AJ18" s="13">
-        <v>1081742</v>
+        <v>1092806</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.9795140379185886</v>
+        <v>0.98953245572572857</v>
       </c>
       <c r="AL18" s="7">
         <v>1131950</v>
@@ -2790,14 +3108,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>170888</v>
+        <v>187394</v>
       </c>
       <c r="AO18" s="13">
-        <v>1113664</v>
+        <v>1130170</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98384557621803082</v>
+        <v>0.99842749238040551</v>
       </c>
       <c r="AQ18" s="7">
         <v>1717059</v>
@@ -2807,14 +3125,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>208765</v>
+        <v>255463</v>
       </c>
       <c r="AT18" s="13">
-        <v>1654563</v>
+        <v>1701261</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.96360288143855277</v>
+        <v>0.99079938429605507</v>
       </c>
       <c r="AV18" s="7">
         <v>1151692</v>
@@ -2824,17 +3142,51 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>104173</v>
+        <v>176408</v>
       </c>
       <c r="AY18" s="13">
-        <v>1069690</v>
+        <v>1141925</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.92879867186713116</v>
+        <v>0.99151943401534437</v>
+      </c>
+      <c r="BA18" s="7">
+        <v>1182353</v>
+      </c>
+      <c r="BB18" s="6">
+        <v>985583</v>
+      </c>
+      <c r="BC18" s="4">
+        <f t="shared" si="20"/>
+        <v>171917</v>
+      </c>
+      <c r="BD18" s="13">
+        <v>1157500</v>
+      </c>
+      <c r="BE18" s="5">
+        <f t="shared" si="21"/>
+        <v>0.97898005079701245</v>
+      </c>
+      <c r="BF18" s="7">
+        <v>1777125</v>
+      </c>
+      <c r="BG18" s="6">
+        <v>1397229</v>
+      </c>
+      <c r="BH18" s="4">
+        <f t="shared" si="22"/>
+        <v>297567</v>
+      </c>
+      <c r="BI18" s="13">
+        <v>1694796</v>
+      </c>
+      <c r="BJ18" s="5">
+        <f t="shared" si="23"/>
+        <v>0.95367292677780124</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>10</v>
       </c>
@@ -2849,14 +3201,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>64985</v>
+        <v>65712</v>
       </c>
       <c r="F19" s="13">
-        <v>298826</v>
+        <v>299553</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.97777297877422542</v>
+        <v>0.98015175758051687</v>
       </c>
       <c r="H19" s="7">
         <v>314567</v>
@@ -2866,14 +3218,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>67251</v>
+        <v>68173</v>
       </c>
       <c r="K19" s="13">
-        <v>305240</v>
+        <v>306162</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97034971881983811</v>
+        <v>0.97328073192674369</v>
       </c>
       <c r="M19" s="7">
         <v>534704</v>
@@ -2883,14 +3235,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>112302</v>
+        <v>114397</v>
       </c>
       <c r="P19" s="13">
-        <v>523425</v>
+        <v>525520</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.97890608635805976</v>
+        <v>0.9828241419551752</v>
       </c>
       <c r="R19" s="7">
         <v>310887</v>
@@ -2900,14 +3252,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>62344</v>
+        <v>64018</v>
       </c>
       <c r="U19" s="13">
-        <v>303647</v>
+        <v>305321</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97671179560419064</v>
+        <v>0.98209638872001725</v>
       </c>
       <c r="W19" s="7">
         <v>321022</v>
@@ -2917,14 +3269,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>65149</v>
+        <v>67681</v>
       </c>
       <c r="Z19" s="13">
-        <v>307468</v>
+        <v>310000</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.95777859461345327</v>
+        <v>0.96566590451744738</v>
       </c>
       <c r="AB19" s="7">
         <v>548160</v>
@@ -2934,14 +3286,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>105921</v>
+        <v>112682</v>
       </c>
       <c r="AE19" s="13">
-        <v>528156</v>
+        <v>534917</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.96350700525394051</v>
+        <v>0.97584099532983071</v>
       </c>
       <c r="AG19" s="7">
         <v>315587</v>
@@ -2951,14 +3303,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>61515</v>
+        <v>66478</v>
       </c>
       <c r="AJ19" s="13">
-        <v>303469</v>
+        <v>308432</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.96160171363205704</v>
+        <v>0.97732796344589601</v>
       </c>
       <c r="AL19" s="7">
         <v>327315</v>
@@ -2968,14 +3320,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>53561</v>
+        <v>60542</v>
       </c>
       <c r="AO19" s="13">
-        <v>313629</v>
+        <v>320610</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.9581870675037808</v>
+        <v>0.97951514596031342</v>
       </c>
       <c r="AQ19" s="7">
         <v>564697</v>
@@ -2985,14 +3337,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>82053</v>
+        <v>102790</v>
       </c>
       <c r="AT19" s="13">
-        <v>533096</v>
+        <v>553833</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.94403901561368309</v>
+        <v>0.98076136405895553</v>
       </c>
       <c r="AV19" s="7">
         <v>330794</v>
@@ -3002,17 +3354,51 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>30848</v>
+        <v>56582</v>
       </c>
       <c r="AY19" s="13">
-        <v>298973</v>
+        <v>324707</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.90380418024510722</v>
+        <v>0.9815988198093073</v>
+      </c>
+      <c r="BA19" s="7">
+        <v>346688</v>
+      </c>
+      <c r="BB19" s="6">
+        <v>274881</v>
+      </c>
+      <c r="BC19" s="4">
+        <f t="shared" si="20"/>
+        <v>57029</v>
+      </c>
+      <c r="BD19" s="13">
+        <v>331910</v>
+      </c>
+      <c r="BE19" s="5">
+        <f t="shared" si="21"/>
+        <v>0.95737377699833859</v>
+      </c>
+      <c r="BF19" s="7">
+        <v>595475</v>
+      </c>
+      <c r="BG19" s="6">
+        <v>433627</v>
+      </c>
+      <c r="BH19" s="4">
+        <f t="shared" si="22"/>
+        <v>114320</v>
+      </c>
+      <c r="BI19" s="13">
+        <v>547947</v>
+      </c>
+      <c r="BJ19" s="5">
+        <f t="shared" si="23"/>
+        <v>0.9201847264788614</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A20" s="18">
         <v>11</v>
       </c>
@@ -3027,14 +3413,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1718</v>
+        <v>1758</v>
       </c>
       <c r="F20" s="13">
-        <v>6452</v>
+        <v>6492</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.98699709346795161</v>
+        <v>0.99311610830656261</v>
       </c>
       <c r="H20" s="7">
         <v>6601</v>
@@ -3044,14 +3430,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1614</v>
+        <v>1666</v>
       </c>
       <c r="K20" s="13">
-        <v>6463</v>
+        <v>6515</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.97909407665505221</v>
+        <v>0.98697167095894567</v>
       </c>
       <c r="M20" s="7">
         <v>10050</v>
@@ -3061,14 +3447,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2485</v>
+        <v>2560</v>
       </c>
       <c r="P20" s="13">
-        <v>9928</v>
+        <v>10003</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.98786069651741293</v>
+        <v>0.99532338308457713</v>
       </c>
       <c r="R20" s="7">
         <v>6485</v>
@@ -3078,14 +3464,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1558</v>
+        <v>1632</v>
       </c>
       <c r="U20" s="13">
-        <v>6361</v>
+        <v>6435</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.98087895142636849</v>
+        <v>0.99228989976869697</v>
       </c>
       <c r="W20" s="7">
         <v>6573</v>
@@ -3095,14 +3481,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1425</v>
+        <v>1531</v>
       </c>
       <c r="Z20" s="13">
-        <v>6331</v>
+        <v>6437</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.96318271717632742</v>
+        <v>0.97930929560322533</v>
       </c>
       <c r="AB20" s="7">
         <v>10123</v>
@@ -3112,14 +3498,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2390</v>
+        <v>2605</v>
       </c>
       <c r="AE20" s="13">
-        <v>9778</v>
+        <v>9993</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.96591919391484737</v>
+        <v>0.98715795712733378</v>
       </c>
       <c r="AG20" s="7">
         <v>6547</v>
@@ -3129,14 +3515,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1347</v>
+        <v>1551</v>
       </c>
       <c r="AJ20" s="13">
-        <v>6243</v>
+        <v>6447</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.95356651901634337</v>
+        <v>0.98472582862379721</v>
       </c>
       <c r="AL20" s="7">
         <v>6649</v>
@@ -3146,14 +3532,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1245</v>
+        <v>1527</v>
       </c>
       <c r="AO20" s="13">
-        <v>6234</v>
+        <v>6516</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.93758459918784776</v>
+        <v>0.97999699202887647</v>
       </c>
       <c r="AQ20" s="7">
         <v>10228</v>
@@ -3163,14 +3549,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>1465</v>
+        <v>2317</v>
       </c>
       <c r="AT20" s="13">
-        <v>9159</v>
+        <v>10011</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.89548298787641767</v>
+        <v>0.97878373093468907</v>
       </c>
       <c r="AV20" s="7">
         <v>6568</v>
@@ -3180,17 +3566,51 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>494</v>
+        <v>1317</v>
       </c>
       <c r="AY20" s="13">
-        <v>5578</v>
+        <v>6401</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.84926918392204631</v>
+        <v>0.9745736906211937</v>
+      </c>
+      <c r="BA20" s="7">
+        <v>6793</v>
+      </c>
+      <c r="BB20" s="6">
+        <v>5124</v>
+      </c>
+      <c r="BC20" s="4">
+        <f t="shared" si="20"/>
+        <v>1296</v>
+      </c>
+      <c r="BD20" s="13">
+        <v>6420</v>
+      </c>
+      <c r="BE20" s="5">
+        <f t="shared" si="21"/>
+        <v>0.94509053437361989</v>
+      </c>
+      <c r="BF20" s="7">
+        <v>10395</v>
+      </c>
+      <c r="BG20" s="6">
+        <v>7498</v>
+      </c>
+      <c r="BH20" s="4">
+        <f t="shared" si="22"/>
+        <v>2057</v>
+      </c>
+      <c r="BI20" s="13">
+        <v>9555</v>
+      </c>
+      <c r="BJ20" s="5">
+        <f t="shared" si="23"/>
+        <v>0.91919191919191923</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>12</v>
       </c>
@@ -3205,14 +3625,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4029</v>
+        <v>4152</v>
       </c>
       <c r="F21" s="13">
-        <v>11907</v>
+        <v>12030</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.99142381348875941</v>
+        <v>1.0016652789342215</v>
       </c>
       <c r="H21" s="7">
         <v>12254</v>
@@ -3222,14 +3642,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3640</v>
+        <v>3784</v>
       </c>
       <c r="K21" s="13">
-        <v>12094</v>
+        <v>12238</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.986943039007671</v>
+        <v>0.99869430390076708</v>
       </c>
       <c r="M21" s="7">
         <v>16207</v>
@@ -3239,14 +3659,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4817</v>
+        <v>5056</v>
       </c>
       <c r="P21" s="13">
-        <v>16073</v>
+        <v>16312</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>0.99173196766829153</v>
+        <v>1.0064786820509657</v>
       </c>
       <c r="R21" s="7">
         <v>12383</v>
@@ -3256,14 +3676,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3660</v>
+        <v>3877</v>
       </c>
       <c r="U21" s="13">
-        <v>12305</v>
+        <v>12522</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>0.99370104175078733</v>
+        <v>1.0112250666235969</v>
       </c>
       <c r="W21" s="7">
         <v>12782</v>
@@ -3273,14 +3693,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3619</v>
+        <v>3935</v>
       </c>
       <c r="Z21" s="13">
-        <v>12410</v>
+        <v>12726</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.97089657330621182</v>
+        <v>0.99561883899233294</v>
       </c>
       <c r="AB21" s="7">
         <v>16816</v>
@@ -3290,14 +3710,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4065</v>
+        <v>4598</v>
       </c>
       <c r="AE21" s="13">
-        <v>16218</v>
+        <v>16751</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.96443862987630824</v>
+        <v>0.99613463368220745</v>
       </c>
       <c r="AG21" s="7">
         <v>12696</v>
@@ -3307,14 +3727,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3264</v>
+        <v>3819</v>
       </c>
       <c r="AJ21" s="13">
-        <v>12099</v>
+        <v>12654</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.95297731568998112</v>
+        <v>0.99669187145557658</v>
       </c>
       <c r="AL21" s="7">
         <v>13072</v>
@@ -3324,14 +3744,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>2991</v>
+        <v>3735</v>
       </c>
       <c r="AO21" s="13">
-        <v>12120</v>
+        <v>12864</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.92717258261933899</v>
+        <v>0.98408812729498163</v>
       </c>
       <c r="AQ21" s="7">
         <v>17310</v>
@@ -3341,14 +3761,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>2878</v>
+        <v>4329</v>
       </c>
       <c r="AT21" s="13">
-        <v>15504</v>
+        <v>16955</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.89566724436741763</v>
+        <v>0.97949162333911033</v>
       </c>
       <c r="AV21" s="7">
         <v>13094</v>
@@ -3358,17 +3778,51 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>1127</v>
+        <v>3198</v>
       </c>
       <c r="AY21" s="13">
-        <v>10616</v>
+        <v>12687</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.8107530166488468</v>
+        <v>0.96891706124942723</v>
+      </c>
+      <c r="BA21" s="7">
+        <v>13518</v>
+      </c>
+      <c r="BB21" s="6">
+        <v>9781</v>
+      </c>
+      <c r="BC21" s="4">
+        <f t="shared" si="20"/>
+        <v>2898</v>
+      </c>
+      <c r="BD21" s="13">
+        <v>12679</v>
+      </c>
+      <c r="BE21" s="5">
+        <f t="shared" si="21"/>
+        <v>0.93793460571090403</v>
+      </c>
+      <c r="BF21" s="7">
+        <v>17905</v>
+      </c>
+      <c r="BG21" s="6">
+        <v>10944</v>
+      </c>
+      <c r="BH21" s="4">
+        <f t="shared" si="22"/>
+        <v>4481</v>
+      </c>
+      <c r="BI21" s="13">
+        <v>15425</v>
+      </c>
+      <c r="BJ21" s="5">
+        <f t="shared" si="23"/>
+        <v>0.86149120357442055</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="18">
         <v>13</v>
       </c>
@@ -3383,14 +3837,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1834</v>
+        <v>1877</v>
       </c>
       <c r="F22" s="13">
-        <v>6928</v>
+        <v>6971</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.9902801600914809</v>
+        <v>0.99642652944539734</v>
       </c>
       <c r="H22" s="7">
         <v>7077</v>
@@ -3400,14 +3854,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1882</v>
+        <v>1934</v>
       </c>
       <c r="K22" s="13">
-        <v>6974</v>
+        <v>7026</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.98544581037162637</v>
+        <v>0.99279355659177615</v>
       </c>
       <c r="M22" s="7">
         <v>8504</v>
@@ -3417,14 +3871,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2310</v>
+        <v>2388</v>
       </c>
       <c r="P22" s="13">
-        <v>8428</v>
+        <v>8506</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>0.99106302916274691</v>
+        <v>1.0002351834430856</v>
       </c>
       <c r="R22" s="7">
         <v>7111</v>
@@ -3434,14 +3888,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1750</v>
+        <v>1828</v>
       </c>
       <c r="U22" s="13">
-        <v>6991</v>
+        <v>7069</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.9831247363240051</v>
+        <v>0.99409365771340175</v>
       </c>
       <c r="W22" s="7">
         <v>7191</v>
@@ -3451,14 +3905,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1601</v>
+        <v>1729</v>
       </c>
       <c r="Z22" s="13">
-        <v>6992</v>
+        <v>7120</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.97232651926018632</v>
+        <v>0.99012654707272985</v>
       </c>
       <c r="AB22" s="7">
         <v>8707</v>
@@ -3468,14 +3922,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>1784</v>
+        <v>2008</v>
       </c>
       <c r="AE22" s="13">
-        <v>8413</v>
+        <v>8637</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.96623406454576777</v>
+        <v>0.99196049155851618</v>
       </c>
       <c r="AG22" s="7">
         <v>7162</v>
@@ -3485,14 +3939,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1579</v>
+        <v>1813</v>
       </c>
       <c r="AJ22" s="13">
-        <v>6876</v>
+        <v>7110</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.96006702038536718</v>
+        <v>0.99273945825188492</v>
       </c>
       <c r="AL22" s="7">
         <v>7226</v>
@@ -3502,14 +3956,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1290</v>
+        <v>1630</v>
       </c>
       <c r="AO22" s="13">
-        <v>6802</v>
+        <v>7142</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.94132300027677829</v>
+        <v>0.98837531137558821</v>
       </c>
       <c r="AQ22" s="7">
         <v>8754</v>
@@ -3519,14 +3973,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>1643</v>
+        <v>2290</v>
       </c>
       <c r="AT22" s="13">
-        <v>7989</v>
+        <v>8636</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.9126113776559287</v>
+        <v>0.98652044779529358</v>
       </c>
       <c r="AV22" s="7">
         <v>7182</v>
@@ -3536,17 +3990,51 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>623</v>
+        <v>1643</v>
       </c>
       <c r="AY22" s="13">
-        <v>6009</v>
+        <v>7029</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.83667502088554724</v>
+        <v>0.97869674185463662</v>
+      </c>
+      <c r="BA22" s="7">
+        <v>7296</v>
+      </c>
+      <c r="BB22" s="6">
+        <v>5497</v>
+      </c>
+      <c r="BC22" s="4">
+        <f t="shared" si="20"/>
+        <v>1502</v>
+      </c>
+      <c r="BD22" s="13">
+        <v>6999</v>
+      </c>
+      <c r="BE22" s="5">
+        <f t="shared" si="21"/>
+        <v>0.95929276315789469</v>
+      </c>
+      <c r="BF22" s="7">
+        <v>8939</v>
+      </c>
+      <c r="BG22" s="6">
+        <v>6106</v>
+      </c>
+      <c r="BH22" s="4">
+        <f t="shared" si="22"/>
+        <v>1980</v>
+      </c>
+      <c r="BI22" s="13">
+        <v>8086</v>
+      </c>
+      <c r="BJ22" s="5">
+        <f t="shared" si="23"/>
+        <v>0.90457545586754673</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>14</v>
       </c>
@@ -3561,14 +4049,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2894</v>
+        <v>2939</v>
       </c>
       <c r="F23" s="13">
-        <v>9127</v>
+        <v>9172</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.97023493143403849</v>
+        <v>0.97501860316785371</v>
       </c>
       <c r="H23" s="7">
         <v>9786</v>
@@ -3578,14 +4066,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>3165</v>
+        <v>3222</v>
       </c>
       <c r="K23" s="13">
-        <v>9239</v>
+        <v>9296</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.94410382178622521</v>
+        <v>0.94992846924177399</v>
       </c>
       <c r="M23" s="7">
         <v>12056</v>
@@ -3595,14 +4083,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3880</v>
+        <v>3982</v>
       </c>
       <c r="P23" s="13">
-        <v>11733</v>
+        <v>11835</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.97320836098208363</v>
+        <v>0.98166887856668883</v>
       </c>
       <c r="R23" s="7">
         <v>9480</v>
@@ -3612,14 +4100,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2843</v>
+        <v>2933</v>
       </c>
       <c r="U23" s="13">
-        <v>9270</v>
+        <v>9360</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.97784810126582278</v>
+        <v>0.98734177215189878</v>
       </c>
       <c r="W23" s="7">
         <v>9764</v>
@@ -3629,14 +4117,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>2865</v>
+        <v>3011</v>
       </c>
       <c r="Z23" s="13">
-        <v>9284</v>
+        <v>9430</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.95083981974600573</v>
+        <v>0.96579270790659566</v>
       </c>
       <c r="AB23" s="7">
         <v>12327</v>
@@ -3646,14 +4134,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3206</v>
+        <v>3481</v>
       </c>
       <c r="AE23" s="13">
-        <v>11747</v>
+        <v>12022</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.95294881155187794</v>
+        <v>0.97525756469538416</v>
       </c>
       <c r="AG23" s="7">
         <v>9618</v>
@@ -3663,14 +4151,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>2676</v>
+        <v>2972</v>
       </c>
       <c r="AJ23" s="13">
-        <v>9012</v>
+        <v>9308</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.93699313786650029</v>
+        <v>0.96776876689540448</v>
       </c>
       <c r="AL23" s="7">
         <v>9741</v>
@@ -3680,14 +4168,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2378</v>
+        <v>2790</v>
       </c>
       <c r="AO23" s="13">
-        <v>9014</v>
+        <v>9426</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.92536700544091988</v>
+        <v>0.96766245765321834</v>
       </c>
       <c r="AQ23" s="7">
         <v>12556</v>
@@ -3697,14 +4185,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>2593</v>
+        <v>3430</v>
       </c>
       <c r="AT23" s="13">
-        <v>11219</v>
+        <v>12056</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.89351704364447271</v>
+        <v>0.96017840076457472</v>
       </c>
       <c r="AV23" s="7">
         <v>9718</v>
@@ -3714,17 +4202,51 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>1143</v>
+        <v>2443</v>
       </c>
       <c r="AY23" s="13">
-        <v>8007</v>
+        <v>9307</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.82393496604239558</v>
+        <v>0.95770734719077999</v>
+      </c>
+      <c r="BA23" s="7">
+        <v>10107</v>
+      </c>
+      <c r="BB23" s="6">
+        <v>6835</v>
+      </c>
+      <c r="BC23" s="4">
+        <f t="shared" si="20"/>
+        <v>2493</v>
+      </c>
+      <c r="BD23" s="13">
+        <v>9328</v>
+      </c>
+      <c r="BE23" s="5">
+        <f t="shared" si="21"/>
+        <v>0.92292470564954987</v>
+      </c>
+      <c r="BF23" s="7">
+        <v>13018</v>
+      </c>
+      <c r="BG23" s="6">
+        <v>8007</v>
+      </c>
+      <c r="BH23" s="4">
+        <f t="shared" si="22"/>
+        <v>3302</v>
+      </c>
+      <c r="BI23" s="13">
+        <v>11309</v>
+      </c>
+      <c r="BJ23" s="5">
+        <f t="shared" si="23"/>
+        <v>0.86872023352281458</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="18">
         <v>15</v>
       </c>
@@ -3739,14 +4261,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="F24" s="13">
-        <v>6860</v>
+        <v>6881</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.98818784212042643</v>
+        <v>0.99121290694324404</v>
       </c>
       <c r="H24" s="7">
         <v>7059</v>
@@ -3756,14 +4278,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1547</v>
+        <v>1575</v>
       </c>
       <c r="K24" s="13">
-        <v>6902</v>
+        <v>6930</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.97775888936109934</v>
+        <v>0.98172545686357837</v>
       </c>
       <c r="M24" s="7">
         <v>8056</v>
@@ -3773,14 +4295,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1704</v>
+        <v>1748</v>
       </c>
       <c r="P24" s="13">
-        <v>7867</v>
+        <v>7911</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.97653922542204563</v>
+        <v>0.9820009930486594</v>
       </c>
       <c r="R24" s="7">
         <v>7134</v>
@@ -3790,14 +4312,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1323</v>
+        <v>1371</v>
       </c>
       <c r="U24" s="13">
-        <v>6945</v>
+        <v>6993</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.97350714886459211</v>
+        <v>0.98023549201009252</v>
       </c>
       <c r="W24" s="7">
         <v>7208</v>
@@ -3807,14 +4329,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1360</v>
+        <v>1418</v>
       </c>
       <c r="Z24" s="13">
-        <v>6979</v>
+        <v>7037</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.96822974472807988</v>
+        <v>0.9762763596004439</v>
       </c>
       <c r="AB24" s="7">
         <v>8228</v>
@@ -3824,14 +4346,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1119</v>
+        <v>1226</v>
       </c>
       <c r="AE24" s="13">
-        <v>7933</v>
+        <v>8040</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.96414681575109384</v>
+        <v>0.97715119105493442</v>
       </c>
       <c r="AG24" s="7">
         <v>7344</v>
@@ -3841,14 +4363,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1266</v>
+        <v>1390</v>
       </c>
       <c r="AJ24" s="13">
-        <v>7011</v>
+        <v>7135</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.95465686274509809</v>
+        <v>0.97154139433551201</v>
       </c>
       <c r="AL24" s="7">
         <v>7506</v>
@@ -3858,14 +4380,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1112</v>
+        <v>1278</v>
       </c>
       <c r="AO24" s="13">
-        <v>7054</v>
+        <v>7220</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.93978150812683192</v>
+        <v>0.96189714894750866</v>
       </c>
       <c r="AQ24" s="7">
         <v>8509</v>
@@ -3875,14 +4397,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1182</v>
+        <v>1497</v>
       </c>
       <c r="AT24" s="13">
-        <v>7876</v>
+        <v>8191</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.92560817957456809</v>
+        <v>0.96262780585262664</v>
       </c>
       <c r="AV24" s="7">
         <v>7570</v>
@@ -3892,17 +4414,51 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>606</v>
+        <v>1176</v>
       </c>
       <c r="AY24" s="13">
-        <v>6649</v>
+        <v>7219</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.87833553500660499</v>
+        <v>0.95363276089828275</v>
+      </c>
+      <c r="BA24" s="7">
+        <v>7648</v>
+      </c>
+      <c r="BB24" s="6">
+        <v>5994</v>
+      </c>
+      <c r="BC24" s="4">
+        <f t="shared" si="20"/>
+        <v>1284</v>
+      </c>
+      <c r="BD24" s="13">
+        <v>7278</v>
+      </c>
+      <c r="BE24" s="5">
+        <f t="shared" si="21"/>
+        <v>0.95162133891213385</v>
+      </c>
+      <c r="BF24" s="7">
+        <v>8767</v>
+      </c>
+      <c r="BG24" s="6">
+        <v>6767</v>
+      </c>
+      <c r="BH24" s="4">
+        <f t="shared" si="22"/>
+        <v>1391</v>
+      </c>
+      <c r="BI24" s="13">
+        <v>8158</v>
+      </c>
+      <c r="BJ24" s="5">
+        <f t="shared" si="23"/>
+        <v>0.9305349606478841</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>16</v>
       </c>
@@ -3917,14 +4473,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4609</v>
+        <v>4674</v>
       </c>
       <c r="F25" s="13">
-        <v>21269</v>
+        <v>21334</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.99049969729427656</v>
+        <v>0.99352675452894335</v>
       </c>
       <c r="H25" s="7">
         <v>21813</v>
@@ -3934,14 +4490,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>4425</v>
+        <v>4498</v>
       </c>
       <c r="K25" s="13">
-        <v>21447</v>
+        <v>21520</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.9832210149910604</v>
+        <v>0.98656764314858114</v>
       </c>
       <c r="M25" s="7">
         <v>29215</v>
@@ -3951,14 +4507,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>6061</v>
+        <v>6184</v>
       </c>
       <c r="P25" s="13">
-        <v>28852</v>
+        <v>28975</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.98757487591990412</v>
+        <v>0.9917850419305152</v>
       </c>
       <c r="R25" s="7">
         <v>21767</v>
@@ -3968,14 +4524,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4399</v>
+        <v>4517</v>
       </c>
       <c r="U25" s="13">
-        <v>21490</v>
+        <v>21608</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.98727431432903023</v>
+        <v>0.99269536454265628</v>
       </c>
       <c r="W25" s="7">
         <v>22114</v>
@@ -3985,14 +4541,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4061</v>
+        <v>4208</v>
       </c>
       <c r="Z25" s="13">
-        <v>21587</v>
+        <v>21734</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.97616894275119837</v>
+        <v>0.98281631545627202</v>
       </c>
       <c r="AB25" s="7">
         <v>29630</v>
@@ -4002,14 +4558,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5124</v>
+        <v>5427</v>
       </c>
       <c r="AE25" s="13">
-        <v>29010</v>
+        <v>29313</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.97907526155923053</v>
+        <v>0.98930138373270338</v>
       </c>
       <c r="AG25" s="7">
         <v>22174</v>
@@ -4019,14 +4575,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4054</v>
+        <v>4327</v>
       </c>
       <c r="AJ25" s="13">
-        <v>21569</v>
+        <v>21842</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.9727157932713989</v>
+        <v>0.98502750969604036</v>
       </c>
       <c r="AL25" s="7">
         <v>22503</v>
@@ -4036,14 +4592,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3838</v>
+        <v>4234</v>
       </c>
       <c r="AO25" s="13">
-        <v>21800</v>
+        <v>22196</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.96875972092609874</v>
+        <v>0.98635737457227923</v>
       </c>
       <c r="AQ25" s="7">
         <v>30294</v>
@@ -4053,14 +4609,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>4497</v>
+        <v>5515</v>
       </c>
       <c r="AT25" s="13">
-        <v>28829</v>
+        <v>29847</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.95164058889549086</v>
+        <v>0.98524460289166171</v>
       </c>
       <c r="AV25" s="7">
         <v>22740</v>
@@ -4070,17 +4626,51 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>2318</v>
+        <v>4149</v>
       </c>
       <c r="AY25" s="13">
-        <v>20581</v>
+        <v>22412</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.90505716798592784</v>
+        <v>0.98557607739665787</v>
+      </c>
+      <c r="BA25" s="7">
+        <v>23197</v>
+      </c>
+      <c r="BB25" s="6">
+        <v>18655</v>
+      </c>
+      <c r="BC25" s="4">
+        <f t="shared" si="20"/>
+        <v>3888</v>
+      </c>
+      <c r="BD25" s="13">
+        <v>22543</v>
+      </c>
+      <c r="BE25" s="5">
+        <f t="shared" si="21"/>
+        <v>0.97180669914213047</v>
+      </c>
+      <c r="BF25" s="7">
+        <v>31043</v>
+      </c>
+      <c r="BG25" s="6">
+        <v>23068</v>
+      </c>
+      <c r="BH25" s="4">
+        <f t="shared" si="22"/>
+        <v>6061</v>
+      </c>
+      <c r="BI25" s="13">
+        <v>29129</v>
+      </c>
+      <c r="BJ25" s="5">
+        <f t="shared" si="23"/>
+        <v>0.93834358792642458</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A26" s="18">
         <v>17</v>
       </c>
@@ -4095,14 +4685,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3240</v>
+        <v>3297</v>
       </c>
       <c r="F26" s="13">
-        <v>14386</v>
+        <v>14443</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.98859263331500824</v>
+        <v>0.99250962067069814</v>
       </c>
       <c r="H26" s="7">
         <v>14990</v>
@@ -4112,14 +4702,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3203</v>
+        <v>3272</v>
       </c>
       <c r="K26" s="13">
-        <v>14682</v>
+        <v>14751</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.97945296864576381</v>
+        <v>0.98405603735823888</v>
       </c>
       <c r="M26" s="7">
         <v>28508</v>
@@ -4129,14 +4719,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5723</v>
+        <v>5888</v>
       </c>
       <c r="P26" s="13">
-        <v>28162</v>
+        <v>28327</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.98786305598428514</v>
+        <v>0.99365090500912023</v>
       </c>
       <c r="R26" s="7">
         <v>14719</v>
@@ -4146,14 +4736,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3244</v>
+        <v>3367</v>
       </c>
       <c r="U26" s="13">
-        <v>14491</v>
+        <v>14614</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.98450981724301923</v>
+        <v>0.992866363204022</v>
       </c>
       <c r="W26" s="7">
         <v>15123</v>
@@ -4163,14 +4753,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3235</v>
+        <v>3397</v>
       </c>
       <c r="Z26" s="13">
-        <v>14606</v>
+        <v>14768</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.96581366131058655</v>
+        <v>0.97652582159624413</v>
       </c>
       <c r="AB26" s="7">
         <v>29054</v>
@@ -4180,14 +4770,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>4597</v>
+        <v>5019</v>
       </c>
       <c r="AE26" s="13">
-        <v>28175</v>
+        <v>28597</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.96974599022509811</v>
+        <v>0.98427066841054589</v>
       </c>
       <c r="AG26" s="7">
         <v>14835</v>
@@ -4197,14 +4787,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>2876</v>
+        <v>3214</v>
       </c>
       <c r="AJ26" s="13">
-        <v>14237</v>
+        <v>14575</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.95968992248062013</v>
+        <v>0.98247387933940011</v>
       </c>
       <c r="AL26" s="7">
         <v>15316</v>
@@ -4214,14 +4804,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>2657</v>
+        <v>3122</v>
       </c>
       <c r="AO26" s="13">
-        <v>14343</v>
+        <v>14808</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.9364716636197441</v>
+        <v>0.96683207103682423</v>
       </c>
       <c r="AQ26" s="7">
         <v>29312</v>
@@ -4231,14 +4821,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>3663</v>
+        <v>5125</v>
       </c>
       <c r="AT26" s="13">
-        <v>27191</v>
+        <v>28653</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.92764055676855894</v>
+        <v>0.97751774017467252</v>
       </c>
       <c r="AV26" s="7">
         <v>15164</v>
@@ -4248,17 +4838,51 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>1227</v>
+        <v>2722</v>
       </c>
       <c r="AY26" s="13">
-        <v>13223</v>
+        <v>14718</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.87199947243471376</v>
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="BA26" s="7">
+        <v>15499</v>
+      </c>
+      <c r="BB26" s="6">
+        <v>11911</v>
+      </c>
+      <c r="BC26" s="4">
+        <f t="shared" si="20"/>
+        <v>2743</v>
+      </c>
+      <c r="BD26" s="13">
+        <v>14654</v>
+      </c>
+      <c r="BE26" s="5">
+        <f t="shared" si="21"/>
+        <v>0.9454803535711982</v>
+      </c>
+      <c r="BF26" s="7">
+        <v>29635</v>
+      </c>
+      <c r="BG26" s="6">
+        <v>22864</v>
+      </c>
+      <c r="BH26" s="4">
+        <f t="shared" si="22"/>
+        <v>4652</v>
+      </c>
+      <c r="BI26" s="13">
+        <v>27516</v>
+      </c>
+      <c r="BJ26" s="5">
+        <f t="shared" si="23"/>
+        <v>0.92849670997131772</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>18</v>
       </c>
@@ -4273,14 +4897,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34042</v>
+        <v>34530</v>
       </c>
       <c r="F27" s="13">
-        <v>129037</v>
+        <v>129525</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.98405374900860232</v>
+        <v>0.98777530352022447</v>
       </c>
       <c r="H27" s="7">
         <v>134384</v>
@@ -4290,14 +4914,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>33052</v>
+        <v>33645</v>
       </c>
       <c r="K27" s="13">
-        <v>129856</v>
+        <v>130449</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.96630551256101915</v>
+        <v>0.9707182402666984</v>
       </c>
       <c r="M27" s="7">
         <v>190911</v>
@@ -4307,14 +4931,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>49375</v>
+        <v>50592</v>
       </c>
       <c r="P27" s="13">
-        <v>189164</v>
+        <v>190381</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99084913912765638</v>
+        <v>0.99722383728543662</v>
       </c>
       <c r="R27" s="7">
         <v>131264</v>
@@ -4324,14 +4948,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>31682</v>
+        <v>32665</v>
       </c>
       <c r="U27" s="13">
-        <v>129240</v>
+        <v>130223</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.98458069234519752</v>
+        <v>0.99206941735738663</v>
       </c>
       <c r="W27" s="7">
         <v>134144</v>
@@ -4341,14 +4965,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>35707</v>
+        <v>37112</v>
       </c>
       <c r="Z27" s="13">
-        <v>129978</v>
+        <v>131383</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.96894382156488545</v>
+        <v>0.97941764074427484</v>
       </c>
       <c r="AB27" s="7">
         <v>194609</v>
@@ -4358,14 +4982,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>44326</v>
+        <v>47610</v>
       </c>
       <c r="AE27" s="13">
-        <v>188910</v>
+        <v>192194</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.9707156400783109</v>
+        <v>0.98759050198089504</v>
       </c>
       <c r="AG27" s="7">
         <v>134089</v>
@@ -4375,14 +4999,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>30225</v>
+        <v>33172</v>
       </c>
       <c r="AJ27" s="13">
-        <v>128574</v>
+        <v>131521</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.95887060086957165</v>
+        <v>0.98084854089448048</v>
       </c>
       <c r="AL27" s="7">
         <v>137688</v>
@@ -4392,14 +5016,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>26931</v>
+        <v>31217</v>
       </c>
       <c r="AO27" s="13">
-        <v>131053</v>
+        <v>135339</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.95181134158387082</v>
+        <v>0.98293968973331014</v>
       </c>
       <c r="AQ27" s="7">
         <v>200322</v>
@@ -4409,14 +5033,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>35289</v>
+        <v>46202</v>
       </c>
       <c r="AT27" s="13">
-        <v>185578</v>
+        <v>196491</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.92639849841754773</v>
+        <v>0.98087578997813518</v>
       </c>
       <c r="AV27" s="7">
         <v>139481</v>
@@ -4426,17 +5050,51 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>13454</v>
+        <v>28116</v>
       </c>
       <c r="AY27" s="13">
-        <v>120696</v>
+        <v>135358</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.8653221585735692</v>
+        <v>0.97044041840824202</v>
+      </c>
+      <c r="BA27" s="7">
+        <v>143305</v>
+      </c>
+      <c r="BB27" s="6">
+        <v>108417</v>
+      </c>
+      <c r="BC27" s="4">
+        <f t="shared" si="20"/>
+        <v>27598</v>
+      </c>
+      <c r="BD27" s="13">
+        <v>136015</v>
+      </c>
+      <c r="BE27" s="5">
+        <f t="shared" si="21"/>
+        <v>0.94912947908307455</v>
+      </c>
+      <c r="BF27" s="7">
+        <v>208143</v>
+      </c>
+      <c r="BG27" s="6">
+        <v>140127</v>
+      </c>
+      <c r="BH27" s="4">
+        <f t="shared" si="22"/>
+        <v>47391</v>
+      </c>
+      <c r="BI27" s="13">
+        <v>187518</v>
+      </c>
+      <c r="BJ27" s="5">
+        <f t="shared" si="23"/>
+        <v>0.90090947089260753</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="18">
         <v>19</v>
       </c>
@@ -4451,14 +5109,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>69511</v>
+        <v>70016</v>
       </c>
       <c r="F28" s="13">
-        <v>434366</v>
+        <v>434871</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99280707087560827</v>
+        <v>0.99396132229213763</v>
       </c>
       <c r="H28" s="7">
         <v>447363</v>
@@ -4468,14 +5126,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>69517</v>
+        <v>70143</v>
       </c>
       <c r="K28" s="13">
-        <v>441614</v>
+        <v>442240</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98714913839544172</v>
+        <v>0.98854844946944653</v>
       </c>
       <c r="M28" s="7">
         <v>722935</v>
@@ -4485,14 +5143,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>116087</v>
+        <v>117515</v>
       </c>
       <c r="P28" s="13">
-        <v>715526</v>
+        <v>716954</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.98975149909742921</v>
+        <v>0.99172678041594331</v>
       </c>
       <c r="R28" s="7">
         <v>448339</v>
@@ -4502,14 +5160,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>68156</v>
+        <v>69404</v>
       </c>
       <c r="U28" s="13">
-        <v>444056</v>
+        <v>445304</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99044696089343109</v>
+        <v>0.99323056883295902</v>
       </c>
       <c r="W28" s="7">
         <v>458076</v>
@@ -4519,14 +5177,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>71041</v>
+        <v>73214</v>
       </c>
       <c r="Z28" s="13">
-        <v>447982</v>
+        <v>450155</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.97796435525982583</v>
+        <v>0.98270810957133747</v>
       </c>
       <c r="AB28" s="7">
         <v>737235</v>
@@ -4536,14 +5194,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>107241</v>
+        <v>112891</v>
       </c>
       <c r="AE28" s="13">
-        <v>722763</v>
+        <v>728413</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98036989562351218</v>
+        <v>0.98803366633434386</v>
       </c>
       <c r="AG28" s="7">
         <v>456666</v>
@@ -4553,14 +5211,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>65226</v>
+        <v>70252</v>
       </c>
       <c r="AJ28" s="13">
-        <v>445430</v>
+        <v>450456</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.97539558451910147</v>
+        <v>0.98640144000210217</v>
       </c>
       <c r="AL28" s="7">
         <v>468801</v>
@@ -4570,14 +5228,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>60341</v>
+        <v>67705</v>
       </c>
       <c r="AO28" s="13">
-        <v>455578</v>
+        <v>462942</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.97179400214589984</v>
+        <v>0.98750215976501754</v>
       </c>
       <c r="AQ28" s="7">
         <v>756132</v>
@@ -4587,14 +5245,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>80624</v>
+        <v>102690</v>
       </c>
       <c r="AT28" s="13">
-        <v>724198</v>
+        <v>746264</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.95776663333915246</v>
+        <v>0.98694936862875793</v>
       </c>
       <c r="AV28" s="7">
         <v>474991</v>
@@ -4604,17 +5262,51 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>31595</v>
+        <v>61369</v>
       </c>
       <c r="AY28" s="13">
-        <v>436630</v>
+        <v>466404</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.91923846978153267</v>
+        <v>0.98192176272813592</v>
+      </c>
+      <c r="BA28" s="7">
+        <v>487540</v>
+      </c>
+      <c r="BB28" s="6">
+        <v>410764</v>
+      </c>
+      <c r="BC28" s="4">
+        <f t="shared" si="20"/>
+        <v>60860</v>
+      </c>
+      <c r="BD28" s="13">
+        <v>471624</v>
+      </c>
+      <c r="BE28" s="5">
+        <f t="shared" si="21"/>
+        <v>0.9673544734790992</v>
+      </c>
+      <c r="BF28" s="7">
+        <v>779284</v>
+      </c>
+      <c r="BG28" s="6">
+        <v>624198</v>
+      </c>
+      <c r="BH28" s="4">
+        <f t="shared" si="22"/>
+        <v>109749</v>
+      </c>
+      <c r="BI28" s="13">
+        <v>733947</v>
+      </c>
+      <c r="BJ28" s="5">
+        <f t="shared" si="23"/>
+        <v>0.94182223682251909</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>20</v>
       </c>
@@ -4629,14 +5321,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>27912</v>
+        <v>28129</v>
       </c>
       <c r="F29" s="13">
-        <v>142419</v>
+        <v>142636</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99072708553620126</v>
+        <v>0.99223662975123827</v>
       </c>
       <c r="H29" s="7">
         <v>146310</v>
@@ -4646,14 +5338,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>27214</v>
+        <v>27480</v>
       </c>
       <c r="K29" s="13">
-        <v>143809</v>
+        <v>144075</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98290615815733717</v>
+        <v>0.98472421570637692</v>
       </c>
       <c r="M29" s="7">
         <v>194093</v>
@@ -4663,14 +5355,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>37121</v>
+        <v>37596</v>
       </c>
       <c r="P29" s="13">
-        <v>190973</v>
+        <v>191448</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98392523171881519</v>
+        <v>0.98637251214623922</v>
       </c>
       <c r="R29" s="7">
         <v>146918</v>
@@ -4680,14 +5372,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>25988</v>
+        <v>26508</v>
       </c>
       <c r="U29" s="13">
-        <v>144537</v>
+        <v>145057</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98379368082876162</v>
+        <v>0.98733307014797367</v>
       </c>
       <c r="W29" s="7">
         <v>149105</v>
@@ -4697,14 +5389,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>26024</v>
+        <v>26879</v>
       </c>
       <c r="Z29" s="13">
-        <v>145442</v>
+        <v>146297</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.97543341940243455</v>
+        <v>0.98116763354682945</v>
       </c>
       <c r="AB29" s="7">
         <v>197403</v>
@@ -4714,14 +5406,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>30812</v>
+        <v>32679</v>
       </c>
       <c r="AE29" s="13">
-        <v>192346</v>
+        <v>194213</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.97438235487809199</v>
+        <v>0.98384016453650658</v>
       </c>
       <c r="AG29" s="7">
         <v>149309</v>
@@ -4731,14 +5423,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>25319</v>
+        <v>27276</v>
       </c>
       <c r="AJ29" s="13">
-        <v>144990</v>
+        <v>146947</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.97107341151571569</v>
+        <v>0.98418045797641129</v>
       </c>
       <c r="AL29" s="7">
         <v>152026</v>
@@ -4748,14 +5440,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>22544</v>
+        <v>25370</v>
       </c>
       <c r="AO29" s="13">
-        <v>148557</v>
+        <v>151383</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.97718153473747915</v>
+        <v>0.99577046031599858</v>
       </c>
       <c r="AQ29" s="7">
         <v>203571</v>
@@ -4765,14 +5457,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>26257</v>
+        <v>33042</v>
       </c>
       <c r="AT29" s="13">
-        <v>194471</v>
+        <v>201256</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.9552981515048804</v>
+        <v>0.9886280462344833</v>
       </c>
       <c r="AV29" s="7">
         <v>155780</v>
@@ -4782,17 +5474,51 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>12494</v>
+        <v>24251</v>
       </c>
       <c r="AY29" s="13">
-        <v>141843</v>
+        <v>153600</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.91053408653228918</v>
+        <v>0.98600590576453973</v>
+      </c>
+      <c r="BA29" s="7">
+        <v>159604</v>
+      </c>
+      <c r="BB29" s="6">
+        <v>131066</v>
+      </c>
+      <c r="BC29" s="4">
+        <f t="shared" si="20"/>
+        <v>24056</v>
+      </c>
+      <c r="BD29" s="13">
+        <v>155122</v>
+      </c>
+      <c r="BE29" s="5">
+        <f t="shared" si="21"/>
+        <v>0.97191799704268067</v>
+      </c>
+      <c r="BF29" s="7">
+        <v>211893</v>
+      </c>
+      <c r="BG29" s="6">
+        <v>164370</v>
+      </c>
+      <c r="BH29" s="4">
+        <f t="shared" si="22"/>
+        <v>35261</v>
+      </c>
+      <c r="BI29" s="13">
+        <v>199631</v>
+      </c>
+      <c r="BJ29" s="5">
+        <f t="shared" si="23"/>
+        <v>0.94213116997729984</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="18">
         <v>21</v>
       </c>
@@ -4807,14 +5533,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>40822</v>
+        <v>41100</v>
       </c>
       <c r="F30" s="13">
-        <v>185186</v>
+        <v>185464</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99416981618278644</v>
+        <v>0.99566225734409897</v>
       </c>
       <c r="H30" s="7">
         <v>190966</v>
@@ -4824,14 +5550,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41142</v>
+        <v>41496</v>
       </c>
       <c r="K30" s="13">
-        <v>187954</v>
+        <v>188308</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98422755883246227</v>
+        <v>0.98608129195773064</v>
       </c>
       <c r="M30" s="7">
         <v>320227</v>
@@ -4841,14 +5567,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>66686</v>
+        <v>67520</v>
       </c>
       <c r="P30" s="13">
-        <v>316688</v>
+        <v>317522</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98894846468286557</v>
+        <v>0.9915528671848407</v>
       </c>
       <c r="R30" s="7">
         <v>189502</v>
@@ -4858,14 +5584,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37108</v>
+        <v>37779</v>
       </c>
       <c r="U30" s="13">
-        <v>187623</v>
+        <v>188294</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99008453736636026</v>
+        <v>0.99362539709343434</v>
       </c>
       <c r="W30" s="7">
         <v>194334</v>
@@ -4875,14 +5601,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>36550</v>
+        <v>37624</v>
       </c>
       <c r="Z30" s="13">
-        <v>189428</v>
+        <v>190502</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.97475480358557942</v>
+        <v>0.98028137124743997</v>
       </c>
       <c r="AB30" s="7">
         <v>325942</v>
@@ -4892,14 +5618,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>56932</v>
+        <v>60105</v>
       </c>
       <c r="AE30" s="13">
-        <v>318874</v>
+        <v>322047</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.97831516036595467</v>
+        <v>0.98805002116941054</v>
       </c>
       <c r="AG30" s="7">
         <v>192789</v>
@@ -4909,14 +5635,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>36791</v>
+        <v>39405</v>
       </c>
       <c r="AJ30" s="13">
-        <v>188270</v>
+        <v>190884</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.9765598659674567</v>
+        <v>0.99011873084045254</v>
       </c>
       <c r="AL30" s="7">
         <v>197994</v>
@@ -4926,14 +5652,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>32543</v>
+        <v>36604</v>
       </c>
       <c r="AO30" s="13">
-        <v>191317</v>
+        <v>195378</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.96627675586128869</v>
+        <v>0.98678747840843661</v>
       </c>
       <c r="AQ30" s="7">
         <v>333633</v>
@@ -4943,14 +5669,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>45963</v>
+        <v>58629</v>
       </c>
       <c r="AT30" s="13">
-        <v>316106</v>
+        <v>328772</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.94746622786115287</v>
+        <v>0.9854300983415909</v>
       </c>
       <c r="AV30" s="7">
         <v>198460</v>
@@ -4960,17 +5686,51 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>18314</v>
+        <v>34912</v>
       </c>
       <c r="AY30" s="13">
-        <v>178609</v>
+        <v>195207</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.89997480600624813</v>
+        <v>0.98360878766502069</v>
+      </c>
+      <c r="BA30" s="7">
+        <v>203942</v>
+      </c>
+      <c r="BB30" s="6">
+        <v>162272</v>
+      </c>
+      <c r="BC30" s="4">
+        <f t="shared" si="20"/>
+        <v>34673</v>
+      </c>
+      <c r="BD30" s="13">
+        <v>196945</v>
+      </c>
+      <c r="BE30" s="5">
+        <f t="shared" si="21"/>
+        <v>0.96569122593678591</v>
+      </c>
+      <c r="BF30" s="7">
+        <v>342999</v>
+      </c>
+      <c r="BG30" s="6">
+        <v>255925</v>
+      </c>
+      <c r="BH30" s="4">
+        <f t="shared" si="22"/>
+        <v>63084</v>
+      </c>
+      <c r="BI30" s="13">
+        <v>319009</v>
+      </c>
+      <c r="BJ30" s="5">
+        <f t="shared" si="23"/>
+        <v>0.93005810512567089</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>22</v>
       </c>
@@ -4985,14 +5745,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>19105</v>
+        <v>19209</v>
       </c>
       <c r="F31" s="13">
-        <v>83445</v>
+        <v>83549</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0067806425925703</v>
+        <v>1.0080354234282061</v>
       </c>
       <c r="H31" s="7">
         <v>85478</v>
@@ -5002,14 +5762,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>17841</v>
+        <v>17984</v>
       </c>
       <c r="K31" s="13">
-        <v>84928</v>
+        <v>85071</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99356559582582649</v>
+        <v>0.99523854091111164</v>
       </c>
       <c r="M31" s="7">
         <v>149930</v>
@@ -5019,14 +5779,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>38337</v>
+        <v>38724</v>
       </c>
       <c r="P31" s="13">
-        <v>150189</v>
+        <v>150576</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0017274728206496</v>
+        <v>1.0043086773827787</v>
       </c>
       <c r="R31" s="7">
         <v>83981</v>
@@ -5036,14 +5796,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>18242</v>
+        <v>18487</v>
       </c>
       <c r="U31" s="13">
-        <v>84051</v>
+        <v>84296</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0008335218680415</v>
+        <v>1.0037508484061872</v>
       </c>
       <c r="W31" s="7">
         <v>85994</v>
@@ -5053,14 +5813,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>18513</v>
+        <v>18874</v>
       </c>
       <c r="Z31" s="13">
-        <v>85077</v>
+        <v>85438</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.9893364653347908</v>
+        <v>0.99353443263483499</v>
       </c>
       <c r="AB31" s="7">
         <v>153633</v>
@@ -5070,14 +5830,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>38715</v>
+        <v>39890</v>
       </c>
       <c r="AE31" s="13">
-        <v>151956</v>
+        <v>153131</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.9890843764035071</v>
+        <v>0.99673247284112132</v>
       </c>
       <c r="AG31" s="7">
         <v>85109</v>
@@ -5087,14 +5847,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>19267</v>
+        <v>20096</v>
       </c>
       <c r="AJ31" s="13">
-        <v>84785</v>
+        <v>85614</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.99619311706165037</v>
+        <v>1.0059335675427981</v>
       </c>
       <c r="AL31" s="7">
         <v>88549</v>
@@ -5104,14 +5864,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>16622</v>
+        <v>17954</v>
       </c>
       <c r="AO31" s="13">
-        <v>86793</v>
+        <v>88125</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.98016917187094155</v>
+        <v>0.99521169070232296</v>
       </c>
       <c r="AQ31" s="7">
         <v>156407</v>
@@ -5121,14 +5881,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>27641</v>
+        <v>33140</v>
       </c>
       <c r="AT31" s="13">
-        <v>150764</v>
+        <v>156263</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.963921052126823</v>
+        <v>0.99907932509414543</v>
       </c>
       <c r="AV31" s="7">
         <v>87916</v>
@@ -5138,17 +5898,51 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>9434</v>
+        <v>16745</v>
       </c>
       <c r="AY31" s="13">
-        <v>80860</v>
+        <v>88171</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>0.9197415715000683</v>
+        <v>1.0029004959279313</v>
+      </c>
+      <c r="BA31" s="7">
+        <v>90084</v>
+      </c>
+      <c r="BB31" s="6">
+        <v>72758</v>
+      </c>
+      <c r="BC31" s="4">
+        <f t="shared" si="20"/>
+        <v>16335</v>
+      </c>
+      <c r="BD31" s="13">
+        <v>89093</v>
+      </c>
+      <c r="BE31" s="5">
+        <f t="shared" si="21"/>
+        <v>0.98899915634296875</v>
+      </c>
+      <c r="BF31" s="7">
+        <v>159779</v>
+      </c>
+      <c r="BG31" s="6">
+        <v>109294</v>
+      </c>
+      <c r="BH31" s="4">
+        <f t="shared" si="22"/>
+        <v>40989</v>
+      </c>
+      <c r="BI31" s="13">
+        <v>150283</v>
+      </c>
+      <c r="BJ31" s="5">
+        <f t="shared" si="23"/>
+        <v>0.9405679094248931</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A32" s="18">
         <v>23</v>
       </c>
@@ -5163,14 +5957,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>48155</v>
+        <v>48371</v>
       </c>
       <c r="F32" s="13">
-        <v>231368</v>
+        <v>231584</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99721568526037219</v>
+        <v>0.99814666356340565</v>
       </c>
       <c r="H32" s="7">
         <v>238678</v>
@@ -5180,14 +5974,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46217</v>
+        <v>46490</v>
       </c>
       <c r="K32" s="13">
-        <v>235489</v>
+        <v>235762</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98663890262194254</v>
+        <v>0.98778270305600013</v>
       </c>
       <c r="M32" s="7">
         <v>498323</v>
@@ -5197,14 +5991,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>106895</v>
+        <v>107771</v>
       </c>
       <c r="P32" s="13">
-        <v>493571</v>
+        <v>494447</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99046401631070613</v>
+        <v>0.9922219122938335</v>
       </c>
       <c r="R32" s="7">
         <v>234167</v>
@@ -5214,14 +6008,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>43267</v>
+        <v>43806</v>
       </c>
       <c r="U32" s="13">
-        <v>233054</v>
+        <v>233593</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99524698185483007</v>
+        <v>0.99754875793771114</v>
       </c>
       <c r="W32" s="7">
         <v>242821</v>
@@ -5231,14 +6025,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>45067</v>
+        <v>46038</v>
       </c>
       <c r="Z32" s="13">
-        <v>237029</v>
+        <v>238000</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.97614703835335492</v>
+        <v>0.98014586876752829</v>
       </c>
       <c r="AB32" s="7">
         <v>507064</v>
@@ -5248,14 +6042,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>106940</v>
+        <v>110614</v>
       </c>
       <c r="AE32" s="13">
-        <v>499448</v>
+        <v>503122</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98498019973810014</v>
+        <v>0.99222583342536641</v>
       </c>
       <c r="AG32" s="7">
         <v>238186</v>
@@ -5265,14 +6059,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>45057</v>
+        <v>47382</v>
       </c>
       <c r="AJ32" s="13">
-        <v>235190</v>
+        <v>237515</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.98742159488802872</v>
+        <v>0.99718287388847371</v>
       </c>
       <c r="AL32" s="7">
         <v>247675</v>
@@ -5282,14 +6076,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>39307</v>
+        <v>43095</v>
       </c>
       <c r="AO32" s="13">
-        <v>242920</v>
+        <v>246708</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.98080145351771475</v>
+        <v>0.99609568991622088</v>
       </c>
       <c r="AQ32" s="7">
         <v>518099</v>
@@ -5299,14 +6093,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>81774</v>
+        <v>98099</v>
       </c>
       <c r="AT32" s="13">
-        <v>498600</v>
+        <v>514925</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.96236433577366487</v>
+        <v>0.99387375771811948</v>
       </c>
       <c r="AV32" s="7">
         <v>246693</v>
@@ -5316,17 +6110,51 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>23756</v>
+        <v>41835</v>
       </c>
       <c r="AY32" s="13">
-        <v>228592</v>
+        <v>246671</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.92662540080180633</v>
+        <v>0.99991082033134304</v>
+      </c>
+      <c r="BA32" s="7">
+        <v>255610</v>
+      </c>
+      <c r="BB32" s="6">
+        <v>213119</v>
+      </c>
+      <c r="BC32" s="4">
+        <f t="shared" si="20"/>
+        <v>38722</v>
+      </c>
+      <c r="BD32" s="13">
+        <v>251841</v>
+      </c>
+      <c r="BE32" s="5">
+        <f t="shared" si="21"/>
+        <v>0.98525488048198429</v>
+      </c>
+      <c r="BF32" s="7">
+        <v>535637</v>
+      </c>
+      <c r="BG32" s="6">
+        <v>398643</v>
+      </c>
+      <c r="BH32" s="4">
+        <f t="shared" si="22"/>
+        <v>109545</v>
+      </c>
+      <c r="BI32" s="13">
+        <v>508188</v>
+      </c>
+      <c r="BJ32" s="5">
+        <f t="shared" si="23"/>
+        <v>0.94875447364539789</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>24</v>
       </c>
@@ -5341,14 +6169,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>81206</v>
+        <v>81411</v>
       </c>
       <c r="F33" s="13">
-        <v>718422</v>
+        <v>718627</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0036728495528735</v>
+        <v>1.0039592452007773</v>
       </c>
       <c r="H33" s="7">
         <v>726544</v>
@@ -5358,14 +6186,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>72912</v>
+        <v>73179</v>
       </c>
       <c r="K33" s="13">
-        <v>729645</v>
+        <v>729912</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>1.0042681516879914</v>
+        <v>1.0046356449162059</v>
       </c>
       <c r="M33" s="7">
         <v>1152516</v>
@@ -5375,14 +6203,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>139511</v>
+        <v>140167</v>
       </c>
       <c r="P33" s="13">
-        <v>1153438</v>
+        <v>1154094</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>1.0007999888938635</v>
+        <v>1.0013691783888468</v>
       </c>
       <c r="R33" s="7">
         <v>733468</v>
@@ -5392,14 +6220,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>82436</v>
+        <v>83002</v>
       </c>
       <c r="U33" s="13">
-        <v>736561</v>
+        <v>737127</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0042169528868334</v>
+        <v>1.0049886293607901</v>
       </c>
       <c r="W33" s="7">
         <v>745690</v>
@@ -5409,14 +6237,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>79889</v>
+        <v>80848</v>
       </c>
       <c r="Z33" s="13">
-        <v>745441</v>
+        <v>746400</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>0.99966608107926891</v>
+        <v>1.0009521382880286</v>
       </c>
       <c r="AB33" s="7">
         <v>1180887</v>
@@ -5426,14 +6254,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>137584</v>
+        <v>140471</v>
       </c>
       <c r="AE33" s="13">
-        <v>1177469</v>
+        <v>1180356</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.9971055655621579</v>
+        <v>0.99955033800863247</v>
       </c>
       <c r="AG33" s="7">
         <v>749948</v>
@@ -5443,14 +6271,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>78142</v>
+        <v>80805</v>
       </c>
       <c r="AJ33" s="13">
-        <v>748628</v>
+        <v>751291</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>0.99823987796487224</v>
+        <v>1.001790790828164</v>
       </c>
       <c r="AL33" s="7">
         <v>765123</v>
@@ -5460,14 +6288,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>70469</v>
+        <v>75022</v>
       </c>
       <c r="AO33" s="13">
-        <v>768940</v>
+        <v>773493</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>1.0049887403724629</v>
+        <v>1.0109394175838395</v>
       </c>
       <c r="AQ33" s="7">
         <v>1217820</v>
@@ -5477,14 +6305,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>118427</v>
+        <v>137435</v>
       </c>
       <c r="AT33" s="13">
-        <v>1202253</v>
+        <v>1221261</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>0.98721732275705765</v>
+        <v>1.0028255407203035</v>
       </c>
       <c r="AV33" s="7">
         <v>779865</v>
@@ -5494,17 +6322,51 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>40733</v>
+        <v>71045</v>
       </c>
       <c r="AY33" s="13">
-        <v>753262</v>
+        <v>783574</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>0.96588768568918981</v>
+        <v>1.0047559513505542</v>
+      </c>
+      <c r="BA33" s="7">
+        <v>794982</v>
+      </c>
+      <c r="BB33" s="6">
+        <v>724830</v>
+      </c>
+      <c r="BC33" s="20">
+        <f t="shared" si="20"/>
+        <v>70934</v>
+      </c>
+      <c r="BD33" s="13">
+        <v>795764</v>
+      </c>
+      <c r="BE33" s="21">
+        <f t="shared" si="21"/>
+        <v>1.0009836700705173</v>
+      </c>
+      <c r="BF33" s="7">
+        <v>1258934</v>
+      </c>
+      <c r="BG33" s="6">
+        <v>1090188</v>
+      </c>
+      <c r="BH33" s="20">
+        <f t="shared" si="22"/>
+        <v>142585</v>
+      </c>
+      <c r="BI33" s="13">
+        <v>1232773</v>
+      </c>
+      <c r="BJ33" s="21">
+        <f t="shared" si="23"/>
+        <v>0.97921972081141662</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34" s="18">
         <v>25</v>
       </c>
@@ -5661,8 +6523,38 @@
       <c r="AZ34" s="14" t="s">
         <v>47</v>
       </c>
+      <c r="BA34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BC34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="BD34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="BF34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BG34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI34" s="14">
+        <v>0</v>
+      </c>
+      <c r="BJ34" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A35" s="18">
         <v>26</v>
       </c>
@@ -5676,15 +6568,15 @@
         <v>9978</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" ref="E35:E48" si="20">F35-D35</f>
-        <v>2253</v>
+        <f t="shared" ref="E35:E48" si="24">F35-D35</f>
+        <v>2261</v>
       </c>
       <c r="F35" s="13">
-        <v>12231</v>
+        <v>12239</v>
       </c>
       <c r="G35" s="5">
-        <f t="shared" ref="G35:G48" si="21">F35/C35</f>
-        <v>0.99779735682819382</v>
+        <f t="shared" ref="G35:G48" si="25">F35/C35</f>
+        <v>0.99844999184206229</v>
       </c>
       <c r="H35" s="7">
         <v>12343</v>
@@ -5693,15 +6585,15 @@
         <v>10149</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" ref="J35:J48" si="22">K35-I35</f>
-        <v>2166</v>
+        <f t="shared" ref="J35:J48" si="26">K35-I35</f>
+        <v>2177</v>
       </c>
       <c r="K35" s="13">
-        <v>12315</v>
+        <v>12326</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" ref="L35:L48" si="23">K35/H35</f>
-        <v>0.997731507737179</v>
+        <f t="shared" ref="L35:L48" si="27">K35/H35</f>
+        <v>0.99862270112614437</v>
       </c>
       <c r="M35" s="7">
         <v>15097</v>
@@ -5710,15 +6602,15 @@
         <v>12214</v>
       </c>
       <c r="O35" s="4">
-        <f t="shared" ref="O35:O48" si="24">P35-N35</f>
-        <v>2825</v>
+        <f t="shared" ref="O35:O48" si="28">P35-N35</f>
+        <v>2847</v>
       </c>
       <c r="P35" s="13">
-        <v>15039</v>
+        <v>15061</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" ref="Q35:Q48" si="25">P35/M35</f>
-        <v>0.99615817712128241</v>
+        <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
+        <v>0.99761542028217531</v>
       </c>
       <c r="R35" s="7">
         <v>12455</v>
@@ -5727,15 +6619,15 @@
         <v>10110</v>
       </c>
       <c r="T35" s="4">
-        <f t="shared" ref="T35:T48" si="26">U35-S35</f>
-        <v>2264</v>
+        <f t="shared" ref="T35:T48" si="30">U35-S35</f>
+        <v>2286</v>
       </c>
       <c r="U35" s="13">
-        <v>12374</v>
+        <v>12396</v>
       </c>
       <c r="V35" s="5">
-        <f t="shared" ref="V35:V48" si="27">U35/R35</f>
-        <v>0.99349658771577676</v>
+        <f t="shared" ref="V35:V48" si="31">U35/R35</f>
+        <v>0.99526294660778802</v>
       </c>
       <c r="W35" s="7">
         <v>12547</v>
@@ -5744,15 +6636,15 @@
         <v>10356</v>
       </c>
       <c r="Y35" s="4">
-        <f t="shared" ref="Y35:Y48" si="28">Z35-X35</f>
-        <v>2033</v>
+        <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
+        <v>2074</v>
       </c>
       <c r="Z35" s="13">
-        <v>12389</v>
+        <v>12430</v>
       </c>
       <c r="AA35" s="5">
-        <f t="shared" ref="AA35:AA48" si="29">Z35/W35</f>
-        <v>0.98740734837012833</v>
+        <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
+        <v>0.99067506176775322</v>
       </c>
       <c r="AB35" s="7">
         <v>15257</v>
@@ -5761,15 +6653,15 @@
         <v>12475</v>
       </c>
       <c r="AD35" s="4">
-        <f t="shared" ref="AD35:AD48" si="30">AE35-AC35</f>
-        <v>2575</v>
+        <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
+        <v>2683</v>
       </c>
       <c r="AE35" s="13">
-        <v>15050</v>
+        <v>15158</v>
       </c>
       <c r="AF35" s="5">
-        <f t="shared" ref="AF35:AF48" si="31">AE35/AB35</f>
-        <v>0.98643245723274564</v>
+        <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
+        <v>0.99351117519826959</v>
       </c>
       <c r="AG35" s="7">
         <v>12574</v>
@@ -5778,15 +6670,15 @@
         <v>10323</v>
       </c>
       <c r="AI35" s="4">
-        <f t="shared" ref="AI35:AI48" si="32">AJ35-AH35</f>
-        <v>2031</v>
+        <f t="shared" ref="AI35:AI48" si="36">AJ35-AH35</f>
+        <v>2170</v>
       </c>
       <c r="AJ35" s="13">
-        <v>12354</v>
+        <v>12493</v>
       </c>
       <c r="AK35" s="5">
-        <f t="shared" ref="AK35:AK48" si="33">AJ35/AG35</f>
-        <v>0.98250357881342454</v>
+        <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
+        <v>0.99355813583585173</v>
       </c>
       <c r="AL35" s="7">
         <v>12702</v>
@@ -5795,15 +6687,15 @@
         <v>10524</v>
       </c>
       <c r="AN35" s="4">
-        <f t="shared" ref="AN35:AN48" si="34">AO35-AM35</f>
-        <v>1846</v>
+        <f t="shared" ref="AN35:AN48" si="38">AO35-AM35</f>
+        <v>2054</v>
       </c>
       <c r="AO35" s="13">
-        <v>12370</v>
+        <v>12578</v>
       </c>
       <c r="AP35" s="5">
-        <f t="shared" ref="AP35:AP48" si="35">AO35/AL35</f>
-        <v>0.97386238387655488</v>
+        <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
+        <v>0.99023775783341206</v>
       </c>
       <c r="AQ35" s="7">
         <v>15458</v>
@@ -5812,15 +6704,15 @@
         <v>12718</v>
       </c>
       <c r="AS35" s="4">
-        <f t="shared" ref="AS35:AS48" si="36">AT35-AR35</f>
-        <v>2042</v>
+        <f t="shared" ref="AS35:AS48" si="40">AT35-AR35</f>
+        <v>2560</v>
       </c>
       <c r="AT35" s="13">
-        <v>14760</v>
+        <v>15278</v>
       </c>
       <c r="AU35" s="5">
-        <f t="shared" ref="AU35:AU48" si="37">AT35/AQ35</f>
-        <v>0.95484538750161729</v>
+        <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
+        <v>0.98835554405485837</v>
       </c>
       <c r="AV35" s="7">
         <v>12806</v>
@@ -5829,18 +6721,52 @@
         <v>10688</v>
       </c>
       <c r="AX35" s="4">
-        <f t="shared" ref="AX35:AX48" si="38">AY35-AW35</f>
-        <v>864</v>
+        <f t="shared" ref="AX35:AX48" si="42">AY35-AW35</f>
+        <v>1879</v>
       </c>
       <c r="AY35" s="13">
-        <v>11552</v>
+        <v>12567</v>
       </c>
       <c r="AZ35" s="5">
-        <f t="shared" ref="AZ35:AZ48" si="39">AY35/AV35</f>
-        <v>0.90207715133531152</v>
+        <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
+        <v>0.98133687334062158</v>
+      </c>
+      <c r="BA35" s="7">
+        <v>12915</v>
+      </c>
+      <c r="BB35" s="6">
+        <v>10758</v>
+      </c>
+      <c r="BC35" s="4">
+        <f t="shared" ref="BC35:BC48" si="44">BD35-BB35</f>
+        <v>1788</v>
+      </c>
+      <c r="BD35" s="13">
+        <v>12546</v>
+      </c>
+      <c r="BE35" s="5">
+        <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="BF35" s="7">
+        <v>15661</v>
+      </c>
+      <c r="BG35" s="6">
+        <v>12599</v>
+      </c>
+      <c r="BH35" s="4">
+        <f t="shared" ref="BH35:BH48" si="46">BI35-BG35</f>
+        <v>2223</v>
+      </c>
+      <c r="BI35" s="13">
+        <v>14822</v>
+      </c>
+      <c r="BJ35" s="5">
+        <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
+        <v>0.94642743119851858</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A36" s="18">
         <v>27</v>
       </c>
@@ -5854,15 +6780,15 @@
         <v>770178</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="20"/>
-        <v>184777</v>
+        <f t="shared" si="24"/>
+        <v>185672</v>
       </c>
       <c r="F36" s="13">
-        <v>954955</v>
+        <v>955850</v>
       </c>
       <c r="G36" s="5">
-        <f t="shared" si="21"/>
-        <v>1.0022512358182638</v>
+        <f t="shared" si="25"/>
+        <v>1.0031905626515254</v>
       </c>
       <c r="H36" s="7">
         <v>975466</v>
@@ -5871,15 +6797,15 @@
         <v>795220</v>
       </c>
       <c r="J36" s="4">
-        <f t="shared" si="22"/>
-        <v>174787</v>
+        <f t="shared" si="26"/>
+        <v>175982</v>
       </c>
       <c r="K36" s="13">
-        <v>970007</v>
+        <v>971202</v>
       </c>
       <c r="L36" s="5">
-        <f t="shared" si="23"/>
-        <v>0.99440370038525172</v>
+        <f t="shared" si="27"/>
+        <v>0.99562875589718147</v>
       </c>
       <c r="M36" s="7">
         <v>1668278</v>
@@ -5888,15 +6814,15 @@
         <v>1322073</v>
       </c>
       <c r="O36" s="4">
-        <f t="shared" si="24"/>
-        <v>342230</v>
+        <f t="shared" si="28"/>
+        <v>345477</v>
       </c>
       <c r="P36" s="13">
-        <v>1664303</v>
+        <v>1667550</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="25"/>
-        <v>0.99761730359088829</v>
+        <f t="shared" si="29"/>
+        <v>0.99956362189035641</v>
       </c>
       <c r="R36" s="7">
         <v>976879</v>
@@ -5905,15 +6831,15 @@
         <v>792042</v>
       </c>
       <c r="T36" s="4">
-        <f t="shared" si="26"/>
-        <v>182530</v>
+        <f t="shared" si="30"/>
+        <v>184903</v>
       </c>
       <c r="U36" s="13">
-        <v>974572</v>
+        <v>976945</v>
       </c>
       <c r="V36" s="5">
-        <f t="shared" si="27"/>
-        <v>0.99763839738596083</v>
+        <f t="shared" si="31"/>
+        <v>1.0000675621033925</v>
       </c>
       <c r="W36" s="7">
         <v>1000117</v>
@@ -5922,15 +6848,15 @@
         <v>807823</v>
       </c>
       <c r="Y36" s="4">
-        <f t="shared" si="28"/>
-        <v>176725</v>
+        <f t="shared" si="32"/>
+        <v>180743</v>
       </c>
       <c r="Z36" s="13">
-        <v>984548</v>
+        <v>988566</v>
       </c>
       <c r="AA36" s="5">
-        <f t="shared" si="29"/>
-        <v>0.98443282135990084</v>
+        <f t="shared" si="33"/>
+        <v>0.98845035130889691</v>
       </c>
       <c r="AB36" s="7">
         <v>1701420</v>
@@ -5939,15 +6865,15 @@
         <v>1360894</v>
       </c>
       <c r="AD36" s="4">
-        <f t="shared" si="30"/>
-        <v>322064</v>
+        <f t="shared" si="34"/>
+        <v>334976</v>
       </c>
       <c r="AE36" s="13">
-        <v>1682958</v>
+        <v>1695870</v>
       </c>
       <c r="AF36" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98914906372324296</v>
+        <f t="shared" si="35"/>
+        <v>0.99673801883132918</v>
       </c>
       <c r="AG36" s="7">
         <v>996655</v>
@@ -5956,15 +6882,15 @@
         <v>810626</v>
       </c>
       <c r="AI36" s="4">
-        <f t="shared" si="32"/>
-        <v>174273</v>
+        <f t="shared" si="36"/>
+        <v>185004</v>
       </c>
       <c r="AJ36" s="13">
-        <v>984899</v>
+        <v>995630</v>
       </c>
       <c r="AK36" s="5">
-        <f t="shared" si="33"/>
-        <v>0.9882045442003502</v>
+        <f t="shared" si="37"/>
+        <v>0.99897155986775765</v>
       </c>
       <c r="AL36" s="7">
         <v>1027093</v>
@@ -5973,15 +6899,15 @@
         <v>854719</v>
       </c>
       <c r="AN36" s="4">
-        <f t="shared" si="34"/>
-        <v>158259</v>
+        <f t="shared" si="38"/>
+        <v>175514</v>
       </c>
       <c r="AO36" s="13">
-        <v>1012978</v>
+        <v>1030233</v>
       </c>
       <c r="AP36" s="5">
-        <f t="shared" si="35"/>
-        <v>0.98625733015413408</v>
+        <f t="shared" si="39"/>
+        <v>1.0030571720379751</v>
       </c>
       <c r="AQ36" s="7">
         <v>1750886</v>
@@ -5990,15 +6916,15 @@
         <v>1441378</v>
       </c>
       <c r="AS36" s="4">
-        <f t="shared" si="36"/>
-        <v>251458</v>
+        <f t="shared" si="40"/>
+        <v>313751</v>
       </c>
       <c r="AT36" s="13">
-        <v>1692836</v>
+        <v>1755129</v>
       </c>
       <c r="AU36" s="5">
-        <f t="shared" si="37"/>
-        <v>0.96684535715060838</v>
+        <f t="shared" si="41"/>
+        <v>1.0024233445238582</v>
       </c>
       <c r="AV36" s="7">
         <v>1041088</v>
@@ -6007,18 +6933,52 @@
         <v>882000</v>
       </c>
       <c r="AX36" s="4">
-        <f t="shared" si="38"/>
-        <v>82430</v>
+        <f t="shared" si="42"/>
+        <v>160992</v>
       </c>
       <c r="AY36" s="13">
-        <v>964430</v>
+        <v>1042992</v>
       </c>
       <c r="AZ36" s="5">
-        <f t="shared" si="39"/>
-        <v>0.92636741562672897</v>
+        <f t="shared" si="43"/>
+        <v>1.0018288559660662</v>
+      </c>
+      <c r="BA36" s="7">
+        <v>1070068</v>
+      </c>
+      <c r="BB36" s="6">
+        <v>896417</v>
+      </c>
+      <c r="BC36" s="4">
+        <f t="shared" si="44"/>
+        <v>162516</v>
+      </c>
+      <c r="BD36" s="13">
+        <v>1058933</v>
+      </c>
+      <c r="BE36" s="5">
+        <f t="shared" si="45"/>
+        <v>0.98959411925223439</v>
+      </c>
+      <c r="BF36" s="7">
+        <v>1814069</v>
+      </c>
+      <c r="BG36" s="6">
+        <v>1427757</v>
+      </c>
+      <c r="BH36" s="4">
+        <f t="shared" si="46"/>
+        <v>292962</v>
+      </c>
+      <c r="BI36" s="13">
+        <v>1720719</v>
+      </c>
+      <c r="BJ36" s="5">
+        <f t="shared" si="47"/>
+        <v>0.94854109738934955</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A37" s="18">
         <v>29</v>
       </c>
@@ -6032,15 +6992,15 @@
         <v>588070</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="20"/>
-        <v>145292</v>
+        <f t="shared" si="24"/>
+        <v>146256</v>
       </c>
       <c r="F37" s="13">
-        <v>733362</v>
+        <v>734326</v>
       </c>
       <c r="G37" s="5">
-        <f t="shared" si="21"/>
-        <v>0.98906763339753034</v>
+        <f t="shared" si="25"/>
+        <v>0.99036775693624002</v>
       </c>
       <c r="H37" s="7">
         <v>747767</v>
@@ -6049,15 +7009,15 @@
         <v>599022</v>
       </c>
       <c r="J37" s="4">
-        <f t="shared" si="22"/>
-        <v>138695</v>
+        <f t="shared" si="26"/>
+        <v>139928</v>
       </c>
       <c r="K37" s="13">
-        <v>737717</v>
+        <v>738950</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="23"/>
-        <v>0.98655998459413163</v>
+        <f t="shared" si="27"/>
+        <v>0.98820889394691125</v>
       </c>
       <c r="M37" s="7">
         <v>922163</v>
@@ -6066,15 +7026,15 @@
         <v>725538</v>
       </c>
       <c r="O37" s="4">
-        <f t="shared" si="24"/>
-        <v>185643</v>
+        <f t="shared" si="28"/>
+        <v>187749</v>
       </c>
       <c r="P37" s="13">
-        <v>911181</v>
+        <v>913287</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="25"/>
-        <v>0.98809104247296842</v>
+        <f t="shared" si="29"/>
+        <v>0.99037480358678454</v>
       </c>
       <c r="R37" s="7">
         <v>751356</v>
@@ -6083,15 +7043,15 @@
         <v>604444</v>
       </c>
       <c r="T37" s="4">
-        <f t="shared" si="26"/>
-        <v>137091</v>
+        <f t="shared" si="30"/>
+        <v>139465</v>
       </c>
       <c r="U37" s="13">
-        <v>741535</v>
+        <v>743909</v>
       </c>
       <c r="V37" s="5">
-        <f t="shared" si="27"/>
-        <v>0.98692896576323341</v>
+        <f t="shared" si="31"/>
+        <v>0.99008858650227061</v>
       </c>
       <c r="W37" s="7">
         <v>760191</v>
@@ -6100,15 +7060,15 @@
         <v>611552</v>
       </c>
       <c r="Y37" s="4">
-        <f t="shared" si="28"/>
-        <v>133806</v>
+        <f t="shared" si="32"/>
+        <v>137595</v>
       </c>
       <c r="Z37" s="13">
-        <v>745358</v>
+        <v>749147</v>
       </c>
       <c r="AA37" s="5">
-        <f t="shared" si="29"/>
-        <v>0.98048779846117617</v>
+        <f t="shared" si="33"/>
+        <v>0.98547207215028854</v>
       </c>
       <c r="AB37" s="7">
         <v>938023</v>
@@ -6117,15 +7077,15 @@
         <v>767374</v>
       </c>
       <c r="AD37" s="4">
-        <f t="shared" si="30"/>
-        <v>151425</v>
+        <f t="shared" si="34"/>
+        <v>159233</v>
       </c>
       <c r="AE37" s="13">
-        <v>918799</v>
+        <v>926607</v>
       </c>
       <c r="AF37" s="5">
-        <f t="shared" si="31"/>
-        <v>0.97950583301262339</v>
+        <f t="shared" si="35"/>
+        <v>0.98782972272534897</v>
       </c>
       <c r="AG37" s="7">
         <v>763648</v>
@@ -6134,15 +7094,15 @@
         <v>613209</v>
       </c>
       <c r="AI37" s="4">
-        <f t="shared" si="32"/>
-        <v>131736</v>
+        <f t="shared" si="36"/>
+        <v>140729</v>
       </c>
       <c r="AJ37" s="13">
-        <v>744945</v>
+        <v>753938</v>
       </c>
       <c r="AK37" s="5">
-        <f t="shared" si="33"/>
-        <v>0.9755083493965806</v>
+        <f t="shared" si="37"/>
+        <v>0.9872847175662085</v>
       </c>
       <c r="AL37" s="7">
         <v>773685</v>
@@ -6151,15 +7111,15 @@
         <v>635264</v>
       </c>
       <c r="AN37" s="4">
-        <f t="shared" si="34"/>
-        <v>116930</v>
+        <f t="shared" si="38"/>
+        <v>130394</v>
       </c>
       <c r="AO37" s="13">
-        <v>752194</v>
+        <v>765658</v>
       </c>
       <c r="AP37" s="5">
-        <f t="shared" si="35"/>
-        <v>0.97222254535114416</v>
+        <f t="shared" si="39"/>
+        <v>0.98962497657315318</v>
       </c>
       <c r="AQ37" s="7">
         <v>957323</v>
@@ -6168,15 +7128,15 @@
         <v>783463</v>
       </c>
       <c r="AS37" s="4">
-        <f t="shared" si="36"/>
-        <v>130515</v>
+        <f t="shared" si="40"/>
+        <v>160201</v>
       </c>
       <c r="AT37" s="13">
-        <v>913978</v>
+        <v>943664</v>
       </c>
       <c r="AU37" s="5">
-        <f t="shared" si="37"/>
-        <v>0.95472270069767462</v>
+        <f t="shared" si="41"/>
+        <v>0.98573208833382253</v>
       </c>
       <c r="AV37" s="7">
         <v>783693</v>
@@ -6185,18 +7145,52 @@
         <v>650792</v>
       </c>
       <c r="AX37" s="4">
-        <f t="shared" si="38"/>
-        <v>62480</v>
+        <f t="shared" si="42"/>
+        <v>118357</v>
       </c>
       <c r="AY37" s="13">
-        <v>713272</v>
+        <v>769149</v>
       </c>
       <c r="AZ37" s="5">
-        <f t="shared" si="39"/>
-        <v>0.91014210921878846</v>
+        <f t="shared" si="43"/>
+        <v>0.98144171250732115</v>
+      </c>
+      <c r="BA37" s="7">
+        <v>794943</v>
+      </c>
+      <c r="BB37" s="6">
+        <v>643660</v>
+      </c>
+      <c r="BC37" s="4">
+        <f t="shared" si="44"/>
+        <v>126146</v>
+      </c>
+      <c r="BD37" s="13">
+        <v>769806</v>
+      </c>
+      <c r="BE37" s="5">
+        <f t="shared" si="45"/>
+        <v>0.96837886489974756</v>
+      </c>
+      <c r="BF37" s="7">
+        <v>980352</v>
+      </c>
+      <c r="BG37" s="6">
+        <v>756431</v>
+      </c>
+      <c r="BH37" s="4">
+        <f t="shared" si="46"/>
+        <v>163062</v>
+      </c>
+      <c r="BI37" s="13">
+        <v>919493</v>
+      </c>
+      <c r="BJ37" s="5">
+        <f t="shared" si="47"/>
+        <v>0.93792127725551644</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A38" s="18">
         <v>30</v>
       </c>
@@ -6210,15 +7204,15 @@
         <v>19588</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="20"/>
-        <v>6519</v>
+        <f t="shared" si="24"/>
+        <v>6578</v>
       </c>
       <c r="F38" s="13">
-        <v>26107</v>
+        <v>26166</v>
       </c>
       <c r="G38" s="5">
-        <f t="shared" si="21"/>
-        <v>1.001726651830251</v>
+        <f t="shared" si="25"/>
+        <v>1.0039904842299132</v>
       </c>
       <c r="H38" s="7">
         <v>26657</v>
@@ -6227,15 +7221,15 @@
         <v>20239</v>
       </c>
       <c r="J38" s="4">
-        <f t="shared" si="22"/>
-        <v>6155</v>
+        <f t="shared" si="26"/>
+        <v>6236</v>
       </c>
       <c r="K38" s="13">
-        <v>26394</v>
+        <v>26475</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" si="23"/>
-        <v>0.99013392354728591</v>
+        <f t="shared" si="27"/>
+        <v>0.99317252504032716</v>
       </c>
       <c r="M38" s="7">
         <v>40003</v>
@@ -6244,15 +7238,15 @@
         <v>30131</v>
       </c>
       <c r="O38" s="4">
-        <f t="shared" si="24"/>
-        <v>9699</v>
+        <f t="shared" si="28"/>
+        <v>9846</v>
       </c>
       <c r="P38" s="13">
-        <v>39830</v>
+        <v>39977</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="25"/>
-        <v>0.99567532435067374</v>
+        <f t="shared" si="29"/>
+        <v>0.99935004874634403</v>
       </c>
       <c r="R38" s="7">
         <v>26603</v>
@@ -6261,15 +7255,15 @@
         <v>20495</v>
       </c>
       <c r="T38" s="4">
-        <f t="shared" si="26"/>
-        <v>5964</v>
+        <f t="shared" si="30"/>
+        <v>6097</v>
       </c>
       <c r="U38" s="13">
-        <v>26459</v>
+        <v>26592</v>
       </c>
       <c r="V38" s="5">
-        <f t="shared" si="27"/>
-        <v>0.99458707664549106</v>
+        <f t="shared" si="31"/>
+        <v>0.99958651279930832</v>
       </c>
       <c r="W38" s="7">
         <v>27177</v>
@@ -6278,15 +7272,15 @@
         <v>20685</v>
       </c>
       <c r="Y38" s="4">
-        <f t="shared" si="28"/>
-        <v>5906</v>
+        <f t="shared" si="32"/>
+        <v>6148</v>
       </c>
       <c r="Z38" s="13">
-        <v>26591</v>
+        <v>26833</v>
       </c>
       <c r="AA38" s="5">
-        <f t="shared" si="29"/>
-        <v>0.9784376494830187</v>
+        <f t="shared" si="33"/>
+        <v>0.98734223792177211</v>
       </c>
       <c r="AB38" s="7">
         <v>40627</v>
@@ -6295,15 +7289,15 @@
         <v>31829</v>
       </c>
       <c r="AD38" s="4">
-        <f t="shared" si="30"/>
-        <v>8119</v>
+        <f t="shared" si="34"/>
+        <v>8672</v>
       </c>
       <c r="AE38" s="13">
-        <v>39948</v>
+        <v>40501</v>
       </c>
       <c r="AF38" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98328697664114995</v>
+        <f t="shared" si="35"/>
+        <v>0.99689861422206905</v>
       </c>
       <c r="AG38" s="7">
         <v>26952</v>
@@ -6312,15 +7306,15 @@
         <v>20902</v>
       </c>
       <c r="AI38" s="4">
-        <f t="shared" si="32"/>
-        <v>5395</v>
+        <f t="shared" si="36"/>
+        <v>6005</v>
       </c>
       <c r="AJ38" s="13">
-        <v>26297</v>
+        <v>26907</v>
       </c>
       <c r="AK38" s="5">
-        <f t="shared" si="33"/>
-        <v>0.97569753636093792</v>
+        <f t="shared" si="37"/>
+        <v>0.99833036509349959</v>
       </c>
       <c r="AL38" s="7">
         <v>27600</v>
@@ -6329,15 +7323,15 @@
         <v>21153</v>
       </c>
       <c r="AN38" s="4">
-        <f t="shared" si="34"/>
-        <v>5357</v>
+        <f t="shared" si="38"/>
+        <v>6207</v>
       </c>
       <c r="AO38" s="13">
-        <v>26510</v>
+        <v>27360</v>
       </c>
       <c r="AP38" s="5">
-        <f t="shared" si="35"/>
-        <v>0.96050724637681162</v>
+        <f t="shared" si="39"/>
+        <v>0.99130434782608701</v>
       </c>
       <c r="AQ38" s="7">
         <v>41434</v>
@@ -6346,15 +7340,15 @@
         <v>32574</v>
       </c>
       <c r="AS38" s="4">
-        <f t="shared" si="36"/>
-        <v>6415</v>
+        <f t="shared" si="40"/>
+        <v>8531</v>
       </c>
       <c r="AT38" s="13">
-        <v>38989</v>
+        <v>41105</v>
       </c>
       <c r="AU38" s="5">
-        <f t="shared" si="37"/>
-        <v>0.94099049090119224</v>
+        <f t="shared" si="41"/>
+        <v>0.9920596611478496</v>
       </c>
       <c r="AV38" s="7">
         <v>27593</v>
@@ -6363,18 +7357,52 @@
         <v>22356</v>
       </c>
       <c r="AX38" s="4">
-        <f t="shared" si="38"/>
-        <v>2146</v>
+        <f t="shared" si="42"/>
+        <v>4805</v>
       </c>
       <c r="AY38" s="13">
-        <v>24502</v>
+        <v>27161</v>
       </c>
       <c r="AZ38" s="5">
-        <f t="shared" si="39"/>
-        <v>0.88797883521182908</v>
+        <f t="shared" si="43"/>
+        <v>0.98434385532562607</v>
+      </c>
+      <c r="BA38" s="7">
+        <v>28279</v>
+      </c>
+      <c r="BB38" s="6">
+        <v>22278</v>
+      </c>
+      <c r="BC38" s="4">
+        <f t="shared" si="44"/>
+        <v>4825</v>
+      </c>
+      <c r="BD38" s="13">
+        <v>27103</v>
+      </c>
+      <c r="BE38" s="5">
+        <f t="shared" si="45"/>
+        <v>0.95841437108808658</v>
+      </c>
+      <c r="BF38" s="7">
+        <v>42642</v>
+      </c>
+      <c r="BG38" s="6">
+        <v>31511</v>
+      </c>
+      <c r="BH38" s="4">
+        <f t="shared" si="46"/>
+        <v>7501</v>
+      </c>
+      <c r="BI38" s="13">
+        <v>39012</v>
+      </c>
+      <c r="BJ38" s="5">
+        <f t="shared" si="47"/>
+        <v>0.91487266075700013</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A39" s="18">
         <v>31</v>
       </c>
@@ -6388,15 +7416,15 @@
         <v>198</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="20"/>
-        <v>55</v>
+        <f t="shared" si="24"/>
+        <v>57</v>
       </c>
       <c r="F39" s="13">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" si="21"/>
-        <v>0.98828125</v>
+        <f t="shared" si="25"/>
+        <v>0.99609375</v>
       </c>
       <c r="H39" s="7">
         <v>262</v>
@@ -6405,15 +7433,15 @@
         <v>192</v>
       </c>
       <c r="J39" s="4">
-        <f t="shared" si="22"/>
-        <v>62</v>
+        <f t="shared" si="26"/>
+        <v>64</v>
       </c>
       <c r="K39" s="13">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="23"/>
-        <v>0.96946564885496178</v>
+        <f t="shared" si="27"/>
+        <v>0.97709923664122134</v>
       </c>
       <c r="M39" s="7">
         <v>313</v>
@@ -6422,15 +7450,15 @@
         <v>237</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" si="28"/>
+        <v>70</v>
       </c>
       <c r="P39" s="13">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" si="25"/>
-        <v>0.97763578274760388</v>
+        <f t="shared" si="29"/>
+        <v>0.98083067092651754</v>
       </c>
       <c r="R39" s="7">
         <v>264</v>
@@ -6439,15 +7467,15 @@
         <v>192</v>
       </c>
       <c r="T39" s="4">
-        <f t="shared" si="26"/>
-        <v>57</v>
+        <f t="shared" si="30"/>
+        <v>59</v>
       </c>
       <c r="U39" s="13">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="27"/>
-        <v>0.94318181818181823</v>
+        <f t="shared" si="31"/>
+        <v>0.9507575757575758</v>
       </c>
       <c r="W39" s="7">
         <v>265</v>
@@ -6456,15 +7484,15 @@
         <v>190</v>
       </c>
       <c r="Y39" s="4">
-        <f t="shared" si="28"/>
-        <v>59</v>
+        <f t="shared" si="32"/>
+        <v>64</v>
       </c>
       <c r="Z39" s="13">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="29"/>
-        <v>0.93962264150943398</v>
+        <f t="shared" si="33"/>
+        <v>0.95849056603773586</v>
       </c>
       <c r="AB39" s="7">
         <v>322</v>
@@ -6473,15 +7501,15 @@
         <v>241</v>
       </c>
       <c r="AD39" s="4">
-        <f t="shared" si="30"/>
-        <v>59</v>
+        <f t="shared" si="34"/>
+        <v>69</v>
       </c>
       <c r="AE39" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AF39" s="5">
-        <f t="shared" si="31"/>
-        <v>0.93167701863354035</v>
+        <f t="shared" si="35"/>
+        <v>0.96273291925465843</v>
       </c>
       <c r="AG39" s="7">
         <v>267</v>
@@ -6490,15 +7518,15 @@
         <v>196</v>
       </c>
       <c r="AI39" s="4">
-        <f t="shared" si="32"/>
-        <v>47</v>
+        <f t="shared" si="36"/>
+        <v>56</v>
       </c>
       <c r="AJ39" s="13">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AK39" s="5">
-        <f t="shared" si="33"/>
-        <v>0.9101123595505618</v>
+        <f t="shared" si="37"/>
+        <v>0.9438202247191011</v>
       </c>
       <c r="AL39" s="7">
         <v>276</v>
@@ -6507,15 +7535,15 @@
         <v>202</v>
       </c>
       <c r="AN39" s="4">
-        <f t="shared" si="34"/>
-        <v>46</v>
+        <f t="shared" si="38"/>
+        <v>57</v>
       </c>
       <c r="AO39" s="13">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AP39" s="5">
-        <f t="shared" si="35"/>
-        <v>0.89855072463768115</v>
+        <f t="shared" si="39"/>
+        <v>0.93840579710144922</v>
       </c>
       <c r="AQ39" s="7">
         <v>338</v>
@@ -6524,15 +7552,15 @@
         <v>252</v>
       </c>
       <c r="AS39" s="4">
-        <f t="shared" si="36"/>
-        <v>48</v>
+        <f t="shared" si="40"/>
+        <v>64</v>
       </c>
       <c r="AT39" s="13">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="AU39" s="5">
-        <f t="shared" si="37"/>
-        <v>0.8875739644970414</v>
+        <f t="shared" si="41"/>
+        <v>0.9349112426035503</v>
       </c>
       <c r="AV39" s="7">
         <v>279</v>
@@ -6541,18 +7569,52 @@
         <v>216</v>
       </c>
       <c r="AX39" s="4">
-        <f t="shared" si="38"/>
-        <v>22</v>
+        <f t="shared" si="42"/>
+        <v>45</v>
       </c>
       <c r="AY39" s="13">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AZ39" s="5">
-        <f t="shared" si="39"/>
-        <v>0.8530465949820788</v>
+        <f t="shared" si="43"/>
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="BA39" s="7">
+        <v>291</v>
+      </c>
+      <c r="BB39" s="6">
+        <v>218</v>
+      </c>
+      <c r="BC39" s="4">
+        <f t="shared" si="44"/>
+        <v>48</v>
+      </c>
+      <c r="BD39" s="13">
+        <v>266</v>
+      </c>
+      <c r="BE39" s="5">
+        <f t="shared" si="45"/>
+        <v>0.91408934707903777</v>
+      </c>
+      <c r="BF39" s="7">
+        <v>344</v>
+      </c>
+      <c r="BG39" s="6">
+        <v>251</v>
+      </c>
+      <c r="BH39" s="4">
+        <f t="shared" si="46"/>
+        <v>64</v>
+      </c>
+      <c r="BI39" s="13">
+        <v>315</v>
+      </c>
+      <c r="BJ39" s="5">
+        <f t="shared" si="47"/>
+        <v>0.91569767441860461</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A40" s="18">
         <v>32</v>
       </c>
@@ -6566,15 +7628,15 @@
         <v>227915</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="20"/>
-        <v>72827</v>
+        <f t="shared" si="24"/>
+        <v>73282</v>
       </c>
       <c r="F40" s="13">
-        <v>300742</v>
+        <v>301197</v>
       </c>
       <c r="G40" s="5">
-        <f t="shared" si="21"/>
-        <v>0.98962796238161987</v>
+        <f t="shared" si="25"/>
+        <v>0.99112519496929852</v>
       </c>
       <c r="H40" s="7">
         <v>306465</v>
@@ -6583,15 +7645,15 @@
         <v>231460</v>
       </c>
       <c r="J40" s="4">
-        <f t="shared" si="22"/>
-        <v>70461</v>
+        <f t="shared" si="26"/>
+        <v>71058</v>
       </c>
       <c r="K40" s="13">
-        <v>301921</v>
+        <v>302518</v>
       </c>
       <c r="L40" s="5">
-        <f t="shared" si="23"/>
-        <v>0.98517285823829803</v>
+        <f t="shared" si="27"/>
+        <v>0.98712087840373286</v>
       </c>
       <c r="M40" s="7">
         <v>361770</v>
@@ -6600,15 +7662,15 @@
         <v>267814</v>
       </c>
       <c r="O40" s="4">
-        <f t="shared" si="24"/>
-        <v>89383</v>
+        <f t="shared" si="28"/>
+        <v>90366</v>
       </c>
       <c r="P40" s="13">
-        <v>357197</v>
+        <v>358180</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="25"/>
-        <v>0.98735937197667023</v>
+        <f t="shared" si="29"/>
+        <v>0.99007656798518395</v>
       </c>
       <c r="R40" s="7">
         <v>306479</v>
@@ -6617,15 +7679,15 @@
         <v>234439</v>
       </c>
       <c r="T40" s="4">
-        <f t="shared" si="26"/>
-        <v>68558</v>
+        <f t="shared" si="30"/>
+        <v>69806</v>
       </c>
       <c r="U40" s="13">
-        <v>302997</v>
+        <v>304245</v>
       </c>
       <c r="V40" s="5">
-        <f t="shared" si="27"/>
-        <v>0.98863869955200845</v>
+        <f t="shared" si="31"/>
+        <v>0.99271075669132303</v>
       </c>
       <c r="W40" s="7">
         <v>309858</v>
@@ -6634,15 +7696,15 @@
         <v>235614</v>
       </c>
       <c r="Y40" s="4">
-        <f t="shared" si="28"/>
-        <v>67907</v>
+        <f t="shared" si="32"/>
+        <v>70018</v>
       </c>
       <c r="Z40" s="13">
-        <v>303521</v>
+        <v>305632</v>
       </c>
       <c r="AA40" s="5">
-        <f t="shared" si="29"/>
-        <v>0.9795486964996869</v>
+        <f t="shared" si="33"/>
+        <v>0.98636149462011635</v>
       </c>
       <c r="AB40" s="7">
         <v>365821</v>
@@ -6651,15 +7713,15 @@
         <v>296785</v>
       </c>
       <c r="AD40" s="4">
-        <f t="shared" si="30"/>
-        <v>60617</v>
+        <f t="shared" si="34"/>
+        <v>64926</v>
       </c>
       <c r="AE40" s="13">
-        <v>357402</v>
+        <v>361711</v>
       </c>
       <c r="AF40" s="5">
-        <f t="shared" si="31"/>
-        <v>0.97698601228469661</v>
+        <f t="shared" si="35"/>
+        <v>0.98876499708874011</v>
       </c>
       <c r="AG40" s="7">
         <v>311342</v>
@@ -6668,15 +7730,15 @@
         <v>235940</v>
       </c>
       <c r="AI40" s="4">
-        <f t="shared" si="32"/>
-        <v>66169</v>
+        <f t="shared" si="36"/>
+        <v>71700</v>
       </c>
       <c r="AJ40" s="13">
-        <v>302109</v>
+        <v>307640</v>
       </c>
       <c r="AK40" s="5">
-        <f t="shared" si="33"/>
-        <v>0.97034450861110932</v>
+        <f t="shared" si="37"/>
+        <v>0.98810953870663132</v>
       </c>
       <c r="AL40" s="7">
         <v>314792</v>
@@ -6685,15 +7747,15 @@
         <v>241859</v>
       </c>
       <c r="AN40" s="4">
-        <f t="shared" si="34"/>
-        <v>60870</v>
+        <f t="shared" si="38"/>
+        <v>68738</v>
       </c>
       <c r="AO40" s="13">
-        <v>302729</v>
+        <v>310597</v>
       </c>
       <c r="AP40" s="5">
-        <f t="shared" si="35"/>
-        <v>0.96167945818191058</v>
+        <f t="shared" si="39"/>
+        <v>0.9866737401204605</v>
       </c>
       <c r="AQ40" s="7">
         <v>372144</v>
@@ -6702,15 +7764,15 @@
         <v>294142</v>
       </c>
       <c r="AS40" s="4">
-        <f t="shared" si="36"/>
-        <v>56774</v>
+        <f t="shared" si="40"/>
+        <v>71357</v>
       </c>
       <c r="AT40" s="13">
-        <v>350916</v>
+        <v>365499</v>
       </c>
       <c r="AU40" s="5">
-        <f t="shared" si="37"/>
-        <v>0.94295756481362059</v>
+        <f t="shared" si="41"/>
+        <v>0.98214400877079844</v>
       </c>
       <c r="AV40" s="7">
         <v>317868</v>
@@ -6719,18 +7781,52 @@
         <v>249816</v>
       </c>
       <c r="AX40" s="4">
-        <f t="shared" si="38"/>
-        <v>32170</v>
+        <f t="shared" si="42"/>
+        <v>60048</v>
       </c>
       <c r="AY40" s="13">
-        <v>281986</v>
+        <v>309864</v>
       </c>
       <c r="AZ40" s="5">
-        <f t="shared" si="39"/>
-        <v>0.88711666477909068</v>
+        <f t="shared" si="43"/>
+        <v>0.97481973649439391</v>
+      </c>
+      <c r="BA40" s="7">
+        <v>321637</v>
+      </c>
+      <c r="BB40" s="6">
+        <v>244633</v>
+      </c>
+      <c r="BC40" s="4">
+        <f t="shared" si="44"/>
+        <v>64628</v>
+      </c>
+      <c r="BD40" s="13">
+        <v>309261</v>
+      </c>
+      <c r="BE40" s="5">
+        <f t="shared" si="45"/>
+        <v>0.96152183983807837</v>
+      </c>
+      <c r="BF40" s="7">
+        <v>380248</v>
+      </c>
+      <c r="BG40" s="6">
+        <v>280381</v>
+      </c>
+      <c r="BH40" s="4">
+        <f t="shared" si="46"/>
+        <v>73924</v>
+      </c>
+      <c r="BI40" s="13">
+        <v>354305</v>
+      </c>
+      <c r="BJ40" s="5">
+        <f t="shared" si="47"/>
+        <v>0.93177347415371026</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A41" s="18">
         <v>33</v>
       </c>
@@ -6744,15 +7840,15 @@
         <v>812212</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="20"/>
-        <v>162325</v>
+        <f t="shared" si="24"/>
+        <v>163117</v>
       </c>
       <c r="F41" s="13">
-        <v>974537</v>
+        <v>975329</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" si="21"/>
-        <v>0.99703713707231079</v>
+        <f t="shared" si="25"/>
+        <v>0.9978474227901043</v>
       </c>
       <c r="H41" s="7">
         <v>983280</v>
@@ -6761,15 +7857,15 @@
         <v>816694</v>
       </c>
       <c r="J41" s="4">
-        <f t="shared" si="22"/>
-        <v>161915</v>
+        <f t="shared" si="26"/>
+        <v>162956</v>
       </c>
       <c r="K41" s="13">
-        <v>978609</v>
+        <v>979650</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="23"/>
-        <v>0.99524957285818894</v>
+        <f t="shared" si="27"/>
+        <v>0.99630827434708324</v>
       </c>
       <c r="M41" s="7">
         <v>1084276</v>
@@ -6778,15 +7874,15 @@
         <v>891207</v>
       </c>
       <c r="O41" s="4">
-        <f t="shared" si="24"/>
-        <v>188644</v>
+        <f t="shared" si="28"/>
+        <v>190145</v>
       </c>
       <c r="P41" s="13">
-        <v>1079851</v>
+        <v>1081352</v>
       </c>
       <c r="Q41" s="5">
-        <f t="shared" si="25"/>
-        <v>0.99591893576912149</v>
+        <f t="shared" si="29"/>
+        <v>0.99730326964721161</v>
       </c>
       <c r="R41" s="7">
         <v>988018</v>
@@ -6795,15 +7891,15 @@
         <v>824291</v>
       </c>
       <c r="T41" s="4">
-        <f t="shared" si="26"/>
-        <v>161428</v>
+        <f t="shared" si="30"/>
+        <v>163302</v>
       </c>
       <c r="U41" s="13">
-        <v>985719</v>
+        <v>987593</v>
       </c>
       <c r="V41" s="5">
-        <f t="shared" si="27"/>
-        <v>0.99767311931563996</v>
+        <f t="shared" si="31"/>
+        <v>0.99956984589349585</v>
       </c>
       <c r="W41" s="7">
         <v>994033</v>
@@ -6812,15 +7908,15 @@
         <v>831459</v>
       </c>
       <c r="Y41" s="4">
-        <f t="shared" si="28"/>
-        <v>158079</v>
+        <f t="shared" si="32"/>
+        <v>160883</v>
       </c>
       <c r="Z41" s="13">
-        <v>989538</v>
+        <v>992342</v>
       </c>
       <c r="AA41" s="5">
-        <f t="shared" si="29"/>
-        <v>0.99547801732940455</v>
+        <f t="shared" si="33"/>
+        <v>0.99829884923337553</v>
       </c>
       <c r="AB41" s="7">
         <v>1097882</v>
@@ -6829,15 +7925,15 @@
         <v>956599</v>
       </c>
       <c r="AD41" s="4">
-        <f t="shared" si="30"/>
-        <v>133917</v>
+        <f t="shared" si="34"/>
+        <v>138880</v>
       </c>
       <c r="AE41" s="13">
-        <v>1090516</v>
+        <v>1095479</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" si="31"/>
-        <v>0.99329071794600876</v>
+        <f t="shared" si="35"/>
+        <v>0.99781124018792544</v>
       </c>
       <c r="AG41" s="7">
         <v>1002140</v>
@@ -6846,15 +7942,15 @@
         <v>844704</v>
       </c>
       <c r="AI41" s="4">
-        <f t="shared" si="32"/>
-        <v>149014</v>
+        <f t="shared" si="36"/>
+        <v>155684</v>
       </c>
       <c r="AJ41" s="13">
-        <v>993718</v>
+        <v>1000388</v>
       </c>
       <c r="AK41" s="5">
-        <f t="shared" si="33"/>
-        <v>0.99159598459297105</v>
+        <f t="shared" si="37"/>
+        <v>0.99825174127367433</v>
       </c>
       <c r="AL41" s="7">
         <v>1011306</v>
@@ -6863,15 +7959,15 @@
         <v>863109</v>
       </c>
       <c r="AN41" s="4">
-        <f t="shared" si="34"/>
-        <v>139167</v>
+        <f t="shared" si="38"/>
+        <v>149499</v>
       </c>
       <c r="AO41" s="13">
-        <v>1002276</v>
+        <v>1012608</v>
       </c>
       <c r="AP41" s="5">
-        <f t="shared" si="35"/>
-        <v>0.99107095181873739</v>
+        <f t="shared" si="39"/>
+        <v>1.0012874441563682</v>
       </c>
       <c r="AQ41" s="7">
         <v>1119532</v>
@@ -6880,15 +7976,15 @@
         <v>935550</v>
       </c>
       <c r="AS41" s="4">
-        <f t="shared" si="36"/>
-        <v>161551</v>
+        <f t="shared" si="40"/>
+        <v>183638</v>
       </c>
       <c r="AT41" s="13">
-        <v>1097101</v>
+        <v>1119188</v>
       </c>
       <c r="AU41" s="5">
-        <f t="shared" si="37"/>
-        <v>0.9799639492216391</v>
+        <f t="shared" si="41"/>
+        <v>0.99969272874736947</v>
       </c>
       <c r="AV41" s="7">
         <v>1028062</v>
@@ -6897,18 +7993,52 @@
         <v>879708</v>
       </c>
       <c r="AX41" s="4">
-        <f t="shared" si="38"/>
-        <v>85108</v>
+        <f t="shared" si="42"/>
+        <v>144327</v>
       </c>
       <c r="AY41" s="13">
-        <v>964816</v>
+        <v>1024035</v>
       </c>
       <c r="AZ41" s="5">
-        <f t="shared" si="39"/>
-        <v>0.93848036402473778</v>
+        <f t="shared" si="43"/>
+        <v>0.99608292106896279</v>
+      </c>
+      <c r="BA41" s="7">
+        <v>1037044</v>
+      </c>
+      <c r="BB41" s="6">
+        <v>885686</v>
+      </c>
+      <c r="BC41" s="4">
+        <f t="shared" si="44"/>
+        <v>141760</v>
+      </c>
+      <c r="BD41" s="13">
+        <v>1027446</v>
+      </c>
+      <c r="BE41" s="5">
+        <f t="shared" si="45"/>
+        <v>0.99074484785602157</v>
+      </c>
+      <c r="BF41" s="7">
+        <v>1143357</v>
+      </c>
+      <c r="BG41" s="6">
+        <v>943789</v>
+      </c>
+      <c r="BH41" s="4">
+        <f t="shared" si="46"/>
+        <v>168091</v>
+      </c>
+      <c r="BI41" s="13">
+        <v>1111880</v>
+      </c>
+      <c r="BJ41" s="5">
+        <f t="shared" si="47"/>
+        <v>0.97246966607979834</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A42" s="18">
         <v>34</v>
       </c>
@@ -6922,15 +8052,15 @@
         <v>15291</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="20"/>
-        <v>4257</v>
+        <f t="shared" si="24"/>
+        <v>4271</v>
       </c>
       <c r="F42" s="13">
-        <v>19548</v>
+        <v>19562</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" si="21"/>
-        <v>0.99349461272616391</v>
+        <f t="shared" si="25"/>
+        <v>0.99420613945923964</v>
       </c>
       <c r="H42" s="7">
         <v>19882</v>
@@ -6939,15 +8069,15 @@
         <v>15358</v>
       </c>
       <c r="J42" s="4">
-        <f t="shared" si="22"/>
-        <v>4279</v>
+        <f t="shared" si="26"/>
+        <v>4301</v>
       </c>
       <c r="K42" s="13">
-        <v>19637</v>
+        <v>19659</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" si="23"/>
-        <v>0.98767729604667542</v>
+        <f t="shared" si="27"/>
+        <v>0.98878382456493308</v>
       </c>
       <c r="M42" s="7">
         <v>21930</v>
@@ -6956,15 +8086,15 @@
         <v>16537</v>
       </c>
       <c r="O42" s="4">
-        <f t="shared" si="24"/>
-        <v>5161</v>
+        <f t="shared" si="28"/>
+        <v>5193</v>
       </c>
       <c r="P42" s="13">
-        <v>21698</v>
+        <v>21730</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" si="25"/>
-        <v>0.98942088463292288</v>
+        <f t="shared" si="29"/>
+        <v>0.99088007295941627</v>
       </c>
       <c r="R42" s="7">
         <v>20021</v>
@@ -6973,15 +8103,15 @@
         <v>15436</v>
       </c>
       <c r="T42" s="4">
-        <f t="shared" si="26"/>
-        <v>4305</v>
+        <f t="shared" si="30"/>
+        <v>4356</v>
       </c>
       <c r="U42" s="13">
-        <v>19741</v>
+        <v>19792</v>
       </c>
       <c r="V42" s="5">
-        <f t="shared" si="27"/>
-        <v>0.98601468458118979</v>
+        <f t="shared" si="31"/>
+        <v>0.98856200988961596</v>
       </c>
       <c r="W42" s="7">
         <v>20153</v>
@@ -6990,15 +8120,15 @@
         <v>15663</v>
       </c>
       <c r="Y42" s="4">
-        <f t="shared" si="28"/>
-        <v>4111</v>
+        <f t="shared" si="32"/>
+        <v>4219</v>
       </c>
       <c r="Z42" s="13">
-        <v>19774</v>
+        <v>19882</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="29"/>
-        <v>0.98119386691807675</v>
+        <f t="shared" si="33"/>
+        <v>0.98655287054036622</v>
       </c>
       <c r="AB42" s="7">
         <v>22238</v>
@@ -7007,15 +8137,15 @@
         <v>18157</v>
       </c>
       <c r="AD42" s="4">
-        <f t="shared" si="30"/>
-        <v>3666</v>
+        <f t="shared" si="34"/>
+        <v>3859</v>
       </c>
       <c r="AE42" s="13">
-        <v>21823</v>
+        <v>22016</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98133824984261175</v>
+        <f t="shared" si="35"/>
+        <v>0.990017087867614</v>
       </c>
       <c r="AG42" s="7">
         <v>20276</v>
@@ -7024,15 +8154,15 @@
         <v>15808</v>
       </c>
       <c r="AI42" s="4">
-        <f t="shared" si="32"/>
-        <v>4012</v>
+        <f t="shared" si="36"/>
+        <v>4287</v>
       </c>
       <c r="AJ42" s="13">
-        <v>19820</v>
+        <v>20095</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="33"/>
-        <v>0.97751035707240086</v>
+        <f t="shared" si="37"/>
+        <v>0.99107318997829952</v>
       </c>
       <c r="AL42" s="7">
         <v>20453</v>
@@ -7041,15 +8171,15 @@
         <v>16418</v>
       </c>
       <c r="AN42" s="4">
-        <f t="shared" si="34"/>
-        <v>3367</v>
+        <f t="shared" si="38"/>
+        <v>3820</v>
       </c>
       <c r="AO42" s="13">
-        <v>19785</v>
+        <v>20238</v>
       </c>
       <c r="AP42" s="5">
-        <f t="shared" si="35"/>
-        <v>0.96733975455923338</v>
+        <f t="shared" si="39"/>
+        <v>0.98948809465604071</v>
       </c>
       <c r="AQ42" s="7">
         <v>22621</v>
@@ -7058,15 +8188,15 @@
         <v>17730</v>
       </c>
       <c r="AS42" s="4">
-        <f t="shared" si="36"/>
-        <v>3854</v>
+        <f t="shared" si="40"/>
+        <v>4641</v>
       </c>
       <c r="AT42" s="13">
-        <v>21584</v>
+        <v>22371</v>
       </c>
       <c r="AU42" s="5">
-        <f t="shared" si="37"/>
-        <v>0.95415764112992352</v>
+        <f t="shared" si="41"/>
+        <v>0.98894832235533359</v>
       </c>
       <c r="AV42" s="7">
         <v>20714</v>
@@ -7075,18 +8205,52 @@
         <v>16696</v>
       </c>
       <c r="AX42" s="4">
-        <f t="shared" si="38"/>
-        <v>1910</v>
+        <f t="shared" si="42"/>
+        <v>3630</v>
       </c>
       <c r="AY42" s="13">
-        <v>18606</v>
+        <v>20326</v>
       </c>
       <c r="AZ42" s="5">
-        <f t="shared" si="39"/>
-        <v>0.89823307907695282</v>
+        <f t="shared" si="43"/>
+        <v>0.98126870715458148</v>
+      </c>
+      <c r="BA42" s="7">
+        <v>20927</v>
+      </c>
+      <c r="BB42" s="6">
+        <v>16868</v>
+      </c>
+      <c r="BC42" s="4">
+        <f t="shared" si="44"/>
+        <v>3426</v>
+      </c>
+      <c r="BD42" s="13">
+        <v>20294</v>
+      </c>
+      <c r="BE42" s="5">
+        <f t="shared" si="45"/>
+        <v>0.96975199503034359</v>
+      </c>
+      <c r="BF42" s="7">
+        <v>23165</v>
+      </c>
+      <c r="BG42" s="6">
+        <v>17947</v>
+      </c>
+      <c r="BH42" s="4">
+        <f t="shared" si="46"/>
+        <v>3949</v>
+      </c>
+      <c r="BI42" s="13">
+        <v>21896</v>
+      </c>
+      <c r="BJ42" s="5">
+        <f t="shared" si="47"/>
+        <v>0.94521908050938919</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A43" s="18">
         <v>35</v>
       </c>
@@ -7100,15 +8264,15 @@
         <v>2718</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="20"/>
-        <v>1148</v>
+        <f t="shared" si="24"/>
+        <v>1166</v>
       </c>
       <c r="F43" s="13">
-        <v>3866</v>
+        <v>3884</v>
       </c>
       <c r="G43" s="5">
-        <f t="shared" si="21"/>
-        <v>0.98773633111905978</v>
+        <f t="shared" si="25"/>
+        <v>0.99233520694941235</v>
       </c>
       <c r="H43" s="7">
         <v>3941</v>
@@ -7117,15 +8281,15 @@
         <v>2597</v>
       </c>
       <c r="J43" s="4">
-        <f t="shared" si="22"/>
-        <v>1302</v>
+        <f t="shared" si="26"/>
+        <v>1320</v>
       </c>
       <c r="K43" s="13">
-        <v>3899</v>
+        <v>3917</v>
       </c>
       <c r="L43" s="5">
-        <f t="shared" si="23"/>
-        <v>0.98934280639431615</v>
+        <f t="shared" si="27"/>
+        <v>0.99391017508246637</v>
       </c>
       <c r="M43" s="7">
         <v>4896</v>
@@ -7134,15 +8298,15 @@
         <v>3189</v>
       </c>
       <c r="O43" s="4">
-        <f t="shared" si="24"/>
-        <v>1631</v>
+        <f t="shared" si="28"/>
+        <v>1661</v>
       </c>
       <c r="P43" s="13">
-        <v>4820</v>
+        <v>4850</v>
       </c>
       <c r="Q43" s="5">
-        <f t="shared" si="25"/>
-        <v>0.98447712418300659</v>
+        <f t="shared" si="29"/>
+        <v>0.99060457516339873</v>
       </c>
       <c r="R43" s="7">
         <v>3969</v>
@@ -7151,15 +8315,15 @@
         <v>2703</v>
       </c>
       <c r="T43" s="4">
-        <f t="shared" si="26"/>
-        <v>1190</v>
+        <f t="shared" si="30"/>
+        <v>1221</v>
       </c>
       <c r="U43" s="13">
-        <v>3893</v>
+        <v>3924</v>
       </c>
       <c r="V43" s="5">
-        <f t="shared" si="27"/>
-        <v>0.980851599899219</v>
+        <f t="shared" si="31"/>
+        <v>0.9886621315192744</v>
       </c>
       <c r="W43" s="7">
         <v>4009</v>
@@ -7168,15 +8332,15 @@
         <v>2726</v>
       </c>
       <c r="Y43" s="4">
-        <f t="shared" si="28"/>
-        <v>1181</v>
+        <f t="shared" si="32"/>
+        <v>1238</v>
       </c>
       <c r="Z43" s="13">
-        <v>3907</v>
+        <v>3964</v>
       </c>
       <c r="AA43" s="5">
-        <f t="shared" si="29"/>
-        <v>0.97455724619605888</v>
+        <f t="shared" si="33"/>
+        <v>0.9887752556747319</v>
       </c>
       <c r="AB43" s="7">
         <v>4962</v>
@@ -7185,15 +8349,15 @@
         <v>3609</v>
       </c>
       <c r="AD43" s="4">
-        <f t="shared" si="30"/>
-        <v>1182</v>
+        <f t="shared" si="34"/>
+        <v>1304</v>
       </c>
       <c r="AE43" s="13">
-        <v>4791</v>
+        <v>4913</v>
       </c>
       <c r="AF43" s="5">
-        <f t="shared" si="31"/>
-        <v>0.96553808948004838</v>
+        <f t="shared" si="35"/>
+        <v>0.99012494961708986</v>
       </c>
       <c r="AG43" s="7">
         <v>4018</v>
@@ -7202,15 +8366,15 @@
         <v>2785</v>
       </c>
       <c r="AI43" s="4">
-        <f t="shared" si="32"/>
-        <v>1046</v>
+        <f t="shared" si="36"/>
+        <v>1192</v>
       </c>
       <c r="AJ43" s="13">
-        <v>3831</v>
+        <v>3977</v>
       </c>
       <c r="AK43" s="5">
-        <f t="shared" si="33"/>
-        <v>0.95345943255350918</v>
+        <f t="shared" si="37"/>
+        <v>0.98979591836734693</v>
       </c>
       <c r="AL43" s="7">
         <v>4086</v>
@@ -7219,15 +8383,15 @@
         <v>2872</v>
       </c>
       <c r="AN43" s="4">
-        <f t="shared" si="34"/>
-        <v>967</v>
+        <f t="shared" si="38"/>
+        <v>1154</v>
       </c>
       <c r="AO43" s="13">
-        <v>3839</v>
+        <v>4026</v>
       </c>
       <c r="AP43" s="5">
-        <f t="shared" si="35"/>
-        <v>0.93954968184043075</v>
+        <f t="shared" si="39"/>
+        <v>0.98531571218795888</v>
       </c>
       <c r="AQ43" s="7">
         <v>5072</v>
@@ -7236,15 +8400,15 @@
         <v>3513</v>
       </c>
       <c r="AS43" s="4">
-        <f t="shared" si="36"/>
-        <v>1062</v>
+        <f t="shared" si="40"/>
+        <v>1469</v>
       </c>
       <c r="AT43" s="13">
-        <v>4575</v>
+        <v>4982</v>
       </c>
       <c r="AU43" s="5">
-        <f t="shared" si="37"/>
-        <v>0.90201104100946372</v>
+        <f t="shared" si="41"/>
+        <v>0.98225552050473186</v>
       </c>
       <c r="AV43" s="7">
         <v>4151</v>
@@ -7253,18 +8417,52 @@
         <v>2841</v>
       </c>
       <c r="AX43" s="4">
-        <f t="shared" si="38"/>
-        <v>501</v>
+        <f t="shared" si="42"/>
+        <v>1153</v>
       </c>
       <c r="AY43" s="13">
-        <v>3342</v>
+        <v>3994</v>
       </c>
       <c r="AZ43" s="5">
-        <f t="shared" si="39"/>
-        <v>0.80510720308359429</v>
+        <f t="shared" si="43"/>
+        <v>0.96217778848470248</v>
+      </c>
+      <c r="BA43" s="7">
+        <v>4249</v>
+      </c>
+      <c r="BB43" s="6">
+        <v>2971</v>
+      </c>
+      <c r="BC43" s="4">
+        <f t="shared" si="44"/>
+        <v>1016</v>
+      </c>
+      <c r="BD43" s="13">
+        <v>3987</v>
+      </c>
+      <c r="BE43" s="5">
+        <f t="shared" si="45"/>
+        <v>0.93833843257236993</v>
+      </c>
+      <c r="BF43" s="7">
+        <v>5295</v>
+      </c>
+      <c r="BG43" s="6">
+        <v>3299</v>
+      </c>
+      <c r="BH43" s="4">
+        <f t="shared" si="46"/>
+        <v>1312</v>
+      </c>
+      <c r="BI43" s="13">
+        <v>4611</v>
+      </c>
+      <c r="BJ43" s="5">
+        <f t="shared" si="47"/>
+        <v>0.87082152974504246</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A44" s="18">
         <v>36</v>
       </c>
@@ -7278,15 +8476,15 @@
         <v>295419</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="20"/>
-        <v>83550</v>
+        <f t="shared" si="24"/>
+        <v>84055</v>
       </c>
       <c r="F44" s="13">
-        <v>378969</v>
+        <v>379474</v>
       </c>
       <c r="G44" s="5">
-        <f t="shared" si="21"/>
-        <v>0.98808722994853182</v>
+        <f t="shared" si="25"/>
+        <v>0.98940391825581819</v>
       </c>
       <c r="H44" s="7">
         <v>388149</v>
@@ -7295,15 +8493,15 @@
         <v>300418</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" si="22"/>
-        <v>81698</v>
+        <f t="shared" si="26"/>
+        <v>82331</v>
       </c>
       <c r="K44" s="13">
-        <v>382116</v>
+        <v>382749</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" si="23"/>
-        <v>0.98445699976040124</v>
+        <f t="shared" si="27"/>
+        <v>0.98608781679200508</v>
       </c>
       <c r="M44" s="7">
         <v>456953</v>
@@ -7312,15 +8510,15 @@
         <v>349612</v>
       </c>
       <c r="O44" s="4">
-        <f t="shared" si="24"/>
-        <v>102197</v>
+        <f t="shared" si="28"/>
+        <v>103156</v>
       </c>
       <c r="P44" s="13">
-        <v>451809</v>
+        <v>452768</v>
       </c>
       <c r="Q44" s="5">
-        <f t="shared" si="25"/>
-        <v>0.98874282475440578</v>
+        <f t="shared" si="29"/>
+        <v>0.99084150886415012</v>
       </c>
       <c r="R44" s="7">
         <v>388846</v>
@@ -7329,15 +8527,15 @@
         <v>301787</v>
       </c>
       <c r="T44" s="4">
-        <f t="shared" si="26"/>
-        <v>82125</v>
+        <f t="shared" si="30"/>
+        <v>83191</v>
       </c>
       <c r="U44" s="13">
-        <v>383912</v>
+        <v>384978</v>
       </c>
       <c r="V44" s="5">
-        <f t="shared" si="27"/>
-        <v>0.98731117203211549</v>
+        <f t="shared" si="31"/>
+        <v>0.9900526172315004</v>
       </c>
       <c r="W44" s="7">
         <v>393146</v>
@@ -7346,15 +8544,15 @@
         <v>305708</v>
       </c>
       <c r="Y44" s="4">
-        <f t="shared" si="28"/>
-        <v>80158</v>
+        <f t="shared" si="32"/>
+        <v>81723</v>
       </c>
       <c r="Z44" s="13">
-        <v>385866</v>
+        <v>387431</v>
       </c>
       <c r="AA44" s="5">
-        <f t="shared" si="29"/>
-        <v>0.98148270617022682</v>
+        <f t="shared" si="33"/>
+        <v>0.98546341562676465</v>
       </c>
       <c r="AB44" s="7">
         <v>465292</v>
@@ -7363,15 +8561,15 @@
         <v>378392</v>
       </c>
       <c r="AD44" s="4">
-        <f t="shared" si="30"/>
-        <v>78152</v>
+        <f t="shared" si="34"/>
+        <v>81145</v>
       </c>
       <c r="AE44" s="13">
-        <v>456544</v>
+        <v>459537</v>
       </c>
       <c r="AF44" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98119890305442603</v>
+        <f t="shared" si="35"/>
+        <v>0.98763142284844785</v>
       </c>
       <c r="AG44" s="7">
         <v>393778</v>
@@ -7380,15 +8578,15 @@
         <v>311206</v>
       </c>
       <c r="AI44" s="4">
-        <f t="shared" si="32"/>
-        <v>75827</v>
+        <f t="shared" si="36"/>
+        <v>79624</v>
       </c>
       <c r="AJ44" s="13">
-        <v>387033</v>
+        <v>390830</v>
       </c>
       <c r="AK44" s="5">
-        <f t="shared" si="33"/>
-        <v>0.98287105932784458</v>
+        <f t="shared" si="37"/>
+        <v>0.9925135482429186</v>
       </c>
       <c r="AL44" s="7">
         <v>398873</v>
@@ -7397,15 +8595,15 @@
         <v>323525</v>
       </c>
       <c r="AN44" s="4">
-        <f t="shared" si="34"/>
-        <v>70193</v>
+        <f t="shared" si="38"/>
+        <v>76321</v>
       </c>
       <c r="AO44" s="13">
-        <v>393718</v>
+        <v>399846</v>
       </c>
       <c r="AP44" s="5">
-        <f t="shared" si="35"/>
-        <v>0.98707608687476966</v>
+        <f t="shared" si="39"/>
+        <v>1.0024393729332395</v>
       </c>
       <c r="AQ44" s="7">
         <v>476819</v>
@@ -7414,15 +8612,15 @@
         <v>391434</v>
       </c>
       <c r="AS44" s="4">
-        <f t="shared" si="36"/>
-        <v>69676</v>
+        <f t="shared" si="40"/>
+        <v>83679</v>
       </c>
       <c r="AT44" s="13">
-        <v>461110</v>
+        <v>475113</v>
       </c>
       <c r="AU44" s="5">
-        <f t="shared" si="37"/>
-        <v>0.96705458465371552</v>
+        <f t="shared" si="41"/>
+        <v>0.9964221224405907</v>
       </c>
       <c r="AV44" s="7">
         <v>408878</v>
@@ -7431,18 +8629,52 @@
         <v>335378</v>
       </c>
       <c r="AX44" s="4">
-        <f t="shared" si="38"/>
-        <v>41366</v>
+        <f t="shared" si="42"/>
+        <v>70398</v>
       </c>
       <c r="AY44" s="13">
-        <v>376744</v>
+        <v>405776</v>
       </c>
       <c r="AZ44" s="5">
-        <f t="shared" si="39"/>
-        <v>0.92140932013950372</v>
+        <f t="shared" si="43"/>
+        <v>0.99241338492166364</v>
+      </c>
+      <c r="BA44" s="7">
+        <v>416024</v>
+      </c>
+      <c r="BB44" s="6">
+        <v>332685</v>
+      </c>
+      <c r="BC44" s="4">
+        <f t="shared" si="44"/>
+        <v>75330</v>
+      </c>
+      <c r="BD44" s="13">
+        <v>408015</v>
+      </c>
+      <c r="BE44" s="5">
+        <f t="shared" si="45"/>
+        <v>0.98074870680537662</v>
+      </c>
+      <c r="BF44" s="7">
+        <v>493955</v>
+      </c>
+      <c r="BG44" s="6">
+        <v>380586</v>
+      </c>
+      <c r="BH44" s="4">
+        <f t="shared" si="46"/>
+        <v>88079</v>
+      </c>
+      <c r="BI44" s="13">
+        <v>468665</v>
+      </c>
+      <c r="BJ44" s="5">
+        <f t="shared" si="47"/>
+        <v>0.94880100414005319</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>37</v>
       </c>
@@ -7456,15 +8688,15 @@
         <v>220958</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="20"/>
-        <v>55701</v>
+        <f t="shared" si="24"/>
+        <v>55932</v>
       </c>
       <c r="F45" s="13">
-        <v>276659</v>
+        <v>276890</v>
       </c>
       <c r="G45" s="5">
-        <f t="shared" si="21"/>
-        <v>0.99698374030616654</v>
+        <f t="shared" si="25"/>
+        <v>0.99781618473779798</v>
       </c>
       <c r="H45" s="7">
         <v>280269</v>
@@ -7473,15 +8705,15 @@
         <v>223137</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" si="22"/>
-        <v>55154</v>
+        <f t="shared" si="26"/>
+        <v>55460</v>
       </c>
       <c r="K45" s="13">
-        <v>278291</v>
+        <v>278597</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="23"/>
-        <v>0.99294249453203887</v>
+        <f t="shared" si="27"/>
+        <v>0.99403430275913496</v>
       </c>
       <c r="M45" s="7">
         <v>334005</v>
@@ -7490,15 +8722,15 @@
         <v>261510</v>
       </c>
       <c r="O45" s="4">
-        <f t="shared" si="24"/>
-        <v>69484</v>
+        <f t="shared" si="28"/>
+        <v>70040</v>
       </c>
       <c r="P45" s="13">
-        <v>330994</v>
+        <v>331550</v>
       </c>
       <c r="Q45" s="5">
-        <f t="shared" si="25"/>
-        <v>0.99098516489274113</v>
+        <f t="shared" si="29"/>
+        <v>0.99264981063157742</v>
       </c>
       <c r="R45" s="7">
         <v>281510</v>
@@ -7507,15 +8739,15 @@
         <v>226061</v>
       </c>
       <c r="T45" s="4">
-        <f t="shared" si="26"/>
-        <v>52977</v>
+        <f t="shared" si="30"/>
+        <v>53603</v>
       </c>
       <c r="U45" s="13">
-        <v>279038</v>
+        <v>279664</v>
       </c>
       <c r="V45" s="5">
-        <f t="shared" si="27"/>
-        <v>0.99121878441263189</v>
+        <f t="shared" si="31"/>
+        <v>0.99344250648289578</v>
       </c>
       <c r="W45" s="7">
         <v>284325</v>
@@ -7524,15 +8756,15 @@
         <v>226325</v>
       </c>
       <c r="Y45" s="4">
-        <f t="shared" si="28"/>
-        <v>53297</v>
+        <f t="shared" si="32"/>
+        <v>54326</v>
       </c>
       <c r="Z45" s="13">
-        <v>279622</v>
+        <v>280651</v>
       </c>
       <c r="AA45" s="5">
-        <f t="shared" si="29"/>
-        <v>0.98345906972654529</v>
+        <f t="shared" si="33"/>
+        <v>0.98707816758990596</v>
       </c>
       <c r="AB45" s="7">
         <v>338696</v>
@@ -7541,15 +8773,15 @@
         <v>273192</v>
       </c>
       <c r="AD45" s="4">
-        <f t="shared" si="30"/>
-        <v>58884</v>
+        <f t="shared" si="34"/>
+        <v>61069</v>
       </c>
       <c r="AE45" s="13">
-        <v>332076</v>
+        <v>334261</v>
       </c>
       <c r="AF45" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98045444882726696</v>
+        <f t="shared" si="35"/>
+        <v>0.98690566171433969</v>
       </c>
       <c r="AG45" s="7">
         <v>285325</v>
@@ -7558,15 +8790,15 @@
         <v>225955</v>
       </c>
       <c r="AI45" s="4">
-        <f t="shared" si="32"/>
-        <v>53730</v>
+        <f t="shared" si="36"/>
+        <v>56258</v>
       </c>
       <c r="AJ45" s="13">
-        <v>279685</v>
+        <v>282213</v>
       </c>
       <c r="AK45" s="5">
-        <f t="shared" si="33"/>
-        <v>0.98023306755454309</v>
+        <f t="shared" si="37"/>
+        <v>0.98909313940243582</v>
       </c>
       <c r="AL45" s="7">
         <v>289428</v>
@@ -7575,15 +8807,15 @@
         <v>236121</v>
       </c>
       <c r="AN45" s="4">
-        <f t="shared" si="34"/>
-        <v>48393</v>
+        <f t="shared" si="38"/>
+        <v>52436</v>
       </c>
       <c r="AO45" s="13">
-        <v>284514</v>
+        <v>288557</v>
       </c>
       <c r="AP45" s="5">
-        <f t="shared" si="35"/>
-        <v>0.98302168414942581</v>
+        <f t="shared" si="39"/>
+        <v>0.99699061597357541</v>
       </c>
       <c r="AQ45" s="7">
         <v>348161</v>
@@ -7592,15 +8824,15 @@
         <v>280294</v>
       </c>
       <c r="AS45" s="4">
-        <f t="shared" si="36"/>
-        <v>54802</v>
+        <f t="shared" si="40"/>
+        <v>64508</v>
       </c>
       <c r="AT45" s="13">
-        <v>335096</v>
+        <v>344802</v>
       </c>
       <c r="AU45" s="5">
-        <f t="shared" si="37"/>
-        <v>0.96247425759921412</v>
+        <f t="shared" si="41"/>
+        <v>0.99035216465945353</v>
       </c>
       <c r="AV45" s="7">
         <v>296165</v>
@@ -7609,18 +8841,52 @@
         <v>242033</v>
       </c>
       <c r="AX45" s="4">
-        <f t="shared" si="38"/>
-        <v>28596</v>
+        <f t="shared" si="42"/>
+        <v>50207</v>
       </c>
       <c r="AY45" s="13">
-        <v>270629</v>
+        <v>292240</v>
       </c>
       <c r="AZ45" s="5">
-        <f t="shared" si="39"/>
-        <v>0.91377779278442761</v>
+        <f t="shared" si="43"/>
+        <v>0.98674725237620919</v>
+      </c>
+      <c r="BA45" s="7">
+        <v>300603</v>
+      </c>
+      <c r="BB45" s="6">
+        <v>239483</v>
+      </c>
+      <c r="BC45" s="4">
+        <f t="shared" si="44"/>
+        <v>54455</v>
+      </c>
+      <c r="BD45" s="13">
+        <v>293938</v>
+      </c>
+      <c r="BE45" s="5">
+        <f t="shared" si="45"/>
+        <v>0.97782789925582914</v>
+      </c>
+      <c r="BF45" s="7">
+        <v>359430</v>
+      </c>
+      <c r="BG45" s="6">
+        <v>273907</v>
+      </c>
+      <c r="BH45" s="4">
+        <f t="shared" si="46"/>
+        <v>66625</v>
+      </c>
+      <c r="BI45" s="13">
+        <v>340532</v>
+      </c>
+      <c r="BJ45" s="5">
+        <f t="shared" si="47"/>
+        <v>0.9474223075424979</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>38</v>
       </c>
@@ -7634,15 +8900,15 @@
         <v>1866</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="20"/>
-        <v>628</v>
+        <f t="shared" si="24"/>
+        <v>638</v>
       </c>
       <c r="F46" s="13">
-        <v>2494</v>
+        <v>2504</v>
       </c>
       <c r="G46" s="5">
-        <f t="shared" si="21"/>
-        <v>1.0263374485596708</v>
+        <f t="shared" si="25"/>
+        <v>1.0304526748971194</v>
       </c>
       <c r="H46" s="7">
         <v>2594</v>
@@ -7651,15 +8917,15 @@
         <v>1913</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="22"/>
-        <v>719</v>
+        <f t="shared" si="26"/>
+        <v>731</v>
       </c>
       <c r="K46" s="13">
-        <v>2632</v>
+        <v>2644</v>
       </c>
       <c r="L46" s="5">
-        <f t="shared" si="23"/>
-        <v>1.0146491904394757</v>
+        <f t="shared" si="27"/>
+        <v>1.0192752505782574</v>
       </c>
       <c r="M46" s="7">
         <v>8454</v>
@@ -7668,15 +8934,15 @@
         <v>6596</v>
       </c>
       <c r="O46" s="4">
-        <f t="shared" si="24"/>
-        <v>1931</v>
+        <f t="shared" si="28"/>
+        <v>1987</v>
       </c>
       <c r="P46" s="13">
-        <v>8527</v>
+        <v>8583</v>
       </c>
       <c r="Q46" s="5">
-        <f t="shared" si="25"/>
-        <v>1.0086349656967115</v>
+        <f t="shared" si="29"/>
+        <v>1.0152590489709012</v>
       </c>
       <c r="R46" s="7">
         <v>2484</v>
@@ -7685,15 +8951,15 @@
         <v>1814</v>
       </c>
       <c r="T46" s="4">
-        <f t="shared" si="26"/>
-        <v>754</v>
+        <f t="shared" si="30"/>
+        <v>777</v>
       </c>
       <c r="U46" s="13">
-        <v>2568</v>
+        <v>2591</v>
       </c>
       <c r="V46" s="5">
-        <f t="shared" si="27"/>
-        <v>1.0338164251207729</v>
+        <f t="shared" si="31"/>
+        <v>1.0430756843800322</v>
       </c>
       <c r="W46" s="7">
         <v>2748</v>
@@ -7702,15 +8968,15 @@
         <v>1922</v>
       </c>
       <c r="Y46" s="4">
-        <f t="shared" si="28"/>
-        <v>728</v>
+        <f t="shared" si="32"/>
+        <v>765</v>
       </c>
       <c r="Z46" s="13">
-        <v>2650</v>
+        <v>2687</v>
       </c>
       <c r="AA46" s="5">
-        <f t="shared" si="29"/>
-        <v>0.96433770014556042</v>
+        <f t="shared" si="33"/>
+        <v>0.97780203784570596</v>
       </c>
       <c r="AB46" s="7">
         <v>8770</v>
@@ -7719,15 +8985,15 @@
         <v>6743</v>
       </c>
       <c r="AD46" s="4">
-        <f t="shared" si="30"/>
-        <v>1897</v>
+        <f t="shared" si="34"/>
+        <v>2055</v>
       </c>
       <c r="AE46" s="13">
-        <v>8640</v>
+        <v>8798</v>
       </c>
       <c r="AF46" s="5">
-        <f t="shared" si="31"/>
-        <v>0.98517673888255419</v>
+        <f t="shared" si="35"/>
+        <v>1.0031927023945268</v>
       </c>
       <c r="AG46" s="7">
         <v>2523</v>
@@ -7736,15 +9002,15 @@
         <v>1887</v>
       </c>
       <c r="AI46" s="4">
-        <f t="shared" si="32"/>
-        <v>594</v>
+        <f t="shared" si="36"/>
+        <v>663</v>
       </c>
       <c r="AJ46" s="13">
-        <v>2481</v>
+        <v>2550</v>
       </c>
       <c r="AK46" s="5">
-        <f t="shared" si="33"/>
-        <v>0.98335315101070153</v>
+        <f t="shared" si="37"/>
+        <v>1.0107015457788346</v>
       </c>
       <c r="AL46" s="7">
         <v>2722</v>
@@ -7753,15 +9019,15 @@
         <v>1987</v>
       </c>
       <c r="AN46" s="4">
-        <f t="shared" si="34"/>
-        <v>577</v>
+        <f t="shared" si="38"/>
+        <v>685</v>
       </c>
       <c r="AO46" s="13">
-        <v>2564</v>
+        <v>2672</v>
       </c>
       <c r="AP46" s="5">
-        <f t="shared" si="35"/>
-        <v>0.9419544452608376</v>
+        <f t="shared" si="39"/>
+        <v>0.98163115356355624</v>
       </c>
       <c r="AQ46" s="7">
         <v>8967</v>
@@ -7770,15 +9036,15 @@
         <v>7230</v>
       </c>
       <c r="AS46" s="4">
-        <f t="shared" si="36"/>
-        <v>1084</v>
+        <f t="shared" si="40"/>
+        <v>1620</v>
       </c>
       <c r="AT46" s="13">
-        <v>8314</v>
+        <v>8850</v>
       </c>
       <c r="AU46" s="5">
-        <f t="shared" si="37"/>
-        <v>0.92717742834838857</v>
+        <f t="shared" si="41"/>
+        <v>0.98695215791234525</v>
       </c>
       <c r="AV46" s="7">
         <v>2626</v>
@@ -7787,18 +9053,52 @@
         <v>2130</v>
       </c>
       <c r="AX46" s="4">
-        <f t="shared" si="38"/>
-        <v>196</v>
+        <f t="shared" si="42"/>
+        <v>466</v>
       </c>
       <c r="AY46" s="13">
-        <v>2326</v>
+        <v>2596</v>
       </c>
       <c r="AZ46" s="5">
-        <f t="shared" si="39"/>
-        <v>0.88575780654988578</v>
+        <f t="shared" si="43"/>
+        <v>0.98857578065498852</v>
+      </c>
+      <c r="BA46" s="7">
+        <v>2791</v>
+      </c>
+      <c r="BB46" s="6">
+        <v>2165</v>
+      </c>
+      <c r="BC46" s="4">
+        <f t="shared" si="44"/>
+        <v>461</v>
+      </c>
+      <c r="BD46" s="13">
+        <v>2626</v>
+      </c>
+      <c r="BE46" s="5">
+        <f t="shared" si="45"/>
+        <v>0.94088140451451097</v>
+      </c>
+      <c r="BF46" s="7">
+        <v>9093</v>
+      </c>
+      <c r="BG46" s="6">
+        <v>7187</v>
+      </c>
+      <c r="BH46" s="4">
+        <f t="shared" si="46"/>
+        <v>1295</v>
+      </c>
+      <c r="BI46" s="13">
+        <v>8482</v>
+      </c>
+      <c r="BJ46" s="5">
+        <f t="shared" si="47"/>
+        <v>0.93280545474540855</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>97</v>
       </c>
@@ -7812,14 +9112,14 @@
         <v>81</v>
       </c>
       <c r="E47" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>23</v>
       </c>
       <c r="F47" s="13">
         <v>104</v>
       </c>
       <c r="G47" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.95412844036697253</v>
       </c>
       <c r="H47" s="7">
@@ -7829,14 +9129,14 @@
         <v>85</v>
       </c>
       <c r="J47" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>24</v>
       </c>
       <c r="K47" s="13">
         <v>109</v>
       </c>
       <c r="L47" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.1122448979591837</v>
       </c>
       <c r="M47" s="7">
@@ -7846,14 +9146,14 @@
         <v>94</v>
       </c>
       <c r="O47" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>21</v>
       </c>
       <c r="P47" s="13">
         <v>115</v>
       </c>
       <c r="Q47" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.93495934959349591</v>
       </c>
       <c r="R47" s="7">
@@ -7863,14 +9163,14 @@
         <v>78</v>
       </c>
       <c r="T47" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>6</v>
       </c>
       <c r="U47" s="13">
         <v>84</v>
       </c>
       <c r="V47" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.63157894736842102</v>
       </c>
       <c r="W47" s="7">
@@ -7880,14 +9180,14 @@
         <v>69</v>
       </c>
       <c r="Y47" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4</v>
       </c>
       <c r="Z47" s="13">
         <v>73</v>
       </c>
       <c r="AA47" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.85882352941176465</v>
       </c>
       <c r="AB47" s="7">
@@ -7897,14 +9197,14 @@
         <v>71</v>
       </c>
       <c r="AD47" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>5</v>
       </c>
       <c r="AE47" s="13">
         <v>76</v>
       </c>
       <c r="AF47" s="21">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0.91566265060240959</v>
       </c>
       <c r="AG47" s="7">
@@ -7914,14 +9214,14 @@
         <v>65</v>
       </c>
       <c r="AI47" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>7</v>
       </c>
       <c r="AJ47" s="13">
         <v>72</v>
       </c>
       <c r="AK47" s="21">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.94736842105263153</v>
       </c>
       <c r="AL47" s="7">
@@ -7931,14 +9231,14 @@
         <v>67</v>
       </c>
       <c r="AN47" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4</v>
       </c>
       <c r="AO47" s="13">
         <v>71</v>
       </c>
       <c r="AP47" s="21">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>0.93421052631578949</v>
       </c>
       <c r="AQ47" s="7">
@@ -7948,14 +9248,14 @@
         <v>70</v>
       </c>
       <c r="AS47" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>4</v>
       </c>
       <c r="AT47" s="13">
         <v>74</v>
       </c>
       <c r="AU47" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0.93670886075949367</v>
       </c>
       <c r="AV47" s="7">
@@ -7965,18 +9265,52 @@
         <v>67</v>
       </c>
       <c r="AX47" s="20">
-        <f t="shared" si="38"/>
-        <v>1</v>
+        <f t="shared" si="42"/>
+        <v>4</v>
       </c>
       <c r="AY47" s="13">
+        <v>71</v>
+      </c>
+      <c r="AZ47" s="21">
+        <f t="shared" si="43"/>
+        <v>0.94666666666666666</v>
+      </c>
+      <c r="BA47" s="7">
+        <v>76</v>
+      </c>
+      <c r="BB47" s="6">
+        <v>62</v>
+      </c>
+      <c r="BC47" s="20">
+        <f t="shared" si="44"/>
+        <v>5</v>
+      </c>
+      <c r="BD47" s="13">
+        <v>67</v>
+      </c>
+      <c r="BE47" s="21">
+        <f t="shared" si="45"/>
+        <v>0.88157894736842102</v>
+      </c>
+      <c r="BF47" s="7">
+        <v>72</v>
+      </c>
+      <c r="BG47" s="6">
         <v>68</v>
       </c>
-      <c r="AZ47" s="21">
-        <f t="shared" si="39"/>
-        <v>0.90666666666666662</v>
+      <c r="BH47" s="20">
+        <f t="shared" si="46"/>
+        <v>2</v>
+      </c>
+      <c r="BI47" s="13">
+        <v>70</v>
+      </c>
+      <c r="BJ47" s="21">
+        <f t="shared" si="47"/>
+        <v>0.97222222222222221</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
@@ -7990,16 +9324,16 @@
         <v>7002047</v>
       </c>
       <c r="E48" s="11">
-        <f t="shared" si="20"/>
-        <v>1577628</v>
+        <f t="shared" si="24"/>
+        <v>1587709</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8579675</v>
+        <v>8589756</v>
       </c>
       <c r="G48" s="12">
-        <f t="shared" si="21"/>
-        <v>0.99496595417602329</v>
+        <f t="shared" si="25"/>
+        <v>0.99613502547348487</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -8010,16 +9344,16 @@
         <v>7149246</v>
       </c>
       <c r="J48" s="11">
-        <f t="shared" si="22"/>
-        <v>1535953</v>
+        <f t="shared" si="26"/>
+        <v>1548869</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8685199</v>
+        <v>8698115</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="23"/>
-        <v>0.98997847857757315</v>
+        <f t="shared" si="27"/>
+        <v>0.99145070299399796</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -8030,16 +9364,16 @@
         <v>10769597</v>
       </c>
       <c r="O48" s="11">
-        <f t="shared" si="24"/>
-        <v>2488860</v>
+        <f t="shared" si="28"/>
+        <v>2516724</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>13258457</v>
+        <v>13286321</v>
       </c>
       <c r="Q48" s="12">
-        <f t="shared" si="25"/>
-        <v>0.99273452394973727</v>
+        <f t="shared" si="29"/>
+        <v>0.9948208568295992</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -8050,16 +9384,16 @@
         <v>7178201</v>
       </c>
       <c r="T48" s="11">
-        <f t="shared" si="26"/>
-        <v>1529760</v>
+        <f t="shared" si="30"/>
+        <v>1553819</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8707961</v>
+        <v>8732020</v>
       </c>
       <c r="V48" s="12">
-        <f t="shared" si="27"/>
-        <v>0.9928533167811433</v>
+        <f t="shared" si="31"/>
+        <v>0.99559644550535753</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -8070,16 +9404,16 @@
         <v>7255973</v>
       </c>
       <c r="Y48" s="11">
-        <f t="shared" si="28"/>
-        <v>1525723</v>
+        <f t="shared" si="32"/>
+        <v>1564457</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8781696</v>
+        <v>8820430</v>
       </c>
       <c r="AA48" s="12">
-        <f t="shared" si="29"/>
-        <v>0.9831093459857535</v>
+        <f t="shared" si="33"/>
+        <v>0.98744561057603453</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -8090,16 +9424,16 @@
         <v>11136723</v>
       </c>
       <c r="AD48" s="11">
-        <f t="shared" si="30"/>
-        <v>2259826</v>
+        <f t="shared" si="34"/>
+        <v>2359452</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>13396549</v>
+        <v>13496175</v>
       </c>
       <c r="AF48" s="12">
-        <f t="shared" si="31"/>
-        <v>0.98447501839017448</v>
+        <f t="shared" si="35"/>
+        <v>0.9917962552387195</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -8110,16 +9444,16 @@
         <v>7284859</v>
       </c>
       <c r="AI48" s="11">
-        <f t="shared" si="32"/>
-        <v>1481857</v>
+        <f t="shared" si="36"/>
+        <v>1572341</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8766716</v>
+        <v>8857200</v>
       </c>
       <c r="AK48" s="12">
-        <f t="shared" si="33"/>
-        <v>0.98313488325357645</v>
+        <f t="shared" si="37"/>
+        <v>0.99328212388237258</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -8130,16 +9464,16 @@
         <v>7623880</v>
       </c>
       <c r="AN48" s="11">
-        <f t="shared" si="34"/>
-        <v>1345050</v>
+        <f t="shared" si="38"/>
+        <v>1482647</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>8968930</v>
+        <v>9106527</v>
       </c>
       <c r="AP48" s="12">
-        <f t="shared" si="35"/>
-        <v>0.98264229744416787</v>
+        <f t="shared" si="39"/>
+        <v>0.99771752182449247</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -8150,16 +9484,16 @@
         <v>11641061</v>
       </c>
       <c r="AS48" s="11">
-        <f t="shared" si="36"/>
-        <v>1836782</v>
+        <f t="shared" si="40"/>
+        <v>2247457</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>13477843</v>
+        <v>13888518</v>
       </c>
       <c r="AU48" s="12">
-        <f t="shared" si="37"/>
-        <v>0.96427863383921941</v>
+        <f t="shared" si="41"/>
+        <v>0.99366057039627254</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -8170,16 +9504,56 @@
         <v>7799062</v>
       </c>
       <c r="AX48" s="11">
-        <f t="shared" si="38"/>
-        <v>760815</v>
+        <f t="shared" si="42"/>
+        <v>1380167</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>8559877</v>
+        <v>9179229</v>
       </c>
       <c r="AZ48" s="12">
-        <f t="shared" si="39"/>
-        <v>0.92533588770066078</v>
+        <f t="shared" si="43"/>
+        <v>0.99228879283226257</v>
+      </c>
+      <c r="BA48" s="9">
+        <f>SUM(BA10:BA47)</f>
+        <v>9470705</v>
+      </c>
+      <c r="BB48" s="9">
+        <f>SUM(BB10:BB47)</f>
+        <v>7891202</v>
+      </c>
+      <c r="BC48" s="11">
+        <f t="shared" si="44"/>
+        <v>1389411</v>
+      </c>
+      <c r="BD48" s="10">
+        <f>SUM(BD10:BD47)</f>
+        <v>9280613</v>
+      </c>
+      <c r="BE48" s="12">
+        <f t="shared" si="45"/>
+        <v>0.97992842137940106</v>
+      </c>
+      <c r="BF48" s="9">
+        <f>SUM(BF10:BF47)</f>
+        <v>14430593</v>
+      </c>
+      <c r="BG48" s="9">
+        <f>SUM(BG10:BG47)</f>
+        <v>11404971</v>
+      </c>
+      <c r="BH48" s="11">
+        <f t="shared" si="46"/>
+        <v>2320264</v>
+      </c>
+      <c r="BI48" s="10">
+        <f>SUM(BI10:BI47)</f>
+        <v>13725235</v>
+      </c>
+      <c r="BJ48" s="12">
+        <f t="shared" si="47"/>
+        <v>0.95112065041263372</v>
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.3">
@@ -8445,12 +9819,14 @@
       <c r="AF59" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>

--- a/gstdatabase/GSTR-3B-2025-2026.xlsx
+++ b/gstdatabase/GSTR-3B-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A29D22F-EE48-45D6-8E73-9ABA72EDCFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C73E93-B0A7-4236-A837-1B5BFFCDECB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -415,9 +415,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,6 +432,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -829,10 +829,10 @@
       <c r="AF2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="23"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1003,100 +1003,100 @@
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>45748</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="24">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23">
         <v>45778</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="24">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23">
         <v>45809</v>
       </c>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="24">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="23">
         <v>45839</v>
       </c>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="24">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="23">
         <v>45870</v>
       </c>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="24">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="23">
         <v>45901</v>
       </c>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-      <c r="AE8" s="25"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="24">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="23">
         <v>45931</v>
       </c>
-      <c r="AH8" s="25"/>
-      <c r="AI8" s="25"/>
-      <c r="AJ8" s="25"/>
-      <c r="AK8" s="26"/>
-      <c r="AL8" s="24">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="23">
         <v>45962</v>
       </c>
-      <c r="AM8" s="25"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="25"/>
-      <c r="AP8" s="26"/>
-      <c r="AQ8" s="24">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="23">
         <v>45992</v>
       </c>
-      <c r="AR8" s="25"/>
-      <c r="AS8" s="25"/>
-      <c r="AT8" s="25"/>
-      <c r="AU8" s="26"/>
-      <c r="AV8" s="24">
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="23">
         <v>46023</v>
       </c>
-      <c r="AW8" s="25"/>
-      <c r="AX8" s="25"/>
-      <c r="AY8" s="25"/>
-      <c r="AZ8" s="26"/>
-      <c r="BA8" s="24">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="23">
         <v>46054</v>
       </c>
-      <c r="BB8" s="25"/>
-      <c r="BC8" s="25"/>
-      <c r="BD8" s="25"/>
-      <c r="BE8" s="26"/>
-      <c r="BF8" s="24">
+      <c r="BB8" s="24"/>
+      <c r="BC8" s="24"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="23">
         <v>46082</v>
       </c>
-      <c r="BG8" s="25"/>
-      <c r="BH8" s="25"/>
-      <c r="BI8" s="25"/>
-      <c r="BJ8" s="26"/>
+      <c r="BG8" s="24"/>
+      <c r="BH8" s="24"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="25"/>
     </row>
     <row r="9" spans="1:62" s="15" customFormat="1" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1293,14 +1293,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15039</v>
+        <v>15056</v>
       </c>
       <c r="F10" s="13">
-        <v>74271</v>
+        <v>74288</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0011052851500897</v>
+        <v>1.0013344296324254</v>
       </c>
       <c r="H10" s="7">
         <v>75899</v>
@@ -1310,14 +1310,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>14887</v>
+        <v>14909</v>
       </c>
       <c r="K10" s="13">
-        <v>74971</v>
+        <v>74993</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.98777322494367514</v>
+        <v>0.98806308383509667</v>
       </c>
       <c r="M10" s="7">
         <v>134494</v>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>26203</v>
+        <v>26248</v>
       </c>
       <c r="P10" s="13">
-        <v>134039</v>
+        <v>134084</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99661694945499424</v>
+        <v>0.99695153687153326</v>
       </c>
       <c r="R10" s="7">
         <v>73914</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>13907</v>
+        <v>13933</v>
       </c>
       <c r="U10" s="13">
-        <v>73763</v>
+        <v>73789</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>0.9979570852612496</v>
+        <v>0.99830884541494169</v>
       </c>
       <c r="W10" s="7">
         <v>75592</v>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>13978</v>
+        <v>14015</v>
       </c>
       <c r="Z10" s="13">
-        <v>74661</v>
+        <v>74698</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.98768388189226375</v>
+        <v>0.98817335167742615</v>
       </c>
       <c r="AB10" s="7">
         <v>136558</v>
@@ -1378,14 +1378,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>23953</v>
+        <v>24066</v>
       </c>
       <c r="AE10" s="13">
-        <v>135805</v>
+        <v>135918</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99448585948827606</v>
+        <v>0.99531334670982297</v>
       </c>
       <c r="AG10" s="7">
         <v>73704</v>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>13974</v>
+        <v>14073</v>
       </c>
       <c r="AJ10" s="13">
-        <v>73386</v>
+        <v>73485</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99568544448062524</v>
+        <v>0.99702865516118533</v>
       </c>
       <c r="AL10" s="7">
         <v>75897</v>
@@ -1412,14 +1412,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>12714</v>
+        <v>12852</v>
       </c>
       <c r="AO10" s="13">
-        <v>75909</v>
+        <v>76047</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>1.0001581090161666</v>
+        <v>1.001976362702083</v>
       </c>
       <c r="AQ10" s="7">
         <v>140117</v>
@@ -1429,14 +1429,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>24516</v>
+        <v>24949</v>
       </c>
       <c r="AT10" s="13">
-        <v>139474</v>
+        <v>139907</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.99541097796841216</v>
+        <v>0.99850125252467581</v>
       </c>
       <c r="AV10" s="7">
         <v>75508</v>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>13069</v>
+        <v>13359</v>
       </c>
       <c r="AY10" s="13">
-        <v>75465</v>
+        <v>75755</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.99943052391799547</v>
+        <v>1.0032711765640727</v>
       </c>
       <c r="BA10" s="7">
         <v>78056</v>
@@ -1463,14 +1463,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>12641</v>
+        <v>13164</v>
       </c>
       <c r="BD10" s="13">
-        <v>76637</v>
+        <v>77160</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.98182074408117248</v>
+        <v>0.98852106180178334</v>
       </c>
       <c r="BF10" s="7">
         <v>144885</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>28182</v>
-      </c>
-      <c r="BI10" s="13">
-        <v>138224</v>
+        <v>30304</v>
+      </c>
+      <c r="BI10" s="6">
+        <v>140346</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.95402560651551227</v>
+        <v>0.96867170514546019</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8620</v>
+        <v>8641</v>
       </c>
       <c r="F11" s="13">
-        <v>47766</v>
+        <v>47787</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99855754154907495</v>
+        <v>0.99899655064283477</v>
       </c>
       <c r="H11" s="7">
         <v>49123</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8289</v>
+        <v>8317</v>
       </c>
       <c r="K11" s="13">
-        <v>48275</v>
+        <v>48303</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98273721067524378</v>
+        <v>0.98330720843596686</v>
       </c>
       <c r="M11" s="7">
         <v>111861</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>18957</v>
+        <v>19012</v>
       </c>
       <c r="P11" s="13">
-        <v>111146</v>
+        <v>111201</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99360813867210196</v>
+        <v>0.99409982031270949</v>
       </c>
       <c r="R11" s="7">
         <v>47958</v>
@@ -1556,14 +1556,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8063</v>
+        <v>8102</v>
       </c>
       <c r="U11" s="13">
-        <v>47657</v>
+        <v>47696</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.9937236748821886</v>
+        <v>0.99453688644230365</v>
       </c>
       <c r="W11" s="7">
         <v>49731</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8077</v>
+        <v>8118</v>
       </c>
       <c r="Z11" s="13">
-        <v>48279</v>
+        <v>48320</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97080291970802923</v>
+        <v>0.971627355170819</v>
       </c>
       <c r="AB11" s="7">
         <v>113134</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>19452</v>
+        <v>19550</v>
       </c>
       <c r="AE11" s="13">
-        <v>111832</v>
+        <v>111930</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.98849152332632095</v>
+        <v>0.98935775275337212</v>
       </c>
       <c r="AG11" s="7">
         <v>48119</v>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>7798</v>
+        <v>7865</v>
       </c>
       <c r="AJ11" s="13">
-        <v>47670</v>
+        <v>47737</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99066896652050129</v>
+        <v>0.99206134790831069</v>
       </c>
       <c r="AL11" s="7">
         <v>49938</v>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7247</v>
+        <v>7342</v>
       </c>
       <c r="AO11" s="13">
-        <v>48933</v>
+        <v>49028</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97987504505586931</v>
+        <v>0.98177740398093638</v>
       </c>
       <c r="AQ11" s="7">
         <v>114343</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15431</v>
+        <v>15769</v>
       </c>
       <c r="AT11" s="13">
-        <v>113170</v>
+        <v>113508</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.98974139212719625</v>
+        <v>0.99269741042302551</v>
       </c>
       <c r="AV11" s="7">
         <v>49251</v>
@@ -1658,14 +1658,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>6712</v>
+        <v>6911</v>
       </c>
       <c r="AY11" s="13">
-        <v>48475</v>
+        <v>48674</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.98424397474162961</v>
+        <v>0.98828450183752614</v>
       </c>
       <c r="BA11" s="7">
         <v>50523</v>
@@ -1675,14 +1675,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>6791</v>
+        <v>7099</v>
       </c>
       <c r="BD11" s="13">
-        <v>48990</v>
+        <v>49298</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.96965738376580968</v>
+        <v>0.97575361716445974</v>
       </c>
       <c r="BF11" s="7">
         <v>116408</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>15349</v>
-      </c>
-      <c r="BI11" s="13">
-        <v>110806</v>
+        <v>16923</v>
+      </c>
+      <c r="BI11" s="6">
+        <v>112380</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.95187615971410899</v>
+        <v>0.96539756717751357</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>29233</v>
+        <v>29263</v>
       </c>
       <c r="F12" s="13">
-        <v>182206</v>
+        <v>182236</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.9970341672685884</v>
+        <v>0.99719832775187689</v>
       </c>
       <c r="H12" s="7">
         <v>186824</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>26505</v>
+        <v>26548</v>
       </c>
       <c r="K12" s="13">
-        <v>184620</v>
+        <v>184663</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98820280049672415</v>
+        <v>0.98843296364492783</v>
       </c>
       <c r="M12" s="7">
         <v>372375</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>60867</v>
+        <v>61002</v>
       </c>
       <c r="P12" s="13">
-        <v>370481</v>
+        <v>370616</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99491372943940914</v>
+        <v>0.99527626720375961</v>
       </c>
       <c r="R12" s="7">
         <v>184659</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>28266</v>
+        <v>28321</v>
       </c>
       <c r="U12" s="13">
-        <v>183610</v>
+        <v>183665</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99431925874178895</v>
+        <v>0.99461710504226708</v>
       </c>
       <c r="W12" s="7">
         <v>189081</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>29666</v>
+        <v>29732</v>
       </c>
       <c r="Z12" s="13">
-        <v>185583</v>
+        <v>185649</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98149999206689198</v>
+        <v>0.98184904882034685</v>
       </c>
       <c r="AB12" s="7">
         <v>377441</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>65087</v>
+        <v>65371</v>
       </c>
       <c r="AE12" s="13">
-        <v>373708</v>
+        <v>373992</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99010971251135937</v>
+        <v>0.99086214799134165</v>
       </c>
       <c r="AG12" s="7">
         <v>186148</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>28288</v>
+        <v>28490</v>
       </c>
       <c r="AJ12" s="13">
-        <v>184729</v>
+        <v>184931</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99237703332831939</v>
+        <v>0.99346219137460512</v>
       </c>
       <c r="AL12" s="7">
         <v>192239</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>26389</v>
+        <v>26709</v>
       </c>
       <c r="AO12" s="13">
-        <v>190642</v>
+        <v>190962</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.99169263260836771</v>
+        <v>0.99335722720155639</v>
       </c>
       <c r="AQ12" s="7">
         <v>384779</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>59044</v>
+        <v>60418</v>
       </c>
       <c r="AT12" s="13">
-        <v>381246</v>
+        <v>382620</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99081810597771713</v>
+        <v>0.99438898692496214</v>
       </c>
       <c r="AV12" s="7">
         <v>191743</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>24565</v>
+        <v>25266</v>
       </c>
       <c r="AY12" s="13">
-        <v>190070</v>
+        <v>190771</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99127477926182439</v>
+        <v>0.99493071455020521</v>
       </c>
       <c r="BA12" s="7">
         <v>197493</v>
@@ -1887,14 +1887,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>25301</v>
+        <v>26346</v>
       </c>
       <c r="BD12" s="13">
-        <v>192608</v>
+        <v>193653</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.97526494609935543</v>
+        <v>0.9805562728805578</v>
       </c>
       <c r="BF12" s="7">
         <v>393305</v>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>59818</v>
-      </c>
-      <c r="BI12" s="13">
-        <v>375797</v>
+        <v>65901</v>
+      </c>
+      <c r="BI12" s="6">
+        <v>381880</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.95548492899912285</v>
+        <v>0.97095129733921515</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1929,14 +1929,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="F13" s="13">
-        <v>18066</v>
+        <v>18068</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.0017188799556418</v>
+        <v>1.001829775436651</v>
       </c>
       <c r="H13" s="7">
         <v>18257</v>
@@ -1946,14 +1946,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="K13" s="13">
-        <v>18098</v>
+        <v>18099</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>0.99129101166675793</v>
+        <v>0.99134578517828775</v>
       </c>
       <c r="M13" s="7">
         <v>29011</v>
@@ -1963,14 +1963,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>4996</v>
+        <v>5001</v>
       </c>
       <c r="P13" s="13">
-        <v>28990</v>
+        <v>28995</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99927613663782699</v>
+        <v>0.99944848505739203</v>
       </c>
       <c r="R13" s="7">
         <v>18140</v>
@@ -1980,14 +1980,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2793</v>
+        <v>2796</v>
       </c>
       <c r="U13" s="13">
-        <v>18160</v>
+        <v>18163</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>1.0011025358324146</v>
+        <v>1.0012679162072768</v>
       </c>
       <c r="W13" s="7">
         <v>18401</v>
@@ -1997,14 +1997,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2801</v>
+        <v>2807</v>
       </c>
       <c r="Z13" s="13">
-        <v>18232</v>
+        <v>18238</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.99081571653714473</v>
+        <v>0.99114178577251233</v>
       </c>
       <c r="AB13" s="7">
         <v>29242</v>
@@ -2014,14 +2014,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4797</v>
+        <v>4822</v>
       </c>
       <c r="AE13" s="13">
-        <v>29160</v>
+        <v>29185</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.99719581423979209</v>
+        <v>0.99805074892278234</v>
       </c>
       <c r="AG13" s="7">
         <v>18261</v>
@@ -2031,14 +2031,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2679</v>
+        <v>2705</v>
       </c>
       <c r="AJ13" s="13">
-        <v>18386</v>
+        <v>18412</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>1.0068451892010295</v>
+        <v>1.0082689885548437</v>
       </c>
       <c r="AL13" s="7">
         <v>18637</v>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2518</v>
+        <v>2558</v>
       </c>
       <c r="AO13" s="13">
-        <v>18680</v>
+        <v>18720</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>1.0023072382894243</v>
+        <v>1.0044535064656328</v>
       </c>
       <c r="AQ13" s="7">
         <v>29668</v>
@@ -2065,14 +2065,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4151</v>
+        <v>4256</v>
       </c>
       <c r="AT13" s="13">
-        <v>29627</v>
+        <v>29732</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>0.99861803963866791</v>
+        <v>1.0021572064176891</v>
       </c>
       <c r="AV13" s="7">
         <v>18676</v>
@@ -2082,14 +2082,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2381</v>
+        <v>2459</v>
       </c>
       <c r="AY13" s="13">
-        <v>18752</v>
+        <v>18830</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.0040693938744913</v>
+        <v>1.0082458770614693</v>
       </c>
       <c r="BA13" s="7">
         <v>19025</v>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2337</v>
+        <v>2450</v>
       </c>
       <c r="BD13" s="13">
-        <v>18924</v>
+        <v>19037</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>0.99469119579500653</v>
+        <v>1.0006307490144546</v>
       </c>
       <c r="BF13" s="7">
         <v>30254</v>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>3992</v>
-      </c>
-      <c r="BI13" s="13">
-        <v>29117</v>
+        <v>4446</v>
+      </c>
+      <c r="BI13" s="6">
+        <v>29571</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>0.96241819263568451</v>
+        <v>0.97742447279698552</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>19304</v>
+        <v>19331</v>
       </c>
       <c r="F14" s="13">
-        <v>95452</v>
+        <v>95479</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>1.0088677031697546</v>
+        <v>1.0091530762157421</v>
       </c>
       <c r="H14" s="7">
         <v>97351</v>
@@ -2158,14 +2158,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18839</v>
+        <v>18870</v>
       </c>
       <c r="K14" s="13">
-        <v>97265</v>
+        <v>97296</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.99911659869955116</v>
+        <v>0.99943503405203848</v>
       </c>
       <c r="M14" s="7">
         <v>172809</v>
@@ -2175,14 +2175,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>35633</v>
+        <v>35713</v>
       </c>
       <c r="P14" s="13">
-        <v>172396</v>
+        <v>172476</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99761007817879854</v>
+        <v>0.998073017030363</v>
       </c>
       <c r="R14" s="7">
         <v>97326</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>17897</v>
+        <v>17942</v>
       </c>
       <c r="U14" s="13">
-        <v>96750</v>
+        <v>96795</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.9940817458849639</v>
+        <v>0.99454410948770111</v>
       </c>
       <c r="W14" s="7">
         <v>98912</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17588</v>
+        <v>17656</v>
       </c>
       <c r="Z14" s="13">
-        <v>97867</v>
+        <v>97935</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98943505338078297</v>
+        <v>0.99012253316078935</v>
       </c>
       <c r="AB14" s="7">
         <v>175426</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34187</v>
+        <v>34367</v>
       </c>
       <c r="AE14" s="13">
-        <v>174895</v>
+        <v>175075</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.99697308266733553</v>
+        <v>0.99799915633942515</v>
       </c>
       <c r="AG14" s="7">
         <v>98057</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>18400</v>
+        <v>18542</v>
       </c>
       <c r="AJ14" s="13">
-        <v>97998</v>
+        <v>98140</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99939830914672079</v>
+        <v>1.0008464464546132</v>
       </c>
       <c r="AL14" s="7">
         <v>101581</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17527</v>
+        <v>17736</v>
       </c>
       <c r="AO14" s="13">
-        <v>102206</v>
+        <v>102415</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>1.0061527254112481</v>
+        <v>1.0082101967887696</v>
       </c>
       <c r="AQ14" s="7">
         <v>182247</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>30198</v>
+        <v>30921</v>
       </c>
       <c r="AT14" s="13">
-        <v>181092</v>
+        <v>181815</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99366244711847107</v>
+        <v>0.99762959061054501</v>
       </c>
       <c r="AV14" s="7">
         <v>102257</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>16876</v>
+        <v>17283</v>
       </c>
       <c r="AY14" s="13">
-        <v>102384</v>
+        <v>102791</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.0012419687649745</v>
+        <v>1.0052221363818614</v>
       </c>
       <c r="BA14" s="7">
         <v>106311</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16480</v>
+        <v>17132</v>
       </c>
       <c r="BD14" s="13">
-        <v>104390</v>
+        <v>105042</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98193037409111006</v>
+        <v>0.988063323644778</v>
       </c>
       <c r="BF14" s="7">
         <v>189210</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>32443</v>
-      </c>
-      <c r="BI14" s="13">
-        <v>180082</v>
+        <v>35521</v>
+      </c>
+      <c r="BI14" s="6">
+        <v>183160</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.95175730669626346</v>
+        <v>0.96802494582738752</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>55159</v>
+        <v>55193</v>
       </c>
       <c r="F15" s="13">
-        <v>324332</v>
+        <v>324366</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99857141097796775</v>
+        <v>0.99867609207009933</v>
       </c>
       <c r="H15" s="7">
         <v>331968</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>52142</v>
+        <v>52179</v>
       </c>
       <c r="K15" s="13">
-        <v>329505</v>
+        <v>329542</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.99258061017929444</v>
+        <v>0.99269206670522459</v>
       </c>
       <c r="M15" s="7">
         <v>549212</v>
@@ -2387,14 +2387,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>93275</v>
+        <v>93368</v>
       </c>
       <c r="P15" s="13">
-        <v>547211</v>
+        <v>547304</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99635659818066613</v>
+        <v>0.99652593169850623</v>
       </c>
       <c r="R15" s="7">
         <v>333160</v>
@@ -2404,14 +2404,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>53827</v>
+        <v>53902</v>
       </c>
       <c r="U15" s="13">
-        <v>332159</v>
+        <v>332234</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99699543762756637</v>
+        <v>0.99722055468843795</v>
       </c>
       <c r="W15" s="7">
         <v>340519</v>
@@ -2421,14 +2421,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>54730</v>
+        <v>54844</v>
       </c>
       <c r="Z15" s="13">
-        <v>336625</v>
+        <v>336739</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98856451475541751</v>
+        <v>0.98889929783653774</v>
       </c>
       <c r="AB15" s="7">
         <v>562036</v>
@@ -2438,14 +2438,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>94528</v>
+        <v>94806</v>
       </c>
       <c r="AE15" s="13">
-        <v>557942</v>
+        <v>558220</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.9927157690966415</v>
+        <v>0.99321039933385047</v>
       </c>
       <c r="AG15" s="7">
         <v>340264</v>
@@ -2455,14 +2455,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>55615</v>
+        <v>55946</v>
       </c>
       <c r="AJ15" s="13">
-        <v>338749</v>
+        <v>339080</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99554757482425416</v>
+        <v>0.99652034890555563</v>
       </c>
       <c r="AL15" s="7">
         <v>350627</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>53720</v>
+        <v>54226</v>
       </c>
       <c r="AO15" s="13">
-        <v>351603</v>
+        <v>352109</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>1.0027835848351667</v>
+        <v>1.0042267138583167</v>
       </c>
       <c r="AQ15" s="7">
         <v>580651</v>
@@ -2489,14 +2489,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>80350</v>
+        <v>82155</v>
       </c>
       <c r="AT15" s="13">
-        <v>578275</v>
+        <v>580080</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99590804114691955</v>
+        <v>0.99901662099953326</v>
       </c>
       <c r="AV15" s="7">
         <v>355536</v>
@@ -2506,14 +2506,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>49375</v>
+        <v>50646</v>
       </c>
       <c r="AY15" s="13">
-        <v>354395</v>
+        <v>355666</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.9967907609918546</v>
+        <v>1.000365645110481</v>
       </c>
       <c r="BA15" s="7">
         <v>365201</v>
@@ -2523,14 +2523,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>48638</v>
+        <v>50693</v>
       </c>
       <c r="BD15" s="13">
-        <v>359620</v>
+        <v>361675</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98471800460568293</v>
+        <v>0.9903450428668048</v>
       </c>
       <c r="BF15" s="7">
         <v>600313</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>85276</v>
-      </c>
-      <c r="BI15" s="13">
-        <v>576312</v>
+        <v>94013</v>
+      </c>
+      <c r="BI15" s="6">
+        <v>585049</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.96001918998922231</v>
+        <v>0.97457326428046698</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>76969</v>
+        <v>77078</v>
       </c>
       <c r="F16" s="13">
-        <v>451708</v>
+        <v>451817</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99600897869544314</v>
+        <v>0.99624932196737503</v>
       </c>
       <c r="H16" s="7">
         <v>461360</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74690</v>
+        <v>74818</v>
       </c>
       <c r="K16" s="13">
-        <v>458509</v>
+        <v>458637</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.99382044390497659</v>
+        <v>0.99409788451534598</v>
       </c>
       <c r="M16" s="7">
         <v>788355</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>133994</v>
+        <v>134286</v>
       </c>
       <c r="P16" s="13">
-        <v>786993</v>
+        <v>787285</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99827235192267438</v>
+        <v>0.99864274343411286</v>
       </c>
       <c r="R16" s="7">
         <v>462019</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>77940</v>
+        <v>78129</v>
       </c>
       <c r="U16" s="13">
-        <v>462088</v>
+        <v>462277</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>1.0001493445074769</v>
+        <v>1.0005584185931748</v>
       </c>
       <c r="W16" s="7">
         <v>472236</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>78556</v>
+        <v>78798</v>
       </c>
       <c r="Z16" s="13">
-        <v>466635</v>
+        <v>466877</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98813940487383423</v>
+        <v>0.98865186051042275</v>
       </c>
       <c r="AB16" s="7">
         <v>804216</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>132851</v>
+        <v>133425</v>
       </c>
       <c r="AE16" s="13">
-        <v>798912</v>
+        <v>799486</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.99340475693097374</v>
+        <v>0.99411849552856446</v>
       </c>
       <c r="AG16" s="7">
         <v>471201</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>78259</v>
+        <v>78815</v>
       </c>
       <c r="AJ16" s="13">
-        <v>468648</v>
+        <v>469204</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.99458193000439299</v>
+        <v>0.9957618935443685</v>
       </c>
       <c r="AL16" s="7">
         <v>484445</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>77739</v>
+        <v>78562</v>
       </c>
       <c r="AO16" s="13">
-        <v>487883</v>
+        <v>488706</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>1.0070967808523155</v>
+        <v>1.0087956321151008</v>
       </c>
       <c r="AQ16" s="7">
         <v>831010</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>125606</v>
+        <v>128272</v>
       </c>
       <c r="AT16" s="13">
-        <v>827788</v>
+        <v>830454</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99612279033946638</v>
+        <v>0.99933093464579248</v>
       </c>
       <c r="AV16" s="7">
         <v>496237</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>70572</v>
+        <v>72491</v>
       </c>
       <c r="AY16" s="13">
-        <v>493440</v>
+        <v>495359</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.9943635803053783</v>
+        <v>0.99823068412875304</v>
       </c>
       <c r="BA16" s="7">
         <v>510690</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70040</v>
+        <v>73189</v>
       </c>
       <c r="BD16" s="13">
-        <v>499941</v>
+        <v>503090</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.97895200610938138</v>
+        <v>0.98511817345160468</v>
       </c>
       <c r="BF16" s="7">
         <v>859721</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>114704</v>
-      </c>
-      <c r="BI16" s="13">
-        <v>824397</v>
+        <v>126756</v>
+      </c>
+      <c r="BI16" s="6">
+        <v>836449</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.95891225176539829</v>
+        <v>0.97293075311641797</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>58522</v>
+        <v>58591</v>
       </c>
       <c r="F17" s="13">
-        <v>341290</v>
+        <v>341359</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99716881075442865</v>
+        <v>0.99737041246541358</v>
       </c>
       <c r="H17" s="7">
         <v>352243</v>
@@ -2794,14 +2794,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>55045</v>
+        <v>55135</v>
       </c>
       <c r="K17" s="13">
-        <v>348264</v>
+        <v>348354</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98870382094179299</v>
+        <v>0.98895932637412243</v>
       </c>
       <c r="M17" s="7">
         <v>765449</v>
@@ -2811,14 +2811,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>132854</v>
+        <v>133172</v>
       </c>
       <c r="P17" s="13">
-        <v>763608</v>
+        <v>763926</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99759487568734173</v>
+        <v>0.9980103181270078</v>
       </c>
       <c r="R17" s="7">
         <v>346814</v>
@@ -2828,14 +2828,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>56808</v>
+        <v>56943</v>
       </c>
       <c r="U17" s="13">
-        <v>348275</v>
+        <v>348410</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0042126327080221</v>
+        <v>1.0046018903504472</v>
       </c>
       <c r="W17" s="7">
         <v>360071</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>59078</v>
+        <v>59275</v>
       </c>
       <c r="Z17" s="13">
-        <v>356283</v>
+        <v>356480</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.98947985258462912</v>
+        <v>0.99002696690374958</v>
       </c>
       <c r="AB17" s="7">
         <v>784641</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>144607</v>
+        <v>145315</v>
       </c>
       <c r="AE17" s="13">
-        <v>781485</v>
+        <v>782193</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99597777837252965</v>
+        <v>0.99688010185549825</v>
       </c>
       <c r="AG17" s="7">
         <v>355351</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59545</v>
+        <v>59962</v>
       </c>
       <c r="AJ17" s="13">
-        <v>356112</v>
+        <v>356529</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>1.0021415445573532</v>
+        <v>1.0033150321794508</v>
       </c>
       <c r="AL17" s="7">
         <v>371770</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>54691</v>
+        <v>55316</v>
       </c>
       <c r="AO17" s="13">
-        <v>371648</v>
+        <v>372273</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.99967184011620092</v>
+        <v>1.0013529870618931</v>
       </c>
       <c r="AQ17" s="7">
         <v>810773</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>120145</v>
+        <v>122907</v>
       </c>
       <c r="AT17" s="13">
-        <v>806800</v>
+        <v>809562</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.9950997381511224</v>
+        <v>0.99850636368009293</v>
       </c>
       <c r="AV17" s="7">
         <v>369648</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>52395</v>
+        <v>53609</v>
       </c>
       <c r="AY17" s="13">
-        <v>369826</v>
+        <v>371040</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.000481539194044</v>
+        <v>1.0037657447084793</v>
       </c>
       <c r="BA17" s="7">
         <v>385393</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>52551</v>
+        <v>54518</v>
       </c>
       <c r="BD17" s="13">
-        <v>379500</v>
+        <v>381467</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.9847091151110684</v>
+        <v>0.98981299608451634</v>
       </c>
       <c r="BF17" s="7">
         <v>839843</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>126996</v>
-      </c>
-      <c r="BI17" s="13">
-        <v>802428</v>
+        <v>139318</v>
+      </c>
+      <c r="BI17" s="6">
+        <v>814750</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.95545000672744784</v>
+        <v>0.97012179657388342</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2989,14 +2989,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>190217</v>
+        <v>190466</v>
       </c>
       <c r="F18" s="13">
-        <v>1063753</v>
+        <v>1064002</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99336698865206896</v>
+        <v>0.99359951291303406</v>
       </c>
       <c r="H18" s="7">
         <v>1089051</v>
@@ -3006,14 +3006,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>194743</v>
+        <v>195052</v>
       </c>
       <c r="K18" s="13">
-        <v>1079301</v>
+        <v>1079610</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.99104725123065862</v>
+        <v>0.99133098449934853</v>
       </c>
       <c r="M18" s="7">
         <v>1637429</v>
@@ -3023,14 +3023,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>299299</v>
+        <v>299903</v>
       </c>
       <c r="P18" s="13">
-        <v>1623336</v>
+        <v>1623940</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99139321460655694</v>
+        <v>0.99176208556218315</v>
       </c>
       <c r="R18" s="7">
         <v>1090030</v>
@@ -3040,14 +3040,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>190052</v>
+        <v>190536</v>
       </c>
       <c r="U18" s="13">
-        <v>1078778</v>
+        <v>1079262</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.98967734832986243</v>
+        <v>0.99012137280625301</v>
       </c>
       <c r="W18" s="7">
         <v>1107435</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>192684</v>
+        <v>193320</v>
       </c>
       <c r="Z18" s="13">
-        <v>1088946</v>
+        <v>1089582</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98330466347912071</v>
+        <v>0.9838789635509082</v>
       </c>
       <c r="AB18" s="7">
         <v>1665905</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>299808</v>
+        <v>301235</v>
       </c>
       <c r="AE18" s="13">
-        <v>1645453</v>
+        <v>1646880</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98772318949760041</v>
+        <v>0.98857978095989862</v>
       </c>
       <c r="AG18" s="7">
         <v>1104366</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>200452</v>
+        <v>201904</v>
       </c>
       <c r="AJ18" s="13">
-        <v>1092806</v>
+        <v>1094258</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.98953245572572857</v>
+        <v>0.99084723723837931</v>
       </c>
       <c r="AL18" s="7">
         <v>1131950</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>187394</v>
+        <v>189549</v>
       </c>
       <c r="AO18" s="13">
-        <v>1130170</v>
+        <v>1132325</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.99842749238040551</v>
+        <v>1.0003312867176113</v>
       </c>
       <c r="AQ18" s="7">
         <v>1717059</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>255463</v>
+        <v>261110</v>
       </c>
       <c r="AT18" s="13">
-        <v>1701261</v>
+        <v>1706908</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99079938429605507</v>
+        <v>0.99408814723314687</v>
       </c>
       <c r="AV18" s="7">
         <v>1151692</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>176408</v>
+        <v>180943</v>
       </c>
       <c r="AY18" s="13">
-        <v>1141925</v>
+        <v>1146460</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99151943401534437</v>
+        <v>0.99545711874355292</v>
       </c>
       <c r="BA18" s="7">
         <v>1182353</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>171917</v>
+        <v>178961</v>
       </c>
       <c r="BD18" s="13">
-        <v>1157500</v>
+        <v>1164544</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.97898005079701245</v>
+        <v>0.9849376624409123</v>
       </c>
       <c r="BF18" s="7">
         <v>1777125</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>297567</v>
-      </c>
-      <c r="BI18" s="13">
-        <v>1694796</v>
+        <v>323086</v>
+      </c>
+      <c r="BI18" s="6">
+        <v>1720315</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.95367292677780124</v>
+        <v>0.96803263698389252</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3201,14 +3201,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>65712</v>
+        <v>65871</v>
       </c>
       <c r="F19" s="13">
-        <v>299553</v>
+        <v>299712</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98015175758051687</v>
+        <v>0.98067201319289699</v>
       </c>
       <c r="H19" s="7">
         <v>314567</v>
@@ -3218,14 +3218,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>68173</v>
+        <v>68373</v>
       </c>
       <c r="K19" s="13">
-        <v>306162</v>
+        <v>306362</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97328073192674369</v>
+        <v>0.97391652652694016</v>
       </c>
       <c r="M19" s="7">
         <v>534704</v>
@@ -3235,14 +3235,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>114397</v>
+        <v>114808</v>
       </c>
       <c r="P19" s="13">
-        <v>525520</v>
+        <v>525931</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.9828241419551752</v>
+        <v>0.98359279152577872</v>
       </c>
       <c r="R19" s="7">
         <v>310887</v>
@@ -3252,14 +3252,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>64018</v>
+        <v>64301</v>
       </c>
       <c r="U19" s="13">
-        <v>305321</v>
+        <v>305604</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.98209638872001725</v>
+        <v>0.98300668731725671</v>
       </c>
       <c r="W19" s="7">
         <v>321022</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>67681</v>
+        <v>68049</v>
       </c>
       <c r="Z19" s="13">
-        <v>310000</v>
+        <v>310368</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96566590451744738</v>
+        <v>0.96681224339764871</v>
       </c>
       <c r="AB19" s="7">
         <v>548160</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>112682</v>
+        <v>113554</v>
       </c>
       <c r="AE19" s="13">
-        <v>534917</v>
+        <v>535789</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97584099532983071</v>
+        <v>0.9774317717454758</v>
       </c>
       <c r="AG19" s="7">
         <v>315587</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>66478</v>
+        <v>67181</v>
       </c>
       <c r="AJ19" s="13">
-        <v>308432</v>
+        <v>309135</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97732796344589601</v>
+        <v>0.97955555837217634</v>
       </c>
       <c r="AL19" s="7">
         <v>327315</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>60542</v>
+        <v>61520</v>
       </c>
       <c r="AO19" s="13">
-        <v>320610</v>
+        <v>321588</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.97951514596031342</v>
+        <v>0.98250309335044228</v>
       </c>
       <c r="AQ19" s="7">
         <v>564697</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>102790</v>
+        <v>105771</v>
       </c>
       <c r="AT19" s="13">
-        <v>553833</v>
+        <v>556814</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98076136405895553</v>
+        <v>0.98604030125890518</v>
       </c>
       <c r="AV19" s="7">
         <v>330794</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>56582</v>
+        <v>58697</v>
       </c>
       <c r="AY19" s="13">
-        <v>324707</v>
+        <v>326822</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.9815988198093073</v>
+        <v>0.98799252707122864</v>
       </c>
       <c r="BA19" s="7">
         <v>346688</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>57029</v>
+        <v>60170</v>
       </c>
       <c r="BD19" s="13">
-        <v>331910</v>
+        <v>335051</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.95737377699833859</v>
+        <v>0.96643379638176108</v>
       </c>
       <c r="BF19" s="7">
         <v>595475</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>114320</v>
-      </c>
-      <c r="BI19" s="13">
-        <v>547947</v>
+        <v>126924</v>
+      </c>
+      <c r="BI19" s="6">
+        <v>560551</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.9201847264788614</v>
+        <v>0.94135102229312728</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="F20" s="13">
-        <v>6492</v>
+        <v>6498</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99311610830656261</v>
+        <v>0.99403396053235427</v>
       </c>
       <c r="H20" s="7">
         <v>6601</v>
@@ -3430,14 +3430,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="K20" s="13">
-        <v>6515</v>
+        <v>6521</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.98697167095894567</v>
+        <v>0.98788062414785638</v>
       </c>
       <c r="M20" s="7">
         <v>10050</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2560</v>
+        <v>2569</v>
       </c>
       <c r="P20" s="13">
-        <v>10003</v>
+        <v>10012</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.99532338308457713</v>
+        <v>0.99621890547263681</v>
       </c>
       <c r="R20" s="7">
         <v>6485</v>
@@ -3464,14 +3464,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1632</v>
+        <v>1639</v>
       </c>
       <c r="U20" s="13">
-        <v>6435</v>
+        <v>6442</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.99228989976869697</v>
+        <v>0.9933693138010794</v>
       </c>
       <c r="W20" s="7">
         <v>6573</v>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="Z20" s="13">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.97930929560322533</v>
+        <v>0.98067853339418831</v>
       </c>
       <c r="AB20" s="7">
         <v>10123</v>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2605</v>
+        <v>2625</v>
       </c>
       <c r="AE20" s="13">
-        <v>9993</v>
+        <v>10013</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.98715795712733378</v>
+        <v>0.98913365603082093</v>
       </c>
       <c r="AG20" s="7">
         <v>6547</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1551</v>
+        <v>1569</v>
       </c>
       <c r="AJ20" s="13">
-        <v>6447</v>
+        <v>6465</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.98472582862379721</v>
+        <v>0.98747517947151364</v>
       </c>
       <c r="AL20" s="7">
         <v>6649</v>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1527</v>
+        <v>1550</v>
       </c>
       <c r="AO20" s="13">
-        <v>6516</v>
+        <v>6539</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.97999699202887647</v>
+        <v>0.98345615882087534</v>
       </c>
       <c r="AQ20" s="7">
         <v>10228</v>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2317</v>
+        <v>2378</v>
       </c>
       <c r="AT20" s="13">
-        <v>10011</v>
+        <v>10072</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.97878373093468907</v>
+        <v>0.98474775127102077</v>
       </c>
       <c r="AV20" s="7">
         <v>6568</v>
@@ -3566,14 +3566,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1317</v>
+        <v>1359</v>
       </c>
       <c r="AY20" s="13">
-        <v>6401</v>
+        <v>6443</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.9745736906211937</v>
+        <v>0.98096833130328864</v>
       </c>
       <c r="BA20" s="7">
         <v>6793</v>
@@ -3583,14 +3583,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1296</v>
+        <v>1354</v>
       </c>
       <c r="BD20" s="13">
-        <v>6420</v>
+        <v>6478</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.94509053437361989</v>
+        <v>0.95362873546297655</v>
       </c>
       <c r="BF20" s="7">
         <v>10395</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2057</v>
-      </c>
-      <c r="BI20" s="13">
-        <v>9555</v>
+        <v>2342</v>
+      </c>
+      <c r="BI20" s="6">
+        <v>9840</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.91919191919191923</v>
+        <v>0.94660894660894657</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4152</v>
+        <v>4171</v>
       </c>
       <c r="F21" s="13">
-        <v>12030</v>
+        <v>12049</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.0016652789342215</v>
+        <v>1.0032472939217318</v>
       </c>
       <c r="H21" s="7">
         <v>12254</v>
@@ -3642,14 +3642,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3784</v>
+        <v>3806</v>
       </c>
       <c r="K21" s="13">
-        <v>12238</v>
+        <v>12260</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99869430390076708</v>
+        <v>1.0004896360372124</v>
       </c>
       <c r="M21" s="7">
         <v>16207</v>
@@ -3659,14 +3659,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>5056</v>
+        <v>5091</v>
       </c>
       <c r="P21" s="13">
-        <v>16312</v>
+        <v>16347</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0064786820509657</v>
+        <v>1.0086382427346208</v>
       </c>
       <c r="R21" s="7">
         <v>12383</v>
@@ -3676,14 +3676,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3877</v>
+        <v>3908</v>
       </c>
       <c r="U21" s="13">
-        <v>12522</v>
+        <v>12553</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0112250666235969</v>
+        <v>1.013728498748284</v>
       </c>
       <c r="W21" s="7">
         <v>12782</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3935</v>
+        <v>3970</v>
       </c>
       <c r="Z21" s="13">
-        <v>12726</v>
+        <v>12761</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.99561883899233294</v>
+        <v>0.99835706462212481</v>
       </c>
       <c r="AB21" s="7">
         <v>16816</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4598</v>
+        <v>4661</v>
       </c>
       <c r="AE21" s="13">
-        <v>16751</v>
+        <v>16814</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.99613463368220745</v>
+        <v>0.99988106565176027</v>
       </c>
       <c r="AG21" s="7">
         <v>12696</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3819</v>
+        <v>3884</v>
       </c>
       <c r="AJ21" s="13">
-        <v>12654</v>
+        <v>12719</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>0.99669187145557658</v>
+        <v>1.0018115942028984</v>
       </c>
       <c r="AL21" s="7">
         <v>13072</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3735</v>
+        <v>3814</v>
       </c>
       <c r="AO21" s="13">
-        <v>12864</v>
+        <v>12943</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.98408812729498163</v>
+        <v>0.99013157894736847</v>
       </c>
       <c r="AQ21" s="7">
         <v>17310</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4329</v>
+        <v>4486</v>
       </c>
       <c r="AT21" s="13">
-        <v>16955</v>
+        <v>17112</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.97949162333911033</v>
+        <v>0.98856152512998263</v>
       </c>
       <c r="AV21" s="7">
         <v>13094</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3198</v>
+        <v>3348</v>
       </c>
       <c r="AY21" s="13">
-        <v>12687</v>
+        <v>12837</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.96891706124942723</v>
+        <v>0.98037268978157932</v>
       </c>
       <c r="BA21" s="7">
         <v>13518</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>2898</v>
+        <v>3128</v>
       </c>
       <c r="BD21" s="13">
-        <v>12679</v>
+        <v>12909</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>0.93793460571090403</v>
+        <v>0.95494895694629378</v>
       </c>
       <c r="BF21" s="7">
         <v>17905</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>4481</v>
-      </c>
-      <c r="BI21" s="13">
-        <v>15425</v>
+        <v>5236</v>
+      </c>
+      <c r="BI21" s="6">
+        <v>16180</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>0.86149120357442055</v>
+        <v>0.90365819603462716</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3837,14 +3837,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="F22" s="13">
-        <v>6971</v>
+        <v>6980</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.99642652944539734</v>
+        <v>0.99771297884505428</v>
       </c>
       <c r="H22" s="7">
         <v>7077</v>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1934</v>
+        <v>1943</v>
       </c>
       <c r="K22" s="13">
-        <v>7026</v>
+        <v>7035</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99279355659177615</v>
+        <v>0.99406528189910981</v>
       </c>
       <c r="M22" s="7">
         <v>8504</v>
@@ -3871,14 +3871,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2388</v>
+        <v>2397</v>
       </c>
       <c r="P22" s="13">
-        <v>8506</v>
+        <v>8515</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0002351834430856</v>
+        <v>1.0012935089369708</v>
       </c>
       <c r="R22" s="7">
         <v>7111</v>
@@ -3888,14 +3888,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1828</v>
+        <v>1835</v>
       </c>
       <c r="U22" s="13">
-        <v>7069</v>
+        <v>7076</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.99409365771340175</v>
+        <v>0.99507804809450151</v>
       </c>
       <c r="W22" s="7">
         <v>7191</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1729</v>
+        <v>1743</v>
       </c>
       <c r="Z22" s="13">
-        <v>7120</v>
+        <v>7134</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99012654707272985</v>
+        <v>0.99207342511472674</v>
       </c>
       <c r="AB22" s="7">
         <v>8707</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2008</v>
+        <v>2027</v>
       </c>
       <c r="AE22" s="13">
-        <v>8637</v>
+        <v>8656</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.99196049155851618</v>
+        <v>0.99414264384977602</v>
       </c>
       <c r="AG22" s="7">
         <v>7162</v>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1813</v>
+        <v>1838</v>
       </c>
       <c r="AJ22" s="13">
-        <v>7110</v>
+        <v>7135</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.99273945825188492</v>
+        <v>0.99623010332309414</v>
       </c>
       <c r="AL22" s="7">
         <v>7226</v>
@@ -3956,14 +3956,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="AO22" s="13">
-        <v>7142</v>
+        <v>7172</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.98837531137558821</v>
+        <v>0.99252698588430666</v>
       </c>
       <c r="AQ22" s="7">
         <v>8754</v>
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2290</v>
+        <v>2350</v>
       </c>
       <c r="AT22" s="13">
-        <v>8636</v>
+        <v>8696</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.98652044779529358</v>
+        <v>0.99337445739090702</v>
       </c>
       <c r="AV22" s="7">
         <v>7182</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1643</v>
+        <v>1709</v>
       </c>
       <c r="AY22" s="13">
-        <v>7029</v>
+        <v>7095</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.97869674185463662</v>
+        <v>0.9878863826232247</v>
       </c>
       <c r="BA22" s="7">
         <v>7296</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1502</v>
+        <v>1599</v>
       </c>
       <c r="BD22" s="13">
-        <v>6999</v>
+        <v>7096</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.95929276315789469</v>
+        <v>0.97258771929824561</v>
       </c>
       <c r="BF22" s="7">
         <v>8939</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>1980</v>
-      </c>
-      <c r="BI22" s="13">
-        <v>8086</v>
+        <v>2248</v>
+      </c>
+      <c r="BI22" s="6">
+        <v>8354</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.90457545586754673</v>
+        <v>0.93455643808032218</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4049,14 +4049,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2939</v>
+        <v>2949</v>
       </c>
       <c r="F23" s="13">
-        <v>9172</v>
+        <v>9182</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.97501860316785371</v>
+        <v>0.97608164133092379</v>
       </c>
       <c r="H23" s="7">
         <v>9786</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>3222</v>
+        <v>3234</v>
       </c>
       <c r="K23" s="13">
-        <v>9296</v>
+        <v>9308</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.94992846924177399</v>
+        <v>0.95115471081136316</v>
       </c>
       <c r="M23" s="7">
         <v>12056</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3982</v>
+        <v>4000</v>
       </c>
       <c r="P23" s="13">
-        <v>11835</v>
+        <v>11853</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.98166887856668883</v>
+        <v>0.9831619110816191</v>
       </c>
       <c r="R23" s="7">
         <v>9480</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2933</v>
+        <v>2948</v>
       </c>
       <c r="U23" s="13">
-        <v>9360</v>
+        <v>9375</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.98734177215189878</v>
+        <v>0.98892405063291144</v>
       </c>
       <c r="W23" s="7">
         <v>9764</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3011</v>
+        <v>3031</v>
       </c>
       <c r="Z23" s="13">
-        <v>9430</v>
+        <v>9450</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.96579270790659566</v>
+        <v>0.96784104875051213</v>
       </c>
       <c r="AB23" s="7">
         <v>12327</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3481</v>
+        <v>3515</v>
       </c>
       <c r="AE23" s="13">
-        <v>12022</v>
+        <v>12056</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97525756469538416</v>
+        <v>0.97801573781130846</v>
       </c>
       <c r="AG23" s="7">
         <v>9618</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>2972</v>
+        <v>3018</v>
       </c>
       <c r="AJ23" s="13">
-        <v>9308</v>
+        <v>9354</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.96776876689540448</v>
+        <v>0.97255146600124764</v>
       </c>
       <c r="AL23" s="7">
         <v>9741</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2790</v>
+        <v>2850</v>
       </c>
       <c r="AO23" s="13">
-        <v>9426</v>
+        <v>9486</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.96766245765321834</v>
+        <v>0.97382198952879584</v>
       </c>
       <c r="AQ23" s="7">
         <v>12556</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3430</v>
+        <v>3544</v>
       </c>
       <c r="AT23" s="13">
-        <v>12056</v>
+        <v>12170</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.96017840076457472</v>
+        <v>0.96925772539025168</v>
       </c>
       <c r="AV23" s="7">
         <v>9718</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2443</v>
+        <v>2556</v>
       </c>
       <c r="AY23" s="13">
-        <v>9307</v>
+        <v>9420</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.95770734719077999</v>
+        <v>0.9693352541675242</v>
       </c>
       <c r="BA23" s="7">
         <v>10107</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2493</v>
+        <v>2697</v>
       </c>
       <c r="BD23" s="13">
-        <v>9328</v>
+        <v>9532</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.92292470564954987</v>
+        <v>0.9431087365192441</v>
       </c>
       <c r="BF23" s="7">
         <v>13018</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>3302</v>
-      </c>
-      <c r="BI23" s="13">
-        <v>11309</v>
+        <v>3806</v>
+      </c>
+      <c r="BI23" s="6">
+        <v>11813</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.86872023352281458</v>
+        <v>0.9074358580427101</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="F24" s="13">
-        <v>6881</v>
+        <v>6887</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.99121290694324404</v>
+        <v>0.99207721117833481</v>
       </c>
       <c r="H24" s="7">
         <v>7059</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="K24" s="13">
-        <v>6930</v>
+        <v>6940</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.98172545686357837</v>
+        <v>0.9831420881144638</v>
       </c>
       <c r="M24" s="7">
         <v>8056</v>
@@ -4295,14 +4295,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1748</v>
+        <v>1761</v>
       </c>
       <c r="P24" s="13">
-        <v>7911</v>
+        <v>7924</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.9820009930486594</v>
+        <v>0.98361469712015892</v>
       </c>
       <c r="R24" s="7">
         <v>7134</v>
@@ -4312,14 +4312,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="U24" s="13">
-        <v>6993</v>
+        <v>7007</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.98023549201009252</v>
+        <v>0.98219792542753015</v>
       </c>
       <c r="W24" s="7">
         <v>7208</v>
@@ -4329,14 +4329,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1418</v>
+        <v>1438</v>
       </c>
       <c r="Z24" s="13">
-        <v>7037</v>
+        <v>7057</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.9762763596004439</v>
+        <v>0.97905105438401774</v>
       </c>
       <c r="AB24" s="7">
         <v>8228</v>
@@ -4346,14 +4346,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="AE24" s="13">
-        <v>8040</v>
+        <v>8065</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.97715119105493442</v>
+        <v>0.9801895964997569</v>
       </c>
       <c r="AG24" s="7">
         <v>7344</v>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1390</v>
+        <v>1418</v>
       </c>
       <c r="AJ24" s="13">
-        <v>7135</v>
+        <v>7163</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97154139433551201</v>
+        <v>0.97535403050108938</v>
       </c>
       <c r="AL24" s="7">
         <v>7506</v>
@@ -4380,14 +4380,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1278</v>
+        <v>1318</v>
       </c>
       <c r="AO24" s="13">
-        <v>7220</v>
+        <v>7260</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.96189714894750866</v>
+        <v>0.96722621902478012</v>
       </c>
       <c r="AQ24" s="7">
         <v>8509</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1497</v>
+        <v>1549</v>
       </c>
       <c r="AT24" s="13">
-        <v>8191</v>
+        <v>8243</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.96262780585262664</v>
+        <v>0.96873898225408395</v>
       </c>
       <c r="AV24" s="7">
         <v>7570</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1176</v>
+        <v>1239</v>
       </c>
       <c r="AY24" s="13">
-        <v>7219</v>
+        <v>7282</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.95363276089828275</v>
+        <v>0.96195508586525758</v>
       </c>
       <c r="BA24" s="7">
         <v>7648</v>
@@ -4431,14 +4431,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1284</v>
+        <v>1375</v>
       </c>
       <c r="BD24" s="13">
-        <v>7278</v>
+        <v>7369</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.95162133891213385</v>
+        <v>0.96351987447698739</v>
       </c>
       <c r="BF24" s="7">
         <v>8767</v>
@@ -4448,14 +4448,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1391</v>
-      </c>
-      <c r="BI24" s="13">
-        <v>8158</v>
+        <v>1561</v>
+      </c>
+      <c r="BI24" s="6">
+        <v>8328</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.9305349606478841</v>
+        <v>0.94992585833238274</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4674</v>
+        <v>4681</v>
       </c>
       <c r="F25" s="13">
-        <v>21334</v>
+        <v>21341</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.99352675452894335</v>
+        <v>0.99385274530806134</v>
       </c>
       <c r="H25" s="7">
         <v>21813</v>
@@ -4490,14 +4490,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>4498</v>
+        <v>4506</v>
       </c>
       <c r="K25" s="13">
-        <v>21520</v>
+        <v>21528</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.98656764314858114</v>
+        <v>0.98693439691926832</v>
       </c>
       <c r="M25" s="7">
         <v>29215</v>
@@ -4507,14 +4507,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>6184</v>
+        <v>6204</v>
       </c>
       <c r="P25" s="13">
-        <v>28975</v>
+        <v>28995</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.9917850419305152</v>
+        <v>0.99246962176963893</v>
       </c>
       <c r="R25" s="7">
         <v>21767</v>
@@ -4524,14 +4524,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4517</v>
+        <v>4531</v>
       </c>
       <c r="U25" s="13">
-        <v>21608</v>
+        <v>21622</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.99269536454265628</v>
+        <v>0.99333853999173061</v>
       </c>
       <c r="W25" s="7">
         <v>22114</v>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4208</v>
+        <v>4226</v>
       </c>
       <c r="Z25" s="13">
-        <v>21734</v>
+        <v>21752</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.98281631545627202</v>
+        <v>0.98363027946097492</v>
       </c>
       <c r="AB25" s="7">
         <v>29630</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5427</v>
+        <v>5461</v>
       </c>
       <c r="AE25" s="13">
-        <v>29313</v>
+        <v>29347</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.98930138373270338</v>
+        <v>0.99044886938913268</v>
       </c>
       <c r="AG25" s="7">
         <v>22174</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4327</v>
+        <v>4358</v>
       </c>
       <c r="AJ25" s="13">
-        <v>21842</v>
+        <v>21873</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.98502750969604036</v>
+        <v>0.98642554342924149</v>
       </c>
       <c r="AL25" s="7">
         <v>22503</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4234</v>
+        <v>4281</v>
       </c>
       <c r="AO25" s="13">
-        <v>22196</v>
+        <v>22243</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.98635737457227923</v>
+        <v>0.98844598497978042</v>
       </c>
       <c r="AQ25" s="7">
         <v>30294</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="AT25" s="13">
-        <v>29847</v>
+        <v>29942</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.98524460289166171</v>
+        <v>0.9883805374001452</v>
       </c>
       <c r="AV25" s="7">
         <v>22740</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4149</v>
+        <v>4257</v>
       </c>
       <c r="AY25" s="13">
-        <v>22412</v>
+        <v>22520</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.98557607739665787</v>
+        <v>0.99032541776605099</v>
       </c>
       <c r="BA25" s="7">
         <v>23197</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3888</v>
+        <v>4050</v>
       </c>
       <c r="BD25" s="13">
-        <v>22543</v>
+        <v>22705</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.97180669914213047</v>
+        <v>0.97879036082252013</v>
       </c>
       <c r="BF25" s="7">
         <v>31043</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>6061</v>
-      </c>
-      <c r="BI25" s="13">
-        <v>29129</v>
+        <v>6713</v>
+      </c>
+      <c r="BI25" s="6">
+        <v>29781</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.93834358792642458</v>
+        <v>0.95934671262442417</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4685,14 +4685,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3297</v>
+        <v>3314</v>
       </c>
       <c r="F26" s="13">
-        <v>14443</v>
+        <v>14460</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99250962067069814</v>
+        <v>0.99367784496976364</v>
       </c>
       <c r="H26" s="7">
         <v>14990</v>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3272</v>
+        <v>3291</v>
       </c>
       <c r="K26" s="13">
-        <v>14751</v>
+        <v>14770</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98405603735823888</v>
+        <v>0.98532354903268848</v>
       </c>
       <c r="M26" s="7">
         <v>28508</v>
@@ -4719,14 +4719,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5888</v>
+        <v>5930</v>
       </c>
       <c r="P26" s="13">
-        <v>28327</v>
+        <v>28369</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99365090500912023</v>
+        <v>0.99512417566998734</v>
       </c>
       <c r="R26" s="7">
         <v>14719</v>
@@ -4736,14 +4736,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3367</v>
+        <v>3391</v>
       </c>
       <c r="U26" s="13">
-        <v>14614</v>
+        <v>14638</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.992866363204022</v>
+        <v>0.99449690875738839</v>
       </c>
       <c r="W26" s="7">
         <v>15123</v>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3397</v>
+        <v>3432</v>
       </c>
       <c r="Z26" s="13">
-        <v>14768</v>
+        <v>14803</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.97652582159624413</v>
+        <v>0.97884017721351579</v>
       </c>
       <c r="AB26" s="7">
         <v>29054</v>
@@ -4770,14 +4770,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5019</v>
+        <v>5100</v>
       </c>
       <c r="AE26" s="13">
-        <v>28597</v>
+        <v>28678</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98427066841054589</v>
+        <v>0.98705858057410334</v>
       </c>
       <c r="AG26" s="7">
         <v>14835</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3214</v>
+        <v>3274</v>
       </c>
       <c r="AJ26" s="13">
-        <v>14575</v>
+        <v>14635</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.98247387933940011</v>
+        <v>0.98651836872261545</v>
       </c>
       <c r="AL26" s="7">
         <v>15316</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3122</v>
+        <v>3205</v>
       </c>
       <c r="AO26" s="13">
-        <v>14808</v>
+        <v>14891</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.96683207103682423</v>
+        <v>0.97225124053277623</v>
       </c>
       <c r="AQ26" s="7">
         <v>29312</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5125</v>
+        <v>5348</v>
       </c>
       <c r="AT26" s="13">
-        <v>28653</v>
+        <v>28876</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.97751774017467252</v>
+        <v>0.98512554585152834</v>
       </c>
       <c r="AV26" s="7">
         <v>15164</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>2722</v>
+        <v>2880</v>
       </c>
       <c r="AY26" s="13">
-        <v>14718</v>
+        <v>14876</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.97058823529411764</v>
+        <v>0.98100764969665</v>
       </c>
       <c r="BA26" s="7">
         <v>15499</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>2743</v>
+        <v>2942</v>
       </c>
       <c r="BD26" s="13">
-        <v>14654</v>
+        <v>14853</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.9454803535711982</v>
+        <v>0.95831989160591002</v>
       </c>
       <c r="BF26" s="7">
         <v>29635</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>4652</v>
-      </c>
-      <c r="BI26" s="13">
-        <v>27516</v>
+        <v>5289</v>
+      </c>
+      <c r="BI26" s="6">
+        <v>28153</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.92849670997131772</v>
+        <v>0.94999156402901974</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34530</v>
+        <v>34673</v>
       </c>
       <c r="F27" s="13">
-        <v>129525</v>
+        <v>129668</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.98777530352022447</v>
+        <v>0.9888658410103105</v>
       </c>
       <c r="H27" s="7">
         <v>134384</v>
@@ -4914,14 +4914,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>33645</v>
+        <v>33808</v>
       </c>
       <c r="K27" s="13">
-        <v>130449</v>
+        <v>130612</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.9707182402666984</v>
+        <v>0.9719311822836052</v>
       </c>
       <c r="M27" s="7">
         <v>190911</v>
@@ -4931,14 +4931,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>50592</v>
+        <v>50884</v>
       </c>
       <c r="P27" s="13">
-        <v>190381</v>
+        <v>190673</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99722383728543662</v>
+        <v>0.99875334579987529</v>
       </c>
       <c r="R27" s="7">
         <v>131264</v>
@@ -4948,14 +4948,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32665</v>
+        <v>32874</v>
       </c>
       <c r="U27" s="13">
-        <v>130223</v>
+        <v>130432</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99206941735738663</v>
+        <v>0.99366162847391515</v>
       </c>
       <c r="W27" s="7">
         <v>134144</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>37112</v>
+        <v>37369</v>
       </c>
       <c r="Z27" s="13">
-        <v>131383</v>
+        <v>131640</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97941764074427484</v>
+        <v>0.98133349236641221</v>
       </c>
       <c r="AB27" s="7">
         <v>194609</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>47610</v>
+        <v>48140</v>
       </c>
       <c r="AE27" s="13">
-        <v>192194</v>
+        <v>192724</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.98759050198089504</v>
+        <v>0.99031391148405268</v>
       </c>
       <c r="AG27" s="7">
         <v>134089</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33172</v>
+        <v>33629</v>
       </c>
       <c r="AJ27" s="13">
-        <v>131521</v>
+        <v>131978</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.98084854089448048</v>
+        <v>0.98425672501100014</v>
       </c>
       <c r="AL27" s="7">
         <v>137688</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31217</v>
+        <v>31898</v>
       </c>
       <c r="AO27" s="13">
-        <v>135339</v>
+        <v>136020</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98293968973331014</v>
+        <v>0.98788565452327004</v>
       </c>
       <c r="AQ27" s="7">
         <v>200322</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>46202</v>
+        <v>47931</v>
       </c>
       <c r="AT27" s="13">
-        <v>196491</v>
+        <v>198220</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.98087578997813518</v>
+        <v>0.9895068939008197</v>
       </c>
       <c r="AV27" s="7">
         <v>139481</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>28116</v>
+        <v>29501</v>
       </c>
       <c r="AY27" s="13">
-        <v>135358</v>
+        <v>136743</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.97044041840824202</v>
+        <v>0.98037008624830624</v>
       </c>
       <c r="BA27" s="7">
         <v>143305</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>27598</v>
+        <v>29655</v>
       </c>
       <c r="BD27" s="13">
-        <v>136015</v>
+        <v>138072</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.94912947908307455</v>
+        <v>0.96348347929241829</v>
       </c>
       <c r="BF27" s="7">
         <v>208143</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>47391</v>
-      </c>
-      <c r="BI27" s="13">
-        <v>187518</v>
+        <v>54528</v>
+      </c>
+      <c r="BI27" s="6">
+        <v>194655</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.90090947089260753</v>
+        <v>0.93519839725573284</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5109,14 +5109,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>70016</v>
+        <v>70152</v>
       </c>
       <c r="F28" s="13">
-        <v>434871</v>
+        <v>435007</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99396132229213763</v>
+        <v>0.99427217019837122</v>
       </c>
       <c r="H28" s="7">
         <v>447363</v>
@@ -5126,14 +5126,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>70143</v>
+        <v>70309</v>
       </c>
       <c r="K28" s="13">
-        <v>442240</v>
+        <v>442406</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98854844946944653</v>
+        <v>0.98891951278939028</v>
       </c>
       <c r="M28" s="7">
         <v>722935</v>
@@ -5143,14 +5143,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>117515</v>
+        <v>117825</v>
       </c>
       <c r="P28" s="13">
-        <v>716954</v>
+        <v>717264</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99172678041594331</v>
+        <v>0.99215558798508852</v>
       </c>
       <c r="R28" s="7">
         <v>448339</v>
@@ -5160,14 +5160,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>69404</v>
+        <v>69640</v>
       </c>
       <c r="U28" s="13">
-        <v>445304</v>
+        <v>445540</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99323056883295902</v>
+        <v>0.99375695623177995</v>
       </c>
       <c r="W28" s="7">
         <v>458076</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>73214</v>
+        <v>73523</v>
       </c>
       <c r="Z28" s="13">
-        <v>450155</v>
+        <v>450464</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.98270810957133747</v>
+        <v>0.98338267012460812</v>
       </c>
       <c r="AB28" s="7">
         <v>737235</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>112891</v>
+        <v>113586</v>
       </c>
       <c r="AE28" s="13">
-        <v>728413</v>
+        <v>729108</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98803366633434386</v>
+        <v>0.98897637795275595</v>
       </c>
       <c r="AG28" s="7">
         <v>456666</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>70252</v>
+        <v>70941</v>
       </c>
       <c r="AJ28" s="13">
-        <v>450456</v>
+        <v>451145</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98640144000210217</v>
+        <v>0.98791020132876106</v>
       </c>
       <c r="AL28" s="7">
         <v>468801</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>67705</v>
+        <v>68758</v>
       </c>
       <c r="AO28" s="13">
-        <v>462942</v>
+        <v>463995</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98750215976501754</v>
+        <v>0.98974831538328634</v>
       </c>
       <c r="AQ28" s="7">
         <v>756132</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>102690</v>
+        <v>105755</v>
       </c>
       <c r="AT28" s="13">
-        <v>746264</v>
+        <v>749329</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.98694936862875793</v>
+        <v>0.99100289367464944</v>
       </c>
       <c r="AV28" s="7">
         <v>474991</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>61369</v>
+        <v>63726</v>
       </c>
       <c r="AY28" s="13">
-        <v>466404</v>
+        <v>468761</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.98192176272813592</v>
+        <v>0.98688396201191175</v>
       </c>
       <c r="BA28" s="7">
         <v>487540</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>60860</v>
+        <v>64415</v>
       </c>
       <c r="BD28" s="13">
-        <v>471624</v>
+        <v>475179</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.9673544734790992</v>
+        <v>0.97464618287730242</v>
       </c>
       <c r="BF28" s="7">
         <v>779284</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>109749</v>
-      </c>
-      <c r="BI28" s="13">
-        <v>733947</v>
+        <v>123426</v>
+      </c>
+      <c r="BI28" s="6">
+        <v>747624</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.94182223682251909</v>
+        <v>0.95937296287361218</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>28129</v>
+        <v>28162</v>
       </c>
       <c r="F29" s="13">
-        <v>142636</v>
+        <v>142669</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99223662975123827</v>
+        <v>0.99246619177472317</v>
       </c>
       <c r="H29" s="7">
         <v>146310</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>27480</v>
+        <v>27520</v>
       </c>
       <c r="K29" s="13">
-        <v>144075</v>
+        <v>144115</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98472421570637692</v>
+        <v>0.98499760781901446</v>
       </c>
       <c r="M29" s="7">
         <v>194093</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>37596</v>
+        <v>37673</v>
       </c>
       <c r="P29" s="13">
-        <v>191448</v>
+        <v>191525</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98637251214623922</v>
+        <v>0.98676922918394794</v>
       </c>
       <c r="R29" s="7">
         <v>146918</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26508</v>
+        <v>26574</v>
       </c>
       <c r="U29" s="13">
-        <v>145057</v>
+        <v>145123</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98733307014797367</v>
+        <v>0.98778230033079673</v>
       </c>
       <c r="W29" s="7">
         <v>149105</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>26879</v>
+        <v>26969</v>
       </c>
       <c r="Z29" s="13">
-        <v>146297</v>
+        <v>146387</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98116763354682945</v>
+        <v>0.98177123503571306</v>
       </c>
       <c r="AB29" s="7">
         <v>197403</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32679</v>
+        <v>32856</v>
       </c>
       <c r="AE29" s="13">
-        <v>194213</v>
+        <v>194390</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98384016453650658</v>
+        <v>0.98473680744466907</v>
       </c>
       <c r="AG29" s="7">
         <v>149309</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>27276</v>
+        <v>27511</v>
       </c>
       <c r="AJ29" s="13">
-        <v>146947</v>
+        <v>147182</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98418045797641129</v>
+        <v>0.98575437515488018</v>
       </c>
       <c r="AL29" s="7">
         <v>152026</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>25370</v>
+        <v>25732</v>
       </c>
       <c r="AO29" s="13">
-        <v>151383</v>
+        <v>151745</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.99577046031599858</v>
+        <v>0.99815163195769141</v>
       </c>
       <c r="AQ29" s="7">
         <v>203571</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>33042</v>
+        <v>33839</v>
       </c>
       <c r="AT29" s="13">
-        <v>201256</v>
+        <v>202053</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.9886280462344833</v>
+        <v>0.99254314219608886</v>
       </c>
       <c r="AV29" s="7">
         <v>155780</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>24251</v>
+        <v>25053</v>
       </c>
       <c r="AY29" s="13">
-        <v>153600</v>
+        <v>154402</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.98600590576453973</v>
+        <v>0.99115419180896136</v>
       </c>
       <c r="BA29" s="7">
         <v>159604</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>24056</v>
+        <v>25320</v>
       </c>
       <c r="BD29" s="13">
-        <v>155122</v>
+        <v>156386</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.97191799704268067</v>
+        <v>0.97983759805518655</v>
       </c>
       <c r="BF29" s="7">
         <v>211893</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>35261</v>
-      </c>
-      <c r="BI29" s="13">
-        <v>199631</v>
+        <v>39135</v>
+      </c>
+      <c r="BI29" s="6">
+        <v>203505</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.94213116997729984</v>
+        <v>0.96041398252891785</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41100</v>
+        <v>41171</v>
       </c>
       <c r="F30" s="13">
-        <v>185464</v>
+        <v>185535</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99566225734409897</v>
+        <v>0.99604342037450611</v>
       </c>
       <c r="H30" s="7">
         <v>190966</v>
@@ -5550,14 +5550,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41496</v>
+        <v>41578</v>
       </c>
       <c r="K30" s="13">
-        <v>188308</v>
+        <v>188390</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98608129195773064</v>
+        <v>0.98651068776640871</v>
       </c>
       <c r="M30" s="7">
         <v>320227</v>
@@ -5567,14 +5567,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>67520</v>
+        <v>67670</v>
       </c>
       <c r="P30" s="13">
-        <v>317522</v>
+        <v>317672</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.9915528671848407</v>
+        <v>0.99202128490102337</v>
       </c>
       <c r="R30" s="7">
         <v>189502</v>
@@ -5584,14 +5584,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37779</v>
+        <v>37883</v>
       </c>
       <c r="U30" s="13">
-        <v>188294</v>
+        <v>188398</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99362539709343434</v>
+        <v>0.99417420396618505</v>
       </c>
       <c r="W30" s="7">
         <v>194334</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>37624</v>
+        <v>37760</v>
       </c>
       <c r="Z30" s="13">
-        <v>190502</v>
+        <v>190638</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98028137124743997</v>
+        <v>0.98098119732007782</v>
       </c>
       <c r="AB30" s="7">
         <v>325942</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>60105</v>
+        <v>60450</v>
       </c>
       <c r="AE30" s="13">
-        <v>322047</v>
+        <v>322392</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98805002116941054</v>
+        <v>0.98910849169484139</v>
       </c>
       <c r="AG30" s="7">
         <v>192789</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>39405</v>
+        <v>39723</v>
       </c>
       <c r="AJ30" s="13">
-        <v>190884</v>
+        <v>191202</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99011873084045254</v>
+        <v>0.99176820254267617</v>
       </c>
       <c r="AL30" s="7">
         <v>197994</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>36604</v>
+        <v>37087</v>
       </c>
       <c r="AO30" s="13">
-        <v>195378</v>
+        <v>195861</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98678747840843661</v>
+        <v>0.98922694627109908</v>
       </c>
       <c r="AQ30" s="7">
         <v>333633</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>58629</v>
+        <v>60135</v>
       </c>
       <c r="AT30" s="13">
-        <v>328772</v>
+        <v>330278</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.9854300983415909</v>
+        <v>0.98994404030776328</v>
       </c>
       <c r="AV30" s="7">
         <v>198460</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>34912</v>
+        <v>36056</v>
       </c>
       <c r="AY30" s="13">
-        <v>195207</v>
+        <v>196351</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.98360878766502069</v>
+        <v>0.98937317343545295</v>
       </c>
       <c r="BA30" s="7">
         <v>203942</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>34673</v>
+        <v>36505</v>
       </c>
       <c r="BD30" s="13">
-        <v>196945</v>
+        <v>198777</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.96569122593678591</v>
+        <v>0.97467417206852924</v>
       </c>
       <c r="BF30" s="7">
         <v>342999</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>63084</v>
-      </c>
-      <c r="BI30" s="13">
-        <v>319009</v>
+        <v>70553</v>
+      </c>
+      <c r="BI30" s="6">
+        <v>326478</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.93005810512567089</v>
+        <v>0.95183367881539016</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5745,14 +5745,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>19209</v>
+        <v>19224</v>
       </c>
       <c r="F31" s="13">
-        <v>83549</v>
+        <v>83564</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0080354234282061</v>
+        <v>1.0082164014333459</v>
       </c>
       <c r="H31" s="7">
         <v>85478</v>
@@ -5762,14 +5762,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>17984</v>
+        <v>18006</v>
       </c>
       <c r="K31" s="13">
-        <v>85071</v>
+        <v>85093</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99523854091111164</v>
+        <v>0.99549591707807861</v>
       </c>
       <c r="M31" s="7">
         <v>149930</v>
@@ -5779,14 +5779,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>38724</v>
+        <v>38794</v>
       </c>
       <c r="P31" s="13">
-        <v>150576</v>
+        <v>150646</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0043086773827787</v>
+        <v>1.0047755619289001</v>
       </c>
       <c r="R31" s="7">
         <v>83981</v>
@@ -5796,14 +5796,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>18487</v>
+        <v>18522</v>
       </c>
       <c r="U31" s="13">
-        <v>84296</v>
+        <v>84331</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0037508484061872</v>
+        <v>1.0041676093402079</v>
       </c>
       <c r="W31" s="7">
         <v>85994</v>
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>18874</v>
+        <v>18926</v>
       </c>
       <c r="Z31" s="13">
-        <v>85438</v>
+        <v>85490</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99353443263483499</v>
+        <v>0.99413912598553389</v>
       </c>
       <c r="AB31" s="7">
         <v>153633</v>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>39890</v>
+        <v>40041</v>
       </c>
       <c r="AE31" s="13">
-        <v>153131</v>
+        <v>153282</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.99673247284112132</v>
+        <v>0.99771533459608286</v>
       </c>
       <c r="AG31" s="7">
         <v>85109</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>20096</v>
+        <v>20181</v>
       </c>
       <c r="AJ31" s="13">
-        <v>85614</v>
+        <v>85699</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0059335675427981</v>
+        <v>1.0069322868321799</v>
       </c>
       <c r="AL31" s="7">
         <v>88549</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>17954</v>
+        <v>18094</v>
       </c>
       <c r="AO31" s="13">
-        <v>88125</v>
+        <v>88265</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99521169070232296</v>
+        <v>0.99679273622514086</v>
       </c>
       <c r="AQ31" s="7">
         <v>156407</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>33140</v>
+        <v>33713</v>
       </c>
       <c r="AT31" s="13">
-        <v>156263</v>
+        <v>156836</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.99907932509414543</v>
+        <v>1.0027428439903585</v>
       </c>
       <c r="AV31" s="7">
         <v>87916</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>16745</v>
+        <v>17083</v>
       </c>
       <c r="AY31" s="13">
-        <v>88171</v>
+        <v>88509</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0029004959279313</v>
+        <v>1.0067450748441695</v>
       </c>
       <c r="BA31" s="7">
         <v>90084</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>16335</v>
+        <v>16962</v>
       </c>
       <c r="BD31" s="13">
-        <v>89093</v>
+        <v>89720</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.98899915634296875</v>
+        <v>0.99595932685049504</v>
       </c>
       <c r="BF31" s="7">
         <v>159779</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>40989</v>
-      </c>
-      <c r="BI31" s="13">
-        <v>150283</v>
+        <v>45214</v>
+      </c>
+      <c r="BI31" s="6">
+        <v>154508</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.9405679094248931</v>
+        <v>0.96701068350659347</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>48371</v>
+        <v>48406</v>
       </c>
       <c r="F32" s="13">
-        <v>231584</v>
+        <v>231619</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99814666356340565</v>
+        <v>0.99829751652917498</v>
       </c>
       <c r="H32" s="7">
         <v>238678</v>
@@ -5974,14 +5974,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46490</v>
+        <v>46534</v>
       </c>
       <c r="K32" s="13">
-        <v>235762</v>
+        <v>235806</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98778270305600013</v>
+        <v>0.98796705184390687</v>
       </c>
       <c r="M32" s="7">
         <v>498323</v>
@@ -5991,14 +5991,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>107771</v>
+        <v>107909</v>
       </c>
       <c r="P32" s="13">
-        <v>494447</v>
+        <v>494585</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.9922219122938335</v>
+        <v>0.99249884111309328</v>
       </c>
       <c r="R32" s="7">
         <v>234167</v>
@@ -6008,14 +6008,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>43806</v>
+        <v>43873</v>
       </c>
       <c r="U32" s="13">
-        <v>233593</v>
+        <v>233660</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99754875793771114</v>
+        <v>0.99783487852686326</v>
       </c>
       <c r="W32" s="7">
         <v>242821</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>46038</v>
+        <v>46148</v>
       </c>
       <c r="Z32" s="13">
-        <v>238000</v>
+        <v>238110</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98014586876752829</v>
+        <v>0.98059887736233686</v>
       </c>
       <c r="AB32" s="7">
         <v>507064</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>110614</v>
+        <v>110995</v>
       </c>
       <c r="AE32" s="13">
-        <v>503122</v>
+        <v>503503</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99222583342536641</v>
+        <v>0.99297721786598925</v>
       </c>
       <c r="AG32" s="7">
         <v>238186</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>47382</v>
+        <v>47627</v>
       </c>
       <c r="AJ32" s="13">
-        <v>237515</v>
+        <v>237760</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99718287388847371</v>
+        <v>0.99821148178314423</v>
       </c>
       <c r="AL32" s="7">
         <v>247675</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>43095</v>
+        <v>43496</v>
       </c>
       <c r="AO32" s="13">
-        <v>246708</v>
+        <v>247109</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.99609568991622088</v>
+        <v>0.99771474714848085</v>
       </c>
       <c r="AQ32" s="7">
         <v>518099</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>98099</v>
+        <v>99836</v>
       </c>
       <c r="AT32" s="13">
-        <v>514925</v>
+        <v>516662</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99387375771811948</v>
+        <v>0.99722639881567032</v>
       </c>
       <c r="AV32" s="7">
         <v>246693</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>41835</v>
+        <v>42718</v>
       </c>
       <c r="AY32" s="13">
-        <v>246671</v>
+        <v>247554</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99991082033134304</v>
+        <v>1.0034901679415307</v>
       </c>
       <c r="BA32" s="7">
         <v>255610</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>38722</v>
+        <v>40155</v>
       </c>
       <c r="BD32" s="13">
-        <v>251841</v>
+        <v>253274</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98525488048198429</v>
+        <v>0.99086107742263607</v>
       </c>
       <c r="BF32" s="7">
         <v>535637</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>109545</v>
-      </c>
-      <c r="BI32" s="13">
-        <v>508188</v>
+        <v>118845</v>
+      </c>
+      <c r="BI32" s="6">
+        <v>517488</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.94875447364539789</v>
+        <v>0.96611697847609479</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>81411</v>
+        <v>81446</v>
       </c>
       <c r="F33" s="13">
-        <v>718627</v>
+        <v>718662</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0039592452007773</v>
+        <v>1.0040081420187121</v>
       </c>
       <c r="H33" s="7">
         <v>726544</v>
@@ -6186,14 +6186,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>73179</v>
+        <v>73226</v>
       </c>
       <c r="K33" s="13">
-        <v>729912</v>
+        <v>729959</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>1.0046356449162059</v>
+        <v>1.0047003347354049</v>
       </c>
       <c r="M33" s="7">
         <v>1152516</v>
@@ -6203,14 +6203,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>140167</v>
+        <v>140263</v>
       </c>
       <c r="P33" s="13">
-        <v>1154094</v>
+        <v>1154190</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>1.0013691783888468</v>
+        <v>1.0014524744125026</v>
       </c>
       <c r="R33" s="7">
         <v>733468</v>
@@ -6220,14 +6220,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>83002</v>
+        <v>83082</v>
       </c>
       <c r="U33" s="13">
-        <v>737127</v>
+        <v>737207</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0049886293607901</v>
+        <v>1.0050977002405013</v>
       </c>
       <c r="W33" s="7">
         <v>745690</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>80848</v>
+        <v>80949</v>
       </c>
       <c r="Z33" s="13">
-        <v>746400</v>
+        <v>746501</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>1.0009521382880286</v>
+        <v>1.0010875833121002</v>
       </c>
       <c r="AB33" s="7">
         <v>1180887</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>140471</v>
+        <v>140736</v>
       </c>
       <c r="AE33" s="13">
-        <v>1180356</v>
+        <v>1180621</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99955033800863247</v>
+        <v>0.99977474559377821</v>
       </c>
       <c r="AG33" s="7">
         <v>749948</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>80805</v>
+        <v>81063</v>
       </c>
       <c r="AJ33" s="13">
-        <v>751291</v>
+        <v>751549</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.001790790828164</v>
+        <v>1.0021348146804845</v>
       </c>
       <c r="AL33" s="7">
         <v>765123</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>75022</v>
+        <v>75431</v>
       </c>
       <c r="AO33" s="13">
-        <v>773493</v>
+        <v>773902</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>1.0109394175838395</v>
+        <v>1.0114739721587247</v>
       </c>
       <c r="AQ33" s="7">
         <v>1217820</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>137435</v>
+        <v>138979</v>
       </c>
       <c r="AT33" s="13">
-        <v>1221261</v>
+        <v>1222805</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0028255407203035</v>
+        <v>1.0040933799740519</v>
       </c>
       <c r="AV33" s="7">
         <v>779865</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>71045</v>
+        <v>72273</v>
       </c>
       <c r="AY33" s="13">
-        <v>783574</v>
+        <v>784802</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0047559513505542</v>
+        <v>1.0063305828572895</v>
       </c>
       <c r="BA33" s="7">
         <v>794982</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>70934</v>
+        <v>73164</v>
       </c>
       <c r="BD33" s="13">
-        <v>795764</v>
+        <v>797994</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0009836700705173</v>
+        <v>1.0037887650286421</v>
       </c>
       <c r="BF33" s="7">
         <v>1258934</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>142585</v>
-      </c>
-      <c r="BI33" s="13">
-        <v>1232773</v>
+        <v>155014</v>
+      </c>
+      <c r="BI33" s="6">
+        <v>1245202</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>0.97921972081141662</v>
+        <v>0.98909235909110405</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6547,7 +6547,7 @@
       <c r="BH34" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="BI34" s="14">
+      <c r="BI34" s="6">
         <v>0</v>
       </c>
       <c r="BJ34" s="14" t="s">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" ref="E35:E48" si="24">F35-D35</f>
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="F35" s="13">
-        <v>12239</v>
+        <v>12241</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99844999184206229</v>
+        <v>0.99861315059552946</v>
       </c>
       <c r="H35" s="7">
         <v>12343</v>
@@ -6586,14 +6586,14 @@
       </c>
       <c r="J35" s="4">
         <f t="shared" ref="J35:J48" si="26">K35-I35</f>
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="K35" s="13">
-        <v>12326</v>
+        <v>12329</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99862270112614437</v>
+        <v>0.99886575386858945</v>
       </c>
       <c r="M35" s="7">
         <v>15097</v>
@@ -6603,14 +6603,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2847</v>
+        <v>2851</v>
       </c>
       <c r="P35" s="13">
-        <v>15061</v>
+        <v>15065</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99761542028217531</v>
+        <v>0.99788037358415582</v>
       </c>
       <c r="R35" s="7">
         <v>12455</v>
@@ -6620,14 +6620,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="U35" s="13">
-        <v>12396</v>
+        <v>12400</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99526294660778802</v>
+        <v>0.99558410276997189</v>
       </c>
       <c r="W35" s="7">
         <v>12547</v>
@@ -6637,14 +6637,14 @@
       </c>
       <c r="Y35" s="4">
         <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="Z35" s="13">
-        <v>12430</v>
+        <v>12436</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.99067506176775322</v>
+        <v>0.99115326372838131</v>
       </c>
       <c r="AB35" s="7">
         <v>15257</v>
@@ -6654,14 +6654,14 @@
       </c>
       <c r="AD35" s="4">
         <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="AE35" s="13">
-        <v>15158</v>
+        <v>15170</v>
       </c>
       <c r="AF35" s="5">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99351117519826959</v>
+        <v>0.99429769941666124</v>
       </c>
       <c r="AG35" s="7">
         <v>12574</v>
@@ -6671,14 +6671,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" ref="AI35:AI48" si="36">AJ35-AH35</f>
-        <v>2170</v>
+        <v>2186</v>
       </c>
       <c r="AJ35" s="13">
-        <v>12493</v>
+        <v>12509</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99355813583585173</v>
+        <v>0.99483060283123903</v>
       </c>
       <c r="AL35" s="7">
         <v>12702</v>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="38">AO35-AM35</f>
-        <v>2054</v>
+        <v>2077</v>
       </c>
       <c r="AO35" s="13">
-        <v>12578</v>
+        <v>12601</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99023775783341206</v>
+        <v>0.9920484962997953</v>
       </c>
       <c r="AQ35" s="7">
         <v>15458</v>
@@ -6705,14 +6705,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="40">AT35-AR35</f>
-        <v>2560</v>
+        <v>2621</v>
       </c>
       <c r="AT35" s="13">
-        <v>15278</v>
+        <v>15339</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.98835554405485837</v>
+        <v>0.99230172079182299</v>
       </c>
       <c r="AV35" s="7">
         <v>12806</v>
@@ -6722,14 +6722,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="42">AY35-AW35</f>
-        <v>1879</v>
+        <v>1942</v>
       </c>
       <c r="AY35" s="13">
-        <v>12567</v>
+        <v>12630</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.98133687334062158</v>
+        <v>0.98625644229267528</v>
       </c>
       <c r="BA35" s="7">
         <v>12915</v>
@@ -6739,14 +6739,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="44">BD35-BB35</f>
-        <v>1788</v>
+        <v>1894</v>
       </c>
       <c r="BD35" s="13">
-        <v>12546</v>
+        <v>12652</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.97142857142857142</v>
+        <v>0.97963608207510644</v>
       </c>
       <c r="BF35" s="7">
         <v>15661</v>
@@ -6756,14 +6756,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="46">BI35-BG35</f>
-        <v>2223</v>
-      </c>
-      <c r="BI35" s="13">
-        <v>14822</v>
+        <v>2544</v>
+      </c>
+      <c r="BI35" s="6">
+        <v>15143</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.94642743119851858</v>
+        <v>0.96692420662792922</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>185672</v>
+        <v>185829</v>
       </c>
       <c r="F36" s="13">
-        <v>955850</v>
+        <v>956007</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>1.0031905626515254</v>
+        <v>1.0033553384200418</v>
       </c>
       <c r="H36" s="7">
         <v>975466</v>
@@ -6798,14 +6798,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>175982</v>
+        <v>176179</v>
       </c>
       <c r="K36" s="13">
-        <v>971202</v>
+        <v>971399</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.99562875589718147</v>
+        <v>0.995830710655215</v>
       </c>
       <c r="M36" s="7">
         <v>1668278</v>
@@ -6815,14 +6815,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>345477</v>
+        <v>345947</v>
       </c>
       <c r="P36" s="13">
-        <v>1667550</v>
+        <v>1668020</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.99956362189035641</v>
+        <v>0.99984534951608783</v>
       </c>
       <c r="R36" s="7">
         <v>976879</v>
@@ -6832,14 +6832,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>184903</v>
+        <v>185194</v>
       </c>
       <c r="U36" s="13">
-        <v>976945</v>
+        <v>977236</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>1.0000675621033925</v>
+        <v>1.0003654495592595</v>
       </c>
       <c r="W36" s="7">
         <v>1000117</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>180743</v>
+        <v>181135</v>
       </c>
       <c r="Z36" s="13">
-        <v>988566</v>
+        <v>988958</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98845035130889691</v>
+        <v>0.9888423054502623</v>
       </c>
       <c r="AB36" s="7">
         <v>1701420</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>334976</v>
+        <v>335983</v>
       </c>
       <c r="AE36" s="13">
-        <v>1695870</v>
+        <v>1696877</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.99673801883132918</v>
+        <v>0.99732987739652756</v>
       </c>
       <c r="AG36" s="7">
         <v>996655</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="36"/>
-        <v>185004</v>
+        <v>185958</v>
       </c>
       <c r="AJ36" s="13">
-        <v>995630</v>
+        <v>996584</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="37"/>
-        <v>0.99897155986775765</v>
+        <v>0.99992876170791301</v>
       </c>
       <c r="AL36" s="7">
         <v>1027093</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="38"/>
-        <v>175514</v>
+        <v>176983</v>
       </c>
       <c r="AO36" s="13">
-        <v>1030233</v>
+        <v>1031702</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="39"/>
-        <v>1.0030571720379751</v>
+        <v>1.0044874222684801</v>
       </c>
       <c r="AQ36" s="7">
         <v>1750886</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="40"/>
-        <v>313751</v>
+        <v>318506</v>
       </c>
       <c r="AT36" s="13">
-        <v>1755129</v>
+        <v>1759884</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="41"/>
-        <v>1.0024233445238582</v>
+        <v>1.0051391124265086</v>
       </c>
       <c r="AV36" s="7">
         <v>1041088</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="42"/>
-        <v>160992</v>
+        <v>164562</v>
       </c>
       <c r="AY36" s="13">
-        <v>1042992</v>
+        <v>1046562</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="43"/>
-        <v>1.0018288559660662</v>
+        <v>1.0052579609024406</v>
       </c>
       <c r="BA36" s="7">
         <v>1070068</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="44"/>
-        <v>162516</v>
+        <v>168280</v>
       </c>
       <c r="BD36" s="13">
-        <v>1058933</v>
+        <v>1064697</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="45"/>
-        <v>0.98959411925223439</v>
+        <v>0.99498069281578372</v>
       </c>
       <c r="BF36" s="7">
         <v>1814069</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="46"/>
-        <v>292962</v>
-      </c>
-      <c r="BI36" s="13">
-        <v>1720719</v>
+        <v>330039</v>
+      </c>
+      <c r="BI36" s="6">
+        <v>1757796</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="47"/>
-        <v>0.94854109738934955</v>
+        <v>0.96897968048624394</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6993,14 +6993,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>146256</v>
+        <v>146448</v>
       </c>
       <c r="F37" s="13">
-        <v>734326</v>
+        <v>734518</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.99036775693624002</v>
+        <v>0.9906267027032859</v>
       </c>
       <c r="H37" s="7">
         <v>747767</v>
@@ -7010,14 +7010,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>139928</v>
+        <v>140160</v>
       </c>
       <c r="K37" s="13">
-        <v>738950</v>
+        <v>739182</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98820889394691125</v>
+        <v>0.98851915101896715</v>
       </c>
       <c r="M37" s="7">
         <v>922163</v>
@@ -7027,14 +7027,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>187749</v>
+        <v>188107</v>
       </c>
       <c r="P37" s="13">
-        <v>913287</v>
+        <v>913645</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99037480358678454</v>
+        <v>0.99076302128799354</v>
       </c>
       <c r="R37" s="7">
         <v>751356</v>
@@ -7044,14 +7044,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>139465</v>
+        <v>139850</v>
       </c>
       <c r="U37" s="13">
-        <v>743909</v>
+        <v>744294</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99008858650227061</v>
+        <v>0.99060099340392571</v>
       </c>
       <c r="W37" s="7">
         <v>760191</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>137595</v>
+        <v>138109</v>
       </c>
       <c r="Z37" s="13">
-        <v>749147</v>
+        <v>749661</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98547207215028854</v>
+        <v>0.98614821801363084</v>
       </c>
       <c r="AB37" s="7">
         <v>938023</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>159233</v>
+        <v>160160</v>
       </c>
       <c r="AE37" s="13">
-        <v>926607</v>
+        <v>927534</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98782972272534897</v>
+        <v>0.98881797141434702</v>
       </c>
       <c r="AG37" s="7">
         <v>763648</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="36"/>
-        <v>140729</v>
+        <v>141993</v>
       </c>
       <c r="AJ37" s="13">
-        <v>753938</v>
+        <v>755202</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="37"/>
-        <v>0.9872847175662085</v>
+        <v>0.98893993043915518</v>
       </c>
       <c r="AL37" s="7">
         <v>773685</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="38"/>
-        <v>130394</v>
+        <v>132235</v>
       </c>
       <c r="AO37" s="13">
-        <v>765658</v>
+        <v>767499</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="39"/>
-        <v>0.98962497657315318</v>
+        <v>0.99200449795459389</v>
       </c>
       <c r="AQ37" s="7">
         <v>957323</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="40"/>
-        <v>160201</v>
+        <v>164103</v>
       </c>
       <c r="AT37" s="13">
-        <v>943664</v>
+        <v>947566</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="41"/>
-        <v>0.98573208833382253</v>
+        <v>0.98980803762157599</v>
       </c>
       <c r="AV37" s="7">
         <v>783693</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="42"/>
-        <v>118357</v>
+        <v>122722</v>
       </c>
       <c r="AY37" s="13">
-        <v>769149</v>
+        <v>773514</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="43"/>
-        <v>0.98144171250732115</v>
+        <v>0.98701149557288381</v>
       </c>
       <c r="BA37" s="7">
         <v>794943</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="44"/>
-        <v>126146</v>
+        <v>132984</v>
       </c>
       <c r="BD37" s="13">
-        <v>769806</v>
+        <v>776644</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="45"/>
-        <v>0.96837886489974756</v>
+        <v>0.97698073949956166</v>
       </c>
       <c r="BF37" s="7">
         <v>980352</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="46"/>
-        <v>163062</v>
-      </c>
-      <c r="BI37" s="13">
-        <v>919493</v>
+        <v>182855</v>
+      </c>
+      <c r="BI37" s="6">
+        <v>939286</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="47"/>
-        <v>0.93792127725551644</v>
+        <v>0.95811096422509467</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6578</v>
+        <v>6588</v>
       </c>
       <c r="F38" s="13">
-        <v>26166</v>
+        <v>26176</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0039904842299132</v>
+        <v>1.0043741846366356</v>
       </c>
       <c r="H38" s="7">
         <v>26657</v>
@@ -7222,14 +7222,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>6236</v>
+        <v>6249</v>
       </c>
       <c r="K38" s="13">
-        <v>26475</v>
+        <v>26488</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99317252504032716</v>
+        <v>0.99366020182316095</v>
       </c>
       <c r="M38" s="7">
         <v>40003</v>
@@ -7239,14 +7239,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>9846</v>
+        <v>9874</v>
       </c>
       <c r="P38" s="13">
-        <v>39977</v>
+        <v>40005</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>0.99935004874634403</v>
+        <v>1.0000499962502811</v>
       </c>
       <c r="R38" s="7">
         <v>26603</v>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>6097</v>
+        <v>6124</v>
       </c>
       <c r="U38" s="13">
-        <v>26592</v>
+        <v>26619</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>0.99958651279930832</v>
+        <v>1.0006014359282787</v>
       </c>
       <c r="W38" s="7">
         <v>27177</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6148</v>
+        <v>6180</v>
       </c>
       <c r="Z38" s="13">
-        <v>26833</v>
+        <v>26865</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.98734223792177211</v>
+        <v>0.98851970416160728</v>
       </c>
       <c r="AB38" s="7">
         <v>40627</v>
@@ -7290,14 +7290,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>8672</v>
+        <v>8741</v>
       </c>
       <c r="AE38" s="13">
-        <v>40501</v>
+        <v>40570</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>0.99689861422206905</v>
+        <v>0.99859699214807884</v>
       </c>
       <c r="AG38" s="7">
         <v>26952</v>
@@ -7307,14 +7307,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="36"/>
-        <v>6005</v>
+        <v>6087</v>
       </c>
       <c r="AJ38" s="13">
-        <v>26907</v>
+        <v>26989</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="37"/>
-        <v>0.99833036509349959</v>
+        <v>1.0013728109231226</v>
       </c>
       <c r="AL38" s="7">
         <v>27600</v>
@@ -7324,14 +7324,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="38"/>
-        <v>6207</v>
+        <v>6333</v>
       </c>
       <c r="AO38" s="13">
-        <v>27360</v>
+        <v>27486</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="39"/>
-        <v>0.99130434782608701</v>
+        <v>0.99586956521739134</v>
       </c>
       <c r="AQ38" s="7">
         <v>41434</v>
@@ -7341,14 +7341,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="40"/>
-        <v>8531</v>
+        <v>8827</v>
       </c>
       <c r="AT38" s="13">
-        <v>41105</v>
+        <v>41401</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="41"/>
-        <v>0.9920596611478496</v>
+        <v>0.99920355263793015</v>
       </c>
       <c r="AV38" s="7">
         <v>27593</v>
@@ -7358,14 +7358,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="42"/>
-        <v>4805</v>
+        <v>5093</v>
       </c>
       <c r="AY38" s="13">
-        <v>27161</v>
+        <v>27449</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="43"/>
-        <v>0.98434385532562607</v>
+        <v>0.99478128510854202</v>
       </c>
       <c r="BA38" s="7">
         <v>28279</v>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="44"/>
-        <v>4825</v>
+        <v>5239</v>
       </c>
       <c r="BD38" s="13">
-        <v>27103</v>
+        <v>27517</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="45"/>
-        <v>0.95841437108808658</v>
+        <v>0.97305420983768875</v>
       </c>
       <c r="BF38" s="7">
         <v>42642</v>
@@ -7392,14 +7392,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="46"/>
-        <v>7501</v>
-      </c>
-      <c r="BI38" s="13">
-        <v>39012</v>
+        <v>8753</v>
+      </c>
+      <c r="BI38" s="6">
+        <v>40264</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="47"/>
-        <v>0.91487266075700013</v>
+        <v>0.94423338492566011</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7451,14 +7451,14 @@
       </c>
       <c r="O39" s="4">
         <f t="shared" si="28"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P39" s="13">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q39" s="5">
         <f t="shared" si="29"/>
-        <v>0.98083067092651754</v>
+        <v>0.98402555910543132</v>
       </c>
       <c r="R39" s="7">
         <v>264</v>
@@ -7468,14 +7468,14 @@
       </c>
       <c r="T39" s="4">
         <f t="shared" si="30"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U39" s="13">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="V39" s="5">
         <f t="shared" si="31"/>
-        <v>0.9507575757575758</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="W39" s="7">
         <v>265</v>
@@ -7485,14 +7485,14 @@
       </c>
       <c r="Y39" s="4">
         <f t="shared" si="32"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z39" s="13">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA39" s="5">
         <f t="shared" si="33"/>
-        <v>0.95849056603773586</v>
+        <v>0.96226415094339623</v>
       </c>
       <c r="AB39" s="7">
         <v>322</v>
@@ -7502,14 +7502,14 @@
       </c>
       <c r="AD39" s="4">
         <f t="shared" si="34"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE39" s="13">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AF39" s="5">
         <f t="shared" si="35"/>
-        <v>0.96273291925465843</v>
+        <v>0.96583850931677018</v>
       </c>
       <c r="AG39" s="7">
         <v>267</v>
@@ -7519,14 +7519,14 @@
       </c>
       <c r="AI39" s="4">
         <f t="shared" si="36"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AJ39" s="13">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AK39" s="5">
         <f t="shared" si="37"/>
-        <v>0.9438202247191011</v>
+        <v>0.94756554307116103</v>
       </c>
       <c r="AL39" s="7">
         <v>276</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="AN39" s="4">
         <f t="shared" si="38"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AO39" s="13">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP39" s="5">
         <f t="shared" si="39"/>
-        <v>0.93840579710144922</v>
+        <v>0.94565217391304346</v>
       </c>
       <c r="AQ39" s="7">
         <v>338</v>
@@ -7553,14 +7553,14 @@
       </c>
       <c r="AS39" s="4">
         <f t="shared" si="40"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AT39" s="13">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AU39" s="5">
         <f t="shared" si="41"/>
-        <v>0.9349112426035503</v>
+        <v>0.94378698224852076</v>
       </c>
       <c r="AV39" s="7">
         <v>279</v>
@@ -7570,14 +7570,14 @@
       </c>
       <c r="AX39" s="4">
         <f t="shared" si="42"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AY39" s="13">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AZ39" s="5">
         <f t="shared" si="43"/>
-        <v>0.93548387096774188</v>
+        <v>0.94265232974910396</v>
       </c>
       <c r="BA39" s="7">
         <v>291</v>
@@ -7587,14 +7587,14 @@
       </c>
       <c r="BC39" s="4">
         <f t="shared" si="44"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD39" s="13">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BE39" s="5">
         <f t="shared" si="45"/>
-        <v>0.91408934707903777</v>
+        <v>0.92096219931271472</v>
       </c>
       <c r="BF39" s="7">
         <v>344</v>
@@ -7604,14 +7604,14 @@
       </c>
       <c r="BH39" s="4">
         <f t="shared" si="46"/>
-        <v>64</v>
-      </c>
-      <c r="BI39" s="13">
-        <v>315</v>
+        <v>75</v>
+      </c>
+      <c r="BI39" s="6">
+        <v>326</v>
       </c>
       <c r="BJ39" s="5">
         <f t="shared" si="47"/>
-        <v>0.91569767441860461</v>
+        <v>0.94767441860465118</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7629,14 +7629,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>73282</v>
+        <v>73370</v>
       </c>
       <c r="F40" s="13">
-        <v>301197</v>
+        <v>301285</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99112519496929852</v>
+        <v>0.99141476962361874</v>
       </c>
       <c r="H40" s="7">
         <v>306465</v>
@@ -7646,14 +7646,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>71058</v>
+        <v>71156</v>
       </c>
       <c r="K40" s="13">
-        <v>302518</v>
+        <v>302616</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98712087840373286</v>
+        <v>0.98744065390827662</v>
       </c>
       <c r="M40" s="7">
         <v>361770</v>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>90366</v>
+        <v>90526</v>
       </c>
       <c r="P40" s="13">
-        <v>358180</v>
+        <v>358340</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99007656798518395</v>
+        <v>0.99051883793570505</v>
       </c>
       <c r="R40" s="7">
         <v>306479</v>
@@ -7680,14 +7680,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>69806</v>
+        <v>69968</v>
       </c>
       <c r="U40" s="13">
-        <v>304245</v>
+        <v>304407</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99271075669132303</v>
+        <v>0.99323934103152256</v>
       </c>
       <c r="W40" s="7">
         <v>309858</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>70018</v>
+        <v>70256</v>
       </c>
       <c r="Z40" s="13">
-        <v>305632</v>
+        <v>305870</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.98636149462011635</v>
+        <v>0.98712958839210219</v>
       </c>
       <c r="AB40" s="7">
         <v>365821</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>64926</v>
+        <v>65399</v>
       </c>
       <c r="AE40" s="13">
-        <v>361711</v>
+        <v>362184</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.98876499708874011</v>
+        <v>0.99005797917560778</v>
       </c>
       <c r="AG40" s="7">
         <v>311342</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="36"/>
-        <v>71700</v>
+        <v>72357</v>
       </c>
       <c r="AJ40" s="13">
-        <v>307640</v>
+        <v>308297</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="37"/>
-        <v>0.98810953870663132</v>
+        <v>0.99021975833649167</v>
       </c>
       <c r="AL40" s="7">
         <v>314792</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="38"/>
-        <v>68738</v>
+        <v>69857</v>
       </c>
       <c r="AO40" s="13">
-        <v>310597</v>
+        <v>311716</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="39"/>
-        <v>0.9866737401204605</v>
+        <v>0.99022846832193956</v>
       </c>
       <c r="AQ40" s="7">
         <v>372144</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="40"/>
-        <v>71357</v>
+        <v>73716</v>
       </c>
       <c r="AT40" s="13">
-        <v>365499</v>
+        <v>367858</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="41"/>
-        <v>0.98214400877079844</v>
+        <v>0.9884829528354615</v>
       </c>
       <c r="AV40" s="7">
         <v>317868</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="42"/>
-        <v>60048</v>
+        <v>62649</v>
       </c>
       <c r="AY40" s="13">
-        <v>309864</v>
+        <v>312465</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="43"/>
-        <v>0.97481973649439391</v>
+        <v>0.98300237834572846</v>
       </c>
       <c r="BA40" s="7">
         <v>321637</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="44"/>
-        <v>64628</v>
+        <v>68306</v>
       </c>
       <c r="BD40" s="13">
-        <v>309261</v>
+        <v>312939</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="45"/>
-        <v>0.96152183983807837</v>
+        <v>0.97295709137941222</v>
       </c>
       <c r="BF40" s="7">
         <v>380248</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="46"/>
-        <v>73924</v>
-      </c>
-      <c r="BI40" s="13">
-        <v>354305</v>
+        <v>82633</v>
+      </c>
+      <c r="BI40" s="6">
+        <v>363014</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="47"/>
-        <v>0.93177347415371026</v>
+        <v>0.95467694767625344</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>163117</v>
+        <v>163257</v>
       </c>
       <c r="F41" s="13">
-        <v>975329</v>
+        <v>975469</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.9978474227901043</v>
+        <v>0.99799065511395668</v>
       </c>
       <c r="H41" s="7">
         <v>983280</v>
@@ -7858,14 +7858,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>162956</v>
+        <v>163122</v>
       </c>
       <c r="K41" s="13">
-        <v>979650</v>
+        <v>979816</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.99630827434708324</v>
+        <v>0.99647709706289156</v>
       </c>
       <c r="M41" s="7">
         <v>1084276</v>
@@ -7875,14 +7875,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>190145</v>
+        <v>190366</v>
       </c>
       <c r="P41" s="13">
-        <v>1081352</v>
+        <v>1081573</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99730326964721161</v>
+        <v>0.99750709229015488</v>
       </c>
       <c r="R41" s="7">
         <v>988018</v>
@@ -7892,14 +7892,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>163302</v>
+        <v>163567</v>
       </c>
       <c r="U41" s="13">
-        <v>987593</v>
+        <v>987858</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.99956984589349585</v>
+        <v>0.99983805963049255</v>
       </c>
       <c r="W41" s="7">
         <v>994033</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>160883</v>
+        <v>161222</v>
       </c>
       <c r="Z41" s="13">
-        <v>992342</v>
+        <v>992681</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.99829884923337553</v>
+        <v>0.99863988418895555</v>
       </c>
       <c r="AB41" s="7">
         <v>1097882</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>138880</v>
+        <v>139398</v>
       </c>
       <c r="AE41" s="13">
-        <v>1095479</v>
+        <v>1095997</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99781124018792544</v>
+        <v>0.99828305774208881</v>
       </c>
       <c r="AG41" s="7">
         <v>1002140</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="36"/>
-        <v>155684</v>
+        <v>156392</v>
       </c>
       <c r="AJ41" s="13">
-        <v>1000388</v>
+        <v>1001096</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="37"/>
-        <v>0.99825174127367433</v>
+        <v>0.99895822938910728</v>
       </c>
       <c r="AL41" s="7">
         <v>1011306</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="38"/>
-        <v>149499</v>
+        <v>150550</v>
       </c>
       <c r="AO41" s="13">
-        <v>1012608</v>
+        <v>1013659</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="39"/>
-        <v>1.0012874441563682</v>
+        <v>1.0023266943931906</v>
       </c>
       <c r="AQ41" s="7">
         <v>1119532</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="40"/>
-        <v>183638</v>
+        <v>185740</v>
       </c>
       <c r="AT41" s="13">
-        <v>1119188</v>
+        <v>1121290</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="41"/>
-        <v>0.99969272874736947</v>
+        <v>1.0015702990178039</v>
       </c>
       <c r="AV41" s="7">
         <v>1028062</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="42"/>
-        <v>144327</v>
+        <v>147075</v>
       </c>
       <c r="AY41" s="13">
-        <v>1024035</v>
+        <v>1026783</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="43"/>
-        <v>0.99608292106896279</v>
+        <v>0.9987559116084439</v>
       </c>
       <c r="BA41" s="7">
         <v>1037044</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="44"/>
-        <v>141760</v>
+        <v>146643</v>
       </c>
       <c r="BD41" s="13">
-        <v>1027446</v>
+        <v>1032329</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="45"/>
-        <v>0.99074484785602157</v>
+        <v>0.99545342338415732</v>
       </c>
       <c r="BF41" s="7">
         <v>1143357</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="46"/>
-        <v>168091</v>
-      </c>
-      <c r="BI41" s="13">
-        <v>1111880</v>
+        <v>184084</v>
+      </c>
+      <c r="BI41" s="6">
+        <v>1127873</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="47"/>
-        <v>0.97246966607979834</v>
+        <v>0.98645742318453467</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8053,14 +8053,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>4271</v>
+        <v>4274</v>
       </c>
       <c r="F42" s="13">
-        <v>19562</v>
+        <v>19565</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.99420613945923964</v>
+        <v>0.99435860947347021</v>
       </c>
       <c r="H42" s="7">
         <v>19882</v>
@@ -8070,14 +8070,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="K42" s="13">
-        <v>19659</v>
+        <v>19662</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.98878382456493308</v>
+        <v>0.98893471481742279</v>
       </c>
       <c r="M42" s="7">
         <v>21930</v>
@@ -8087,14 +8087,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>5193</v>
+        <v>5196</v>
       </c>
       <c r="P42" s="13">
-        <v>21730</v>
+        <v>21733</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99088007295941627</v>
+        <v>0.99101687186502507</v>
       </c>
       <c r="R42" s="7">
         <v>20021</v>
@@ -8104,14 +8104,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>4356</v>
+        <v>4365</v>
       </c>
       <c r="U42" s="13">
-        <v>19792</v>
+        <v>19801</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.98856200988961596</v>
+        <v>0.98901153788522056</v>
       </c>
       <c r="W42" s="7">
         <v>20153</v>
@@ -8121,14 +8121,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4219</v>
+        <v>4230</v>
       </c>
       <c r="Z42" s="13">
-        <v>19882</v>
+        <v>19893</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.98655287054036622</v>
+        <v>0.98709869498337721</v>
       </c>
       <c r="AB42" s="7">
         <v>22238</v>
@@ -8138,14 +8138,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>3859</v>
+        <v>3876</v>
       </c>
       <c r="AE42" s="13">
-        <v>22016</v>
+        <v>22033</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.990017087867614</v>
+        <v>0.99078154510297689</v>
       </c>
       <c r="AG42" s="7">
         <v>20276</v>
@@ -8155,14 +8155,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="36"/>
-        <v>4287</v>
+        <v>4322</v>
       </c>
       <c r="AJ42" s="13">
-        <v>20095</v>
+        <v>20130</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="37"/>
-        <v>0.99107318997829952</v>
+        <v>0.99279936871177743</v>
       </c>
       <c r="AL42" s="7">
         <v>20453</v>
@@ -8172,14 +8172,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="38"/>
-        <v>3820</v>
+        <v>3884</v>
       </c>
       <c r="AO42" s="13">
-        <v>20238</v>
+        <v>20302</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="39"/>
-        <v>0.98948809465604071</v>
+        <v>0.99261721996773089</v>
       </c>
       <c r="AQ42" s="7">
         <v>22621</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="40"/>
-        <v>4641</v>
+        <v>4764</v>
       </c>
       <c r="AT42" s="13">
-        <v>22371</v>
+        <v>22494</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="41"/>
-        <v>0.98894832235533359</v>
+        <v>0.99438574775650945</v>
       </c>
       <c r="AV42" s="7">
         <v>20714</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="42"/>
-        <v>3630</v>
+        <v>3810</v>
       </c>
       <c r="AY42" s="13">
-        <v>20326</v>
+        <v>20506</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="43"/>
-        <v>0.98126870715458148</v>
+        <v>0.98995848218596116</v>
       </c>
       <c r="BA42" s="7">
         <v>20927</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="44"/>
-        <v>3426</v>
+        <v>3668</v>
       </c>
       <c r="BD42" s="13">
-        <v>20294</v>
+        <v>20536</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="45"/>
-        <v>0.96975199503034359</v>
+        <v>0.98131600324939072</v>
       </c>
       <c r="BF42" s="7">
         <v>23165</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="46"/>
-        <v>3949</v>
-      </c>
-      <c r="BI42" s="13">
-        <v>21896</v>
+        <v>4447</v>
+      </c>
+      <c r="BI42" s="6">
+        <v>22394</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="47"/>
-        <v>0.94521908050938919</v>
+        <v>0.96671703000215847</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8282,14 +8282,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="K43" s="13">
-        <v>3917</v>
+        <v>3920</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99391017508246637</v>
+        <v>0.99467140319715808</v>
       </c>
       <c r="M43" s="7">
         <v>4896</v>
@@ -8299,14 +8299,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="P43" s="13">
-        <v>4850</v>
+        <v>4854</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99060457516339873</v>
+        <v>0.99142156862745101</v>
       </c>
       <c r="R43" s="7">
         <v>3969</v>
@@ -8316,14 +8316,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="30"/>
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="U43" s="13">
-        <v>3924</v>
+        <v>3929</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="31"/>
-        <v>0.9886621315192744</v>
+        <v>0.98992189468379943</v>
       </c>
       <c r="W43" s="7">
         <v>4009</v>
@@ -8333,14 +8333,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="Z43" s="13">
-        <v>3964</v>
+        <v>3969</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.9887752556747319</v>
+        <v>0.99002244948865059</v>
       </c>
       <c r="AB43" s="7">
         <v>4962</v>
@@ -8350,14 +8350,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="AE43" s="13">
-        <v>4913</v>
+        <v>4922</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99012494961708986</v>
+        <v>0.99193873438129787</v>
       </c>
       <c r="AG43" s="7">
         <v>4018</v>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="36"/>
-        <v>1192</v>
+        <v>1207</v>
       </c>
       <c r="AJ43" s="13">
-        <v>3977</v>
+        <v>3992</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="37"/>
-        <v>0.98979591836734693</v>
+        <v>0.99352911896465901</v>
       </c>
       <c r="AL43" s="7">
         <v>4086</v>
@@ -8384,14 +8384,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="38"/>
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="AO43" s="13">
-        <v>4026</v>
+        <v>4047</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="39"/>
-        <v>0.98531571218795888</v>
+        <v>0.99045521292217331</v>
       </c>
       <c r="AQ43" s="7">
         <v>5072</v>
@@ -8401,14 +8401,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="40"/>
-        <v>1469</v>
+        <v>1516</v>
       </c>
       <c r="AT43" s="13">
-        <v>4982</v>
+        <v>5029</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="41"/>
-        <v>0.98225552050473186</v>
+        <v>0.99152208201892744</v>
       </c>
       <c r="AV43" s="7">
         <v>4151</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="42"/>
-        <v>1153</v>
+        <v>1202</v>
       </c>
       <c r="AY43" s="13">
-        <v>3994</v>
+        <v>4043</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="43"/>
-        <v>0.96217778848470248</v>
+        <v>0.9739821729703686</v>
       </c>
       <c r="BA43" s="7">
         <v>4249</v>
@@ -8435,14 +8435,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="44"/>
-        <v>1016</v>
+        <v>1090</v>
       </c>
       <c r="BD43" s="13">
-        <v>3987</v>
+        <v>4061</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="45"/>
-        <v>0.93833843257236993</v>
+        <v>0.95575429512826549</v>
       </c>
       <c r="BF43" s="7">
         <v>5295</v>
@@ -8452,14 +8452,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="46"/>
-        <v>1312</v>
-      </c>
-      <c r="BI43" s="13">
-        <v>4611</v>
+        <v>1507</v>
+      </c>
+      <c r="BI43" s="6">
+        <v>4806</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="47"/>
-        <v>0.87082152974504246</v>
+        <v>0.90764872521246454</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>84055</v>
+        <v>84132</v>
       </c>
       <c r="F44" s="13">
-        <v>379474</v>
+        <v>379551</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98940391825581819</v>
+        <v>0.98960468063138463</v>
       </c>
       <c r="H44" s="7">
         <v>388149</v>
@@ -8494,14 +8494,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>82331</v>
+        <v>82422</v>
       </c>
       <c r="K44" s="13">
-        <v>382749</v>
+        <v>382840</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98608781679200508</v>
+        <v>0.98632226284236213</v>
       </c>
       <c r="M44" s="7">
         <v>456953</v>
@@ -8511,14 +8511,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>103156</v>
+        <v>103294</v>
       </c>
       <c r="P44" s="13">
-        <v>452768</v>
+        <v>452906</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.99084150886415012</v>
+        <v>0.99114350928870143</v>
       </c>
       <c r="R44" s="7">
         <v>388846</v>
@@ -8528,14 +8528,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>83191</v>
+        <v>83333</v>
       </c>
       <c r="U44" s="13">
-        <v>384978</v>
+        <v>385120</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.9900526172315004</v>
+        <v>0.99041780036312577</v>
       </c>
       <c r="W44" s="7">
         <v>393146</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>81723</v>
+        <v>81909</v>
       </c>
       <c r="Z44" s="13">
-        <v>387431</v>
+        <v>387617</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.98546341562676465</v>
+        <v>0.98593652230977802</v>
       </c>
       <c r="AB44" s="7">
         <v>465292</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>81145</v>
+        <v>81457</v>
       </c>
       <c r="AE44" s="13">
-        <v>459537</v>
+        <v>459849</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.98763142284844785</v>
+        <v>0.98830196951591687</v>
       </c>
       <c r="AG44" s="7">
         <v>393778</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="36"/>
-        <v>79624</v>
+        <v>80021</v>
       </c>
       <c r="AJ44" s="13">
-        <v>390830</v>
+        <v>391227</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="37"/>
-        <v>0.9925135482429186</v>
+        <v>0.9935217305182108</v>
       </c>
       <c r="AL44" s="7">
         <v>398873</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="38"/>
-        <v>76321</v>
+        <v>76986</v>
       </c>
       <c r="AO44" s="13">
-        <v>399846</v>
+        <v>400511</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="39"/>
-        <v>1.0024393729332395</v>
+        <v>1.0041065702617125</v>
       </c>
       <c r="AQ44" s="7">
         <v>476819</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="40"/>
-        <v>83679</v>
+        <v>85205</v>
       </c>
       <c r="AT44" s="13">
-        <v>475113</v>
+        <v>476639</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="41"/>
-        <v>0.9964221224405907</v>
+        <v>0.99962249826454064</v>
       </c>
       <c r="AV44" s="7">
         <v>408878</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="42"/>
-        <v>70398</v>
+        <v>72232</v>
       </c>
       <c r="AY44" s="13">
-        <v>405776</v>
+        <v>407610</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="43"/>
-        <v>0.99241338492166364</v>
+        <v>0.996898830457985</v>
       </c>
       <c r="BA44" s="7">
         <v>416024</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="44"/>
-        <v>75330</v>
+        <v>78635</v>
       </c>
       <c r="BD44" s="13">
-        <v>408015</v>
+        <v>411320</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="45"/>
-        <v>0.98074870680537662</v>
+        <v>0.98869296002153717</v>
       </c>
       <c r="BF44" s="7">
         <v>493955</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="46"/>
-        <v>88079</v>
-      </c>
-      <c r="BI44" s="13">
-        <v>468665</v>
+        <v>98074</v>
+      </c>
+      <c r="BI44" s="6">
+        <v>478660</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="47"/>
-        <v>0.94880100414005319</v>
+        <v>0.96903564089846239</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>55932</v>
+        <v>55972</v>
       </c>
       <c r="F45" s="13">
-        <v>276890</v>
+        <v>276930</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.99781618473779798</v>
+        <v>0.99796033095972558</v>
       </c>
       <c r="H45" s="7">
         <v>280269</v>
@@ -8706,14 +8706,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>55460</v>
+        <v>55508</v>
       </c>
       <c r="K45" s="13">
-        <v>278597</v>
+        <v>278645</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.99403430275913496</v>
+        <v>0.99420556679475791</v>
       </c>
       <c r="M45" s="7">
         <v>334005</v>
@@ -8723,14 +8723,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>70040</v>
+        <v>70116</v>
       </c>
       <c r="P45" s="13">
-        <v>331550</v>
+        <v>331626</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.99264981063157742</v>
+        <v>0.99287735213544703</v>
       </c>
       <c r="R45" s="7">
         <v>281510</v>
@@ -8740,14 +8740,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>53603</v>
+        <v>53676</v>
       </c>
       <c r="U45" s="13">
-        <v>279664</v>
+        <v>279737</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.99344250648289578</v>
+        <v>0.99370182231537063</v>
       </c>
       <c r="W45" s="7">
         <v>284325</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>54326</v>
+        <v>54416</v>
       </c>
       <c r="Z45" s="13">
-        <v>280651</v>
+        <v>280741</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.98707816758990596</v>
+        <v>0.98739470676162844</v>
       </c>
       <c r="AB45" s="7">
         <v>338696</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>61069</v>
+        <v>61279</v>
       </c>
       <c r="AE45" s="13">
-        <v>334261</v>
+        <v>334471</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98690566171433969</v>
+        <v>0.98752568675154118</v>
       </c>
       <c r="AG45" s="7">
         <v>285325</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="36"/>
-        <v>56258</v>
+        <v>56549</v>
       </c>
       <c r="AJ45" s="13">
-        <v>282213</v>
+        <v>282504</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="37"/>
-        <v>0.98909313940243582</v>
+        <v>0.99011302900201525</v>
       </c>
       <c r="AL45" s="7">
         <v>289428</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="38"/>
-        <v>52436</v>
+        <v>52886</v>
       </c>
       <c r="AO45" s="13">
-        <v>288557</v>
+        <v>289007</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="39"/>
-        <v>0.99699061597357541</v>
+        <v>0.99854540680238268</v>
       </c>
       <c r="AQ45" s="7">
         <v>348161</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="40"/>
-        <v>64508</v>
+        <v>65635</v>
       </c>
       <c r="AT45" s="13">
-        <v>344802</v>
+        <v>345929</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="41"/>
-        <v>0.99035216465945353</v>
+        <v>0.99358917282521597</v>
       </c>
       <c r="AV45" s="7">
         <v>296165</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="42"/>
-        <v>50207</v>
+        <v>51353</v>
       </c>
       <c r="AY45" s="13">
-        <v>292240</v>
+        <v>293386</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="43"/>
-        <v>0.98674725237620919</v>
+        <v>0.99061671703273513</v>
       </c>
       <c r="BA45" s="7">
         <v>300603</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="44"/>
-        <v>54455</v>
+        <v>56393</v>
       </c>
       <c r="BD45" s="13">
-        <v>293938</v>
+        <v>295876</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="45"/>
-        <v>0.97782789925582914</v>
+        <v>0.98427494070252131</v>
       </c>
       <c r="BF45" s="7">
         <v>359430</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="46"/>
-        <v>66625</v>
-      </c>
-      <c r="BI45" s="13">
-        <v>340532</v>
+        <v>73383</v>
+      </c>
+      <c r="BI45" s="6">
+        <v>347290</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="47"/>
-        <v>0.9474223075424979</v>
+        <v>0.96622429958545475</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F46" s="13">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.0304526748971194</v>
+        <v>1.0320987654320988</v>
       </c>
       <c r="H46" s="7">
         <v>2594</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="K46" s="13">
-        <v>2644</v>
+        <v>2649</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0192752505782574</v>
+        <v>1.0212027756360833</v>
       </c>
       <c r="M46" s="7">
         <v>8454</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="P46" s="13">
-        <v>8583</v>
+        <v>8596</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0152590489709012</v>
+        <v>1.0167967825881239</v>
       </c>
       <c r="R46" s="7">
         <v>2484</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="U46" s="13">
-        <v>2591</v>
+        <v>2596</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.0430756843800322</v>
+        <v>1.0450885668276972</v>
       </c>
       <c r="W46" s="7">
         <v>2748</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="Z46" s="13">
-        <v>2687</v>
+        <v>2694</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.97780203784570596</v>
+        <v>0.98034934497816595</v>
       </c>
       <c r="AB46" s="7">
         <v>8770</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2055</v>
+        <v>2076</v>
       </c>
       <c r="AE46" s="13">
-        <v>8798</v>
+        <v>8819</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.0031927023945268</v>
+        <v>1.005587229190422</v>
       </c>
       <c r="AG46" s="7">
         <v>2523</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="36"/>
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="AJ46" s="13">
-        <v>2550</v>
+        <v>2560</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="37"/>
-        <v>1.0107015457788346</v>
+        <v>1.0146650812524771</v>
       </c>
       <c r="AL46" s="7">
         <v>2722</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="38"/>
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="AO46" s="13">
-        <v>2672</v>
+        <v>2685</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="39"/>
-        <v>0.98163115356355624</v>
+        <v>0.98640705363703163</v>
       </c>
       <c r="AQ46" s="7">
         <v>8967</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="40"/>
-        <v>1620</v>
+        <v>1693</v>
       </c>
       <c r="AT46" s="13">
-        <v>8850</v>
+        <v>8923</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="41"/>
-        <v>0.98695215791234525</v>
+        <v>0.99509311921489907</v>
       </c>
       <c r="AV46" s="7">
         <v>2626</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="42"/>
-        <v>466</v>
+        <v>499</v>
       </c>
       <c r="AY46" s="13">
-        <v>2596</v>
+        <v>2629</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="43"/>
-        <v>0.98857578065498852</v>
+        <v>1.0011424219345011</v>
       </c>
       <c r="BA46" s="7">
         <v>2791</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="44"/>
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="BD46" s="13">
-        <v>2626</v>
+        <v>2668</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="45"/>
-        <v>0.94088140451451097</v>
+        <v>0.95592977427445358</v>
       </c>
       <c r="BF46" s="7">
         <v>9093</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="46"/>
-        <v>1295</v>
-      </c>
-      <c r="BI46" s="13">
-        <v>8482</v>
+        <v>1478</v>
+      </c>
+      <c r="BI46" s="6">
+        <v>8665</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="47"/>
-        <v>0.93280545474540855</v>
+        <v>0.95293082591004064</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9249,14 +9249,14 @@
       </c>
       <c r="AS47" s="20">
         <f t="shared" si="40"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT47" s="13">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU47" s="21">
         <f t="shared" si="41"/>
-        <v>0.93670886075949367</v>
+        <v>0.94936708860759489</v>
       </c>
       <c r="AV47" s="7">
         <v>75</v>
@@ -9302,7 +9302,7 @@
         <f t="shared" si="46"/>
         <v>2</v>
       </c>
-      <c r="BI47" s="13">
+      <c r="BI47" s="6">
         <v>70</v>
       </c>
       <c r="BJ47" s="21">
@@ -9311,10 +9311,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="9">
         <f>SUM(C10:C47)</f>
         <v>8623084</v>
@@ -9325,15 +9325,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1587709</v>
+        <v>1589681</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8589756</v>
+        <v>8591728</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99613502547348487</v>
+        <v>0.99636371395663081</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9345,15 +9345,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1548869</v>
+        <v>1551267</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8698115</v>
+        <v>8700513</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.99145070299399796</v>
+        <v>0.99172403793907271</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9365,15 +9365,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2516724</v>
+        <v>2521517</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>13286321</v>
+        <v>13291114</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.9948208568295992</v>
+        <v>0.99517973543615879</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9385,15 +9385,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1553819</v>
+        <v>1557431</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8732020</v>
+        <v>8735632</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.99559644550535753</v>
+        <v>0.99600827396671765</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9405,15 +9405,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1564457</v>
+        <v>1569259</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8820430</v>
+        <v>8825232</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98744561057603453</v>
+        <v>0.98798319364420528</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9425,15 +9425,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2359452</v>
+        <v>2370407</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>13496175</v>
+        <v>13507130</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.9917962552387195</v>
+        <v>0.9926013076314264</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9445,15 +9445,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" si="36"/>
-        <v>1572341</v>
+        <v>1583326</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8857200</v>
+        <v>8868185</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" si="37"/>
-        <v>0.99328212388237258</v>
+        <v>0.99451402607842188</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9465,15 +9465,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="38"/>
-        <v>1482647</v>
+        <v>1499271</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>9106527</v>
+        <v>9123151</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="39"/>
-        <v>0.99771752182449247</v>
+        <v>0.99953885899098971</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9485,15 +9485,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="40"/>
-        <v>2247457</v>
+        <v>2294379</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>13888518</v>
+        <v>13935440</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="41"/>
-        <v>0.99366057039627254</v>
+        <v>0.99701762701557006</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9505,15 +9505,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="42"/>
-        <v>1380167</v>
+        <v>1418612</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>9179229</v>
+        <v>9217674</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="43"/>
-        <v>0.99228879283226257</v>
+        <v>0.99644475654560227</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9525,15 +9525,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="44"/>
-        <v>1389411</v>
+        <v>1450733</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>9280613</v>
+        <v>9341935</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="45"/>
-        <v>0.97992842137940106</v>
+        <v>0.98640333533775992</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9545,15 +9545,15 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="46"/>
-        <v>2320264</v>
+        <v>2566976</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13725235</v>
+        <v>13971947</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="47"/>
-        <v>0.95112065041263372</v>
+        <v>0.96821710653193527</v>
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.3">
@@ -9820,6 +9820,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A8:A9"/>
@@ -9830,12 +9836,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2025-2026.xlsx
+++ b/gstdatabase/GSTR-3B-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C73E93-B0A7-4236-A837-1B5BFFCDECB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5B3360-1307-40A2-8D87-E681E0F0D192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -415,6 +415,9 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,9 +435,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -727,7 +727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BJ59"/>
+  <dimension ref="A1:BJ57"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -829,10 +829,10 @@
       <c r="AF2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="29"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1003,100 +1003,100 @@
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <v>45748</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="24">
         <v>45778</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23">
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="24">
         <v>45809</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23">
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="24">
         <v>45839</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="24">
         <v>45870</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="23">
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="24">
         <v>45901</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="23">
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="24">
         <v>45931</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="23">
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="24">
         <v>45962</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="23">
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="26"/>
+      <c r="AQ8" s="24">
         <v>45992</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="23">
+      <c r="AR8" s="25"/>
+      <c r="AS8" s="25"/>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="26"/>
+      <c r="AV8" s="24">
         <v>46023</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="25"/>
-      <c r="BA8" s="23">
+      <c r="AW8" s="25"/>
+      <c r="AX8" s="25"/>
+      <c r="AY8" s="25"/>
+      <c r="AZ8" s="26"/>
+      <c r="BA8" s="24">
         <v>46054</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="23">
+      <c r="BB8" s="25"/>
+      <c r="BC8" s="25"/>
+      <c r="BD8" s="25"/>
+      <c r="BE8" s="26"/>
+      <c r="BF8" s="24">
         <v>46082</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="25"/>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="25"/>
+      <c r="BI8" s="25"/>
+      <c r="BJ8" s="26"/>
     </row>
     <row r="9" spans="1:62" s="15" customFormat="1" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1293,14 +1293,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15056</v>
+        <v>15071</v>
       </c>
       <c r="F10" s="13">
-        <v>74288</v>
+        <v>74303</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0013344296324254</v>
+        <v>1.0015366159403685</v>
       </c>
       <c r="H10" s="7">
         <v>75899</v>
@@ -1310,14 +1310,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>14909</v>
+        <v>14934</v>
       </c>
       <c r="K10" s="13">
-        <v>74993</v>
+        <v>75018</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.98806308383509667</v>
+        <v>0.98839246893898469</v>
       </c>
       <c r="M10" s="7">
         <v>134494</v>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>26248</v>
+        <v>26306</v>
       </c>
       <c r="P10" s="13">
-        <v>134084</v>
+        <v>134142</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99695153687153326</v>
+        <v>0.99738278287507254</v>
       </c>
       <c r="R10" s="7">
         <v>73914</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>13933</v>
+        <v>13970</v>
       </c>
       <c r="U10" s="13">
-        <v>73789</v>
+        <v>73826</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>0.99830884541494169</v>
+        <v>0.99880942717211896</v>
       </c>
       <c r="W10" s="7">
         <v>75592</v>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14015</v>
+        <v>14060</v>
       </c>
       <c r="Z10" s="13">
-        <v>74698</v>
+        <v>74743</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.98817335167742615</v>
+        <v>0.9887686527674886</v>
       </c>
       <c r="AB10" s="7">
         <v>136558</v>
@@ -1378,14 +1378,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>24066</v>
+        <v>24173</v>
       </c>
       <c r="AE10" s="13">
-        <v>135918</v>
+        <v>136025</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99531334670982297</v>
+        <v>0.99609689655677436</v>
       </c>
       <c r="AG10" s="7">
         <v>73704</v>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14073</v>
+        <v>14148</v>
       </c>
       <c r="AJ10" s="13">
-        <v>73485</v>
+        <v>73560</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99702865516118533</v>
+        <v>0.99804623901009448</v>
       </c>
       <c r="AL10" s="7">
         <v>75897</v>
@@ -1412,14 +1412,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>12852</v>
+        <v>12968</v>
       </c>
       <c r="AO10" s="13">
-        <v>76047</v>
+        <v>76163</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>1.001976362702083</v>
+        <v>1.0035047498583607</v>
       </c>
       <c r="AQ10" s="7">
         <v>140117</v>
@@ -1429,14 +1429,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>24949</v>
+        <v>25307</v>
       </c>
       <c r="AT10" s="13">
-        <v>139907</v>
+        <v>140265</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.99850125252467581</v>
+        <v>1.0010562601254667</v>
       </c>
       <c r="AV10" s="7">
         <v>75508</v>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>13359</v>
+        <v>13617</v>
       </c>
       <c r="AY10" s="13">
-        <v>75755</v>
+        <v>76013</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>1.0032711765640727</v>
+        <v>1.0066880330561001</v>
       </c>
       <c r="BA10" s="7">
         <v>78056</v>
@@ -1463,14 +1463,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13164</v>
+        <v>13576</v>
       </c>
       <c r="BD10" s="13">
-        <v>77160</v>
+        <v>77572</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.98852106180178334</v>
+        <v>0.9937993235625705</v>
       </c>
       <c r="BF10" s="7">
         <v>144885</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>30304</v>
+        <v>32461</v>
       </c>
       <c r="BI10" s="6">
-        <v>140346</v>
+        <v>142503</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.96867170514546019</v>
+        <v>0.98355937467646759</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8641</v>
+        <v>8654</v>
       </c>
       <c r="F11" s="13">
-        <v>47787</v>
+        <v>47800</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99899655064283477</v>
+        <v>0.99926831817706696</v>
       </c>
       <c r="H11" s="7">
         <v>49123</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8317</v>
+        <v>8333</v>
       </c>
       <c r="K11" s="13">
-        <v>48303</v>
+        <v>48319</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98330720843596686</v>
+        <v>0.98363292144209435</v>
       </c>
       <c r="M11" s="7">
         <v>111861</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>19012</v>
+        <v>19051</v>
       </c>
       <c r="P11" s="13">
-        <v>111201</v>
+        <v>111240</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99409982031270949</v>
+        <v>0.9944484672942312</v>
       </c>
       <c r="R11" s="7">
         <v>47958</v>
@@ -1556,14 +1556,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8102</v>
+        <v>8122</v>
       </c>
       <c r="U11" s="13">
-        <v>47696</v>
+        <v>47716</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99453688644230365</v>
+        <v>0.9949539180115935</v>
       </c>
       <c r="W11" s="7">
         <v>49731</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8118</v>
+        <v>8144</v>
       </c>
       <c r="Z11" s="13">
-        <v>48320</v>
+        <v>48346</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.971627355170819</v>
+        <v>0.97215016790331987</v>
       </c>
       <c r="AB11" s="7">
         <v>113134</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>19550</v>
+        <v>19630</v>
       </c>
       <c r="AE11" s="13">
-        <v>111930</v>
+        <v>112010</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.98935775275337212</v>
+        <v>0.99006487881627092</v>
       </c>
       <c r="AG11" s="7">
         <v>48119</v>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>7865</v>
+        <v>7904</v>
       </c>
       <c r="AJ11" s="13">
-        <v>47737</v>
+        <v>47776</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99206134790831069</v>
+        <v>0.99287183856688621</v>
       </c>
       <c r="AL11" s="7">
         <v>49938</v>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7342</v>
+        <v>7403</v>
       </c>
       <c r="AO11" s="13">
-        <v>49028</v>
+        <v>49089</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98177740398093638</v>
+        <v>0.98299891865913736</v>
       </c>
       <c r="AQ11" s="7">
         <v>114343</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15769</v>
+        <v>16008</v>
       </c>
       <c r="AT11" s="13">
-        <v>113508</v>
+        <v>113747</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99269741042302551</v>
+        <v>0.99478761270912952</v>
       </c>
       <c r="AV11" s="7">
         <v>49251</v>
@@ -1658,14 +1658,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>6911</v>
+        <v>7055</v>
       </c>
       <c r="AY11" s="13">
-        <v>48674</v>
+        <v>48818</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.98828450183752614</v>
+        <v>0.99120830033907936</v>
       </c>
       <c r="BA11" s="7">
         <v>50523</v>
@@ -1675,14 +1675,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7099</v>
+        <v>7342</v>
       </c>
       <c r="BD11" s="13">
-        <v>49298</v>
+        <v>49541</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97575361716445974</v>
+        <v>0.98056330780040768</v>
       </c>
       <c r="BF11" s="7">
         <v>116408</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>16923</v>
+        <v>18510</v>
       </c>
       <c r="BI11" s="6">
-        <v>112380</v>
+        <v>113967</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.96539756717751357</v>
+        <v>0.97903065081437701</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>29263</v>
+        <v>29293</v>
       </c>
       <c r="F12" s="13">
-        <v>182236</v>
+        <v>182266</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99719832775187689</v>
+        <v>0.99736248823516538</v>
       </c>
       <c r="H12" s="7">
         <v>186824</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>26548</v>
+        <v>26580</v>
       </c>
       <c r="K12" s="13">
-        <v>184663</v>
+        <v>184695</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98843296364492783</v>
+        <v>0.98860424784824219</v>
       </c>
       <c r="M12" s="7">
         <v>372375</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>61002</v>
+        <v>61090</v>
       </c>
       <c r="P12" s="13">
-        <v>370616</v>
+        <v>370704</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99527626720375961</v>
+        <v>0.99551258811681775</v>
       </c>
       <c r="R12" s="7">
         <v>184659</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>28321</v>
+        <v>28372</v>
       </c>
       <c r="U12" s="13">
-        <v>183665</v>
+        <v>183716</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99461710504226708</v>
+        <v>0.99489328979361957</v>
       </c>
       <c r="W12" s="7">
         <v>189081</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>29732</v>
+        <v>29799</v>
       </c>
       <c r="Z12" s="13">
-        <v>185649</v>
+        <v>185716</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98184904882034685</v>
+        <v>0.98220339431249037</v>
       </c>
       <c r="AB12" s="7">
         <v>377441</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>65371</v>
+        <v>65561</v>
       </c>
       <c r="AE12" s="13">
-        <v>373992</v>
+        <v>374182</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99086214799134165</v>
+        <v>0.99136553792513271</v>
       </c>
       <c r="AG12" s="7">
         <v>186148</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>28490</v>
+        <v>28607</v>
       </c>
       <c r="AJ12" s="13">
-        <v>184931</v>
+        <v>185048</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99346219137460512</v>
+        <v>0.99409072351032512</v>
       </c>
       <c r="AL12" s="7">
         <v>192239</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>26709</v>
+        <v>26924</v>
       </c>
       <c r="AO12" s="13">
-        <v>190962</v>
+        <v>191177</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.99335722720155639</v>
+        <v>0.99447562669385503</v>
       </c>
       <c r="AQ12" s="7">
         <v>384779</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>60418</v>
+        <v>61162</v>
       </c>
       <c r="AT12" s="13">
-        <v>382620</v>
+        <v>383364</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99438898692496214</v>
+        <v>0.99632256438111233</v>
       </c>
       <c r="AV12" s="7">
         <v>191743</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>25266</v>
+        <v>25858</v>
       </c>
       <c r="AY12" s="13">
-        <v>190771</v>
+        <v>191363</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99493071455020521</v>
+        <v>0.9980181805854712</v>
       </c>
       <c r="BA12" s="7">
         <v>197493</v>
@@ -1887,14 +1887,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>26346</v>
+        <v>27188</v>
       </c>
       <c r="BD12" s="13">
-        <v>193653</v>
+        <v>194495</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.9805562728805578</v>
+        <v>0.98481971512914379</v>
       </c>
       <c r="BF12" s="7">
         <v>393305</v>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>65901</v>
+        <v>70907</v>
       </c>
       <c r="BI12" s="6">
-        <v>381880</v>
+        <v>386886</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.97095129733921515</v>
+        <v>0.98367933283329734</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1929,14 +1929,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="F13" s="13">
-        <v>18068</v>
+        <v>18070</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.001829775436651</v>
+        <v>1.0019406709176601</v>
       </c>
       <c r="H13" s="7">
         <v>18257</v>
@@ -1946,14 +1946,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="K13" s="13">
-        <v>18099</v>
+        <v>18103</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>0.99134578517828775</v>
+        <v>0.99156487922440706</v>
       </c>
       <c r="M13" s="7">
         <v>29011</v>
@@ -1963,14 +1963,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>5001</v>
+        <v>5012</v>
       </c>
       <c r="P13" s="13">
-        <v>28995</v>
+        <v>29006</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99944848505739203</v>
+        <v>0.99982765158043496</v>
       </c>
       <c r="R13" s="7">
         <v>18140</v>
@@ -1980,14 +1980,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2796</v>
+        <v>2802</v>
       </c>
       <c r="U13" s="13">
-        <v>18163</v>
+        <v>18169</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>1.0012679162072768</v>
+        <v>1.0015986769570011</v>
       </c>
       <c r="W13" s="7">
         <v>18401</v>
@@ -1997,14 +1997,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2807</v>
+        <v>2812</v>
       </c>
       <c r="Z13" s="13">
-        <v>18238</v>
+        <v>18243</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.99114178577251233</v>
+        <v>0.99141351013531875</v>
       </c>
       <c r="AB13" s="7">
         <v>29242</v>
@@ -2014,14 +2014,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4822</v>
+        <v>4843</v>
       </c>
       <c r="AE13" s="13">
-        <v>29185</v>
+        <v>29206</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.99805074892278234</v>
+        <v>0.99876889405649405</v>
       </c>
       <c r="AG13" s="7">
         <v>18261</v>
@@ -2031,14 +2031,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2705</v>
+        <v>2713</v>
       </c>
       <c r="AJ13" s="13">
-        <v>18412</v>
+        <v>18420</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>1.0082689885548437</v>
+        <v>1.0087070806637095</v>
       </c>
       <c r="AL13" s="7">
         <v>18637</v>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2558</v>
+        <v>2573</v>
       </c>
       <c r="AO13" s="13">
-        <v>18720</v>
+        <v>18735</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>1.0044535064656328</v>
+        <v>1.0052583570317111</v>
       </c>
       <c r="AQ13" s="7">
         <v>29668</v>
@@ -2065,14 +2065,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4256</v>
+        <v>4318</v>
       </c>
       <c r="AT13" s="13">
-        <v>29732</v>
+        <v>29794</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.0021572064176891</v>
+        <v>1.0042470001348254</v>
       </c>
       <c r="AV13" s="7">
         <v>18676</v>
@@ -2082,14 +2082,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2459</v>
+        <v>2502</v>
       </c>
       <c r="AY13" s="13">
-        <v>18830</v>
+        <v>18873</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.0082458770614693</v>
+        <v>1.0105482972799316</v>
       </c>
       <c r="BA13" s="7">
         <v>19025</v>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2450</v>
+        <v>2523</v>
       </c>
       <c r="BD13" s="13">
-        <v>19037</v>
+        <v>19110</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>1.0006307490144546</v>
+        <v>1.0044678055190539</v>
       </c>
       <c r="BF13" s="7">
         <v>30254</v>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>4446</v>
+        <v>4838</v>
       </c>
       <c r="BI13" s="6">
-        <v>29571</v>
+        <v>29963</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>0.97742447279698552</v>
+        <v>0.99038143716533356</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>19331</v>
+        <v>19361</v>
       </c>
       <c r="F14" s="13">
-        <v>95479</v>
+        <v>95509</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>1.0091530762157421</v>
+        <v>1.0094701573779501</v>
       </c>
       <c r="H14" s="7">
         <v>97351</v>
@@ -2158,14 +2158,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18870</v>
+        <v>18907</v>
       </c>
       <c r="K14" s="13">
-        <v>97296</v>
+        <v>97333</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.99943503405203848</v>
+        <v>0.99981510205339441</v>
       </c>
       <c r="M14" s="7">
         <v>172809</v>
@@ -2175,14 +2175,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>35713</v>
+        <v>35796</v>
       </c>
       <c r="P14" s="13">
-        <v>172476</v>
+        <v>172559</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.998073017030363</v>
+        <v>0.99855331608886111</v>
       </c>
       <c r="R14" s="7">
         <v>97326</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>17942</v>
+        <v>17991</v>
       </c>
       <c r="U14" s="13">
-        <v>96795</v>
+        <v>96844</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99454410948770111</v>
+        <v>0.99504757207734829</v>
       </c>
       <c r="W14" s="7">
         <v>98912</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17656</v>
+        <v>17719</v>
       </c>
       <c r="Z14" s="13">
-        <v>97935</v>
+        <v>97998</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.99012253316078935</v>
+        <v>0.99075946295697181</v>
       </c>
       <c r="AB14" s="7">
         <v>175426</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34367</v>
+        <v>34523</v>
       </c>
       <c r="AE14" s="13">
-        <v>175075</v>
+        <v>175231</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.99799915633942515</v>
+        <v>0.99888842018856949</v>
       </c>
       <c r="AG14" s="7">
         <v>98057</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>18542</v>
+        <v>18650</v>
       </c>
       <c r="AJ14" s="13">
-        <v>98140</v>
+        <v>98248</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>1.0008464464546132</v>
+        <v>1.0019478466606158</v>
       </c>
       <c r="AL14" s="7">
         <v>101581</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17736</v>
+        <v>17915</v>
       </c>
       <c r="AO14" s="13">
-        <v>102415</v>
+        <v>102594</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>1.0082101967887696</v>
+        <v>1.009972337346551</v>
       </c>
       <c r="AQ14" s="7">
         <v>182247</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>30921</v>
+        <v>31416</v>
       </c>
       <c r="AT14" s="13">
-        <v>181815</v>
+        <v>182310</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99762959061054501</v>
+        <v>1.0003456847026289</v>
       </c>
       <c r="AV14" s="7">
         <v>102257</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17283</v>
+        <v>17614</v>
       </c>
       <c r="AY14" s="13">
-        <v>102791</v>
+        <v>103122</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.0052221363818614</v>
+        <v>1.0084590785960863</v>
       </c>
       <c r="BA14" s="7">
         <v>106311</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17132</v>
+        <v>17594</v>
       </c>
       <c r="BD14" s="13">
-        <v>105042</v>
+        <v>105504</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.988063323644778</v>
+        <v>0.99240906397268391</v>
       </c>
       <c r="BF14" s="7">
         <v>189210</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>35521</v>
+        <v>38259</v>
       </c>
       <c r="BI14" s="6">
-        <v>183160</v>
+        <v>185898</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.96802494582738752</v>
+        <v>0.98249563976534005</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>55193</v>
+        <v>55227</v>
       </c>
       <c r="F15" s="13">
-        <v>324366</v>
+        <v>324400</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99867609207009933</v>
+        <v>0.99878077316223102</v>
       </c>
       <c r="H15" s="7">
         <v>331968</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>52179</v>
+        <v>52221</v>
       </c>
       <c r="K15" s="13">
-        <v>329542</v>
+        <v>329584</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.99269206670522459</v>
+        <v>0.99281858492384811</v>
       </c>
       <c r="M15" s="7">
         <v>549212</v>
@@ -2387,14 +2387,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>93368</v>
+        <v>93456</v>
       </c>
       <c r="P15" s="13">
-        <v>547304</v>
+        <v>547392</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99652593169850623</v>
+        <v>0.9966861612637743</v>
       </c>
       <c r="R15" s="7">
         <v>333160</v>
@@ -2404,14 +2404,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>53902</v>
+        <v>53963</v>
       </c>
       <c r="U15" s="13">
-        <v>332234</v>
+        <v>332295</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99722055468843795</v>
+        <v>0.99740364989794694</v>
       </c>
       <c r="W15" s="7">
         <v>340519</v>
@@ -2421,14 +2421,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>54844</v>
+        <v>54923</v>
       </c>
       <c r="Z15" s="13">
-        <v>336739</v>
+        <v>336818</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98889929783653774</v>
+        <v>0.98913129663836674</v>
       </c>
       <c r="AB15" s="7">
         <v>562036</v>
@@ -2438,14 +2438,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>94806</v>
+        <v>95039</v>
       </c>
       <c r="AE15" s="13">
-        <v>558220</v>
+        <v>558453</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99321039933385047</v>
+        <v>0.99362496352546814</v>
       </c>
       <c r="AG15" s="7">
         <v>340264</v>
@@ -2455,14 +2455,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>55946</v>
+        <v>56129</v>
       </c>
       <c r="AJ15" s="13">
-        <v>339080</v>
+        <v>339263</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99652034890555563</v>
+        <v>0.99705816660005175</v>
       </c>
       <c r="AL15" s="7">
         <v>350627</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>54226</v>
+        <v>54607</v>
       </c>
       <c r="AO15" s="13">
-        <v>352109</v>
+        <v>352490</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>1.0042267138583167</v>
+        <v>1.005313338676143</v>
       </c>
       <c r="AQ15" s="7">
         <v>580651</v>
@@ -2489,14 +2489,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>82155</v>
+        <v>83145</v>
       </c>
       <c r="AT15" s="13">
-        <v>580080</v>
+        <v>581070</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99901662099953326</v>
+        <v>1.0007216038549835</v>
       </c>
       <c r="AV15" s="7">
         <v>355536</v>
@@ -2506,14 +2506,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>50646</v>
+        <v>51608</v>
       </c>
       <c r="AY15" s="13">
-        <v>355666</v>
+        <v>356628</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>1.000365645110481</v>
+        <v>1.003071418928041</v>
       </c>
       <c r="BA15" s="7">
         <v>365201</v>
@@ -2523,14 +2523,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>50693</v>
+        <v>52185</v>
       </c>
       <c r="BD15" s="13">
-        <v>361675</v>
+        <v>363167</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.9903450428668048</v>
+        <v>0.99443046431964865</v>
       </c>
       <c r="BF15" s="7">
         <v>600313</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>94013</v>
+        <v>101035</v>
       </c>
       <c r="BI15" s="6">
-        <v>585049</v>
+        <v>592071</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.97457326428046698</v>
+        <v>0.9862704955581505</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>77078</v>
+        <v>77190</v>
       </c>
       <c r="F16" s="13">
-        <v>451817</v>
+        <v>451929</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99624932196737503</v>
+        <v>0.99649628019174541</v>
       </c>
       <c r="H16" s="7">
         <v>461360</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74818</v>
+        <v>74951</v>
       </c>
       <c r="K16" s="13">
-        <v>458637</v>
+        <v>458770</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.99409788451534598</v>
+        <v>0.99438616264955781</v>
       </c>
       <c r="M16" s="7">
         <v>788355</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>134286</v>
+        <v>134567</v>
       </c>
       <c r="P16" s="13">
-        <v>787285</v>
+        <v>787566</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99864274343411286</v>
+        <v>0.99899918184066827</v>
       </c>
       <c r="R16" s="7">
         <v>462019</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78129</v>
+        <v>78315</v>
       </c>
       <c r="U16" s="13">
-        <v>462277</v>
+        <v>462463</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>1.0005584185931748</v>
+        <v>1.0009609994394171</v>
       </c>
       <c r="W16" s="7">
         <v>472236</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>78798</v>
+        <v>79017</v>
       </c>
       <c r="Z16" s="13">
-        <v>466877</v>
+        <v>467096</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98865186051042275</v>
+        <v>0.98911561168568263</v>
       </c>
       <c r="AB16" s="7">
         <v>804216</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>133425</v>
+        <v>133923</v>
       </c>
       <c r="AE16" s="13">
-        <v>799486</v>
+        <v>799984</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.99411849552856446</v>
+        <v>0.99473773215156125</v>
       </c>
       <c r="AG16" s="7">
         <v>471201</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>78815</v>
+        <v>79156</v>
       </c>
       <c r="AJ16" s="13">
-        <v>469204</v>
+        <v>469545</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.9957618935443685</v>
+        <v>0.99648557621906575</v>
       </c>
       <c r="AL16" s="7">
         <v>484445</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>78562</v>
+        <v>79189</v>
       </c>
       <c r="AO16" s="13">
-        <v>488706</v>
+        <v>489333</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>1.0087956321151008</v>
+        <v>1.0100898966858982</v>
       </c>
       <c r="AQ16" s="7">
         <v>831010</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>128272</v>
+        <v>129840</v>
       </c>
       <c r="AT16" s="13">
-        <v>830454</v>
+        <v>832022</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99933093464579248</v>
+        <v>1.0012177952130541</v>
       </c>
       <c r="AV16" s="7">
         <v>496237</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>72491</v>
+        <v>73928</v>
       </c>
       <c r="AY16" s="13">
-        <v>495359</v>
+        <v>496796</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.99823068412875304</v>
+        <v>1.0011264778724682</v>
       </c>
       <c r="BA16" s="7">
         <v>510690</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>73189</v>
+        <v>75288</v>
       </c>
       <c r="BD16" s="13">
-        <v>503090</v>
+        <v>505189</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98511817345160468</v>
+        <v>0.98922829896806286</v>
       </c>
       <c r="BF16" s="7">
         <v>859721</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>126756</v>
+        <v>136081</v>
       </c>
       <c r="BI16" s="6">
-        <v>836449</v>
+        <v>845774</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.97293075311641797</v>
+        <v>0.98377729519227752</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>58591</v>
+        <v>58639</v>
       </c>
       <c r="F17" s="13">
-        <v>341359</v>
+        <v>341407</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99737041246541358</v>
+        <v>0.99751065713392484</v>
       </c>
       <c r="H17" s="7">
         <v>352243</v>
@@ -2794,14 +2794,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>55135</v>
+        <v>55193</v>
       </c>
       <c r="K17" s="13">
-        <v>348354</v>
+        <v>348412</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98895932637412243</v>
+        <v>0.9891239854305125</v>
       </c>
       <c r="M17" s="7">
         <v>765449</v>
@@ -2811,14 +2811,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>133172</v>
+        <v>133412</v>
       </c>
       <c r="P17" s="13">
-        <v>763926</v>
+        <v>764166</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.9980103181270078</v>
+        <v>0.99832385959090675</v>
       </c>
       <c r="R17" s="7">
         <v>346814</v>
@@ -2828,14 +2828,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>56943</v>
+        <v>57041</v>
       </c>
       <c r="U17" s="13">
-        <v>348410</v>
+        <v>348508</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0046018903504472</v>
+        <v>1.0048844625649485</v>
       </c>
       <c r="W17" s="7">
         <v>360071</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>59275</v>
+        <v>59410</v>
       </c>
       <c r="Z17" s="13">
-        <v>356480</v>
+        <v>356615</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.99002696690374958</v>
+        <v>0.99040189295999959</v>
       </c>
       <c r="AB17" s="7">
         <v>784641</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145315</v>
+        <v>145791</v>
       </c>
       <c r="AE17" s="13">
-        <v>782193</v>
+        <v>782669</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99688010185549825</v>
+        <v>0.99748674871692911</v>
       </c>
       <c r="AG17" s="7">
         <v>355351</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>59962</v>
+        <v>60212</v>
       </c>
       <c r="AJ17" s="13">
-        <v>356529</v>
+        <v>356779</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>1.0033150321794508</v>
+        <v>1.0040185619289097</v>
       </c>
       <c r="AL17" s="7">
         <v>371770</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>55316</v>
+        <v>55782</v>
       </c>
       <c r="AO17" s="13">
-        <v>372273</v>
+        <v>372739</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>1.0013529870618931</v>
+        <v>1.0026064502246013</v>
       </c>
       <c r="AQ17" s="7">
         <v>810773</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>122907</v>
+        <v>124519</v>
       </c>
       <c r="AT17" s="13">
-        <v>809562</v>
+        <v>811174</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99850636368009293</v>
+        <v>1.0004945897310344</v>
       </c>
       <c r="AV17" s="7">
         <v>369648</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>53609</v>
+        <v>54578</v>
       </c>
       <c r="AY17" s="13">
-        <v>371040</v>
+        <v>372009</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0037657447084793</v>
+        <v>1.0063871575120114</v>
       </c>
       <c r="BA17" s="7">
         <v>385393</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>54518</v>
+        <v>56043</v>
       </c>
       <c r="BD17" s="13">
-        <v>381467</v>
+        <v>382992</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98981299608451634</v>
+        <v>0.99376999582244618</v>
       </c>
       <c r="BF17" s="7">
         <v>839843</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>139318</v>
+        <v>150382</v>
       </c>
       <c r="BI17" s="6">
-        <v>814750</v>
+        <v>825814</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.97012179657388342</v>
+        <v>0.9832956874082418</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2989,14 +2989,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>190466</v>
+        <v>190670</v>
       </c>
       <c r="F18" s="13">
-        <v>1064002</v>
+        <v>1064206</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99359951291303406</v>
+        <v>0.99379001471719819</v>
       </c>
       <c r="H18" s="7">
         <v>1089051</v>
@@ -3006,14 +3006,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>195052</v>
+        <v>195301</v>
       </c>
       <c r="K18" s="13">
-        <v>1079610</v>
+        <v>1079859</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.99133098449934853</v>
+        <v>0.99155962392945785</v>
       </c>
       <c r="M18" s="7">
         <v>1637429</v>
@@ -3023,14 +3023,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>299903</v>
+        <v>300432</v>
       </c>
       <c r="P18" s="13">
-        <v>1623940</v>
+        <v>1624469</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99176208556218315</v>
+        <v>0.99208515300510736</v>
       </c>
       <c r="R18" s="7">
         <v>1090030</v>
@@ -3040,14 +3040,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>190536</v>
+        <v>190916</v>
       </c>
       <c r="U18" s="13">
-        <v>1079262</v>
+        <v>1079642</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99012137280625301</v>
+        <v>0.99046998706457623</v>
       </c>
       <c r="W18" s="7">
         <v>1107435</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>193320</v>
+        <v>193828</v>
       </c>
       <c r="Z18" s="13">
-        <v>1089582</v>
+        <v>1090090</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.9838789635509082</v>
+        <v>0.98433768121831078</v>
       </c>
       <c r="AB18" s="7">
         <v>1665905</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>301235</v>
+        <v>302402</v>
       </c>
       <c r="AE18" s="13">
-        <v>1646880</v>
+        <v>1648047</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98857978095989862</v>
+        <v>0.98928030109760157</v>
       </c>
       <c r="AG18" s="7">
         <v>1104366</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>201904</v>
+        <v>202830</v>
       </c>
       <c r="AJ18" s="13">
-        <v>1094258</v>
+        <v>1095184</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99084723723837931</v>
+        <v>0.99168572737661242</v>
       </c>
       <c r="AL18" s="7">
         <v>1131950</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>189549</v>
+        <v>191153</v>
       </c>
       <c r="AO18" s="13">
-        <v>1132325</v>
+        <v>1133929</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>1.0003312867176113</v>
+        <v>1.0017483104377403</v>
       </c>
       <c r="AQ18" s="7">
         <v>1717059</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>261110</v>
+        <v>264945</v>
       </c>
       <c r="AT18" s="13">
-        <v>1706908</v>
+        <v>1710743</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99408814723314687</v>
+        <v>0.99632161737016611</v>
       </c>
       <c r="AV18" s="7">
         <v>1151692</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>180943</v>
+        <v>184537</v>
       </c>
       <c r="AY18" s="13">
-        <v>1146460</v>
+        <v>1150054</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99545711874355292</v>
+        <v>0.99857774474425454</v>
       </c>
       <c r="BA18" s="7">
         <v>1182353</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>178961</v>
+        <v>184223</v>
       </c>
       <c r="BD18" s="13">
-        <v>1164544</v>
+        <v>1169806</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.9849376624409123</v>
+        <v>0.98938810998069104</v>
       </c>
       <c r="BF18" s="7">
         <v>1777125</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>323086</v>
+        <v>344416</v>
       </c>
       <c r="BI18" s="6">
-        <v>1720315</v>
+        <v>1741645</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.96803263698389252</v>
+        <v>0.98003516916367728</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3201,14 +3201,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>65871</v>
+        <v>65971</v>
       </c>
       <c r="F19" s="13">
-        <v>299712</v>
+        <v>299812</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98067201319289699</v>
+        <v>0.98099921798055745</v>
       </c>
       <c r="H19" s="7">
         <v>314567</v>
@@ -3218,14 +3218,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>68373</v>
+        <v>68506</v>
       </c>
       <c r="K19" s="13">
-        <v>306362</v>
+        <v>306495</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97391652652694016</v>
+        <v>0.97433932993607086</v>
       </c>
       <c r="M19" s="7">
         <v>534704</v>
@@ -3235,14 +3235,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>114808</v>
+        <v>115109</v>
       </c>
       <c r="P19" s="13">
-        <v>525931</v>
+        <v>526232</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.98359279152577872</v>
+        <v>0.98415571980011374</v>
       </c>
       <c r="R19" s="7">
         <v>310887</v>
@@ -3252,14 +3252,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>64301</v>
+        <v>64502</v>
       </c>
       <c r="U19" s="13">
-        <v>305604</v>
+        <v>305805</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.98300668731725671</v>
+        <v>0.98365322448349402</v>
       </c>
       <c r="W19" s="7">
         <v>321022</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>68049</v>
+        <v>68307</v>
       </c>
       <c r="Z19" s="13">
-        <v>310368</v>
+        <v>310626</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96681224339764871</v>
+        <v>0.96761592663431162</v>
       </c>
       <c r="AB19" s="7">
         <v>548160</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>113554</v>
+        <v>114241</v>
       </c>
       <c r="AE19" s="13">
-        <v>535789</v>
+        <v>536476</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.9774317717454758</v>
+        <v>0.97868505545826034</v>
       </c>
       <c r="AG19" s="7">
         <v>315587</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>67181</v>
+        <v>67638</v>
       </c>
       <c r="AJ19" s="13">
-        <v>309135</v>
+        <v>309592</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97955555837217634</v>
+        <v>0.98100365350917496</v>
       </c>
       <c r="AL19" s="7">
         <v>327315</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>61520</v>
+        <v>62279</v>
       </c>
       <c r="AO19" s="13">
-        <v>321588</v>
+        <v>322347</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.98250309335044228</v>
+        <v>0.98482196049676918</v>
       </c>
       <c r="AQ19" s="7">
         <v>564697</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>105771</v>
+        <v>107864</v>
       </c>
       <c r="AT19" s="13">
-        <v>556814</v>
+        <v>558907</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98604030125890518</v>
+        <v>0.9897467137243513</v>
       </c>
       <c r="AV19" s="7">
         <v>330794</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>58697</v>
+        <v>60398</v>
       </c>
       <c r="AY19" s="13">
-        <v>326822</v>
+        <v>328523</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98799252707122864</v>
+        <v>0.99313470014571004</v>
       </c>
       <c r="BA19" s="7">
         <v>346688</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>60170</v>
+        <v>62768</v>
       </c>
       <c r="BD19" s="13">
-        <v>335051</v>
+        <v>337649</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.96643379638176108</v>
+        <v>0.97392756599593866</v>
       </c>
       <c r="BF19" s="7">
         <v>595475</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>126924</v>
+        <v>138280</v>
       </c>
       <c r="BI19" s="6">
-        <v>560551</v>
+        <v>571907</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.94135102229312728</v>
+        <v>0.96042151223812922</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="F20" s="13">
-        <v>6498</v>
+        <v>6499</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99403396053235427</v>
+        <v>0.99418693590331952</v>
       </c>
       <c r="H20" s="7">
         <v>6601</v>
@@ -3430,14 +3430,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="K20" s="13">
-        <v>6521</v>
+        <v>6525</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.98788062414785638</v>
+        <v>0.98848659294046359</v>
       </c>
       <c r="M20" s="7">
         <v>10050</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2569</v>
+        <v>2577</v>
       </c>
       <c r="P20" s="13">
-        <v>10012</v>
+        <v>10020</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.99621890547263681</v>
+        <v>0.9970149253731343</v>
       </c>
       <c r="R20" s="7">
         <v>6485</v>
@@ -3464,14 +3464,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="U20" s="13">
-        <v>6442</v>
+        <v>6450</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.9933693138010794</v>
+        <v>0.99460292983808785</v>
       </c>
       <c r="W20" s="7">
         <v>6573</v>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="Z20" s="13">
-        <v>6446</v>
+        <v>6454</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.98067853339418831</v>
+        <v>0.98189563365282218</v>
       </c>
       <c r="AB20" s="7">
         <v>10123</v>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="AE20" s="13">
-        <v>10013</v>
+        <v>10028</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.98913365603082093</v>
+        <v>0.99061543020843623</v>
       </c>
       <c r="AG20" s="7">
         <v>6547</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1569</v>
+        <v>1586</v>
       </c>
       <c r="AJ20" s="13">
-        <v>6465</v>
+        <v>6482</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.98747517947151364</v>
+        <v>0.99007178860546818</v>
       </c>
       <c r="AL20" s="7">
         <v>6649</v>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1550</v>
+        <v>1571</v>
       </c>
       <c r="AO20" s="13">
-        <v>6539</v>
+        <v>6560</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.98345615882087534</v>
+        <v>0.98661452850052644</v>
       </c>
       <c r="AQ20" s="7">
         <v>10228</v>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2378</v>
+        <v>2430</v>
       </c>
       <c r="AT20" s="13">
-        <v>10072</v>
+        <v>10124</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.98474775127102077</v>
+        <v>0.98983183418068044</v>
       </c>
       <c r="AV20" s="7">
         <v>6568</v>
@@ -3566,14 +3566,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1359</v>
+        <v>1399</v>
       </c>
       <c r="AY20" s="13">
-        <v>6443</v>
+        <v>6483</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.98096833130328864</v>
+        <v>0.98705846528623631</v>
       </c>
       <c r="BA20" s="7">
         <v>6793</v>
@@ -3583,14 +3583,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1354</v>
+        <v>1405</v>
       </c>
       <c r="BD20" s="13">
-        <v>6478</v>
+        <v>6529</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.95362873546297655</v>
+        <v>0.96113646400706609</v>
       </c>
       <c r="BF20" s="7">
         <v>10395</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2342</v>
+        <v>2536</v>
       </c>
       <c r="BI20" s="6">
-        <v>9840</v>
+        <v>10034</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.94660894660894657</v>
+        <v>0.96527176527176528</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4171</v>
+        <v>4194</v>
       </c>
       <c r="F21" s="13">
-        <v>12049</v>
+        <v>12072</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.0032472939217318</v>
+        <v>1.0051623646960866</v>
       </c>
       <c r="H21" s="7">
         <v>12254</v>
@@ -3642,14 +3642,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3806</v>
+        <v>3828</v>
       </c>
       <c r="K21" s="13">
-        <v>12260</v>
+        <v>12282</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>1.0004896360372124</v>
+        <v>1.0022849681736576</v>
       </c>
       <c r="M21" s="7">
         <v>16207</v>
@@ -3659,14 +3659,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>5091</v>
+        <v>5127</v>
       </c>
       <c r="P21" s="13">
-        <v>16347</v>
+        <v>16383</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0086382427346208</v>
+        <v>1.0108595051520948</v>
       </c>
       <c r="R21" s="7">
         <v>12383</v>
@@ -3676,14 +3676,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3908</v>
+        <v>3937</v>
       </c>
       <c r="U21" s="13">
-        <v>12553</v>
+        <v>12582</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.013728498748284</v>
+        <v>1.0160704191229912</v>
       </c>
       <c r="W21" s="7">
         <v>12782</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3970</v>
+        <v>4005</v>
       </c>
       <c r="Z21" s="13">
-        <v>12761</v>
+        <v>12796</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>0.99835706462212481</v>
+        <v>1.0010952902519168</v>
       </c>
       <c r="AB21" s="7">
         <v>16816</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4661</v>
+        <v>4714</v>
       </c>
       <c r="AE21" s="13">
-        <v>16814</v>
+        <v>16867</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>0.99988106565176027</v>
+        <v>1.0030328258801142</v>
       </c>
       <c r="AG21" s="7">
         <v>12696</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3884</v>
+        <v>3933</v>
       </c>
       <c r="AJ21" s="13">
-        <v>12719</v>
+        <v>12768</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0018115942028984</v>
+        <v>1.005671077504726</v>
       </c>
       <c r="AL21" s="7">
         <v>13072</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3814</v>
+        <v>3889</v>
       </c>
       <c r="AO21" s="13">
-        <v>12943</v>
+        <v>13018</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.99013157894736847</v>
+        <v>0.99586903304773566</v>
       </c>
       <c r="AQ21" s="7">
         <v>17310</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4486</v>
+        <v>4616</v>
       </c>
       <c r="AT21" s="13">
-        <v>17112</v>
+        <v>17242</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.98856152512998263</v>
+        <v>0.99607163489312533</v>
       </c>
       <c r="AV21" s="7">
         <v>13094</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3348</v>
+        <v>3490</v>
       </c>
       <c r="AY21" s="13">
-        <v>12837</v>
+        <v>12979</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.98037268978157932</v>
+        <v>0.99121735145868339</v>
       </c>
       <c r="BA21" s="7">
         <v>13518</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3128</v>
+        <v>3322</v>
       </c>
       <c r="BD21" s="13">
-        <v>12909</v>
+        <v>13103</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>0.95494895694629378</v>
+        <v>0.9693001923361444</v>
       </c>
       <c r="BF21" s="7">
         <v>17905</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5236</v>
+        <v>5802</v>
       </c>
       <c r="BI21" s="6">
-        <v>16180</v>
+        <v>16746</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>0.90365819603462716</v>
+        <v>0.93526947779949732</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3837,14 +3837,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1886</v>
+        <v>1898</v>
       </c>
       <c r="F22" s="13">
-        <v>6980</v>
+        <v>6992</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.99771297884505428</v>
+        <v>0.99942824471126357</v>
       </c>
       <c r="H22" s="7">
         <v>7077</v>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1943</v>
+        <v>1957</v>
       </c>
       <c r="K22" s="13">
-        <v>7035</v>
+        <v>7049</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99406528189910981</v>
+        <v>0.99604352126607321</v>
       </c>
       <c r="M22" s="7">
         <v>8504</v>
@@ -3871,14 +3871,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2397</v>
+        <v>2417</v>
       </c>
       <c r="P22" s="13">
-        <v>8515</v>
+        <v>8535</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0012935089369708</v>
+        <v>1.003645343367827</v>
       </c>
       <c r="R22" s="7">
         <v>7111</v>
@@ -3888,14 +3888,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1835</v>
+        <v>1855</v>
       </c>
       <c r="U22" s="13">
-        <v>7076</v>
+        <v>7096</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.99507804809450151</v>
+        <v>0.99789059204050068</v>
       </c>
       <c r="W22" s="7">
         <v>7191</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1743</v>
+        <v>1764</v>
       </c>
       <c r="Z22" s="13">
-        <v>7134</v>
+        <v>7155</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99207342511472674</v>
+        <v>0.99499374217772218</v>
       </c>
       <c r="AB22" s="7">
         <v>8707</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2027</v>
+        <v>2055</v>
       </c>
       <c r="AE22" s="13">
-        <v>8656</v>
+        <v>8684</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.99414264384977602</v>
+        <v>0.99735844722636957</v>
       </c>
       <c r="AG22" s="7">
         <v>7162</v>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1838</v>
+        <v>1863</v>
       </c>
       <c r="AJ22" s="13">
-        <v>7135</v>
+        <v>7160</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.99623010332309414</v>
+        <v>0.99972074839430325</v>
       </c>
       <c r="AL22" s="7">
         <v>7226</v>
@@ -3956,14 +3956,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1660</v>
+        <v>1688</v>
       </c>
       <c r="AO22" s="13">
-        <v>7172</v>
+        <v>7200</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99252698588430666</v>
+        <v>0.99640188209244396</v>
       </c>
       <c r="AQ22" s="7">
         <v>8754</v>
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2350</v>
+        <v>2395</v>
       </c>
       <c r="AT22" s="13">
-        <v>8696</v>
+        <v>8741</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.99337445739090702</v>
+        <v>0.99851496458761713</v>
       </c>
       <c r="AV22" s="7">
         <v>7182</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1709</v>
+        <v>1767</v>
       </c>
       <c r="AY22" s="13">
-        <v>7095</v>
+        <v>7153</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.9878863826232247</v>
+        <v>0.99596212754107494</v>
       </c>
       <c r="BA22" s="7">
         <v>7296</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1599</v>
+        <v>1683</v>
       </c>
       <c r="BD22" s="13">
-        <v>7096</v>
+        <v>7180</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.97258771929824561</v>
+        <v>0.98410087719298245</v>
       </c>
       <c r="BF22" s="7">
         <v>8939</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2248</v>
+        <v>2452</v>
       </c>
       <c r="BI22" s="6">
-        <v>8354</v>
+        <v>8558</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.93455643808032218</v>
+        <v>0.95737778274974827</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4049,14 +4049,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2949</v>
+        <v>2960</v>
       </c>
       <c r="F23" s="13">
-        <v>9182</v>
+        <v>9193</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.97608164133092379</v>
+        <v>0.9772509833103008</v>
       </c>
       <c r="H23" s="7">
         <v>9786</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>3234</v>
+        <v>3247</v>
       </c>
       <c r="K23" s="13">
-        <v>9308</v>
+        <v>9321</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.95115471081136316</v>
+        <v>0.9524831391784182</v>
       </c>
       <c r="M23" s="7">
         <v>12056</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>4000</v>
+        <v>4021</v>
       </c>
       <c r="P23" s="13">
-        <v>11853</v>
+        <v>11874</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.9831619110816191</v>
+        <v>0.98490378234903786</v>
       </c>
       <c r="R23" s="7">
         <v>9480</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="U23" s="13">
-        <v>9375</v>
+        <v>9399</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.98892405063291144</v>
+        <v>0.9914556962025316</v>
       </c>
       <c r="W23" s="7">
         <v>9764</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3031</v>
+        <v>3056</v>
       </c>
       <c r="Z23" s="13">
-        <v>9450</v>
+        <v>9475</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.96784104875051213</v>
+        <v>0.97040147480540762</v>
       </c>
       <c r="AB23" s="7">
         <v>12327</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3515</v>
+        <v>3551</v>
       </c>
       <c r="AE23" s="13">
-        <v>12056</v>
+        <v>12092</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97801573781130846</v>
+        <v>0.98093615640464027</v>
       </c>
       <c r="AG23" s="7">
         <v>9618</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3018</v>
+        <v>3054</v>
       </c>
       <c r="AJ23" s="13">
-        <v>9354</v>
+        <v>9390</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.97255146600124764</v>
+        <v>0.97629444791016839</v>
       </c>
       <c r="AL23" s="7">
         <v>9741</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2850</v>
+        <v>2903</v>
       </c>
       <c r="AO23" s="13">
-        <v>9486</v>
+        <v>9539</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.97382198952879584</v>
+        <v>0.9792629093522226</v>
       </c>
       <c r="AQ23" s="7">
         <v>12556</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3544</v>
+        <v>3645</v>
       </c>
       <c r="AT23" s="13">
-        <v>12170</v>
+        <v>12271</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.96925772539025168</v>
+        <v>0.97730168843580756</v>
       </c>
       <c r="AV23" s="7">
         <v>9718</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2556</v>
+        <v>2668</v>
       </c>
       <c r="AY23" s="13">
-        <v>9420</v>
+        <v>9532</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.9693352541675242</v>
+        <v>0.98086025931261578</v>
       </c>
       <c r="BA23" s="7">
         <v>10107</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2697</v>
+        <v>2844</v>
       </c>
       <c r="BD23" s="13">
-        <v>9532</v>
+        <v>9679</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.9431087365192441</v>
+        <v>0.95765311170475909</v>
       </c>
       <c r="BF23" s="7">
         <v>13018</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>3806</v>
+        <v>4179</v>
       </c>
       <c r="BI23" s="6">
-        <v>11813</v>
+        <v>12186</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9074358580427101</v>
+        <v>0.93608849285604545</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="F24" s="13">
-        <v>6887</v>
+        <v>6894</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.99207721117833481</v>
+        <v>0.99308556611927401</v>
       </c>
       <c r="H24" s="7">
         <v>7059</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="K24" s="13">
-        <v>6940</v>
+        <v>6949</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.9831420881144638</v>
+        <v>0.98441705624026066</v>
       </c>
       <c r="M24" s="7">
         <v>8056</v>
@@ -4295,14 +4295,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1761</v>
+        <v>1774</v>
       </c>
       <c r="P24" s="13">
-        <v>7924</v>
+        <v>7937</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.98361469712015892</v>
+        <v>0.98522840119165844</v>
       </c>
       <c r="R24" s="7">
         <v>7134</v>
@@ -4312,14 +4312,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="U24" s="13">
-        <v>7007</v>
+        <v>7017</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.98219792542753015</v>
+        <v>0.98359966358284268</v>
       </c>
       <c r="W24" s="7">
         <v>7208</v>
@@ -4329,14 +4329,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1438</v>
+        <v>1449</v>
       </c>
       <c r="Z24" s="13">
-        <v>7057</v>
+        <v>7068</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.97905105438401774</v>
+        <v>0.98057713651498335</v>
       </c>
       <c r="AB24" s="7">
         <v>8228</v>
@@ -4346,14 +4346,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1251</v>
+        <v>1266</v>
       </c>
       <c r="AE24" s="13">
-        <v>8065</v>
+        <v>8080</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.9801895964997569</v>
+        <v>0.98201263976665043</v>
       </c>
       <c r="AG24" s="7">
         <v>7344</v>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1418</v>
+        <v>1432</v>
       </c>
       <c r="AJ24" s="13">
-        <v>7163</v>
+        <v>7177</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97535403050108938</v>
+        <v>0.977260348583878</v>
       </c>
       <c r="AL24" s="7">
         <v>7506</v>
@@ -4380,14 +4380,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="AO24" s="13">
-        <v>7260</v>
+        <v>7284</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.96722621902478012</v>
+        <v>0.97042366107114308</v>
       </c>
       <c r="AQ24" s="7">
         <v>8509</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1549</v>
+        <v>1583</v>
       </c>
       <c r="AT24" s="13">
-        <v>8243</v>
+        <v>8277</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.96873898225408395</v>
+        <v>0.97273475143965216</v>
       </c>
       <c r="AV24" s="7">
         <v>7570</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1239</v>
+        <v>1279</v>
       </c>
       <c r="AY24" s="13">
-        <v>7282</v>
+        <v>7322</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.96195508586525758</v>
+        <v>0.96723910171730521</v>
       </c>
       <c r="BA24" s="7">
         <v>7648</v>
@@ -4431,14 +4431,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1375</v>
+        <v>1449</v>
       </c>
       <c r="BD24" s="13">
-        <v>7369</v>
+        <v>7443</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.96351987447698739</v>
+        <v>0.97319560669456062</v>
       </c>
       <c r="BF24" s="7">
         <v>8767</v>
@@ -4448,14 +4448,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1561</v>
+        <v>1692</v>
       </c>
       <c r="BI24" s="6">
-        <v>8328</v>
+        <v>8459</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.94992585833238274</v>
+        <v>0.96486825595984949</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4681</v>
+        <v>4692</v>
       </c>
       <c r="F25" s="13">
-        <v>21341</v>
+        <v>21352</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.99385274530806134</v>
+        <v>0.99436501653238951</v>
       </c>
       <c r="H25" s="7">
         <v>21813</v>
@@ -4490,14 +4490,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>4506</v>
+        <v>4522</v>
       </c>
       <c r="K25" s="13">
-        <v>21528</v>
+        <v>21544</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.98693439691926832</v>
+        <v>0.98766790446064279</v>
       </c>
       <c r="M25" s="7">
         <v>29215</v>
@@ -4507,14 +4507,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>6204</v>
+        <v>6228</v>
       </c>
       <c r="P25" s="13">
-        <v>28995</v>
+        <v>29019</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.99246962176963893</v>
+        <v>0.99329111757658739</v>
       </c>
       <c r="R25" s="7">
         <v>21767</v>
@@ -4524,14 +4524,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4531</v>
+        <v>4548</v>
       </c>
       <c r="U25" s="13">
-        <v>21622</v>
+        <v>21639</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.99333853999173061</v>
+        <v>0.99411953875132075</v>
       </c>
       <c r="W25" s="7">
         <v>22114</v>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4226</v>
+        <v>4246</v>
       </c>
       <c r="Z25" s="13">
-        <v>21752</v>
+        <v>21772</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.98363027946097492</v>
+        <v>0.9845346839106448</v>
       </c>
       <c r="AB25" s="7">
         <v>29630</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5461</v>
+        <v>5493</v>
       </c>
       <c r="AE25" s="13">
-        <v>29347</v>
+        <v>29379</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.99044886938913268</v>
+        <v>0.9915288558893014</v>
       </c>
       <c r="AG25" s="7">
         <v>22174</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4358</v>
+        <v>4385</v>
       </c>
       <c r="AJ25" s="13">
-        <v>21873</v>
+        <v>21900</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.98642554342924149</v>
+        <v>0.98764318571299725</v>
       </c>
       <c r="AL25" s="7">
         <v>22503</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4281</v>
+        <v>4316</v>
       </c>
       <c r="AO25" s="13">
-        <v>22243</v>
+        <v>22278</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.98844598497978042</v>
+        <v>0.99000133315557926</v>
       </c>
       <c r="AQ25" s="7">
         <v>30294</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5610</v>
+        <v>5681</v>
       </c>
       <c r="AT25" s="13">
-        <v>29942</v>
+        <v>30013</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.9883805374001452</v>
+        <v>0.99072423582227509</v>
       </c>
       <c r="AV25" s="7">
         <v>22740</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4257</v>
+        <v>4325</v>
       </c>
       <c r="AY25" s="13">
-        <v>22520</v>
+        <v>22588</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.99032541776605099</v>
+        <v>0.9933157431838171</v>
       </c>
       <c r="BA25" s="7">
         <v>23197</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4050</v>
+        <v>4162</v>
       </c>
       <c r="BD25" s="13">
-        <v>22705</v>
+        <v>22817</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.97879036082252013</v>
+        <v>0.98361857136698716</v>
       </c>
       <c r="BF25" s="7">
         <v>31043</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>6713</v>
+        <v>7126</v>
       </c>
       <c r="BI25" s="6">
-        <v>29781</v>
+        <v>30194</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.95934671262442417</v>
+        <v>0.97265083915858652</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4685,14 +4685,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3314</v>
+        <v>3326</v>
       </c>
       <c r="F26" s="13">
-        <v>14460</v>
+        <v>14472</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99367784496976364</v>
+        <v>0.99450247388675095</v>
       </c>
       <c r="H26" s="7">
         <v>14990</v>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3291</v>
+        <v>3306</v>
       </c>
       <c r="K26" s="13">
-        <v>14770</v>
+        <v>14785</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98532354903268848</v>
+        <v>0.98632421614409604</v>
       </c>
       <c r="M26" s="7">
         <v>28508</v>
@@ -4719,14 +4719,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5930</v>
+        <v>5965</v>
       </c>
       <c r="P26" s="13">
-        <v>28369</v>
+        <v>28404</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99512417566998734</v>
+        <v>0.99635190122070993</v>
       </c>
       <c r="R26" s="7">
         <v>14719</v>
@@ -4736,14 +4736,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3391</v>
+        <v>3412</v>
       </c>
       <c r="U26" s="13">
-        <v>14638</v>
+        <v>14659</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.99449690875738839</v>
+        <v>0.99592363611658397</v>
       </c>
       <c r="W26" s="7">
         <v>15123</v>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3432</v>
+        <v>3457</v>
       </c>
       <c r="Z26" s="13">
-        <v>14803</v>
+        <v>14828</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.97884017721351579</v>
+        <v>0.98049328836870986</v>
       </c>
       <c r="AB26" s="7">
         <v>29054</v>
@@ -4770,14 +4770,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5100</v>
+        <v>5160</v>
       </c>
       <c r="AE26" s="13">
-        <v>28678</v>
+        <v>28738</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98705858057410334</v>
+        <v>0.98912370069525712</v>
       </c>
       <c r="AG26" s="7">
         <v>14835</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3274</v>
+        <v>3308</v>
       </c>
       <c r="AJ26" s="13">
-        <v>14635</v>
+        <v>14669</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.98651836872261545</v>
+        <v>0.98881024603977086</v>
       </c>
       <c r="AL26" s="7">
         <v>15316</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3205</v>
+        <v>3247</v>
       </c>
       <c r="AO26" s="13">
-        <v>14891</v>
+        <v>14933</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.97225124053277623</v>
+        <v>0.97499347088012533</v>
       </c>
       <c r="AQ26" s="7">
         <v>29312</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5348</v>
+        <v>5485</v>
       </c>
       <c r="AT26" s="13">
-        <v>28876</v>
+        <v>29013</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.98512554585152834</v>
+        <v>0.98979939956331875</v>
       </c>
       <c r="AV26" s="7">
         <v>15164</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>2880</v>
+        <v>2978</v>
       </c>
       <c r="AY26" s="13">
-        <v>14876</v>
+        <v>14974</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.98100764969665</v>
+        <v>0.98747032445265104</v>
       </c>
       <c r="BA26" s="7">
         <v>15499</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>2942</v>
+        <v>3067</v>
       </c>
       <c r="BD26" s="13">
-        <v>14853</v>
+        <v>14978</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.95831989160591002</v>
+        <v>0.96638492805987486</v>
       </c>
       <c r="BF26" s="7">
         <v>29635</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>5289</v>
+        <v>5832</v>
       </c>
       <c r="BI26" s="6">
-        <v>28153</v>
+        <v>28696</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.94999156402901974</v>
+        <v>0.96831449299814409</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34673</v>
+        <v>34762</v>
       </c>
       <c r="F27" s="13">
-        <v>129668</v>
+        <v>129757</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.9888658410103105</v>
+        <v>0.98954456714050398</v>
       </c>
       <c r="H27" s="7">
         <v>134384</v>
@@ -4914,14 +4914,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>33808</v>
+        <v>33918</v>
       </c>
       <c r="K27" s="13">
-        <v>130612</v>
+        <v>130722</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.9719311822836052</v>
+        <v>0.9727497321109656</v>
       </c>
       <c r="M27" s="7">
         <v>190911</v>
@@ -4931,14 +4931,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>50884</v>
+        <v>51071</v>
       </c>
       <c r="P27" s="13">
-        <v>190673</v>
+        <v>190860</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99875334579987529</v>
+        <v>0.99973285981425897</v>
       </c>
       <c r="R27" s="7">
         <v>131264</v>
@@ -4948,14 +4948,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32874</v>
+        <v>32999</v>
       </c>
       <c r="U27" s="13">
-        <v>130432</v>
+        <v>130557</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99366162847391515</v>
+        <v>0.99461390784982939</v>
       </c>
       <c r="W27" s="7">
         <v>134144</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>37369</v>
+        <v>37529</v>
       </c>
       <c r="Z27" s="13">
-        <v>131640</v>
+        <v>131800</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.98133349236641221</v>
+        <v>0.98252624045801529</v>
       </c>
       <c r="AB27" s="7">
         <v>194609</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>48140</v>
+        <v>48493</v>
       </c>
       <c r="AE27" s="13">
-        <v>192724</v>
+        <v>193077</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99031391148405268</v>
+        <v>0.99212780498332553</v>
       </c>
       <c r="AG27" s="7">
         <v>134089</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33629</v>
+        <v>33887</v>
       </c>
       <c r="AJ27" s="13">
-        <v>131978</v>
+        <v>132236</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.98425672501100014</v>
+        <v>0.98618082020150799</v>
       </c>
       <c r="AL27" s="7">
         <v>137688</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31898</v>
+        <v>32314</v>
       </c>
       <c r="AO27" s="13">
-        <v>136020</v>
+        <v>136436</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98788565452327004</v>
+        <v>0.99090697809540407</v>
       </c>
       <c r="AQ27" s="7">
         <v>200322</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>47931</v>
+        <v>48910</v>
       </c>
       <c r="AT27" s="13">
-        <v>198220</v>
+        <v>199199</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.9895068939008197</v>
+        <v>0.99439402561875379</v>
       </c>
       <c r="AV27" s="7">
         <v>139481</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>29501</v>
+        <v>30447</v>
       </c>
       <c r="AY27" s="13">
-        <v>136743</v>
+        <v>137689</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.98037008624830624</v>
+        <v>0.98715237200765693</v>
       </c>
       <c r="BA27" s="7">
         <v>143305</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>29655</v>
+        <v>30972</v>
       </c>
       <c r="BD27" s="13">
-        <v>138072</v>
+        <v>139389</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.96348347929241829</v>
+        <v>0.97267366805066113</v>
       </c>
       <c r="BF27" s="7">
         <v>208143</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>54528</v>
+        <v>59056</v>
       </c>
       <c r="BI27" s="6">
-        <v>194655</v>
+        <v>199183</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.93519839725573284</v>
+        <v>0.95695267196110367</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5109,14 +5109,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>70152</v>
+        <v>70261</v>
       </c>
       <c r="F28" s="13">
-        <v>435007</v>
+        <v>435116</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99427217019837122</v>
+        <v>0.99452130565263208</v>
       </c>
       <c r="H28" s="7">
         <v>447363</v>
@@ -5126,14 +5126,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>70309</v>
+        <v>70439</v>
       </c>
       <c r="K28" s="13">
-        <v>442406</v>
+        <v>442536</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98891951278939028</v>
+        <v>0.98921010454597269</v>
       </c>
       <c r="M28" s="7">
         <v>722935</v>
@@ -5143,14 +5143,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>117825</v>
+        <v>118143</v>
       </c>
       <c r="P28" s="13">
-        <v>717264</v>
+        <v>717582</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99215558798508852</v>
+        <v>0.99259546155601819</v>
       </c>
       <c r="R28" s="7">
         <v>448339</v>
@@ -5160,14 +5160,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>69640</v>
+        <v>69829</v>
       </c>
       <c r="U28" s="13">
-        <v>445540</v>
+        <v>445729</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99375695623177995</v>
+        <v>0.99417851224185272</v>
       </c>
       <c r="W28" s="7">
         <v>458076</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>73523</v>
+        <v>73771</v>
       </c>
       <c r="Z28" s="13">
-        <v>450464</v>
+        <v>450712</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.98338267012460812</v>
+        <v>0.983924065002314</v>
       </c>
       <c r="AB28" s="7">
         <v>737235</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>113586</v>
+        <v>114172</v>
       </c>
       <c r="AE28" s="13">
-        <v>729108</v>
+        <v>729694</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98897637795275595</v>
+        <v>0.98977123983533066</v>
       </c>
       <c r="AG28" s="7">
         <v>456666</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>70941</v>
+        <v>71399</v>
       </c>
       <c r="AJ28" s="13">
-        <v>451145</v>
+        <v>451603</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98791020132876106</v>
+        <v>0.98891312250090879</v>
       </c>
       <c r="AL28" s="7">
         <v>468801</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>68758</v>
+        <v>69537</v>
       </c>
       <c r="AO28" s="13">
-        <v>463995</v>
+        <v>464774</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98974831538328634</v>
+        <v>0.99141000125852974</v>
       </c>
       <c r="AQ28" s="7">
         <v>756132</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>105755</v>
+        <v>107708</v>
       </c>
       <c r="AT28" s="13">
-        <v>749329</v>
+        <v>751282</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99100289367464944</v>
+        <v>0.99358577602852416</v>
       </c>
       <c r="AV28" s="7">
         <v>474991</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>63726</v>
+        <v>65683</v>
       </c>
       <c r="AY28" s="13">
-        <v>468761</v>
+        <v>470718</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.98688396201191175</v>
+        <v>0.99100404007654885</v>
       </c>
       <c r="BA28" s="7">
         <v>487540</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>64415</v>
+        <v>67125</v>
       </c>
       <c r="BD28" s="13">
-        <v>475179</v>
+        <v>477889</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.97464618287730242</v>
+        <v>0.98020470115272595</v>
       </c>
       <c r="BF28" s="7">
         <v>779284</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>123426</v>
+        <v>134020</v>
       </c>
       <c r="BI28" s="6">
-        <v>747624</v>
+        <v>758218</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.95937296287361218</v>
+        <v>0.97296749323738196</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>28162</v>
+        <v>28190</v>
       </c>
       <c r="F29" s="13">
-        <v>142669</v>
+        <v>142697</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99246619177472317</v>
+        <v>0.99266097167343759</v>
       </c>
       <c r="H29" s="7">
         <v>146310</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>27520</v>
+        <v>27552</v>
       </c>
       <c r="K29" s="13">
-        <v>144115</v>
+        <v>144147</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98499760781901446</v>
+        <v>0.98521632150912442</v>
       </c>
       <c r="M29" s="7">
         <v>194093</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>37673</v>
+        <v>37738</v>
       </c>
       <c r="P29" s="13">
-        <v>191525</v>
+        <v>191590</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98676922918394794</v>
+        <v>0.98710412018980587</v>
       </c>
       <c r="R29" s="7">
         <v>146918</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26574</v>
+        <v>26637</v>
       </c>
       <c r="U29" s="13">
-        <v>145123</v>
+        <v>145186</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98778230033079673</v>
+        <v>0.98821111095985514</v>
       </c>
       <c r="W29" s="7">
         <v>149105</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>26969</v>
+        <v>27052</v>
       </c>
       <c r="Z29" s="13">
-        <v>146387</v>
+        <v>146470</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98177123503571306</v>
+        <v>0.98232788974212804</v>
       </c>
       <c r="AB29" s="7">
         <v>197403</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32856</v>
+        <v>33007</v>
       </c>
       <c r="AE29" s="13">
-        <v>194390</v>
+        <v>194541</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98473680744466907</v>
+        <v>0.98550174009513536</v>
       </c>
       <c r="AG29" s="7">
         <v>149309</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>27511</v>
+        <v>27660</v>
       </c>
       <c r="AJ29" s="13">
-        <v>147182</v>
+        <v>147331</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98575437515488018</v>
+        <v>0.98675230562122851</v>
       </c>
       <c r="AL29" s="7">
         <v>152026</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>25732</v>
+        <v>25990</v>
       </c>
       <c r="AO29" s="13">
-        <v>151745</v>
+        <v>152003</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.99815163195769141</v>
+        <v>0.99984871008906373</v>
       </c>
       <c r="AQ29" s="7">
         <v>203571</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>33839</v>
+        <v>34406</v>
       </c>
       <c r="AT29" s="13">
-        <v>202053</v>
+        <v>202620</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99254314219608886</v>
+        <v>0.99532841121770788</v>
       </c>
       <c r="AV29" s="7">
         <v>155780</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>25053</v>
+        <v>25710</v>
       </c>
       <c r="AY29" s="13">
-        <v>154402</v>
+        <v>155059</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99115419180896136</v>
+        <v>0.99537167800744641</v>
       </c>
       <c r="BA29" s="7">
         <v>159604</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>25320</v>
+        <v>26300</v>
       </c>
       <c r="BD29" s="13">
-        <v>156386</v>
+        <v>157366</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.97983759805518655</v>
+        <v>0.98597779504273075</v>
       </c>
       <c r="BF29" s="7">
         <v>211893</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>39135</v>
+        <v>41987</v>
       </c>
       <c r="BI29" s="6">
-        <v>203505</v>
+        <v>206357</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.96041398252891785</v>
+        <v>0.97387360601813178</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41171</v>
+        <v>41218</v>
       </c>
       <c r="F30" s="13">
-        <v>185535</v>
+        <v>185582</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99604342037450611</v>
+        <v>0.99629573956364881</v>
       </c>
       <c r="H30" s="7">
         <v>190966</v>
@@ -5550,14 +5550,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41578</v>
+        <v>41630</v>
       </c>
       <c r="K30" s="13">
-        <v>188390</v>
+        <v>188442</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98651068776640871</v>
+        <v>0.98678298754752158</v>
       </c>
       <c r="M30" s="7">
         <v>320227</v>
@@ -5567,14 +5567,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>67670</v>
+        <v>67780</v>
       </c>
       <c r="P30" s="13">
-        <v>317672</v>
+        <v>317782</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.99202128490102337</v>
+        <v>0.9923647912262239</v>
       </c>
       <c r="R30" s="7">
         <v>189502</v>
@@ -5584,14 +5584,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37883</v>
+        <v>37962</v>
       </c>
       <c r="U30" s="13">
-        <v>188398</v>
+        <v>188477</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99417420396618505</v>
+        <v>0.99459108610990909</v>
       </c>
       <c r="W30" s="7">
         <v>194334</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>37760</v>
+        <v>37855</v>
       </c>
       <c r="Z30" s="13">
-        <v>190638</v>
+        <v>190733</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98098119732007782</v>
+        <v>0.98147004641493507</v>
       </c>
       <c r="AB30" s="7">
         <v>325942</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>60450</v>
+        <v>60673</v>
       </c>
       <c r="AE30" s="13">
-        <v>322392</v>
+        <v>322615</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98910849169484139</v>
+        <v>0.98979266249823583</v>
       </c>
       <c r="AG30" s="7">
         <v>192789</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>39723</v>
+        <v>39891</v>
       </c>
       <c r="AJ30" s="13">
-        <v>191202</v>
+        <v>191370</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99176820254267617</v>
+        <v>0.99263962155517171</v>
       </c>
       <c r="AL30" s="7">
         <v>197994</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>37087</v>
+        <v>37399</v>
       </c>
       <c r="AO30" s="13">
-        <v>195861</v>
+        <v>196173</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98922694627109908</v>
+        <v>0.99080275159853326</v>
       </c>
       <c r="AQ30" s="7">
         <v>333633</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>60135</v>
+        <v>61047</v>
       </c>
       <c r="AT30" s="13">
-        <v>330278</v>
+        <v>331190</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.98994404030776328</v>
+        <v>0.99267758285301511</v>
       </c>
       <c r="AV30" s="7">
         <v>198460</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36056</v>
+        <v>36859</v>
       </c>
       <c r="AY30" s="13">
-        <v>196351</v>
+        <v>197154</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.98937317343545295</v>
+        <v>0.99341932883200645</v>
       </c>
       <c r="BA30" s="7">
         <v>203942</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>36505</v>
+        <v>37718</v>
       </c>
       <c r="BD30" s="13">
-        <v>198777</v>
+        <v>199990</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.97467417206852924</v>
+        <v>0.98062194153239646</v>
       </c>
       <c r="BF30" s="7">
         <v>342999</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>70553</v>
+        <v>76346</v>
       </c>
       <c r="BI30" s="6">
-        <v>326478</v>
+        <v>332271</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.95183367881539016</v>
+        <v>0.96872294088320954</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5745,14 +5745,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>19224</v>
+        <v>19243</v>
       </c>
       <c r="F31" s="13">
-        <v>83564</v>
+        <v>83583</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0082164014333459</v>
+        <v>1.0084456402398563</v>
       </c>
       <c r="H31" s="7">
         <v>85478</v>
@@ -5762,14 +5762,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18006</v>
+        <v>18026</v>
       </c>
       <c r="K31" s="13">
-        <v>85093</v>
+        <v>85113</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99549591707807861</v>
+        <v>0.99572989541168488</v>
       </c>
       <c r="M31" s="7">
         <v>149930</v>
@@ -5779,14 +5779,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>38794</v>
+        <v>38861</v>
       </c>
       <c r="P31" s="13">
-        <v>150646</v>
+        <v>150713</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0047755619289001</v>
+        <v>1.0052224371373308</v>
       </c>
       <c r="R31" s="7">
         <v>83981</v>
@@ -5796,14 +5796,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>18522</v>
+        <v>18556</v>
       </c>
       <c r="U31" s="13">
-        <v>84331</v>
+        <v>84365</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0041676093402079</v>
+        <v>1.0045724628189709</v>
       </c>
       <c r="W31" s="7">
         <v>85994</v>
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>18926</v>
+        <v>18967</v>
       </c>
       <c r="Z31" s="13">
-        <v>85490</v>
+        <v>85531</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99413912598553389</v>
+        <v>0.99461590343512341</v>
       </c>
       <c r="AB31" s="7">
         <v>153633</v>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>40041</v>
+        <v>40168</v>
       </c>
       <c r="AE31" s="13">
-        <v>153282</v>
+        <v>153409</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.99771533459608286</v>
+        <v>0.99854197991316973</v>
       </c>
       <c r="AG31" s="7">
         <v>85109</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>20181</v>
+        <v>20250</v>
       </c>
       <c r="AJ31" s="13">
-        <v>85699</v>
+        <v>85768</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0069322868321799</v>
+        <v>1.007743011902384</v>
       </c>
       <c r="AL31" s="7">
         <v>88549</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18094</v>
+        <v>18205</v>
       </c>
       <c r="AO31" s="13">
-        <v>88265</v>
+        <v>88376</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99679273622514086</v>
+        <v>0.99804627946108937</v>
       </c>
       <c r="AQ31" s="7">
         <v>156407</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>33713</v>
+        <v>34071</v>
       </c>
       <c r="AT31" s="13">
-        <v>156836</v>
+        <v>157194</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0027428439903585</v>
+        <v>1.0050317441035248</v>
       </c>
       <c r="AV31" s="7">
         <v>87916</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>17083</v>
+        <v>17302</v>
       </c>
       <c r="AY31" s="13">
-        <v>88509</v>
+        <v>88728</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0067450748441695</v>
+        <v>1.0092360889940397</v>
       </c>
       <c r="BA31" s="7">
         <v>90084</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>16962</v>
+        <v>17314</v>
       </c>
       <c r="BD31" s="13">
-        <v>89720</v>
+        <v>90072</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99595932685049504</v>
+        <v>0.99986679099507125</v>
       </c>
       <c r="BF31" s="7">
         <v>159779</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>45214</v>
+        <v>48250</v>
       </c>
       <c r="BI31" s="6">
-        <v>154508</v>
+        <v>157544</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.96701068350659347</v>
+        <v>0.98601192897689938</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>48406</v>
+        <v>48432</v>
       </c>
       <c r="F32" s="13">
-        <v>231619</v>
+        <v>231645</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99829751652917498</v>
+        <v>0.99840957873231784</v>
       </c>
       <c r="H32" s="7">
         <v>238678</v>
@@ -5974,14 +5974,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46534</v>
+        <v>46578</v>
       </c>
       <c r="K32" s="13">
-        <v>235806</v>
+        <v>235850</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98796705184390687</v>
+        <v>0.98815140063181361</v>
       </c>
       <c r="M32" s="7">
         <v>498323</v>
@@ -5991,14 +5991,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>107909</v>
+        <v>108026</v>
       </c>
       <c r="P32" s="13">
-        <v>494585</v>
+        <v>494702</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99249884111309328</v>
+        <v>0.99273362859029179</v>
       </c>
       <c r="R32" s="7">
         <v>234167</v>
@@ -6008,14 +6008,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>43873</v>
+        <v>43939</v>
       </c>
       <c r="U32" s="13">
-        <v>233660</v>
+        <v>233726</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99783487852686326</v>
+        <v>0.99811672865946099</v>
       </c>
       <c r="W32" s="7">
         <v>242821</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>46148</v>
+        <v>46234</v>
       </c>
       <c r="Z32" s="13">
-        <v>238110</v>
+        <v>238196</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98059887736233686</v>
+        <v>0.98095304771827807</v>
       </c>
       <c r="AB32" s="7">
         <v>507064</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>110995</v>
+        <v>111260</v>
       </c>
       <c r="AE32" s="13">
-        <v>503503</v>
+        <v>503768</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99297721786598925</v>
+        <v>0.99349983434043831</v>
       </c>
       <c r="AG32" s="7">
         <v>238186</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>47627</v>
+        <v>47780</v>
       </c>
       <c r="AJ32" s="13">
-        <v>237760</v>
+        <v>237913</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99821148178314423</v>
+        <v>0.99885383691736707</v>
       </c>
       <c r="AL32" s="7">
         <v>247675</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>43496</v>
+        <v>43734</v>
       </c>
       <c r="AO32" s="13">
-        <v>247109</v>
+        <v>247347</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.99771474714848085</v>
+        <v>0.99867568385989702</v>
       </c>
       <c r="AQ32" s="7">
         <v>518099</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>99836</v>
+        <v>100872</v>
       </c>
       <c r="AT32" s="13">
-        <v>516662</v>
+        <v>517698</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99722639881567032</v>
+        <v>0.99922601664932764</v>
       </c>
       <c r="AV32" s="7">
         <v>246693</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>42718</v>
+        <v>43335</v>
       </c>
       <c r="AY32" s="13">
-        <v>247554</v>
+        <v>248171</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>1.0034901679415307</v>
+        <v>1.005991252285229</v>
       </c>
       <c r="BA32" s="7">
         <v>255610</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>40155</v>
+        <v>41160</v>
       </c>
       <c r="BD32" s="13">
-        <v>253274</v>
+        <v>254279</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.99086107742263607</v>
+        <v>0.99479284848010641</v>
       </c>
       <c r="BF32" s="7">
         <v>535637</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>118845</v>
+        <v>127049</v>
       </c>
       <c r="BI32" s="6">
-        <v>517488</v>
+        <v>525692</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.96611697847609479</v>
+        <v>0.9814333214471741</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>81446</v>
+        <v>81470</v>
       </c>
       <c r="F33" s="13">
-        <v>718662</v>
+        <v>718686</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0040081420187121</v>
+        <v>1.004041671265296</v>
       </c>
       <c r="H33" s="7">
         <v>726544</v>
@@ -6186,14 +6186,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>73226</v>
+        <v>73256</v>
       </c>
       <c r="K33" s="13">
-        <v>729959</v>
+        <v>729989</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>1.0047003347354049</v>
+        <v>1.0047416261093616</v>
       </c>
       <c r="M33" s="7">
         <v>1152516</v>
@@ -6203,14 +6203,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>140263</v>
+        <v>140340</v>
       </c>
       <c r="P33" s="13">
-        <v>1154190</v>
+        <v>1154267</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>1.0014524744125026</v>
+        <v>1.0015192847648102</v>
       </c>
       <c r="R33" s="7">
         <v>733468</v>
@@ -6220,14 +6220,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>83082</v>
+        <v>83131</v>
       </c>
       <c r="U33" s="13">
-        <v>737207</v>
+        <v>737256</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0050977002405013</v>
+        <v>1.0051645061543244</v>
       </c>
       <c r="W33" s="7">
         <v>745690</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>80949</v>
+        <v>81023</v>
       </c>
       <c r="Z33" s="13">
-        <v>746501</v>
+        <v>746575</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>1.0010875833121002</v>
+        <v>1.0011868202604299</v>
       </c>
       <c r="AB33" s="7">
         <v>1180887</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>140736</v>
+        <v>140918</v>
       </c>
       <c r="AE33" s="13">
-        <v>1180621</v>
+        <v>1180803</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99977474559377821</v>
+        <v>0.99992886702961414</v>
       </c>
       <c r="AG33" s="7">
         <v>749948</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>81063</v>
+        <v>81219</v>
       </c>
       <c r="AJ33" s="13">
-        <v>751549</v>
+        <v>751705</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.0021348146804845</v>
+        <v>1.0023428291028178</v>
       </c>
       <c r="AL33" s="7">
         <v>765123</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>75431</v>
+        <v>75702</v>
       </c>
       <c r="AO33" s="13">
-        <v>773902</v>
+        <v>774173</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>1.0114739721587247</v>
+        <v>1.0118281635763138</v>
       </c>
       <c r="AQ33" s="7">
         <v>1217820</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>138979</v>
+        <v>139769</v>
       </c>
       <c r="AT33" s="13">
-        <v>1222805</v>
+        <v>1223595</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0040933799740519</v>
+        <v>1.004742080110361</v>
       </c>
       <c r="AV33" s="7">
         <v>779865</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>72273</v>
+        <v>73070</v>
       </c>
       <c r="AY33" s="13">
-        <v>784802</v>
+        <v>785599</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0063305828572895</v>
+        <v>1.0073525546088105</v>
       </c>
       <c r="BA33" s="7">
         <v>794982</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>73164</v>
+        <v>74577</v>
       </c>
       <c r="BD33" s="13">
-        <v>797994</v>
+        <v>799407</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0037887650286421</v>
+        <v>1.0055661637621984</v>
       </c>
       <c r="BF33" s="7">
         <v>1258934</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>155014</v>
+        <v>163662</v>
       </c>
       <c r="BI33" s="6">
-        <v>1245202</v>
+        <v>1253850</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>0.98909235909110405</v>
+        <v>0.99596166280361009</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6603,14 +6603,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="P35" s="13">
-        <v>15065</v>
+        <v>15067</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99788037358415582</v>
+        <v>0.99801285023514608</v>
       </c>
       <c r="R35" s="7">
         <v>12455</v>
@@ -6620,14 +6620,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="U35" s="13">
-        <v>12400</v>
+        <v>12401</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99558410276997189</v>
+        <v>0.99566439181051791</v>
       </c>
       <c r="W35" s="7">
         <v>12547</v>
@@ -6637,14 +6637,14 @@
       </c>
       <c r="Y35" s="4">
         <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="Z35" s="13">
-        <v>12436</v>
+        <v>12438</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.99115326372838131</v>
+        <v>0.991312664381924</v>
       </c>
       <c r="AB35" s="7">
         <v>15257</v>
@@ -6654,14 +6654,14 @@
       </c>
       <c r="AD35" s="4">
         <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
-        <v>2695</v>
+        <v>2703</v>
       </c>
       <c r="AE35" s="13">
-        <v>15170</v>
+        <v>15178</v>
       </c>
       <c r="AF35" s="5">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99429769941666124</v>
+        <v>0.9948220488955889</v>
       </c>
       <c r="AG35" s="7">
         <v>12574</v>
@@ -6671,14 +6671,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" ref="AI35:AI48" si="36">AJ35-AH35</f>
-        <v>2186</v>
+        <v>2193</v>
       </c>
       <c r="AJ35" s="13">
-        <v>12509</v>
+        <v>12516</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99483060283123903</v>
+        <v>0.99538730714172097</v>
       </c>
       <c r="AL35" s="7">
         <v>12702</v>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="38">AO35-AM35</f>
-        <v>2077</v>
+        <v>2093</v>
       </c>
       <c r="AO35" s="13">
-        <v>12601</v>
+        <v>12617</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.9920484962997953</v>
+        <v>0.99330814045032279</v>
       </c>
       <c r="AQ35" s="7">
         <v>15458</v>
@@ -6705,14 +6705,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="40">AT35-AR35</f>
-        <v>2621</v>
+        <v>2657</v>
       </c>
       <c r="AT35" s="13">
-        <v>15339</v>
+        <v>15375</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.99230172079182299</v>
+        <v>0.99463061198085134</v>
       </c>
       <c r="AV35" s="7">
         <v>12806</v>
@@ -6722,14 +6722,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="42">AY35-AW35</f>
-        <v>1942</v>
+        <v>1997</v>
       </c>
       <c r="AY35" s="13">
-        <v>12630</v>
+        <v>12685</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.98625644229267528</v>
+        <v>0.99055130407621428</v>
       </c>
       <c r="BA35" s="7">
         <v>12915</v>
@@ -6739,14 +6739,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="44">BD35-BB35</f>
-        <v>1894</v>
+        <v>1978</v>
       </c>
       <c r="BD35" s="13">
-        <v>12652</v>
+        <v>12736</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.97963608207510644</v>
+        <v>0.98614014711575693</v>
       </c>
       <c r="BF35" s="7">
         <v>15661</v>
@@ -6756,14 +6756,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="46">BI35-BG35</f>
-        <v>2544</v>
+        <v>2751</v>
       </c>
       <c r="BI35" s="6">
-        <v>15143</v>
+        <v>15350</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.96692420662792922</v>
+        <v>0.98014175340016607</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>185829</v>
+        <v>185958</v>
       </c>
       <c r="F36" s="13">
-        <v>956007</v>
+        <v>956136</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>1.0033553384200418</v>
+        <v>1.0034907274272939</v>
       </c>
       <c r="H36" s="7">
         <v>975466</v>
@@ -6798,14 +6798,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>176179</v>
+        <v>176329</v>
       </c>
       <c r="K36" s="13">
-        <v>971399</v>
+        <v>971549</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.995830710655215</v>
+        <v>0.99598448331361622</v>
       </c>
       <c r="M36" s="7">
         <v>1668278</v>
@@ -6815,14 +6815,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>345947</v>
+        <v>346306</v>
       </c>
       <c r="P36" s="13">
-        <v>1668020</v>
+        <v>1668379</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.99984534951608783</v>
+        <v>1.0000605414685082</v>
       </c>
       <c r="R36" s="7">
         <v>976879</v>
@@ -6832,14 +6832,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>185194</v>
+        <v>185414</v>
       </c>
       <c r="U36" s="13">
-        <v>977236</v>
+        <v>977456</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>1.0003654495592595</v>
+        <v>1.000590656570568</v>
       </c>
       <c r="W36" s="7">
         <v>1000117</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>181135</v>
+        <v>181412</v>
       </c>
       <c r="Z36" s="13">
-        <v>988958</v>
+        <v>989235</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.9888423054502623</v>
+        <v>0.98911927304505376</v>
       </c>
       <c r="AB36" s="7">
         <v>1701420</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>335983</v>
+        <v>336730</v>
       </c>
       <c r="AE36" s="13">
-        <v>1696877</v>
+        <v>1697624</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.99732987739652756</v>
+        <v>0.9977689224295001</v>
       </c>
       <c r="AG36" s="7">
         <v>996655</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="36"/>
-        <v>185958</v>
+        <v>186482</v>
       </c>
       <c r="AJ36" s="13">
-        <v>996584</v>
+        <v>997108</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="37"/>
-        <v>0.99992876170791301</v>
+        <v>1.0004545203706399</v>
       </c>
       <c r="AL36" s="7">
         <v>1027093</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="38"/>
-        <v>176983</v>
+        <v>177976</v>
       </c>
       <c r="AO36" s="13">
-        <v>1031702</v>
+        <v>1032695</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="39"/>
-        <v>1.0044874222684801</v>
+        <v>1.0054542285849479</v>
       </c>
       <c r="AQ36" s="7">
         <v>1750886</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="40"/>
-        <v>318506</v>
+        <v>321310</v>
       </c>
       <c r="AT36" s="13">
-        <v>1759884</v>
+        <v>1762688</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="41"/>
-        <v>1.0051391124265086</v>
+        <v>1.0067405873369255</v>
       </c>
       <c r="AV36" s="7">
         <v>1041088</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="42"/>
-        <v>164562</v>
+        <v>167138</v>
       </c>
       <c r="AY36" s="13">
-        <v>1046562</v>
+        <v>1049138</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="43"/>
-        <v>1.0052579609024406</v>
+        <v>1.0077322954447654</v>
       </c>
       <c r="BA36" s="7">
         <v>1070068</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="44"/>
-        <v>168280</v>
+        <v>172271</v>
       </c>
       <c r="BD36" s="13">
-        <v>1064697</v>
+        <v>1068688</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="45"/>
-        <v>0.99498069281578372</v>
+        <v>0.99871036233211352</v>
       </c>
       <c r="BF36" s="7">
         <v>1814069</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="46"/>
-        <v>330039</v>
+        <v>358503</v>
       </c>
       <c r="BI36" s="6">
-        <v>1757796</v>
+        <v>1786260</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="47"/>
-        <v>0.96897968048624394</v>
+        <v>0.98467037361864407</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6993,14 +6993,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>146448</v>
+        <v>146600</v>
       </c>
       <c r="F37" s="13">
-        <v>734518</v>
+        <v>734670</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.9906267027032859</v>
+        <v>0.99083170143553057</v>
       </c>
       <c r="H37" s="7">
         <v>747767</v>
@@ -7010,14 +7010,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>140160</v>
+        <v>140353</v>
       </c>
       <c r="K37" s="13">
-        <v>739182</v>
+        <v>739375</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98851915101896715</v>
+        <v>0.9887772528073584</v>
       </c>
       <c r="M37" s="7">
         <v>922163</v>
@@ -7027,14 +7027,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>188107</v>
+        <v>188418</v>
       </c>
       <c r="P37" s="13">
-        <v>913645</v>
+        <v>913956</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99076302128799354</v>
+        <v>0.99110027186083149</v>
       </c>
       <c r="R37" s="7">
         <v>751356</v>
@@ -7044,14 +7044,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>139850</v>
+        <v>140165</v>
       </c>
       <c r="U37" s="13">
-        <v>744294</v>
+        <v>744609</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99060099340392571</v>
+        <v>0.99102023541437079</v>
       </c>
       <c r="W37" s="7">
         <v>760191</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>138109</v>
+        <v>138516</v>
       </c>
       <c r="Z37" s="13">
-        <v>749661</v>
+        <v>750068</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98614821801363084</v>
+        <v>0.98668360977701652</v>
       </c>
       <c r="AB37" s="7">
         <v>938023</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>160160</v>
+        <v>160880</v>
       </c>
       <c r="AE37" s="13">
-        <v>927534</v>
+        <v>928254</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98881797141434702</v>
+        <v>0.98958554321162706</v>
       </c>
       <c r="AG37" s="7">
         <v>763648</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="36"/>
-        <v>141993</v>
+        <v>142723</v>
       </c>
       <c r="AJ37" s="13">
-        <v>755202</v>
+        <v>755932</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="37"/>
-        <v>0.98893993043915518</v>
+        <v>0.98989586825343612</v>
       </c>
       <c r="AL37" s="7">
         <v>773685</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="38"/>
-        <v>132235</v>
+        <v>133525</v>
       </c>
       <c r="AO37" s="13">
-        <v>767499</v>
+        <v>768789</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="39"/>
-        <v>0.99200449795459389</v>
+        <v>0.99367184319199675</v>
       </c>
       <c r="AQ37" s="7">
         <v>957323</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="40"/>
-        <v>164103</v>
+        <v>166723</v>
       </c>
       <c r="AT37" s="13">
-        <v>947566</v>
+        <v>950186</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="41"/>
-        <v>0.98980803762157599</v>
+        <v>0.99254483596445509</v>
       </c>
       <c r="AV37" s="7">
         <v>783693</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="42"/>
-        <v>122722</v>
+        <v>125979</v>
       </c>
       <c r="AY37" s="13">
-        <v>773514</v>
+        <v>776771</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="43"/>
-        <v>0.98701149557288381</v>
+        <v>0.99116745970679843</v>
       </c>
       <c r="BA37" s="7">
         <v>794943</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="44"/>
-        <v>132984</v>
+        <v>137818</v>
       </c>
       <c r="BD37" s="13">
-        <v>776644</v>
+        <v>781478</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="45"/>
-        <v>0.97698073949956166</v>
+        <v>0.9830616786360783</v>
       </c>
       <c r="BF37" s="7">
         <v>980352</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="46"/>
-        <v>182855</v>
+        <v>196511</v>
       </c>
       <c r="BI37" s="6">
-        <v>939286</v>
+        <v>952942</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="47"/>
-        <v>0.95811096422509467</v>
+        <v>0.97204065478521995</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6588</v>
+        <v>6597</v>
       </c>
       <c r="F38" s="13">
-        <v>26176</v>
+        <v>26185</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0043741846366356</v>
+        <v>1.004719515002686</v>
       </c>
       <c r="H38" s="7">
         <v>26657</v>
@@ -7222,14 +7222,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>6249</v>
+        <v>6260</v>
       </c>
       <c r="K38" s="13">
-        <v>26488</v>
+        <v>26499</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99366020182316095</v>
+        <v>0.99407285140863566</v>
       </c>
       <c r="M38" s="7">
         <v>40003</v>
@@ -7239,14 +7239,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>9874</v>
+        <v>9894</v>
       </c>
       <c r="P38" s="13">
-        <v>40005</v>
+        <v>40025</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0000499962502811</v>
+        <v>1.0005499587530935</v>
       </c>
       <c r="R38" s="7">
         <v>26603</v>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>6124</v>
+        <v>6141</v>
       </c>
       <c r="U38" s="13">
-        <v>26619</v>
+        <v>26636</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.0006014359282787</v>
+        <v>1.0012404616020749</v>
       </c>
       <c r="W38" s="7">
         <v>27177</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6180</v>
+        <v>6202</v>
       </c>
       <c r="Z38" s="13">
-        <v>26865</v>
+        <v>26887</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.98851970416160728</v>
+        <v>0.98932921220149395</v>
       </c>
       <c r="AB38" s="7">
         <v>40627</v>
@@ -7290,14 +7290,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>8741</v>
+        <v>8785</v>
       </c>
       <c r="AE38" s="13">
-        <v>40570</v>
+        <v>40614</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>0.99859699214807884</v>
+        <v>0.99968001575307064</v>
       </c>
       <c r="AG38" s="7">
         <v>26952</v>
@@ -7307,14 +7307,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="36"/>
-        <v>6087</v>
+        <v>6128</v>
       </c>
       <c r="AJ38" s="13">
-        <v>26989</v>
+        <v>27030</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="37"/>
-        <v>1.0013728109231226</v>
+        <v>1.0028940338379342</v>
       </c>
       <c r="AL38" s="7">
         <v>27600</v>
@@ -7324,14 +7324,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="38"/>
-        <v>6333</v>
+        <v>6400</v>
       </c>
       <c r="AO38" s="13">
-        <v>27486</v>
+        <v>27553</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="39"/>
-        <v>0.99586956521739134</v>
+        <v>0.99829710144927541</v>
       </c>
       <c r="AQ38" s="7">
         <v>41434</v>
@@ -7341,14 +7341,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="40"/>
-        <v>8827</v>
+        <v>8992</v>
       </c>
       <c r="AT38" s="13">
-        <v>41401</v>
+        <v>41566</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="41"/>
-        <v>0.99920355263793015</v>
+        <v>1.0031857894482792</v>
       </c>
       <c r="AV38" s="7">
         <v>27593</v>
@@ -7358,14 +7358,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="42"/>
-        <v>5093</v>
+        <v>5277</v>
       </c>
       <c r="AY38" s="13">
-        <v>27449</v>
+        <v>27633</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="43"/>
-        <v>0.99478128510854202</v>
+        <v>1.001449643025405</v>
       </c>
       <c r="BA38" s="7">
         <v>28279</v>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="44"/>
-        <v>5239</v>
+        <v>5516</v>
       </c>
       <c r="BD38" s="13">
-        <v>27517</v>
+        <v>27794</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="45"/>
-        <v>0.97305420983768875</v>
+        <v>0.98284946426677045</v>
       </c>
       <c r="BF38" s="7">
         <v>42642</v>
@@ -7392,14 +7392,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="46"/>
-        <v>8753</v>
+        <v>9663</v>
       </c>
       <c r="BI38" s="6">
-        <v>40264</v>
+        <v>41174</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="47"/>
-        <v>0.94423338492566011</v>
+        <v>0.96557384738051688</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="AN39" s="4">
         <f t="shared" si="38"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AO39" s="13">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP39" s="5">
         <f t="shared" si="39"/>
-        <v>0.94565217391304346</v>
+        <v>0.94927536231884058</v>
       </c>
       <c r="AQ39" s="7">
         <v>338</v>
@@ -7553,14 +7553,14 @@
       </c>
       <c r="AS39" s="4">
         <f t="shared" si="40"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AT39" s="13">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AU39" s="5">
         <f t="shared" si="41"/>
-        <v>0.94378698224852076</v>
+        <v>0.94970414201183428</v>
       </c>
       <c r="AV39" s="7">
         <v>279</v>
@@ -7570,14 +7570,14 @@
       </c>
       <c r="AX39" s="4">
         <f t="shared" si="42"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AY39" s="13">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AZ39" s="5">
         <f t="shared" si="43"/>
-        <v>0.94265232974910396</v>
+        <v>0.94982078853046592</v>
       </c>
       <c r="BA39" s="7">
         <v>291</v>
@@ -7587,14 +7587,14 @@
       </c>
       <c r="BC39" s="4">
         <f t="shared" si="44"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BD39" s="13">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="BE39" s="5">
         <f t="shared" si="45"/>
-        <v>0.92096219931271472</v>
+        <v>0.92783505154639179</v>
       </c>
       <c r="BF39" s="7">
         <v>344</v>
@@ -7604,14 +7604,14 @@
       </c>
       <c r="BH39" s="4">
         <f t="shared" si="46"/>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BI39" s="6">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="BJ39" s="5">
         <f t="shared" si="47"/>
-        <v>0.94767441860465118</v>
+        <v>0.96220930232558144</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7629,14 +7629,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>73370</v>
+        <v>73454</v>
       </c>
       <c r="F40" s="13">
-        <v>301285</v>
+        <v>301369</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99141476962361874</v>
+        <v>0.99169118179365179</v>
       </c>
       <c r="H40" s="7">
         <v>306465</v>
@@ -7646,14 +7646,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>71156</v>
+        <v>71265</v>
       </c>
       <c r="K40" s="13">
-        <v>302616</v>
+        <v>302725</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98744065390827662</v>
+        <v>0.98779632258169769</v>
       </c>
       <c r="M40" s="7">
         <v>361770</v>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>90526</v>
+        <v>90691</v>
       </c>
       <c r="P40" s="13">
-        <v>358340</v>
+        <v>358505</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99051883793570505</v>
+        <v>0.99097492882217986</v>
       </c>
       <c r="R40" s="7">
         <v>306479</v>
@@ -7680,14 +7680,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>69968</v>
+        <v>70132</v>
       </c>
       <c r="U40" s="13">
-        <v>304407</v>
+        <v>304571</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99323934103152256</v>
+        <v>0.99377445110431706</v>
       </c>
       <c r="W40" s="7">
         <v>309858</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>70256</v>
+        <v>70468</v>
       </c>
       <c r="Z40" s="13">
-        <v>305870</v>
+        <v>306082</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.98712958839210219</v>
+        <v>0.9878137727604257</v>
       </c>
       <c r="AB40" s="7">
         <v>365821</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>65399</v>
+        <v>65756</v>
       </c>
       <c r="AE40" s="13">
-        <v>362184</v>
+        <v>362541</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.99005797917560778</v>
+        <v>0.9910338662897975</v>
       </c>
       <c r="AG40" s="7">
         <v>311342</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="36"/>
-        <v>72357</v>
+        <v>72835</v>
       </c>
       <c r="AJ40" s="13">
-        <v>308297</v>
+        <v>308775</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="37"/>
-        <v>0.99021975833649167</v>
+        <v>0.99175504750403098</v>
       </c>
       <c r="AL40" s="7">
         <v>314792</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="38"/>
-        <v>69857</v>
+        <v>70645</v>
       </c>
       <c r="AO40" s="13">
-        <v>311716</v>
+        <v>312504</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="39"/>
-        <v>0.99022846832193956</v>
+        <v>0.99273170855676129</v>
       </c>
       <c r="AQ40" s="7">
         <v>372144</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="40"/>
-        <v>73716</v>
+        <v>75244</v>
       </c>
       <c r="AT40" s="13">
-        <v>367858</v>
+        <v>369386</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="41"/>
-        <v>0.9884829528354615</v>
+        <v>0.99258889032202591</v>
       </c>
       <c r="AV40" s="7">
         <v>317868</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="42"/>
-        <v>62649</v>
+        <v>64776</v>
       </c>
       <c r="AY40" s="13">
-        <v>312465</v>
+        <v>314592</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="43"/>
-        <v>0.98300237834572846</v>
+        <v>0.98969383517686582</v>
       </c>
       <c r="BA40" s="7">
         <v>321637</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="44"/>
-        <v>68306</v>
+        <v>71090</v>
       </c>
       <c r="BD40" s="13">
-        <v>312939</v>
+        <v>315723</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="45"/>
-        <v>0.97295709137941222</v>
+        <v>0.98161281195882311</v>
       </c>
       <c r="BF40" s="7">
         <v>380248</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="46"/>
-        <v>82633</v>
+        <v>88481</v>
       </c>
       <c r="BI40" s="6">
-        <v>363014</v>
+        <v>368862</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="47"/>
-        <v>0.95467694767625344</v>
+        <v>0.97005638425448659</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>163257</v>
+        <v>163389</v>
       </c>
       <c r="F41" s="13">
-        <v>975469</v>
+        <v>975601</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99799065511395668</v>
+        <v>0.99812570273358892</v>
       </c>
       <c r="H41" s="7">
         <v>983280</v>
@@ -7858,14 +7858,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>163122</v>
+        <v>163283</v>
       </c>
       <c r="K41" s="13">
-        <v>979816</v>
+        <v>979977</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.99647709706289156</v>
+        <v>0.99664083475713938</v>
       </c>
       <c r="M41" s="7">
         <v>1084276</v>
@@ -7875,14 +7875,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>190366</v>
+        <v>190584</v>
       </c>
       <c r="P41" s="13">
-        <v>1081573</v>
+        <v>1081791</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99750709229015488</v>
+        <v>0.99770814810989084</v>
       </c>
       <c r="R41" s="7">
         <v>988018</v>
@@ -7892,14 +7892,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>163567</v>
+        <v>163795</v>
       </c>
       <c r="U41" s="13">
-        <v>987858</v>
+        <v>988086</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.99983805963049255</v>
+        <v>1.0000688246570406</v>
       </c>
       <c r="W41" s="7">
         <v>994033</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>161222</v>
+        <v>161507</v>
       </c>
       <c r="Z41" s="13">
-        <v>992681</v>
+        <v>992966</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.99863988418895555</v>
+        <v>0.99892659499231917</v>
       </c>
       <c r="AB41" s="7">
         <v>1097882</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>139398</v>
+        <v>139801</v>
       </c>
       <c r="AE41" s="13">
-        <v>1095997</v>
+        <v>1096400</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99828305774208881</v>
+        <v>0.99865012815584919</v>
       </c>
       <c r="AG41" s="7">
         <v>1002140</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="36"/>
-        <v>156392</v>
+        <v>156891</v>
       </c>
       <c r="AJ41" s="13">
-        <v>1001096</v>
+        <v>1001595</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="37"/>
-        <v>0.99895822938910728</v>
+        <v>0.9994561638094478</v>
       </c>
       <c r="AL41" s="7">
         <v>1011306</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="38"/>
-        <v>150550</v>
+        <v>151372</v>
       </c>
       <c r="AO41" s="13">
-        <v>1013659</v>
+        <v>1014481</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="39"/>
-        <v>1.0023266943931906</v>
+        <v>1.0031395047591927</v>
       </c>
       <c r="AQ41" s="7">
         <v>1119532</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="40"/>
-        <v>185740</v>
+        <v>187124</v>
       </c>
       <c r="AT41" s="13">
-        <v>1121290</v>
+        <v>1122674</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="41"/>
-        <v>1.0015702990178039</v>
+        <v>1.0028065298714106</v>
       </c>
       <c r="AV41" s="7">
         <v>1028062</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="42"/>
-        <v>147075</v>
+        <v>148954</v>
       </c>
       <c r="AY41" s="13">
-        <v>1026783</v>
+        <v>1028662</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="43"/>
-        <v>0.9987559116084439</v>
+        <v>1.0005836223885329</v>
       </c>
       <c r="BA41" s="7">
         <v>1037044</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="44"/>
-        <v>146643</v>
+        <v>149685</v>
       </c>
       <c r="BD41" s="13">
-        <v>1032329</v>
+        <v>1035371</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="45"/>
-        <v>0.99545342338415732</v>
+        <v>0.99838676083174871</v>
       </c>
       <c r="BF41" s="7">
         <v>1143357</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="46"/>
-        <v>184084</v>
+        <v>192424</v>
       </c>
       <c r="BI41" s="6">
-        <v>1127873</v>
+        <v>1136213</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="47"/>
-        <v>0.98645742318453467</v>
+        <v>0.99375173283585094</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8053,14 +8053,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>4274</v>
+        <v>4277</v>
       </c>
       <c r="F42" s="13">
-        <v>19565</v>
+        <v>19568</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.99435860947347021</v>
+        <v>0.99451107948770079</v>
       </c>
       <c r="H42" s="7">
         <v>19882</v>
@@ -8070,14 +8070,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>4304</v>
+        <v>4307</v>
       </c>
       <c r="K42" s="13">
-        <v>19662</v>
+        <v>19665</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.98893471481742279</v>
+        <v>0.9890856050699125</v>
       </c>
       <c r="M42" s="7">
         <v>21930</v>
@@ -8087,14 +8087,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>5196</v>
+        <v>5201</v>
       </c>
       <c r="P42" s="13">
-        <v>21733</v>
+        <v>21738</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99101687186502507</v>
+        <v>0.99124487004103967</v>
       </c>
       <c r="R42" s="7">
         <v>20021</v>
@@ -8104,14 +8104,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>4365</v>
+        <v>4371</v>
       </c>
       <c r="U42" s="13">
-        <v>19801</v>
+        <v>19807</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.98901153788522056</v>
+        <v>0.98931122321562359</v>
       </c>
       <c r="W42" s="7">
         <v>20153</v>
@@ -8121,14 +8121,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4230</v>
+        <v>4239</v>
       </c>
       <c r="Z42" s="13">
-        <v>19893</v>
+        <v>19902</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.98709869498337721</v>
+        <v>0.987545278618568</v>
       </c>
       <c r="AB42" s="7">
         <v>22238</v>
@@ -8138,14 +8138,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>3876</v>
+        <v>3888</v>
       </c>
       <c r="AE42" s="13">
-        <v>22033</v>
+        <v>22045</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.99078154510297689</v>
+        <v>0.99132116197499776</v>
       </c>
       <c r="AG42" s="7">
         <v>20276</v>
@@ -8155,14 +8155,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="36"/>
-        <v>4322</v>
+        <v>4336</v>
       </c>
       <c r="AJ42" s="13">
-        <v>20130</v>
+        <v>20144</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="37"/>
-        <v>0.99279936871177743</v>
+        <v>0.99348984020516862</v>
       </c>
       <c r="AL42" s="7">
         <v>20453</v>
@@ -8172,14 +8172,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="38"/>
-        <v>3884</v>
+        <v>3907</v>
       </c>
       <c r="AO42" s="13">
-        <v>20302</v>
+        <v>20325</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="39"/>
-        <v>0.99261721996773089</v>
+        <v>0.99374174937661952</v>
       </c>
       <c r="AQ42" s="7">
         <v>22621</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="40"/>
-        <v>4764</v>
+        <v>4820</v>
       </c>
       <c r="AT42" s="13">
-        <v>22494</v>
+        <v>22550</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="41"/>
-        <v>0.99438574775650945</v>
+        <v>0.99686132354891477</v>
       </c>
       <c r="AV42" s="7">
         <v>20714</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="42"/>
-        <v>3810</v>
+        <v>3903</v>
       </c>
       <c r="AY42" s="13">
-        <v>20506</v>
+        <v>20599</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="43"/>
-        <v>0.98995848218596116</v>
+        <v>0.99444819928550743</v>
       </c>
       <c r="BA42" s="7">
         <v>20927</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="44"/>
-        <v>3668</v>
+        <v>3818</v>
       </c>
       <c r="BD42" s="13">
-        <v>20536</v>
+        <v>20686</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="45"/>
-        <v>0.98131600324939072</v>
+        <v>0.98848377693888279</v>
       </c>
       <c r="BF42" s="7">
         <v>23165</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="46"/>
-        <v>4447</v>
+        <v>4755</v>
       </c>
       <c r="BI42" s="6">
-        <v>22394</v>
+        <v>22702</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="47"/>
-        <v>0.96671703000215847</v>
+        <v>0.98001295057198357</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="24"/>
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F43" s="13">
-        <v>3884</v>
+        <v>3885</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="25"/>
-        <v>0.99233520694941235</v>
+        <v>0.99259070005109862</v>
       </c>
       <c r="H43" s="7">
         <v>3941</v>
@@ -8282,14 +8282,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="K43" s="13">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99467140319715808</v>
+        <v>0.99492514590205527</v>
       </c>
       <c r="M43" s="7">
         <v>4896</v>
@@ -8299,14 +8299,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="P43" s="13">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99142156862745101</v>
+        <v>0.99162581699346408</v>
       </c>
       <c r="R43" s="7">
         <v>3969</v>
@@ -8333,14 +8333,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="Z43" s="13">
-        <v>3969</v>
+        <v>3971</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.99002244948865059</v>
+        <v>0.99052132701421802</v>
       </c>
       <c r="AB43" s="7">
         <v>4962</v>
@@ -8350,14 +8350,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="AE43" s="13">
-        <v>4922</v>
+        <v>4926</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99193873438129787</v>
+        <v>0.99274486094316805</v>
       </c>
       <c r="AG43" s="7">
         <v>4018</v>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="36"/>
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="AJ43" s="13">
-        <v>3992</v>
+        <v>3999</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="37"/>
-        <v>0.99352911896465901</v>
+        <v>0.99527127924340464</v>
       </c>
       <c r="AL43" s="7">
         <v>4086</v>
@@ -8384,14 +8384,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="38"/>
-        <v>1175</v>
+        <v>1184</v>
       </c>
       <c r="AO43" s="13">
-        <v>4047</v>
+        <v>4056</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="39"/>
-        <v>0.99045521292217331</v>
+        <v>0.9926578560939795</v>
       </c>
       <c r="AQ43" s="7">
         <v>5072</v>
@@ -8401,14 +8401,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="40"/>
-        <v>1516</v>
+        <v>1540</v>
       </c>
       <c r="AT43" s="13">
-        <v>5029</v>
+        <v>5053</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="41"/>
-        <v>0.99152208201892744</v>
+        <v>0.99625394321766558</v>
       </c>
       <c r="AV43" s="7">
         <v>4151</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="42"/>
-        <v>1202</v>
+        <v>1247</v>
       </c>
       <c r="AY43" s="13">
-        <v>4043</v>
+        <v>4088</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="43"/>
-        <v>0.9739821729703686</v>
+        <v>0.98482293423271505</v>
       </c>
       <c r="BA43" s="7">
         <v>4249</v>
@@ -8435,14 +8435,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="44"/>
-        <v>1090</v>
+        <v>1149</v>
       </c>
       <c r="BD43" s="13">
-        <v>4061</v>
+        <v>4120</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="45"/>
-        <v>0.95575429512826549</v>
+        <v>0.96963991527418214</v>
       </c>
       <c r="BF43" s="7">
         <v>5295</v>
@@ -8452,14 +8452,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="46"/>
-        <v>1507</v>
+        <v>1682</v>
       </c>
       <c r="BI43" s="6">
-        <v>4806</v>
+        <v>4981</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="47"/>
-        <v>0.90764872521246454</v>
+        <v>0.94069877242681776</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>84132</v>
+        <v>84201</v>
       </c>
       <c r="F44" s="13">
-        <v>379551</v>
+        <v>379620</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98960468063138463</v>
+        <v>0.98978458457832075</v>
       </c>
       <c r="H44" s="7">
         <v>388149</v>
@@ -8494,14 +8494,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>82422</v>
+        <v>82507</v>
       </c>
       <c r="K44" s="13">
-        <v>382840</v>
+        <v>382925</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98632226284236213</v>
+        <v>0.98654125091137679</v>
       </c>
       <c r="M44" s="7">
         <v>456953</v>
@@ -8511,14 +8511,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>103294</v>
+        <v>103428</v>
       </c>
       <c r="P44" s="13">
-        <v>452906</v>
+        <v>453040</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.99114350928870143</v>
+        <v>0.9914367560777585</v>
       </c>
       <c r="R44" s="7">
         <v>388846</v>
@@ -8528,14 +8528,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>83333</v>
+        <v>83466</v>
       </c>
       <c r="U44" s="13">
-        <v>385120</v>
+        <v>385253</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.99041780036312577</v>
+        <v>0.99075983808500023</v>
       </c>
       <c r="W44" s="7">
         <v>393146</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>81909</v>
+        <v>82059</v>
       </c>
       <c r="Z44" s="13">
-        <v>387617</v>
+        <v>387767</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.98593652230977802</v>
+        <v>0.98631805995736954</v>
       </c>
       <c r="AB44" s="7">
         <v>465292</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>81457</v>
+        <v>81703</v>
       </c>
       <c r="AE44" s="13">
-        <v>459849</v>
+        <v>460095</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.98830196951591687</v>
+        <v>0.98883066977295975</v>
       </c>
       <c r="AG44" s="7">
         <v>393778</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="36"/>
-        <v>80021</v>
+        <v>80284</v>
       </c>
       <c r="AJ44" s="13">
-        <v>391227</v>
+        <v>391490</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="37"/>
-        <v>0.9935217305182108</v>
+        <v>0.99418961953181739</v>
       </c>
       <c r="AL44" s="7">
         <v>398873</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="38"/>
-        <v>76986</v>
+        <v>77490</v>
       </c>
       <c r="AO44" s="13">
-        <v>400511</v>
+        <v>401015</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="39"/>
-        <v>1.0041065702617125</v>
+        <v>1.0053701303422393</v>
       </c>
       <c r="AQ44" s="7">
         <v>476819</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="40"/>
-        <v>85205</v>
+        <v>86214</v>
       </c>
       <c r="AT44" s="13">
-        <v>476639</v>
+        <v>477648</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="41"/>
-        <v>0.99962249826454064</v>
+        <v>1.0017386052149768</v>
       </c>
       <c r="AV44" s="7">
         <v>408878</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="42"/>
-        <v>72232</v>
+        <v>73605</v>
       </c>
       <c r="AY44" s="13">
-        <v>407610</v>
+        <v>408983</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="43"/>
-        <v>0.996898830457985</v>
+        <v>1.000256800316965</v>
       </c>
       <c r="BA44" s="7">
         <v>416024</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="44"/>
-        <v>78635</v>
+        <v>80932</v>
       </c>
       <c r="BD44" s="13">
-        <v>411320</v>
+        <v>413617</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="45"/>
-        <v>0.98869296002153717</v>
+        <v>0.99421427609945578</v>
       </c>
       <c r="BF44" s="7">
         <v>493955</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="46"/>
-        <v>98074</v>
+        <v>104863</v>
       </c>
       <c r="BI44" s="6">
-        <v>478660</v>
+        <v>485449</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="47"/>
-        <v>0.96903564089846239</v>
+        <v>0.98277980787723573</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>55972</v>
+        <v>56008</v>
       </c>
       <c r="F45" s="13">
-        <v>276930</v>
+        <v>276966</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.99796033095972558</v>
+        <v>0.99809006255946031</v>
       </c>
       <c r="H45" s="7">
         <v>280269</v>
@@ -8706,14 +8706,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>55508</v>
+        <v>55553</v>
       </c>
       <c r="K45" s="13">
-        <v>278645</v>
+        <v>278690</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.99420556679475791</v>
+        <v>0.9943661268281544</v>
       </c>
       <c r="M45" s="7">
         <v>334005</v>
@@ -8723,14 +8723,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>70116</v>
+        <v>70189</v>
       </c>
       <c r="P45" s="13">
-        <v>331626</v>
+        <v>331699</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.99287735213544703</v>
+        <v>0.99309591173784828</v>
       </c>
       <c r="R45" s="7">
         <v>281510</v>
@@ -8740,14 +8740,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>53676</v>
+        <v>53746</v>
       </c>
       <c r="U45" s="13">
-        <v>279737</v>
+        <v>279807</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.99370182231537063</v>
+        <v>0.99395048133281239</v>
       </c>
       <c r="W45" s="7">
         <v>284325</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>54416</v>
+        <v>54509</v>
       </c>
       <c r="Z45" s="13">
-        <v>280741</v>
+        <v>280834</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.98739470676162844</v>
+        <v>0.98772179723907505</v>
       </c>
       <c r="AB45" s="7">
         <v>338696</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>61279</v>
+        <v>61443</v>
       </c>
       <c r="AE45" s="13">
-        <v>334471</v>
+        <v>334635</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98752568675154118</v>
+        <v>0.98800989678059381</v>
       </c>
       <c r="AG45" s="7">
         <v>285325</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="36"/>
-        <v>56549</v>
+        <v>56714</v>
       </c>
       <c r="AJ45" s="13">
-        <v>282504</v>
+        <v>282669</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="37"/>
-        <v>0.99011302900201525</v>
+        <v>0.99069131691930257</v>
       </c>
       <c r="AL45" s="7">
         <v>289428</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="38"/>
-        <v>52886</v>
+        <v>53209</v>
       </c>
       <c r="AO45" s="13">
-        <v>289007</v>
+        <v>289330</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="39"/>
-        <v>0.99854540680238268</v>
+        <v>0.99966140110839308</v>
       </c>
       <c r="AQ45" s="7">
         <v>348161</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="40"/>
-        <v>65635</v>
+        <v>66434</v>
       </c>
       <c r="AT45" s="13">
-        <v>345929</v>
+        <v>346728</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="41"/>
-        <v>0.99358917282521597</v>
+        <v>0.99588408810866236</v>
       </c>
       <c r="AV45" s="7">
         <v>296165</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="42"/>
-        <v>51353</v>
+        <v>52411</v>
       </c>
       <c r="AY45" s="13">
-        <v>293386</v>
+        <v>294444</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="43"/>
-        <v>0.99061671703273513</v>
+        <v>0.99418905002279134</v>
       </c>
       <c r="BA45" s="7">
         <v>300603</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="44"/>
-        <v>56393</v>
+        <v>58139</v>
       </c>
       <c r="BD45" s="13">
-        <v>295876</v>
+        <v>297622</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="45"/>
-        <v>0.98427494070252131</v>
+        <v>0.99008326596873619</v>
       </c>
       <c r="BF45" s="7">
         <v>359430</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="46"/>
-        <v>73383</v>
+        <v>78445</v>
       </c>
       <c r="BI45" s="6">
-        <v>347290</v>
+        <v>352352</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="47"/>
-        <v>0.96622429958545475</v>
+        <v>0.98030770942881784</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F46" s="13">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.0320987654320988</v>
+        <v>1.0329218106995885</v>
       </c>
       <c r="H46" s="7">
         <v>2594</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="K46" s="13">
-        <v>2649</v>
+        <v>2652</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0212027756360833</v>
+        <v>1.0223592906707788</v>
       </c>
       <c r="M46" s="7">
         <v>8454</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="P46" s="13">
-        <v>8596</v>
+        <v>8599</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0167967825881239</v>
+        <v>1.0171516441920985</v>
       </c>
       <c r="R46" s="7">
         <v>2484</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="U46" s="13">
-        <v>2596</v>
+        <v>2601</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.0450885668276972</v>
+        <v>1.0471014492753623</v>
       </c>
       <c r="W46" s="7">
         <v>2748</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="Z46" s="13">
-        <v>2694</v>
+        <v>2701</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98034934497816595</v>
+        <v>0.98289665211062593</v>
       </c>
       <c r="AB46" s="7">
         <v>8770</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2076</v>
+        <v>2088</v>
       </c>
       <c r="AE46" s="13">
-        <v>8819</v>
+        <v>8831</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.005587229190422</v>
+        <v>1.0069555302166477</v>
       </c>
       <c r="AG46" s="7">
         <v>2523</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="36"/>
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AJ46" s="13">
-        <v>2560</v>
+        <v>2566</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="37"/>
-        <v>1.0146650812524771</v>
+        <v>1.0170432025366627</v>
       </c>
       <c r="AL46" s="7">
         <v>2722</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="38"/>
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="AO46" s="13">
-        <v>2685</v>
+        <v>2695</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="39"/>
-        <v>0.98640705363703163</v>
+        <v>0.99008082292432031</v>
       </c>
       <c r="AQ46" s="7">
         <v>8967</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="40"/>
-        <v>1693</v>
+        <v>1731</v>
       </c>
       <c r="AT46" s="13">
-        <v>8923</v>
+        <v>8961</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="41"/>
-        <v>0.99509311921489907</v>
+        <v>0.99933087989294078</v>
       </c>
       <c r="AV46" s="7">
         <v>2626</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="42"/>
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AY46" s="13">
-        <v>2629</v>
+        <v>2641</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="43"/>
-        <v>1.0011424219345011</v>
+        <v>1.0057121096725057</v>
       </c>
       <c r="BA46" s="7">
         <v>2791</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="44"/>
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="BD46" s="13">
-        <v>2668</v>
+        <v>2688</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="45"/>
-        <v>0.95592977427445358</v>
+        <v>0.96309566463633112</v>
       </c>
       <c r="BF46" s="7">
         <v>9093</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="46"/>
-        <v>1478</v>
+        <v>1721</v>
       </c>
       <c r="BI46" s="6">
-        <v>8665</v>
+        <v>8908</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="47"/>
-        <v>0.95293082591004064</v>
+        <v>0.97965467942373252</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="AX47" s="20">
         <f t="shared" si="42"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY47" s="13">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AZ47" s="21">
         <f t="shared" si="43"/>
-        <v>0.94666666666666666</v>
+        <v>0.96</v>
       </c>
       <c r="BA47" s="7">
         <v>76</v>
@@ -9283,14 +9283,14 @@
       </c>
       <c r="BC47" s="20">
         <f t="shared" si="44"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD47" s="13">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BE47" s="21">
         <f t="shared" si="45"/>
-        <v>0.88157894736842102</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="BF47" s="7">
         <v>72</v>
@@ -9300,21 +9300,21 @@
       </c>
       <c r="BH47" s="20">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI47" s="6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BJ47" s="21">
         <f t="shared" si="47"/>
-        <v>0.97222222222222221</v>
+        <v>0.98611111111111116</v>
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="26"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="9">
         <f>SUM(C10:C47)</f>
         <v>8623084</v>
@@ -9325,15 +9325,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1589681</v>
+        <v>1591305</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8591728</v>
+        <v>8593352</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99636371395663081</v>
+        <v>0.99655204564863331</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9345,15 +9345,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1551267</v>
+        <v>1553268</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8700513</v>
+        <v>8702514</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.99172403793907271</v>
+        <v>0.99195212101876196</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9365,15 +9365,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2521517</v>
+        <v>2525624</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>13291114</v>
+        <v>13295221</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99517973543615879</v>
+        <v>0.99548724940176292</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9385,15 +9385,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1557431</v>
+        <v>1560413</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8735632</v>
+        <v>8738614</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.99600827396671765</v>
+        <v>0.99634827188249164</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9405,15 +9405,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1569259</v>
+        <v>1573062</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8825232</v>
+        <v>8829035</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98798319364420528</v>
+        <v>0.98840893883542846</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9425,15 +9425,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2370407</v>
+        <v>2378865</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>13507130</v>
+        <v>13515588</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.9926013076314264</v>
+        <v>0.99322286245913194</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9445,15 +9445,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" si="36"/>
-        <v>1583326</v>
+        <v>1590177</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8868185</v>
+        <v>8875036</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" si="37"/>
-        <v>0.99451402607842188</v>
+        <v>0.99528232484447865</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9465,15 +9465,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="38"/>
-        <v>1499271</v>
+        <v>1511203</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>9123151</v>
+        <v>9135083</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="39"/>
-        <v>0.99953885899098971</v>
+        <v>1.0008461373277706</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9485,15 +9485,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="40"/>
-        <v>2294379</v>
+        <v>2324005</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>13935440</v>
+        <v>13965066</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="41"/>
-        <v>0.99701762701557006</v>
+        <v>0.99913723315774883</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9505,15 +9505,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="42"/>
-        <v>1418612</v>
+        <v>1447859</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>9217674</v>
+        <v>9246921</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="43"/>
-        <v>0.99644475654560227</v>
+        <v>0.99960640229209863</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9525,15 +9525,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="44"/>
-        <v>1450733</v>
+        <v>1494805</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>9341935</v>
+        <v>9386007</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="45"/>
-        <v>0.98640333533775992</v>
+        <v>0.99105684318115705</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9545,16 +9545,84 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="46"/>
-        <v>2566976</v>
+        <v>2755040</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13971947</v>
+        <v>14160011</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="47"/>
-        <v>0.96821710653193527</v>
-      </c>
+        <v>0.98124941920266207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+    </row>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -9625,10 +9693,12 @@
       <c r="AF53" s="1"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="A54" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -9659,10 +9729,6 @@
       <c r="AF54" s="1"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -9693,12 +9759,6 @@
       <c r="AF55" s="1"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A56" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -9758,74 +9818,8 @@
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
-      <c r="AF58" s="1"/>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
-      <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
-      <c r="AF59" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A8:A9"/>
@@ -9836,6 +9830,12 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
